--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4979F2C-0057-418F-A13C-26F8577DC452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FD401A-EC92-4F3E-AA71-882231C08B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11235" yWindow="630" windowWidth="16575" windowHeight="14745" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="11235" yWindow="0" windowWidth="16575" windowHeight="15600" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$177</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$590</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="71">
   <si>
     <t>Implied</t>
   </si>
@@ -50,6 +50,9 @@
     <t>R/W</t>
   </si>
   <si>
+    <t>Cycles: 6</t>
+  </si>
+  <si>
     <t>Size: 2</t>
   </si>
   <si>
@@ -68,12 +71,27 @@
     <t>Cycles: 8</t>
   </si>
   <si>
+    <t>Cycles: 3</t>
+  </si>
+  <si>
     <t>Cycles: 2</t>
   </si>
   <si>
     <t>Cycles: 4</t>
   </si>
   <si>
+    <t>Store as Address.L.</t>
+  </si>
+  <si>
+    <t>Absolute (Read)</t>
+  </si>
+  <si>
+    <t>Size: 3</t>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Push </t>
     </r>
@@ -126,6 +144,9 @@
     </r>
   </si>
   <si>
+    <t>Store as Pointer.H.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> +X.1</t>
   </si>
   <si>
@@ -164,6 +185,12 @@
     </r>
   </si>
   <si>
+    <t>Store as Address.H.</t>
+  </si>
+  <si>
+    <t>Read Pointer</t>
+  </si>
+  <si>
     <t>NOP (00)</t>
   </si>
   <si>
@@ -400,6 +427,631 @@
   </si>
   <si>
     <t>Direct Page Bit (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>BBS (03)</t>
+  </si>
+  <si>
+    <t>Direct Page Bit Relative</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (1 &lt;&lt; 0).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If !Jump, end instruction (next half-cycle is 7.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Address = (Operand | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + int8( Operand ).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = Address.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H = Address.H.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cycles: 5-7</t>
+  </si>
+  <si>
+    <t>OR (04)</t>
+  </si>
+  <si>
+    <t>Direct Page (Read)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (05)</t>
+  </si>
+  <si>
+    <t>OR (06)</t>
+  </si>
+  <si>
+    <t>Indirect X (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (07)</t>
+  </si>
+  <si>
+    <t>X-Indexed Indirect (Read)</t>
+  </si>
+  <si>
+    <t>Store as Pointer.L.</t>
+  </si>
+  <si>
+    <r>
+      <t>Read ((Address + 1) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (08)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (09)</t>
+  </si>
+  <si>
+    <t>Store as Operand0.</t>
+  </si>
+  <si>
+    <t>Store as Operand1.</t>
+  </si>
+  <si>
+    <t>Write Operand0.</t>
+  </si>
+  <si>
+    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand0 |= Operand1.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -565,7 +1217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -615,6 +1267,12 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -622,6 +1280,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -958,25 +1619,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C548"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="17" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="17" customWidth="1"/>
-    <col min="3" max="3" width="92.28515625" style="17" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="19" customWidth="1"/>
+    <col min="3" max="3" width="92.28515625" style="19" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="6" max="7" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -994,18 +1655,18 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1014,7 +1675,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1036,28 +1697,28 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B60" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1075,18 +1736,18 @@
         <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1095,7 +1756,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1103,10 +1764,10 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1135,10 +1796,10 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1153,10 +1814,10 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,7 +1826,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1187,10 +1848,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1205,10 +1866,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1223,36 +1884,36 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="8"/>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
-      <c r="B120" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C120" s="19"/>
+      <c r="B120" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="21"/>
     </row>
     <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
@@ -1262,18 +1923,18 @@
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C122" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1282,7 +1943,7 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1290,10 +1951,10 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1302,7 +1963,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1310,30 +1971,30 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B126" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
         <v>3.1</v>
       </c>
-      <c r="B127" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C127" s="2"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
         <v>3.2</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1348,22 +2009,954 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
     </row>
+    <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="13"/>
+      <c r="B179" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C179" s="21"/>
+    </row>
+    <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C181" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B182" s="7"/>
+      <c r="C182" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B184" s="7"/>
+      <c r="C184" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B186" s="7"/>
+      <c r="C186" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B187" s="7"/>
+      <c r="C187" s="2"/>
+    </row>
+    <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B188" s="7"/>
+      <c r="C188" s="2"/>
+    </row>
+    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B191" s="7"/>
+      <c r="C191" s="2"/>
+    </row>
+    <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B192" s="7"/>
+      <c r="C192" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="3"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B194" s="7"/>
+      <c r="C194" s="2"/>
+    </row>
+    <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B195" s="7"/>
+      <c r="C195" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B197" s="9"/>
+      <c r="C197" s="8"/>
+    </row>
+    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A237" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B237" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A238" s="13"/>
+      <c r="B238" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C238" s="18"/>
+    </row>
+    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A240" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C240" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B241" s="7"/>
+      <c r="C241" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A242" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A243" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B243" s="7"/>
+      <c r="C243" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A245" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B245" s="7"/>
+      <c r="C245" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B247" s="9"/>
+      <c r="C247" s="8"/>
+    </row>
+    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A296" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B296" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="13"/>
+      <c r="B297" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C297" s="18"/>
+    </row>
+    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C299" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B300" s="7"/>
+      <c r="C300" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B302" s="7"/>
+      <c r="C302" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A303" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A304" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B304" s="7"/>
+      <c r="C304" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A305" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B306" s="7"/>
+      <c r="C306" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A308" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B308" s="9"/>
+      <c r="C308" s="8"/>
+    </row>
+    <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A355" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B355" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A356" s="13"/>
+      <c r="B356" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C356" s="18"/>
+    </row>
+    <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A357" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A358" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C358" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A359" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B359" s="7"/>
+      <c r="C359" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B360" s="7"/>
+      <c r="C360" s="2"/>
+    </row>
+    <row r="361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A361" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B361" s="7"/>
+      <c r="C361" s="2"/>
+    </row>
+    <row r="362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A362" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A363" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B363" s="7"/>
+      <c r="C363" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A365" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B365" s="9"/>
+      <c r="C365" s="8"/>
+    </row>
+    <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A414" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B414" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A415" s="13"/>
+      <c r="B415" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C415" s="18"/>
+    </row>
+    <row r="416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A416" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A417" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C417" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A418" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B418" s="7"/>
+      <c r="C418" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A419" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A420" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B420" s="7"/>
+      <c r="C420" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A421" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B421" s="7"/>
+      <c r="C421" s="2"/>
+    </row>
+    <row r="422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A422" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B422" s="7"/>
+      <c r="C422" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A423" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A424" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B424" s="7"/>
+      <c r="C424" s="2"/>
+    </row>
+    <row r="425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A425" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B425" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A426" s="3"/>
+      <c r="B426" s="22"/>
+      <c r="C426" s="2"/>
+    </row>
+    <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A427" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B427" s="7"/>
+      <c r="C427" s="2"/>
+    </row>
+    <row r="428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A428" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A429" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B429" s="7"/>
+      <c r="C429" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A430" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A431" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B431" s="9"/>
+      <c r="C431" s="8"/>
+    </row>
+    <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A473" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B473" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C473" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="13"/>
+      <c r="B474" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C474" s="18"/>
+    </row>
+    <row r="475" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B476" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C476" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B477" s="7"/>
+      <c r="C477" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C478" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B479" s="7"/>
+      <c r="C479" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B480" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C480" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B481" s="9"/>
+      <c r="C481" s="8"/>
+    </row>
+    <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B532" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C532" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="13"/>
+      <c r="B533" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C533" s="21"/>
+    </row>
+    <row r="534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C534" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B535" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C535" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B536" s="7"/>
+      <c r="C536" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B537" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B538" s="7"/>
+      <c r="C538" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B539" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B540" s="7"/>
+      <c r="C540" s="2"/>
+    </row>
+    <row r="541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B541" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C541" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B542" s="7"/>
+      <c r="C542" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B543" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B544" s="7"/>
+      <c r="C544" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B545" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B546" s="7"/>
+      <c r="C546" s="2"/>
+    </row>
+    <row r="547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B547" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C547" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B548" s="9"/>
+      <c r="C548" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B425:B426"/>
+    <mergeCell ref="B533:C533"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FD401A-EC92-4F3E-AA71-882231C08B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF57CCB6-E034-4B07-8030-87F4F3897370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11235" yWindow="0" windowWidth="16575" windowHeight="15600" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$590</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$687</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="80">
   <si>
     <t>Implied</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Cycles: 3</t>
   </si>
   <si>
+    <t>Cycles: 5</t>
+  </si>
+  <si>
     <t>Cycles: 2</t>
   </si>
   <si>
@@ -592,6 +595,218 @@
     <t>Direct Page (Read)</t>
   </si>
   <si>
+    <t>OR (05)</t>
+  </si>
+  <si>
+    <t>OR (06)</t>
+  </si>
+  <si>
+    <t>Indirect X (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (07)</t>
+  </si>
+  <si>
+    <t>X-Indexed Indirect (Read)</t>
+  </si>
+  <si>
+    <t>Store as Pointer.L.</t>
+  </si>
+  <si>
+    <r>
+      <t>Read ((Address + 1) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SPW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (08)</t>
+  </si>
+  <si>
+    <t>OR (09)</t>
+  </si>
+  <si>
+    <t>Store as Operand0.</t>
+  </si>
+  <si>
+    <t>Store as Operand1.</t>
+  </si>
+  <si>
+    <t>Write Operand0.</t>
+  </si>
+  <si>
+    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>OR1 (0A)</t>
+  </si>
+  <si>
+    <t>Absolute Boolean Bit</t>
+  </si>
+  <si>
+    <t>Read (Address &amp; $1FFF)</t>
+  </si>
+  <si>
+    <t>Bit = Address &gt;&gt; 13.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -611,7 +826,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> |= Operand.  </t>
+      <t xml:space="preserve"> |= Operand. </t>
     </r>
     <r>
       <rPr>
@@ -699,168 +914,6 @@
     </r>
   </si>
   <si>
-    <t>OR (05)</t>
-  </si>
-  <si>
-    <t>OR (06)</t>
-  </si>
-  <si>
-    <t>Indirect X (Read)</t>
-  </si>
-  <si>
-    <r>
-      <t>Read (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (07)</t>
-  </si>
-  <si>
-    <t>X-Indexed Indirect (Read)</t>
-  </si>
-  <si>
-    <t>Store as Pointer.L.</t>
-  </si>
-  <si>
-    <r>
-      <t>Read ((Address + 1) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Address = ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (08)</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Inc. </t>
     </r>
@@ -904,7 +957,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> |= Operand.  </t>
+      <t xml:space="preserve"> |= Operand. </t>
     </r>
     <r>
       <rPr>
@@ -992,23 +1045,8 @@
     </r>
   </si>
   <si>
-    <t>OR (09)</t>
-  </si>
-  <si>
-    <t>Store as Operand0.</t>
-  </si>
-  <si>
-    <t>Store as Operand1.</t>
-  </si>
-  <si>
-    <t>Write Operand0.</t>
-  </si>
-  <si>
-    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Operand0 |= Operand1.  </t>
+    <r>
+      <t xml:space="preserve">Operand0 |= Operand1. </t>
     </r>
     <r>
       <rPr>
@@ -1051,6 +1089,77 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (0B)</t>
+  </si>
+  <si>
+    <t>Direct Page (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand &lt;&lt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
     </r>
   </si>
 </sst>
@@ -1619,7 +1728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C548"/>
+  <dimension ref="A1:C662"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -1631,10 +1740,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>8</v>
@@ -1655,15 +1764,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -1675,7 +1784,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1697,7 +1806,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -1705,14 +1814,14 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -1736,15 +1845,15 @@
         <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -1756,7 +1865,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1764,7 +1873,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -1796,10 +1905,10 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1814,10 +1923,10 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1826,7 +1935,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1848,10 +1957,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1866,10 +1975,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1884,7 +1993,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -1892,17 +2001,17 @@
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="8"/>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C119" s="12" t="s">
         <v>4</v>
@@ -1911,7 +2020,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -1923,15 +2032,15 @@
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -1943,7 +2052,7 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1951,7 +2060,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -1963,7 +2072,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1983,7 +2092,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1991,10 +2100,10 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2009,7 +2118,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -2017,26 +2126,26 @@
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -2048,15 +2157,15 @@
         <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2068,7 +2177,7 @@
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2076,7 +2185,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -2088,7 +2197,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2108,7 +2217,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2130,7 +2239,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -2142,7 +2251,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2158,14 +2267,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2181,7 +2290,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2189,7 +2298,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -2197,14 +2306,14 @@
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="8"/>
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -2216,7 +2325,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -2228,15 +2337,15 @@
         <v>2</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -2248,7 +2357,7 @@
       </c>
       <c r="B241" s="7"/>
       <c r="C241" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2256,7 +2365,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -2268,7 +2377,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2288,7 +2397,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2296,7 +2405,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -2304,7 +2413,7 @@
     </row>
     <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B247" s="9"/>
       <c r="C247" s="8"/>
@@ -2314,16 +2423,16 @@
         <v>54</v>
       </c>
       <c r="B296" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -2335,15 +2444,15 @@
         <v>2</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -2355,7 +2464,7 @@
       </c>
       <c r="B300" s="7"/>
       <c r="C300" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2363,10 +2472,10 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2375,7 +2484,7 @@
       </c>
       <c r="B302" s="7"/>
       <c r="C302" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2383,10 +2492,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2395,7 +2504,7 @@
       </c>
       <c r="B304" s="7"/>
       <c r="C304" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2415,7 +2524,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2423,7 +2532,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -2431,7 +2540,7 @@
     </row>
     <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B308" s="9"/>
       <c r="C308" s="8"/>
@@ -2462,15 +2571,15 @@
         <v>2</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -2482,7 +2591,7 @@
       </c>
       <c r="B359" s="7"/>
       <c r="C359" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2516,7 +2625,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2524,7 +2633,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -2532,7 +2641,7 @@
     </row>
     <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B365" s="9"/>
       <c r="C365" s="8"/>
@@ -2563,15 +2672,15 @@
         <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -2583,7 +2692,7 @@
       </c>
       <c r="B418" s="7"/>
       <c r="C418" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,7 +2700,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -2603,7 +2712,7 @@
       </c>
       <c r="B420" s="7"/>
       <c r="C420" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2648,7 +2757,7 @@
         <v>61</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2668,7 +2777,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -2680,7 +2789,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2688,7 +2797,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -2696,7 +2805,7 @@
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="8"/>
@@ -2706,7 +2815,7 @@
         <v>63</v>
       </c>
       <c r="B473" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C473" s="12" t="s">
         <v>4</v>
@@ -2715,7 +2824,7 @@
     <row r="474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="13"/>
       <c r="B474" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C474" s="18"/>
     </row>
@@ -2727,15 +2836,15 @@
         <v>2</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -2747,7 +2856,7 @@
       </c>
       <c r="B477" s="7"/>
       <c r="C477" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2755,7 +2864,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -2767,7 +2876,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2775,7 +2884,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -2783,26 +2892,26 @@
     </row>
     <row r="481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="8"/>
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -2814,15 +2923,15 @@
         <v>2</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -2834,7 +2943,7 @@
       </c>
       <c r="B536" s="7"/>
       <c r="C536" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2842,7 +2951,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -2854,7 +2963,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2865,7 +2974,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2880,7 +2989,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -2892,7 +3001,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2903,7 +3012,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2912,7 +3021,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2920,10 +3029,10 @@
         <v>5.2</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2938,7 +3047,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -2946,17 +3055,291 @@
     </row>
     <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B548" s="9"/>
       <c r="C548" s="8"/>
     </row>
+    <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B591" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C591" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="13"/>
+      <c r="B592" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C592" s="18"/>
+    </row>
+    <row r="593" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C593" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B594" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C594" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B595" s="7"/>
+      <c r="C595" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B596" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B597" s="7"/>
+      <c r="C597" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B598" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B599" s="7"/>
+      <c r="C599" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B600" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C600" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B601" s="7"/>
+      <c r="C601" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="3"/>
+      <c r="B602" s="7"/>
+      <c r="C602" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B603" s="7"/>
+      <c r="C603" s="2"/>
+    </row>
+    <row r="604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B604" s="7"/>
+      <c r="C604" s="2"/>
+    </row>
+    <row r="605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A605" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B605" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B606" s="9"/>
+      <c r="C606" s="8"/>
+    </row>
+    <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B650" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C650" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="13"/>
+      <c r="B651" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C651" s="21"/>
+    </row>
+    <row r="652" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B653" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C653" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B654" s="7"/>
+      <c r="C654" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B655" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B656" s="7"/>
+      <c r="C656" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B657" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B658" s="7"/>
+      <c r="C658" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B659" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C659" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B660" s="7"/>
+      <c r="C660" s="2"/>
+    </row>
+    <row r="661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B661" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B662" s="9"/>
+      <c r="C662" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
     <mergeCell ref="B533:C533"/>
+    <mergeCell ref="B651:C651"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF57CCB6-E034-4B07-8030-87F4F3897370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66FFF95-91CD-43C0-81E9-524877467981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11235" yWindow="0" windowWidth="16575" windowHeight="15600" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$687</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$883</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="90">
   <si>
     <t>Implied</t>
   </si>
@@ -86,6 +86,9 @@
     <t>Store as Address.L.</t>
   </si>
   <si>
+    <t>Absolute (Read/Modify/Write)</t>
+  </si>
+  <si>
     <t>Absolute (Read)</t>
   </si>
   <si>
@@ -188,6 +191,9 @@
     </r>
   </si>
   <si>
+    <t>Discard.</t>
+  </si>
+  <si>
     <t>Store as Address.H.</t>
   </si>
   <si>
@@ -300,6 +306,567 @@
     </r>
   </si>
   <si>
+    <t>SET1 (02)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~1) | 1.</t>
+  </si>
+  <si>
+    <t>Write Operand.</t>
+  </si>
+  <si>
+    <t>Direct Page Bit (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>BBS (03)</t>
+  </si>
+  <si>
+    <t>Direct Page Bit Relative</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (1 &lt;&lt; 0).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If !Jump, end instruction (next half-cycle is 7.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Address = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + int8( Operand ).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = Address.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H = Address.H.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cycles: 5-7</t>
+  </si>
+  <si>
+    <t>OR (04)</t>
+  </si>
+  <si>
+    <t>Direct Page (Read)</t>
+  </si>
+  <si>
+    <t>OR (05)</t>
+  </si>
+  <si>
+    <t>OR (06)</t>
+  </si>
+  <si>
+    <t>Indirect X (Read)</t>
+  </si>
+  <si>
+    <t>OR (07)</t>
+  </si>
+  <si>
+    <t>X-Indexed Indirect (Read)</t>
+  </si>
+  <si>
+    <t>Store as Pointer.L.</t>
+  </si>
+  <si>
+    <t>OR (08)</t>
+  </si>
+  <si>
+    <t>OR (09)</t>
+  </si>
+  <si>
+    <t>Store as Operand0.</t>
+  </si>
+  <si>
+    <t>Store as Operand1.</t>
+  </si>
+  <si>
+    <t>Write Operand0.</t>
+  </si>
+  <si>
+    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>OR1 (0A)</t>
+  </si>
+  <si>
+    <t>Absolute Boolean Bit</t>
+  </si>
+  <si>
+    <t>Read (Address &amp; $1FFF)</t>
+  </si>
+  <si>
+    <t>Bit = Address &gt;&gt; 13.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand0 |= Operand1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (0B)</t>
+  </si>
+  <si>
+    <t>Direct Page (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand &lt;&lt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (0C)</t>
+  </si>
+  <si>
+    <t>PUSH (0D)</t>
+  </si>
+  <si>
     <r>
       <t>Write to u8(</t>
     </r>
@@ -312,17 +879,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L+0) | $0100</t>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0) | $0100</t>
     </r>
   </si>
   <si>
@@ -338,27 +905,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L-1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <t>SET1 (02)</t>
-  </si>
-  <si>
-    <t>Operand = (Operand &amp; ~1) | 1.</t>
-  </si>
-  <si>
-    <t>Write Operand.</t>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1) | $0100</t>
+    </r>
   </si>
   <si>
     <r>
@@ -394,7 +952,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SPW</t>
+      <t>PSW</t>
     </r>
     <r>
       <rPr>
@@ -425,20 +983,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3).</t>
-    </r>
-  </si>
-  <si>
-    <t>Direct Page Bit (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <t>BBS (03)</t>
-  </si>
-  <si>
-    <t>Direct Page Bit Relative</t>
-  </si>
-  <si>
-    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (1 &lt;&lt; 0).</t>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
+    </r>
   </si>
   <si>
     <r>
@@ -463,32 +1009,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. If !Jump, end instruction (next half-cycle is 7.2).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>. Address = (Operand | ((</t>
     </r>
     <r>
@@ -500,7 +1020,101 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SPW</t>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3)).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
     </r>
     <r>
       <rPr>
@@ -515,152 +1129,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Address = </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + int8( Operand ).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.L = Address.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H = Address.H.</t>
-    </r>
-  </si>
-  <si>
-    <t>Cycles: 5-7</t>
-  </si>
-  <si>
-    <t>OR (04)</t>
-  </si>
-  <si>
-    <t>Direct Page (Read)</t>
-  </si>
-  <si>
-    <t>OR (05)</t>
-  </si>
-  <si>
-    <t>OR (06)</t>
-  </si>
-  <si>
-    <t>Indirect X (Read)</t>
-  </si>
-  <si>
-    <r>
-      <t>Read (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (07)</t>
-  </si>
-  <si>
-    <t>X-Indexed Indirect (Read)</t>
-  </si>
-  <si>
-    <t>Store as Pointer.L.</t>
-  </si>
-  <si>
-    <r>
       <t>Read ((Address + 1) &amp; $FF) | ((</t>
     </r>
     <r>
@@ -672,7 +1140,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>SPW</t>
+      <t>PSW</t>
     </r>
     <r>
       <rPr>
@@ -708,105 +1176,63 @@
   </si>
   <si>
     <r>
-      <t>Address = ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SPW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (08)</t>
-  </si>
-  <si>
-    <t>OR (09)</t>
-  </si>
-  <si>
-    <t>Store as Operand0.</t>
-  </si>
-  <si>
-    <t>Store as Operand1.</t>
-  </si>
-  <si>
-    <t>Write Operand0.</t>
-  </si>
-  <si>
-    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <t>OR1 (0A)</t>
-  </si>
-  <si>
-    <t>Absolute Boolean Bit</t>
-  </si>
-  <si>
-    <t>Read (Address &amp; $1FFF)</t>
-  </si>
-  <si>
-    <t>Bit = Address &gt;&gt; 13.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. </t>
+    </r>
+  </si>
+  <si>
+    <t>TSET1 (0E)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand |= </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -826,7 +1252,57 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> |= Operand. </t>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Operand = (A - Operand). Z flag = (Operand == 0), N flag = (Operand &amp; $80).</t>
+  </si>
+  <si>
+    <r>
+      <t>Operand = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Operand). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand == 0), </t>
     </r>
     <r>
       <rPr>
@@ -847,319 +1323,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = !</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= Operand. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = !</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Operand0 |= Operand1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = !Operand0.</t>
-    </r>
-  </si>
-  <si>
-    <t>ASL (0B)</t>
-  </si>
-  <si>
-    <t>Direct Page (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand &lt;&lt;= 1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = !Operand.</t>
+      <t xml:space="preserve"> flag = (Operand &amp; $80).</t>
     </r>
   </si>
 </sst>
@@ -1728,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C662"/>
+  <dimension ref="A1:C843"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -1740,7 +1904,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -1764,15 +1928,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -1784,7 +1948,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,7 +1970,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -1814,14 +1978,14 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -1845,15 +2009,15 @@
         <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -1865,7 +2029,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1873,7 +2037,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -1905,10 +2069,10 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,10 +2087,10 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1935,7 +2099,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1957,10 +2121,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1975,10 +2139,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1993,7 +2157,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -2001,7 +2165,7 @@
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="8"/>
@@ -2020,7 +2184,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -2032,15 +2196,15 @@
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -2052,7 +2216,7 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2060,7 +2224,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -2072,7 +2236,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2100,7 +2264,7 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>40</v>
@@ -2118,7 +2282,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -2126,26 +2290,26 @@
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -2157,15 +2321,15 @@
         <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2177,7 +2341,7 @@
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2185,7 +2349,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -2197,7 +2361,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2217,7 +2381,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2239,7 +2403,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -2251,7 +2415,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2267,14 +2431,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2290,7 +2454,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2298,7 +2462,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -2306,14 +2470,14 @@
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="8"/>
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -2325,7 +2489,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -2337,15 +2501,15 @@
         <v>2</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -2357,7 +2521,7 @@
       </c>
       <c r="B241" s="7"/>
       <c r="C241" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2365,7 +2529,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -2377,7 +2541,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2397,7 +2561,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2405,7 +2569,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -2413,26 +2577,26 @@
     </row>
     <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B247" s="9"/>
       <c r="C247" s="8"/>
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -2444,15 +2608,15 @@
         <v>2</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -2464,7 +2628,7 @@
       </c>
       <c r="B300" s="7"/>
       <c r="C300" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2472,7 +2636,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -2484,7 +2648,7 @@
       </c>
       <c r="B302" s="7"/>
       <c r="C302" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2492,10 +2656,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2504,7 +2668,7 @@
       </c>
       <c r="B304" s="7"/>
       <c r="C304" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2524,7 +2688,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2532,7 +2696,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -2540,14 +2704,14 @@
     </row>
     <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B308" s="9"/>
       <c r="C308" s="8"/>
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -2559,7 +2723,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C356" s="18"/>
     </row>
@@ -2571,15 +2735,15 @@
         <v>2</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -2591,7 +2755,7 @@
       </c>
       <c r="B359" s="7"/>
       <c r="C359" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2613,7 +2777,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -2625,7 +2789,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2633,7 +2797,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -2641,14 +2805,14 @@
     </row>
     <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B365" s="9"/>
       <c r="C365" s="8"/>
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -2660,7 +2824,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -2672,15 +2836,15 @@
         <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -2692,7 +2856,7 @@
       </c>
       <c r="B418" s="7"/>
       <c r="C418" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2700,7 +2864,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -2712,7 +2876,7 @@
       </c>
       <c r="B420" s="7"/>
       <c r="C420" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2728,7 +2892,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2739,7 +2903,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2754,10 +2918,10 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2777,7 +2941,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -2789,7 +2953,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2797,7 +2961,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -2805,14 +2969,14 @@
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="8"/>
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -2824,7 +2988,7 @@
     <row r="474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="13"/>
       <c r="B474" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C474" s="18"/>
     </row>
@@ -2836,15 +3000,15 @@
         <v>2</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -2856,7 +3020,7 @@
       </c>
       <c r="B477" s="7"/>
       <c r="C477" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2864,7 +3028,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -2876,7 +3040,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2884,7 +3048,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -2892,26 +3056,26 @@
     </row>
     <row r="481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="8"/>
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -2923,15 +3087,15 @@
         <v>2</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -2943,7 +3107,7 @@
       </c>
       <c r="B536" s="7"/>
       <c r="C536" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2951,7 +3115,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -2963,7 +3127,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2974,7 +3138,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2989,7 +3153,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -3001,7 +3165,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3012,7 +3176,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3021,7 +3185,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3029,10 +3193,10 @@
         <v>5.2</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3047,7 +3211,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -3055,26 +3219,26 @@
     </row>
     <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B548" s="9"/>
       <c r="C548" s="8"/>
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -3086,15 +3250,15 @@
         <v>2</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -3106,7 +3270,7 @@
       </c>
       <c r="B595" s="7"/>
       <c r="C595" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3114,7 +3278,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -3126,7 +3290,7 @@
       </c>
       <c r="B597" s="7"/>
       <c r="C597" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3134,10 +3298,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3146,7 +3310,7 @@
       </c>
       <c r="B599" s="7"/>
       <c r="C599" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3154,7 +3318,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -3166,14 +3330,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3195,7 +3359,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -3203,14 +3367,14 @@
     </row>
     <row r="606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B606" s="9"/>
       <c r="C606" s="8"/>
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -3222,7 +3386,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -3234,15 +3398,15 @@
         <v>2</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -3254,7 +3418,7 @@
       </c>
       <c r="B654" s="7"/>
       <c r="C654" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3262,7 +3426,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -3274,7 +3438,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3294,7 +3458,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3302,7 +3466,7 @@
         <v>3.2</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C659" s="2" t="s">
         <v>40</v>
@@ -3320,7 +3484,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -3328,18 +3492,449 @@
     </row>
     <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B662" s="9"/>
       <c r="C662" s="8"/>
     </row>
+    <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A709" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B709" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C709" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A710" s="13"/>
+      <c r="B710" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C710" s="21"/>
+    </row>
+    <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A711" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B711" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C711" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A712" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B712" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C712" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A713" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B713" s="7"/>
+      <c r="C713" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A714" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B714" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A715" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B715" s="7"/>
+      <c r="C715" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B716" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B717" s="7"/>
+      <c r="C717" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A718" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B718" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C718" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A719" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B719" s="7"/>
+      <c r="C719" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A720" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B720" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A721" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B721" s="7"/>
+      <c r="C721" s="2"/>
+    </row>
+    <row r="722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A722" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B722" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A723" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B723" s="9"/>
+      <c r="C723" s="8"/>
+    </row>
+    <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A768" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B768" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C768" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A769" s="13"/>
+      <c r="B769" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C769" s="18"/>
+    </row>
+    <row r="770" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B770" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C770" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A771" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B771" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C771" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A772" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B772" s="7"/>
+      <c r="C772" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A773" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B773" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C773" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B774" s="7"/>
+      <c r="C774" s="2"/>
+    </row>
+    <row r="775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B775" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C775" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B776" s="7"/>
+      <c r="C776" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A777" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B777" s="7"/>
+      <c r="C777" s="2"/>
+    </row>
+    <row r="778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A778" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B778" s="7"/>
+      <c r="C778" s="2"/>
+    </row>
+    <row r="779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A779" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B779" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C779" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A780" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B780" s="9"/>
+      <c r="C780" s="8"/>
+    </row>
+    <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A827" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B827" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C827" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A828" s="13"/>
+      <c r="B828" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C828" s="21"/>
+    </row>
+    <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A829" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B829" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C829" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A830" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B830" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C830" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A831" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B831" s="7"/>
+      <c r="C831" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A832" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B832" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A833" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B833" s="7"/>
+      <c r="C833" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A834" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B834" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A835" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B835" s="7"/>
+      <c r="C835" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A836" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B836" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A837" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B837" s="7"/>
+      <c r="C837" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A838" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B838" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A839" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B839" s="7"/>
+      <c r="C839" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A840" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B840" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C840" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A841" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B841" s="7"/>
+      <c r="C841" s="2"/>
+    </row>
+    <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A842" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B842" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A843" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B843" s="9"/>
+      <c r="C843" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
     <mergeCell ref="B533:C533"/>
     <mergeCell ref="B651:C651"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B828:C828"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66FFF95-91CD-43C0-81E9-524877467981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264BDB9-D4C9-4025-929C-52606A9C58B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$883</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$944</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="93">
   <si>
     <t>Implied</t>
   </si>
@@ -1231,6 +1231,32 @@
   </si>
   <si>
     <r>
+      <t>Tmp = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Operand).</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Operand |= </t>
     </r>
     <r>
@@ -1256,33 +1282,6 @@
     </r>
   </si>
   <si>
-    <t>Operand = (A - Operand). Z flag = (Operand == 0), N flag = (Operand &amp; $80).</t>
-  </si>
-  <si>
-    <r>
-      <t>Operand = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Operand). </t>
-    </r>
     <r>
       <rPr>
         <b/>
@@ -1302,7 +1301,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag = (Operand == 0), </t>
+      <t xml:space="preserve"> flag = (Tmp == 0), </t>
     </r>
     <r>
       <rPr>
@@ -1323,7 +1322,104 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag = (Operand &amp; $80).</t>
+      <t xml:space="preserve"> flag = (Tmp &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <t>BRK (0F)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = 0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2) | $0100</t>
     </r>
   </si>
 </sst>
@@ -1892,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C843"/>
+  <dimension ref="A1:C906"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -3867,64 +3963,267 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A838" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B838" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A838" s="3"/>
+      <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A839" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="3">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="B840" s="7" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C840" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="3">
-        <v>6.1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="B841" s="7"/>
       <c r="C841" s="2"/>
     </row>
     <row r="842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B842" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A843" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B843" s="7"/>
+      <c r="C843" s="2"/>
+    </row>
+    <row r="844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A844" s="3">
         <v>6.2</v>
       </c>
-      <c r="B842" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C842" s="2" t="s">
+      <c r="B844" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C844" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A843" s="16" t="s">
+    <row r="845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A845" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B843" s="9"/>
-      <c r="C843" s="8"/>
+      <c r="B845" s="9"/>
+      <c r="C845" s="8"/>
+    </row>
+    <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A886" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B886" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C886" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A887" s="13"/>
+      <c r="B887" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C887" s="18"/>
+    </row>
+    <row r="888" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A888" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B888" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C888" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A889" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B889" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C889" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A890" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B890" s="7"/>
+      <c r="C890" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A891" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B891" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C891" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A892" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B892" s="7"/>
+      <c r="C892" s="2"/>
+    </row>
+    <row r="893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A893" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B893" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A894" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B894" s="7"/>
+      <c r="C894" s="2"/>
+    </row>
+    <row r="895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A895" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B895" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C895" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A896" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B896" s="7"/>
+      <c r="C896" s="2"/>
+    </row>
+    <row r="897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A897" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B897" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A898" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B898" s="7"/>
+      <c r="C898" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A899" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B899" s="7"/>
+      <c r="C899" s="2"/>
+    </row>
+    <row r="900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A900" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B900" s="7"/>
+      <c r="C900" s="2"/>
+    </row>
+    <row r="901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A901" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B901" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C901" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A902" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B902" s="7"/>
+      <c r="C902" s="2"/>
+    </row>
+    <row r="903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A903" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B903" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A904" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B904" s="7"/>
+      <c r="C904" s="2"/>
+    </row>
+    <row r="905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A905" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B905" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C905" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A906" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B906" s="9"/>
+      <c r="C906" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264BDB9-D4C9-4025-929C-52606A9C58B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A53ACD-E657-44F8-B015-BAF52C4E33BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$944</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$1218</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="107">
   <si>
     <t>Implied</t>
   </si>
@@ -92,6 +92,9 @@
     <t>Absolute (Read)</t>
   </si>
   <si>
+    <t>BPL (10)</t>
+  </si>
+  <si>
     <t>Size: 3</t>
   </si>
   <si>
@@ -1421,6 +1424,177 @@
       </rPr>
       <t>-2) | $0100</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If !Jump, end instruction (next half-cycle is 4.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80) == $00.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL1 (11)</t>
+  </si>
+  <si>
+    <t>Read $FFDC</t>
+  </si>
+  <si>
+    <t>Read $FFDD</t>
+  </si>
+  <si>
+    <t>CLR1 (12)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~1) | 0.</t>
+  </si>
+  <si>
+    <t>BBC0 (13)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (0 &lt;&lt; 0).</t>
+  </si>
+  <si>
+    <t>Cycles: 2-4</t>
+  </si>
+  <si>
+    <t>OR (14)</t>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <t>X-Indexed Direct Page (Read)</t>
   </si>
 </sst>
 </file>
@@ -1988,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C906"/>
+  <dimension ref="A1:C1193"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -2000,7 +2174,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -2024,15 +2198,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -2044,7 +2218,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2066,7 +2240,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -2074,14 +2248,14 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -2105,15 +2279,15 @@
         <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -2125,7 +2299,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2133,7 +2307,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -2165,10 +2339,10 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2183,10 +2357,10 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2195,7 +2369,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2217,10 +2391,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2235,10 +2409,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2253,7 +2427,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -2261,14 +2435,14 @@
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="8"/>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -2280,7 +2454,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -2292,15 +2466,15 @@
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -2312,7 +2486,7 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2320,7 +2494,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -2332,7 +2506,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2352,7 +2526,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2360,10 +2534,10 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2378,7 +2552,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -2386,26 +2560,26 @@
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -2417,15 +2591,15 @@
         <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2437,7 +2611,7 @@
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2445,7 +2619,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -2457,7 +2631,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2477,7 +2651,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2499,7 +2673,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -2511,7 +2685,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2527,14 +2701,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2550,7 +2724,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2558,7 +2732,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -2566,14 +2740,14 @@
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="8"/>
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -2585,7 +2759,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -2597,15 +2771,15 @@
         <v>2</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -2617,7 +2791,7 @@
       </c>
       <c r="B241" s="7"/>
       <c r="C241" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2625,7 +2799,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -2637,7 +2811,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2657,7 +2831,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2665,7 +2839,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -2673,20 +2847,20 @@
     </row>
     <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B247" s="9"/>
       <c r="C247" s="8"/>
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2704,15 +2878,15 @@
         <v>2</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -2724,7 +2898,7 @@
       </c>
       <c r="B300" s="7"/>
       <c r="C300" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2732,7 +2906,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -2744,7 +2918,7 @@
       </c>
       <c r="B302" s="7"/>
       <c r="C302" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2752,10 +2926,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2764,7 +2938,7 @@
       </c>
       <c r="B304" s="7"/>
       <c r="C304" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2784,7 +2958,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2792,7 +2966,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -2800,14 +2974,14 @@
     </row>
     <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B308" s="9"/>
       <c r="C308" s="8"/>
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -2819,7 +2993,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C356" s="18"/>
     </row>
@@ -2831,15 +3005,15 @@
         <v>2</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -2851,7 +3025,7 @@
       </c>
       <c r="B359" s="7"/>
       <c r="C359" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2873,7 +3047,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -2885,7 +3059,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,7 +3067,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -2901,14 +3075,14 @@
     </row>
     <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B365" s="9"/>
       <c r="C365" s="8"/>
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -2920,7 +3094,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -2932,15 +3106,15 @@
         <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -2952,7 +3126,7 @@
       </c>
       <c r="B418" s="7"/>
       <c r="C418" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2960,7 +3134,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -2972,7 +3146,7 @@
       </c>
       <c r="B420" s="7"/>
       <c r="C420" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2988,7 +3162,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2999,7 +3173,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3014,10 +3188,10 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3037,7 +3211,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -3049,7 +3223,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3057,7 +3231,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -3065,14 +3239,14 @@
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="8"/>
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -3084,7 +3258,7 @@
     <row r="474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="13"/>
       <c r="B474" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C474" s="18"/>
     </row>
@@ -3096,15 +3270,15 @@
         <v>2</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -3116,7 +3290,7 @@
       </c>
       <c r="B477" s="7"/>
       <c r="C477" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3124,7 +3298,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -3136,7 +3310,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3144,7 +3318,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -3152,26 +3326,26 @@
     </row>
     <row r="481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="8"/>
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -3183,15 +3357,15 @@
         <v>2</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -3203,7 +3377,7 @@
       </c>
       <c r="B536" s="7"/>
       <c r="C536" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3211,7 +3385,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -3223,7 +3397,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3234,7 +3408,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3249,7 +3423,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -3261,7 +3435,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3272,7 +3446,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3281,7 +3455,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3289,10 +3463,10 @@
         <v>5.2</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3307,7 +3481,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -3315,26 +3489,26 @@
     </row>
     <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B548" s="9"/>
       <c r="C548" s="8"/>
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -3346,15 +3520,15 @@
         <v>2</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -3366,7 +3540,7 @@
       </c>
       <c r="B595" s="7"/>
       <c r="C595" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3374,7 +3548,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -3386,7 +3560,7 @@
       </c>
       <c r="B597" s="7"/>
       <c r="C597" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3394,10 +3568,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3406,7 +3580,7 @@
       </c>
       <c r="B599" s="7"/>
       <c r="C599" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3414,7 +3588,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -3426,14 +3600,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3455,7 +3629,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -3463,14 +3637,14 @@
     </row>
     <row r="606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B606" s="9"/>
       <c r="C606" s="8"/>
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -3482,7 +3656,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -3494,15 +3668,15 @@
         <v>2</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -3514,7 +3688,7 @@
       </c>
       <c r="B654" s="7"/>
       <c r="C654" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3522,7 +3696,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -3534,7 +3708,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3554,7 +3728,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3562,10 +3736,10 @@
         <v>3.2</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3580,7 +3754,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -3588,20 +3762,20 @@
     </row>
     <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B662" s="9"/>
       <c r="C662" s="8"/>
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C709" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3619,15 +3793,15 @@
         <v>2</v>
       </c>
       <c r="C711" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -3639,7 +3813,7 @@
       </c>
       <c r="B713" s="7"/>
       <c r="C713" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3647,7 +3821,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -3659,7 +3833,7 @@
       </c>
       <c r="B715" s="7"/>
       <c r="C715" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3667,10 +3841,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3679,7 +3853,7 @@
       </c>
       <c r="B717" s="7"/>
       <c r="C717" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3699,7 +3873,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3707,10 +3881,10 @@
         <v>4.2</v>
       </c>
       <c r="B720" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3725,7 +3899,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -3733,14 +3907,14 @@
     </row>
     <row r="723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B723" s="9"/>
       <c r="C723" s="8"/>
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -3764,15 +3938,15 @@
         <v>2</v>
       </c>
       <c r="C770" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -3784,7 +3958,7 @@
       </c>
       <c r="B772" s="7"/>
       <c r="C772" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3792,10 +3966,10 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3810,10 +3984,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3822,7 +3996,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3844,7 +4018,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -3852,20 +4026,20 @@
     </row>
     <row r="780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B780" s="9"/>
       <c r="C780" s="8"/>
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C827" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3883,15 +4057,15 @@
         <v>2</v>
       </c>
       <c r="C829" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -3903,7 +4077,7 @@
       </c>
       <c r="B831" s="7"/>
       <c r="C831" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3911,7 +4085,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -3923,7 +4097,7 @@
       </c>
       <c r="B833" s="7"/>
       <c r="C833" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3931,10 +4105,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3943,7 +4117,7 @@
       </c>
       <c r="B835" s="7"/>
       <c r="C835" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3963,21 +4137,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3988,7 +4162,7 @@
         <v>7</v>
       </c>
       <c r="C840" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4003,10 +4177,10 @@
         <v>5.2</v>
       </c>
       <c r="B842" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4021,7 +4195,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -4029,14 +4203,14 @@
     </row>
     <row r="845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B845" s="9"/>
       <c r="C845" s="8"/>
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -4060,15 +4234,15 @@
         <v>2</v>
       </c>
       <c r="C888" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -4080,7 +4254,7 @@
       </c>
       <c r="B890" s="7"/>
       <c r="C890" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4088,10 +4262,10 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C891" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4106,10 +4280,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4124,10 +4298,10 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C895" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4142,10 +4316,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4154,7 +4328,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4176,10 +4350,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4194,10 +4368,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4212,7 +4386,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -4220,19 +4394,762 @@
     </row>
     <row r="906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B906" s="9"/>
       <c r="C906" s="8"/>
     </row>
+    <row r="945" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A945" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B945" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C945" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A946" s="13"/>
+      <c r="B946" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C946" s="18"/>
+    </row>
+    <row r="947" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A947" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B947" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C947" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A948" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B948" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C948" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A949" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B949" s="7"/>
+      <c r="C949" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A950" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B950" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C950" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A951" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B951" s="7"/>
+      <c r="C951" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A952" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B952" s="7"/>
+      <c r="C952" s="2"/>
+    </row>
+    <row r="953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A953" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B953" s="7"/>
+      <c r="C953" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A954" s="3"/>
+      <c r="B954" s="7"/>
+      <c r="C954" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A955" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B955" s="7"/>
+      <c r="C955" s="2"/>
+    </row>
+    <row r="956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A956" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B956" s="7"/>
+      <c r="C956" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A957" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B957" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A958" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B958" s="9"/>
+      <c r="C958" s="8"/>
+    </row>
+    <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1004" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1004" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1004" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1005" s="13"/>
+      <c r="B1005" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1005" s="18"/>
+    </row>
+    <row r="1006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1006" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1006" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1007" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1007" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1007" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1008" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1008" s="7"/>
+      <c r="C1008" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1009" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1009" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1009" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1010" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1010" s="7"/>
+      <c r="C1010" s="2"/>
+    </row>
+    <row r="1011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1011" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1011" s="7"/>
+      <c r="C1011" s="2"/>
+    </row>
+    <row r="1012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1012" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1012" s="7"/>
+      <c r="C1012" s="2"/>
+    </row>
+    <row r="1013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1013" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1013" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1013" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1014" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1014" s="7"/>
+      <c r="C1014" s="2"/>
+    </row>
+    <row r="1015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1015" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1015" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1015" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1016" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1016" s="7"/>
+      <c r="C1016" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1017" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1017" s="7"/>
+      <c r="C1017" s="2"/>
+    </row>
+    <row r="1018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1018" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1018" s="7"/>
+      <c r="C1018" s="2"/>
+    </row>
+    <row r="1019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1019" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1019" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1019" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1020" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B1020" s="7"/>
+      <c r="C1020" s="2"/>
+    </row>
+    <row r="1021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1021" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B1021" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1021" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1022" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B1022" s="7"/>
+      <c r="C1022" s="2"/>
+    </row>
+    <row r="1023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1023" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B1023" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1023" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1024" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1024" s="9"/>
+      <c r="C1024" s="8"/>
+    </row>
+    <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1063" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1063" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1063" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1064" s="13"/>
+      <c r="B1064" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1064" s="21"/>
+    </row>
+    <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1065" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1065" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1065" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1066" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1066" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1066" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1067" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1067" s="7"/>
+      <c r="C1067" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1068" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1068" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1068" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1069" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1069" s="7"/>
+      <c r="C1069" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1070" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1070" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1070" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1071" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1071" s="7"/>
+      <c r="C1071" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1072" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1072" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1072" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1073" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1073" s="7"/>
+      <c r="C1073" s="2"/>
+    </row>
+    <row r="1074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1074" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1074" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1074" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1075" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1075" s="9"/>
+      <c r="C1075" s="8"/>
+    </row>
+    <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1122" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1122" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1122" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1123" s="13"/>
+      <c r="B1123" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1123" s="18"/>
+    </row>
+    <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1124" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1124" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1124" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1125" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1126" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1126" s="7"/>
+      <c r="C1126" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1127" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1127" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1128" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1128" s="7"/>
+      <c r="C1128" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1129" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1129" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1130" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1130" s="7"/>
+      <c r="C1130" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1131" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1131" s="7"/>
+      <c r="C1131" s="2"/>
+    </row>
+    <row r="1132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1132" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1132" s="7"/>
+      <c r="C1132" s="2"/>
+    </row>
+    <row r="1133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1133" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1133" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1134" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1134" s="7"/>
+      <c r="C1134" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1135" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1135" s="7"/>
+      <c r="C1135" s="2"/>
+    </row>
+    <row r="1136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1136" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1136" s="7"/>
+      <c r="C1136" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1137" s="3"/>
+      <c r="B1137" s="7"/>
+      <c r="C1137" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1138" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1138" s="7"/>
+      <c r="C1138" s="2"/>
+    </row>
+    <row r="1139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1139" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B1139" s="7"/>
+      <c r="C1139" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1140" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B1140" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1140" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1141" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1141" s="9"/>
+      <c r="C1141" s="8"/>
+    </row>
+    <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1181" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1181" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1181" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1182" s="13"/>
+      <c r="B1182" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1182" s="21"/>
+    </row>
+    <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1183" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1183" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1183" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1184" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1184" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1185" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1185" s="7"/>
+      <c r="C1185" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1186" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1186" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1186" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1187" s="7"/>
+      <c r="C1187" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1188" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1188" s="7"/>
+      <c r="C1188" s="2"/>
+    </row>
+    <row r="1189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1189" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1189" s="7"/>
+      <c r="C1189" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1190" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1190" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1190" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1191" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1191" s="7"/>
+      <c r="C1191" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1192" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1192" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1192" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1193" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1193" s="9"/>
+      <c r="C1193" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
     <mergeCell ref="B533:C533"/>
     <mergeCell ref="B651:C651"/>
     <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="B1182:C1182"/>
     <mergeCell ref="B828:C828"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A53ACD-E657-44F8-B015-BAF52C4E33BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACB16F5-1831-419B-B1CE-0F29550D97C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$1218</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$1414</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="118">
   <si>
     <t>Implied</t>
   </si>
@@ -206,6 +206,9 @@
     <t>NOP (00)</t>
   </si>
   <si>
+    <t xml:space="preserve">Inc. PC. </t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Read </t>
     </r>
@@ -1179,6 +1182,53 @@
   </si>
   <si>
     <r>
+      <t>Address = (Operand | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Push </t>
     </r>
     <r>
@@ -1595,6 +1645,102 @@
   </si>
   <si>
     <t>X-Indexed Direct Page (Read)</t>
+  </si>
+  <si>
+    <t>OR (15)</t>
+  </si>
+  <si>
+    <t>X-Indexed Absolute (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pointer = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Address).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (16)</t>
+  </si>
+  <si>
+    <t>Y-Indexed Absolute (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pointer = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Address).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (17)</t>
+  </si>
+  <si>
+    <t>Indirect Y-Indexed [d]+Y (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Address = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Pointer).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2162,7 +2308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C1193"/>
+  <dimension ref="A1:C1375"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -2206,7 +2352,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -2240,7 +2386,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -2255,7 +2401,7 @@
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -2287,7 +2433,7 @@
         <v>24</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -2307,7 +2453,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -2339,7 +2485,7 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>20</v>
@@ -2357,7 +2503,7 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>21</v>
@@ -2369,7 +2515,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2391,10 +2537,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2409,10 +2555,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2427,7 +2573,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -2442,7 +2588,7 @@
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -2454,7 +2600,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -2474,7 +2620,7 @@
         <v>24</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -2494,7 +2640,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -2506,7 +2652,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2526,7 +2672,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2537,7 +2683,7 @@
         <v>25</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2552,7 +2698,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -2567,10 +2713,10 @@
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>18</v>
@@ -2579,7 +2725,7 @@
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -2599,7 +2745,7 @@
         <v>24</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2619,7 +2765,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -2631,7 +2777,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2651,7 +2797,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2673,7 +2819,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -2685,7 +2831,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2701,14 +2847,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2724,7 +2870,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2732,7 +2878,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -2747,7 +2893,7 @@
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -2759,7 +2905,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -2779,7 +2925,7 @@
         <v>24</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -2799,7 +2945,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -2811,7 +2957,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2831,7 +2977,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2839,7 +2985,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -2854,7 +3000,7 @@
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
@@ -2886,7 +3032,7 @@
         <v>24</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -2906,7 +3052,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -2926,7 +3072,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>29</v>
@@ -2958,7 +3104,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2966,7 +3112,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -2981,7 +3127,7 @@
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -2993,7 +3139,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C356" s="18"/>
     </row>
@@ -3013,7 +3159,7 @@
         <v>24</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -3047,7 +3193,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -3059,7 +3205,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3067,7 +3213,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -3082,7 +3228,7 @@
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -3094,7 +3240,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -3114,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -3134,7 +3280,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -3162,7 +3308,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3173,7 +3319,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3188,7 +3334,7 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>22</v>
@@ -3223,7 +3369,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3231,7 +3377,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -3246,7 +3392,7 @@
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -3278,7 +3424,7 @@
         <v>24</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -3298,7 +3444,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -3310,7 +3456,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3318,7 +3464,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -3333,7 +3479,7 @@
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
@@ -3345,7 +3491,7 @@
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -3365,7 +3511,7 @@
         <v>24</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -3385,7 +3531,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -3397,7 +3543,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3408,7 +3554,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3423,7 +3569,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -3435,7 +3581,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3446,7 +3592,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3455,7 +3601,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3466,7 +3612,7 @@
         <v>25</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3481,7 +3627,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -3496,7 +3642,7 @@
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
@@ -3508,7 +3654,7 @@
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -3528,7 +3674,7 @@
         <v>24</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -3548,7 +3694,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -3568,7 +3714,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>29</v>
@@ -3588,7 +3734,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -3600,14 +3746,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3629,7 +3775,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -3644,7 +3790,7 @@
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -3656,7 +3802,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -3676,7 +3822,7 @@
         <v>24</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -3696,7 +3842,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -3708,7 +3854,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3728,7 +3874,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3739,7 +3885,7 @@
         <v>25</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3754,7 +3900,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -3769,7 +3915,7 @@
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
@@ -3801,7 +3947,7 @@
         <v>24</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -3821,7 +3967,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -3841,7 +3987,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>29</v>
@@ -3873,7 +4019,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3884,7 +4030,7 @@
         <v>25</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3899,7 +4045,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -3914,7 +4060,7 @@
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -3946,7 +4092,7 @@
         <v>24</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -3966,7 +4112,7 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>28</v>
@@ -3984,10 +4130,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3996,7 +4142,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4018,7 +4164,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -4033,7 +4179,7 @@
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
@@ -4065,7 +4211,7 @@
         <v>24</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -4085,7 +4231,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -4105,7 +4251,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>29</v>
@@ -4137,21 +4283,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4180,7 +4326,7 @@
         <v>25</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4195,7 +4341,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -4210,7 +4356,7 @@
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -4242,7 +4388,7 @@
         <v>24</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -4262,7 +4408,7 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>28</v>
@@ -4280,7 +4426,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>20</v>
@@ -4298,7 +4444,7 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>21</v>
@@ -4316,10 +4462,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4328,7 +4474,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4350,10 +4496,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4368,10 +4514,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4386,7 +4532,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -4404,7 +4550,7 @@
         <v>17</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -4433,7 +4579,7 @@
         <v>24</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -4445,7 +4591,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4453,7 +4599,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -4465,7 +4611,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4481,14 +4627,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4504,7 +4650,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4512,7 +4658,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -4527,7 +4673,7 @@
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -4559,7 +4705,7 @@
         <v>24</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -4579,7 +4725,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -4611,7 +4757,7 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>20</v>
@@ -4629,7 +4775,7 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>21</v>
@@ -4641,7 +4787,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4663,10 +4809,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4681,10 +4827,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4699,7 +4845,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -4714,7 +4860,7 @@
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -4726,7 +4872,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -4746,7 +4892,7 @@
         <v>24</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -4766,7 +4912,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -4778,7 +4924,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4798,7 +4944,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4809,7 +4955,7 @@
         <v>25</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4824,7 +4970,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -4839,10 +4985,10 @@
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1122" s="12" t="s">
         <v>18</v>
@@ -4851,7 +4997,7 @@
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
       <c r="B1123" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1123" s="18"/>
     </row>
@@ -4871,7 +5017,7 @@
         <v>24</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -4891,7 +5037,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -4903,7 +5049,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4923,7 +5069,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4945,7 +5091,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -4957,7 +5103,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4973,14 +5119,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4996,7 +5142,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5004,7 +5150,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -5019,7 +5165,7 @@
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -5031,7 +5177,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -5051,7 +5197,7 @@
         <v>24</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -5071,7 +5217,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -5099,7 +5245,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5119,7 +5265,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5127,7 +5273,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -5140,8 +5286,460 @@
       <c r="B1193" s="9"/>
       <c r="C1193" s="8"/>
     </row>
+    <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1240" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1240" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1240" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1241" s="13"/>
+      <c r="B1241" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1241" s="18"/>
+    </row>
+    <row r="1242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1242" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1242" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1242" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1243" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1243" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1244" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1244" s="7"/>
+      <c r="C1244" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1245" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1245" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1245" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1246" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1246" s="7"/>
+      <c r="C1246" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1247" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1247" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1247" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1248" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1248" s="7"/>
+      <c r="C1248" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1249" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1249" s="7"/>
+      <c r="C1249" s="2"/>
+    </row>
+    <row r="1250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1250" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1250" s="7"/>
+      <c r="C1250" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1251" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1251" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1251" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1252" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1252" s="7"/>
+      <c r="C1252" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1253" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1253" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1253" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1254" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1254" s="9"/>
+      <c r="C1254" s="8"/>
+    </row>
+    <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1299" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1299" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1299" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1300" s="13"/>
+      <c r="B1300" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1300" s="18"/>
+    </row>
+    <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1301" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1301" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1301" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1302" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1302" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1302" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1303" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1303" s="7"/>
+      <c r="C1303" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1304" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1304" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1304" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1305" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1305" s="7"/>
+      <c r="C1305" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1306" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1306" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1306" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1307" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1307" s="7"/>
+      <c r="C1307" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1308" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1308" s="7"/>
+      <c r="C1308" s="2"/>
+    </row>
+    <row r="1309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1309" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1309" s="7"/>
+      <c r="C1309" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1310" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1310" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1310" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1311" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1311" s="7"/>
+      <c r="C1311" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1312" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1312" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1312" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1313" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1313" s="9"/>
+      <c r="C1313" s="8"/>
+    </row>
+    <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1358" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1358" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1358" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1359" s="13"/>
+      <c r="B1359" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1359" s="21"/>
+    </row>
+    <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1360" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1360" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1360" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1361" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1361" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1361" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1362" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1362" s="7"/>
+      <c r="C1362" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1363" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1363" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1363" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1364" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1364" s="7"/>
+      <c r="C1364" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1365" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1365" s="7"/>
+      <c r="C1365" s="2"/>
+    </row>
+    <row r="1366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1366" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1366" s="7"/>
+      <c r="C1366" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1367" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1367" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1367" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1368" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1368" s="7"/>
+      <c r="C1368" s="2"/>
+    </row>
+    <row r="1369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1369" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1369" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1369" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1370" s="3"/>
+      <c r="B1370" s="22"/>
+      <c r="C1370" s="2"/>
+    </row>
+    <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1371" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1371" s="7"/>
+      <c r="C1371" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1372" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1372" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1372" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1373" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1373" s="7"/>
+      <c r="C1373" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1374" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1374" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1374" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1375" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1375" s="9"/>
+      <c r="C1375" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
@@ -5150,6 +5748,8 @@
     <mergeCell ref="B710:C710"/>
     <mergeCell ref="B1064:C1064"/>
     <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1359:C1359"/>
     <mergeCell ref="B828:C828"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACB16F5-1831-419B-B1CE-0F29550D97C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A382F0C3-5890-4CFD-8D95-6D1F86205245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$1414</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2478</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="162">
   <si>
     <t>Implied</t>
   </si>
@@ -86,12 +86,6 @@
     <t>Store as Address.L.</t>
   </si>
   <si>
-    <t>Absolute (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <t>Absolute (Read)</t>
-  </si>
-  <si>
     <t>BPL (10)</t>
   </si>
   <si>
@@ -197,18 +191,27 @@
     <t>Discard.</t>
   </si>
   <si>
+    <t>AND (25)</t>
+  </si>
+  <si>
+    <t>AND (27)</t>
+  </si>
+  <si>
+    <t>AND (29)</t>
+  </si>
+  <si>
     <t>Store as Address.H.</t>
   </si>
   <si>
     <t>Read Pointer</t>
   </si>
   <si>
+    <t>Read Pointer + 1</t>
+  </si>
+  <si>
     <t>NOP (00)</t>
   </si>
   <si>
-    <t xml:space="preserve">Inc. PC. </t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Read </t>
     </r>
@@ -321,15 +324,6 @@
     <t>Write Operand.</t>
   </si>
   <si>
-    <t>Direct Page Bit (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <t>BBS (03)</t>
-  </si>
-  <si>
-    <t>Direct Page Bit Relative</t>
-  </si>
-  <si>
     <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (1 &lt;&lt; 0).</t>
   </si>
   <si>
@@ -360,6 +354,2073 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.L = Address.L.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H = Address.H.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cycles: 5-7</t>
+  </si>
+  <si>
+    <t>OR (04)</t>
+  </si>
+  <si>
+    <t>OR (05)</t>
+  </si>
+  <si>
+    <t>OR (06)</t>
+  </si>
+  <si>
+    <t>OR (07)</t>
+  </si>
+  <si>
+    <t>Store as Pointer.L.</t>
+  </si>
+  <si>
+    <t>OR (08)</t>
+  </si>
+  <si>
+    <t>OR (09)</t>
+  </si>
+  <si>
+    <t>Store as Operand0.</t>
+  </si>
+  <si>
+    <t>Store as Operand1.</t>
+  </si>
+  <si>
+    <t>Write Operand0.</t>
+  </si>
+  <si>
+    <t>OR1 (0A)</t>
+  </si>
+  <si>
+    <t>Read (Address &amp; $1FFF)</t>
+  </si>
+  <si>
+    <t>Bit = Address &gt;&gt; 13.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> |= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand0 |= Operand1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (0B)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand &lt;&lt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>ASL (0C)</t>
+  </si>
+  <si>
+    <t>PUSH (0D)</t>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+0) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Address = (Operand | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Address = (Operand | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3)).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read ((Address + 1) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Address = (Operand | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 1. </t>
+    </r>
+  </si>
+  <si>
+    <t>TSET1 (0E)</t>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Operand).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand |= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp == 0), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <t>BRK (0F)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dec. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = 0, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. If !Jump, end instruction (next half-cycle is 4.2).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80) == $00.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL1 (11)</t>
+  </si>
+  <si>
+    <t>Read $FFDC</t>
+  </si>
+  <si>
+    <t>Read $FFDD</t>
+  </si>
+  <si>
+    <t>CLR1 (12)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~1) | 0.</t>
+  </si>
+  <si>
+    <t>BBC0 (13)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (0 &lt;&lt; 0).</t>
+  </si>
+  <si>
+    <t>Cycles: 2-4</t>
+  </si>
+  <si>
+    <t>OR (14)</t>
+  </si>
+  <si>
+    <r>
+      <t>Address = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (15)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pointer = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Address).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (16)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pointer = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Address).</t>
+    </r>
+  </si>
+  <si>
+    <t>OR (17)</t>
+  </si>
+  <si>
+    <t>Indirect Y-Indexed [d]+Y (Read)</t>
+  </si>
+  <si>
+    <r>
+      <t>Address = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + Pointer).</t>
+    </r>
+  </si>
+  <si>
+    <t>BBS0 (03)</t>
+  </si>
+  <si>
+    <t>Direct Page Bit Relative d.b, r</t>
+  </si>
+  <si>
+    <t>Direct Page d (Read)</t>
+  </si>
+  <si>
+    <t>Absolute !a (Read)</t>
+  </si>
+  <si>
+    <t>Indirect X (X) (Read)</t>
+  </si>
+  <si>
+    <t>X-Indexed Indirect [d+X] (Read)</t>
+  </si>
+  <si>
+    <t>Direct Page to Direct Page dd, ds (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>Absolute Boolean Bit m.b</t>
+  </si>
+  <si>
+    <t>Direct Page d (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>Absolute !a (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>Direct Page Bit d.b (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>X-Indexed Direct Page d+X (Read)</t>
+  </si>
+  <si>
+    <t>X-Indexed Absolute !a+X (Read)</t>
+  </si>
+  <si>
+    <t>Y-Indexed Absolute !a+Y (Read)</t>
+  </si>
+  <si>
+    <t>OR (18)</t>
+  </si>
+  <si>
+    <t>Immediate Data to Direct Page d, #i (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>OR (19)</t>
+  </si>
+  <si>
+    <t>Indirect Page to Indirect Page (X), (Y) (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Read (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <t>DECW (1A)</t>
+  </si>
+  <si>
+    <t>Direct Page d (Read/Modify/Write 16)</t>
+  </si>
+  <si>
+    <t>Underflow = (Operand == 0).</t>
+  </si>
+  <si>
+    <t>Operand -= 1.</t>
+  </si>
+  <si>
+    <t>LowZero = (Operand == 0).</t>
+  </si>
+  <si>
+    <t>ASL (1B)</t>
+  </si>
+  <si>
+    <t>X-Indexed Direct Page d+X (Read/Modify/Write)</t>
+  </si>
+  <si>
+    <t>ASL (1C)</t>
+  </si>
+  <si>
+    <t>Accumulator A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>DEC (1D)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Write to ((Address + 1) &amp; $FF) | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand -= Underflow. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (LowZero &amp;&amp; !Operand).</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (1E)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tmp = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &gt;= 0), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = !Tmp.</t>
+    </r>
+  </si>
+  <si>
+    <t>JMP (1F)</t>
+  </si>
+  <si>
+    <t>Absolute X-Indexed Indirect [!a+X]</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Address = </t>
     </r>
     <r>
@@ -381,10 +2442,244 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> + int8( Operand ).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve"> + i8(Operand).</t>
+    </r>
+  </si>
+  <si>
+    <t>CLRP (20)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; ~$20).</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL1 (21)</t>
+  </si>
+  <si>
+    <t>Read $FFDA</t>
+  </si>
+  <si>
+    <t>Read $FFDB</t>
+  </si>
+  <si>
+    <t>SET1 (22)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~2) | 2.</t>
+  </si>
+  <si>
+    <t>BBS1 (23)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 1)) == (1 &lt;&lt; 1).</t>
+  </si>
+  <si>
+    <t>AND (24)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (26)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read (X | ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag) &lt;&lt; 3))</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (28)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -404,113 +2699,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>.L = Address.L.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.H = Address.H.</t>
-    </r>
-  </si>
-  <si>
-    <t>Cycles: 5-7</t>
-  </si>
-  <si>
-    <t>OR (04)</t>
-  </si>
-  <si>
-    <t>Direct Page (Read)</t>
-  </si>
-  <si>
-    <t>OR (05)</t>
-  </si>
-  <si>
-    <t>OR (06)</t>
-  </si>
-  <si>
-    <t>Indirect X (Read)</t>
-  </si>
-  <si>
-    <t>OR (07)</t>
-  </si>
-  <si>
-    <t>X-Indexed Indirect (Read)</t>
-  </si>
-  <si>
-    <t>Store as Pointer.L.</t>
-  </si>
-  <si>
-    <t>OR (08)</t>
-  </si>
-  <si>
-    <t>OR (09)</t>
-  </si>
-  <si>
-    <t>Store as Operand0.</t>
-  </si>
-  <si>
-    <t>Store as Operand1.</t>
-  </si>
-  <si>
-    <t>Write Operand0.</t>
-  </si>
-  <si>
-    <t>Direct Page to Direct Page (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <t>OR1 (0A)</t>
-  </si>
-  <si>
-    <t>Absolute Boolean Bit</t>
-  </si>
-  <si>
-    <t>Read (Address &amp; $1FFF)</t>
-  </si>
-  <si>
-    <t>Bit = Address &gt;&gt; 13.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">. </t>
+    </r>
     <r>
       <rPr>
         <b/>
@@ -530,7 +2720,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> |= Operand. </t>
+      <t xml:space="preserve"> &amp;= Operand. </t>
     </r>
     <r>
       <rPr>
@@ -619,49 +2809,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> |= Operand. </t>
+      <t xml:space="preserve">Operand0 &amp;= Operand1. </t>
     </r>
     <r>
       <rPr>
@@ -682,28 +2830,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; $80), </t>
+      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
     </r>
     <r>
       <rPr>
@@ -724,1022 +2851,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> flag = !</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Operand0 |= Operand1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> flag = !Operand0.</t>
-    </r>
-  </si>
-  <si>
-    <t>ASL (0B)</t>
-  </si>
-  <si>
-    <t>Direct Page (Read/Modify/Write)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand &lt;&lt;= 1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = !Operand.</t>
-    </r>
-  </si>
-  <si>
-    <t>ASL (0C)</t>
-  </si>
-  <si>
-    <t>PUSH (0D)</t>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>+0) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-1) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Address = (Operand | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Address = (Operand | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3)).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Address = ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; P flag) &lt;&lt; 3).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Read ((Address + 1) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Address = (Operand | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3)).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Push </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> onto stack.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 1. </t>
-    </r>
-  </si>
-  <si>
-    <t>TSET1 (0E)</t>
-  </si>
-  <si>
-    <r>
-      <t>Tmp = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Operand).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Operand |= </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Z</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Tmp == 0), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = (Tmp &amp; $80).</t>
-    </r>
-  </si>
-  <si>
-    <t>BRK (0F)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Dec. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by 3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = 0, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag = 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Write to u8(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-2) | $0100</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. If !Jump, end instruction (next half-cycle is 4.2).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inc. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Set Jump to (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; $80) == $00.</t>
-    </r>
-  </si>
-  <si>
-    <t>TCALL1 (11)</t>
-  </si>
-  <si>
-    <t>Read $FFDC</t>
-  </si>
-  <si>
-    <t>Read $FFDD</t>
-  </si>
-  <si>
-    <t>CLR1 (12)</t>
-  </si>
-  <si>
-    <t>Operand = (Operand &amp; ~1) | 0.</t>
-  </si>
-  <si>
-    <t>BBC0 (13)</t>
-  </si>
-  <si>
-    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 0)) == (0 &lt;&lt; 0).</t>
-  </si>
-  <si>
-    <t>Cycles: 2-4</t>
-  </si>
-  <si>
-    <t>OR (14)</t>
-  </si>
-  <si>
-    <r>
-      <t>Address = ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Operand) &amp; $FF) | ((</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PSW</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> flag) &lt;&lt; 3).</t>
-    </r>
-  </si>
-  <si>
-    <t>X-Indexed Direct Page (Read)</t>
-  </si>
-  <si>
-    <t>OR (15)</t>
-  </si>
-  <si>
-    <t>X-Indexed Absolute (Read)</t>
-  </si>
-  <si>
-    <r>
-      <t>Pointer = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Address).</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (16)</t>
-  </si>
-  <si>
-    <t>Y-Indexed Absolute (Read)</t>
-  </si>
-  <si>
-    <r>
-      <t>Pointer = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Address).</t>
-    </r>
-  </si>
-  <si>
-    <t>OR (17)</t>
-  </si>
-  <si>
-    <t>Indirect Y-Indexed [d]+Y (Read)</t>
-  </si>
-  <si>
-    <r>
-      <t>Address = (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> + Pointer).</t>
     </r>
   </si>
 </sst>
@@ -2308,7 +3420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C1375"/>
+  <dimension ref="A1:C2436"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -2320,7 +3432,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -2344,15 +3456,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -2364,7 +3476,7 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2386,7 +3498,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -2394,14 +3506,14 @@
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="8"/>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -2425,15 +3537,15 @@
         <v>2</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -2445,7 +3557,7 @@
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2453,7 +3565,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -2485,10 +3597,10 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2503,10 +3615,10 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2515,7 +3627,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2537,10 +3649,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2555,10 +3667,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2573,7 +3685,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -2581,14 +3693,14 @@
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B80" s="9"/>
       <c r="C80" s="8"/>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -2600,7 +3712,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -2612,15 +3724,15 @@
         <v>2</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -2632,7 +3744,7 @@
       </c>
       <c r="B123" s="7"/>
       <c r="C123" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2640,7 +3752,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -2652,7 +3764,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2672,7 +3784,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2680,10 +3792,10 @@
         <v>3.2</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2698,7 +3810,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -2706,26 +3818,26 @@
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B131" s="9"/>
       <c r="C131" s="8"/>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -2737,15 +3849,15 @@
         <v>2</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2757,7 +3869,7 @@
       </c>
       <c r="B182" s="7"/>
       <c r="C182" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2765,7 +3877,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -2777,7 +3889,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2797,7 +3909,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2819,7 +3931,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -2831,7 +3943,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2847,14 +3959,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2870,7 +3982,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2878,7 +3990,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -2886,14 +3998,14 @@
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B197" s="9"/>
       <c r="C197" s="8"/>
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -2905,7 +4017,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>53</v>
+        <v>108</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -2917,15 +4029,15 @@
         <v>2</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -2937,7 +4049,7 @@
       </c>
       <c r="B241" s="7"/>
       <c r="C241" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2945,7 +4057,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -2957,7 +4069,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2977,7 +4089,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2985,7 +4097,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -2993,26 +4105,26 @@
     </row>
     <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B247" s="9"/>
       <c r="C247" s="8"/>
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -3024,15 +4136,15 @@
         <v>2</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -3044,7 +4156,7 @@
       </c>
       <c r="B300" s="7"/>
       <c r="C300" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3052,7 +4164,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -3064,7 +4176,7 @@
       </c>
       <c r="B302" s="7"/>
       <c r="C302" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3072,10 +4184,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3084,7 +4196,7 @@
       </c>
       <c r="B304" s="7"/>
       <c r="C304" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3104,7 +4216,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3112,7 +4224,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -3120,14 +4232,14 @@
     </row>
     <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B308" s="9"/>
       <c r="C308" s="8"/>
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -3138,10 +4250,10 @@
     </row>
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
-      <c r="B356" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="C356" s="18"/>
+      <c r="B356" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C356" s="21"/>
     </row>
     <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
@@ -3151,15 +4263,15 @@
         <v>2</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -3171,7 +4283,7 @@
       </c>
       <c r="B359" s="7"/>
       <c r="C359" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3193,7 +4305,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -3205,7 +4317,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3213,7 +4325,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -3221,14 +4333,14 @@
     </row>
     <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B365" s="9"/>
       <c r="C365" s="8"/>
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -3240,7 +4352,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -3252,15 +4364,15 @@
         <v>2</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -3272,7 +4384,7 @@
       </c>
       <c r="B418" s="7"/>
       <c r="C418" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3280,7 +4392,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -3292,7 +4404,7 @@
       </c>
       <c r="B420" s="7"/>
       <c r="C420" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3308,7 +4420,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3319,7 +4431,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3334,10 +4446,10 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3357,7 +4469,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -3369,7 +4481,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3377,7 +4489,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -3385,14 +4497,14 @@
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="8"/>
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -3404,7 +4516,7 @@
     <row r="474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="13"/>
       <c r="B474" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C474" s="18"/>
     </row>
@@ -3416,15 +4528,15 @@
         <v>2</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -3436,7 +4548,7 @@
       </c>
       <c r="B477" s="7"/>
       <c r="C477" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3444,7 +4556,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -3456,7 +4568,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3464,7 +4576,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -3472,26 +4584,26 @@
     </row>
     <row r="481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B481" s="9"/>
       <c r="C481" s="8"/>
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C532" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -3503,15 +4615,15 @@
         <v>2</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -3523,7 +4635,7 @@
       </c>
       <c r="B536" s="7"/>
       <c r="C536" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3531,7 +4643,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -3543,7 +4655,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3554,7 +4666,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3569,7 +4681,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -3581,7 +4693,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3592,7 +4704,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3601,7 +4713,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3609,10 +4721,10 @@
         <v>5.2</v>
       </c>
       <c r="B545" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3627,7 +4739,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -3635,26 +4747,26 @@
     </row>
     <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B548" s="9"/>
       <c r="C548" s="8"/>
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C591" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -3666,15 +4778,15 @@
         <v>2</v>
       </c>
       <c r="C593" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -3686,7 +4798,7 @@
       </c>
       <c r="B595" s="7"/>
       <c r="C595" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3694,7 +4806,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -3706,7 +4818,7 @@
       </c>
       <c r="B597" s="7"/>
       <c r="C597" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3714,10 +4826,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3726,7 +4838,7 @@
       </c>
       <c r="B599" s="7"/>
       <c r="C599" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3734,7 +4846,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -3746,14 +4858,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3775,7 +4887,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -3783,14 +4895,14 @@
     </row>
     <row r="606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B606" s="9"/>
       <c r="C606" s="8"/>
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -3802,7 +4914,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -3814,15 +4926,15 @@
         <v>2</v>
       </c>
       <c r="C652" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -3834,7 +4946,7 @@
       </c>
       <c r="B654" s="7"/>
       <c r="C654" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3842,7 +4954,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -3854,7 +4966,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3874,7 +4986,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3882,10 +4994,10 @@
         <v>3.2</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3900,7 +5012,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -3908,26 +5020,26 @@
     </row>
     <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B662" s="9"/>
       <c r="C662" s="8"/>
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C709" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
       <c r="B710" s="20" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C710" s="21"/>
     </row>
@@ -3939,15 +5051,15 @@
         <v>2</v>
       </c>
       <c r="C711" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -3959,7 +5071,7 @@
       </c>
       <c r="B713" s="7"/>
       <c r="C713" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3967,7 +5079,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -3979,7 +5091,7 @@
       </c>
       <c r="B715" s="7"/>
       <c r="C715" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3987,10 +5099,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3999,7 +5111,7 @@
       </c>
       <c r="B717" s="7"/>
       <c r="C717" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4019,7 +5131,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4027,10 +5139,10 @@
         <v>4.2</v>
       </c>
       <c r="B720" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4045,7 +5157,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -4053,14 +5165,14 @@
     </row>
     <row r="723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B723" s="9"/>
       <c r="C723" s="8"/>
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -4084,15 +5196,15 @@
         <v>2</v>
       </c>
       <c r="C770" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -4104,7 +5216,7 @@
       </c>
       <c r="B772" s="7"/>
       <c r="C772" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4112,10 +5224,10 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4130,10 +5242,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4142,7 +5254,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4164,7 +5276,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -4172,26 +5284,26 @@
     </row>
     <row r="780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B780" s="9"/>
       <c r="C780" s="8"/>
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
       </c>
       <c r="C827" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
       <c r="B828" s="20" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C828" s="21"/>
     </row>
@@ -4203,15 +5315,15 @@
         <v>2</v>
       </c>
       <c r="C829" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -4223,7 +5335,7 @@
       </c>
       <c r="B831" s="7"/>
       <c r="C831" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4231,7 +5343,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -4243,7 +5355,7 @@
       </c>
       <c r="B833" s="7"/>
       <c r="C833" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4251,10 +5363,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4263,7 +5375,7 @@
       </c>
       <c r="B835" s="7"/>
       <c r="C835" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4283,21 +5395,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4308,7 +5420,7 @@
         <v>7</v>
       </c>
       <c r="C840" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4323,10 +5435,10 @@
         <v>5.2</v>
       </c>
       <c r="B842" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4341,7 +5453,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -4349,14 +5461,14 @@
     </row>
     <row r="845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B845" s="9"/>
       <c r="C845" s="8"/>
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -4380,15 +5492,15 @@
         <v>2</v>
       </c>
       <c r="C888" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -4400,7 +5512,7 @@
       </c>
       <c r="B890" s="7"/>
       <c r="C890" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4408,10 +5520,10 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C891" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4426,10 +5538,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C893" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4444,10 +5556,10 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C895" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4462,10 +5574,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4474,7 +5586,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4496,10 +5608,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4514,10 +5626,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4532,7 +5644,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -4540,17 +5652,17 @@
     </row>
     <row r="906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B906" s="9"/>
       <c r="C906" s="8"/>
     </row>
     <row r="945" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -4571,15 +5683,15 @@
         <v>2</v>
       </c>
       <c r="C947" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -4591,7 +5703,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4599,7 +5711,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -4611,7 +5723,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4627,14 +5739,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4650,7 +5762,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4658,7 +5770,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -4666,14 +5778,14 @@
     </row>
     <row r="958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B958" s="9"/>
       <c r="C958" s="8"/>
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -4697,15 +5809,15 @@
         <v>2</v>
       </c>
       <c r="C1006" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -4717,7 +5829,7 @@
       </c>
       <c r="B1008" s="7"/>
       <c r="C1008" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4725,7 +5837,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -4757,10 +5869,10 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C1013" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4775,10 +5887,10 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C1015" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4787,7 +5899,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4809,10 +5921,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4827,10 +5939,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4845,7 +5957,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -4853,14 +5965,14 @@
     </row>
     <row r="1024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1024" s="9"/>
       <c r="C1024" s="8"/>
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -4872,7 +5984,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -4884,15 +5996,15 @@
         <v>2</v>
       </c>
       <c r="C1065" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -4904,7 +6016,7 @@
       </c>
       <c r="B1067" s="7"/>
       <c r="C1067" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4912,7 +6024,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -4924,7 +6036,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4944,7 +6056,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4952,10 +6064,10 @@
         <v>3.2</v>
       </c>
       <c r="B1072" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4970,7 +6082,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -4978,28 +6090,28 @@
     </row>
     <row r="1075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1075" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1075" s="9"/>
       <c r="C1075" s="8"/>
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1122" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
-      <c r="B1123" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1123" s="18"/>
+      <c r="B1123" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1123" s="21"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="5" t="s">
@@ -5009,15 +6121,15 @@
         <v>2</v>
       </c>
       <c r="C1124" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1125" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -5029,7 +6141,7 @@
       </c>
       <c r="B1126" s="7"/>
       <c r="C1126" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5037,7 +6149,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -5049,7 +6161,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5069,7 +6181,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5091,7 +6203,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -5103,7 +6215,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5119,14 +6231,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5142,7 +6254,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5150,7 +6262,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -5158,14 +6270,14 @@
     </row>
     <row r="1141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1141" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1141" s="9"/>
       <c r="C1141" s="8"/>
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -5177,7 +6289,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -5189,15 +6301,15 @@
         <v>2</v>
       </c>
       <c r="C1183" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1184" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -5209,7 +6321,7 @@
       </c>
       <c r="B1185" s="7"/>
       <c r="C1185" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5217,7 +6329,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -5229,7 +6341,7 @@
       </c>
       <c r="B1187" s="7"/>
       <c r="C1187" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5245,7 +6357,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5265,7 +6377,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5273,7 +6385,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -5281,28 +6393,28 @@
     </row>
     <row r="1193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1193" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1193" s="9"/>
       <c r="C1193" s="8"/>
     </row>
     <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="10" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B1240" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C1240" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
-      <c r="B1241" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1241" s="18"/>
+      <c r="B1241" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1241" s="21"/>
     </row>
     <row r="1242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="5" t="s">
@@ -5312,15 +6424,15 @@
         <v>2</v>
       </c>
       <c r="C1242" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1243" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1243" t="s">
         <v>5</v>
@@ -5332,7 +6444,7 @@
       </c>
       <c r="B1244" s="7"/>
       <c r="C1244" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5340,7 +6452,7 @@
         <v>1.2</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1245" s="2" t="s">
         <v>14</v>
@@ -5352,7 +6464,7 @@
       </c>
       <c r="B1246" s="7"/>
       <c r="C1246" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5360,10 +6472,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1247" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5372,7 +6484,7 @@
       </c>
       <c r="B1248" s="7"/>
       <c r="C1248" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5388,7 +6500,7 @@
       </c>
       <c r="B1250" s="7"/>
       <c r="C1250" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5396,7 +6508,7 @@
         <v>4.2</v>
       </c>
       <c r="B1251" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1251" s="2" t="s">
         <v>6</v>
@@ -5408,7 +6520,7 @@
       </c>
       <c r="B1252" s="7"/>
       <c r="C1252" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5416,7 +6528,7 @@
         <v>5.2</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1253" s="2" t="s">
         <v>5</v>
@@ -5424,28 +6536,28 @@
     </row>
     <row r="1254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1254" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1254" s="9"/>
       <c r="C1254" s="8"/>
     </row>
     <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="10" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B1299" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C1299" s="12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
-      <c r="B1300" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C1300" s="18"/>
+      <c r="B1300" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1300" s="21"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="5" t="s">
@@ -5455,15 +6567,15 @@
         <v>2</v>
       </c>
       <c r="C1301" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1302" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1302" t="s">
         <v>5</v>
@@ -5475,7 +6587,7 @@
       </c>
       <c r="B1303" s="7"/>
       <c r="C1303" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5483,7 +6595,7 @@
         <v>1.2</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1304" s="2" t="s">
         <v>14</v>
@@ -5495,7 +6607,7 @@
       </c>
       <c r="B1305" s="7"/>
       <c r="C1305" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5503,10 +6615,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1306" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5515,7 +6627,7 @@
       </c>
       <c r="B1307" s="7"/>
       <c r="C1307" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5531,7 +6643,7 @@
       </c>
       <c r="B1309" s="7"/>
       <c r="C1309" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5539,7 +6651,7 @@
         <v>4.2</v>
       </c>
       <c r="B1310" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>6</v>
@@ -5551,7 +6663,7 @@
       </c>
       <c r="B1311" s="7"/>
       <c r="C1311" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5559,7 +6671,7 @@
         <v>5.2</v>
       </c>
       <c r="B1312" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>5</v>
@@ -5567,14 +6679,14 @@
     </row>
     <row r="1313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1313" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1313" s="9"/>
       <c r="C1313" s="8"/>
     </row>
     <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="10" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B1358" s="11" t="s">
         <v>3</v>
@@ -5586,7 +6698,7 @@
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
       <c r="B1359" s="20" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C1359" s="21"/>
     </row>
@@ -5598,15 +6710,15 @@
         <v>2</v>
       </c>
       <c r="C1360" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1361" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1361" t="s">
         <v>5</v>
@@ -5618,7 +6730,7 @@
       </c>
       <c r="B1362" s="7"/>
       <c r="C1362" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5626,7 +6738,7 @@
         <v>1.2</v>
       </c>
       <c r="B1363" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1363" s="2" t="s">
         <v>6</v>
@@ -5638,7 +6750,7 @@
       </c>
       <c r="B1364" s="7"/>
       <c r="C1364" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5654,7 +6766,7 @@
       </c>
       <c r="B1366" s="7"/>
       <c r="C1366" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5665,7 +6777,7 @@
         <v>7</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5680,10 +6792,10 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="22" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C1369" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5697,7 +6809,7 @@
       </c>
       <c r="B1371" s="7"/>
       <c r="C1371" s="2" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5717,7 +6829,7 @@
       </c>
       <c r="B1373" s="7"/>
       <c r="C1373" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5725,7 +6837,7 @@
         <v>6.2</v>
       </c>
       <c r="B1374" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1374" s="2" t="s">
         <v>5</v>
@@ -5733,24 +6845,2436 @@
     </row>
     <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1375" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1375" s="9"/>
       <c r="C1375" s="8"/>
     </row>
+    <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1417" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1417" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1417" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1418" s="13"/>
+      <c r="B1418" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1418" s="21"/>
+    </row>
+    <row r="1419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1419" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1419" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1419" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1420" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1420" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1420" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1421" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1421" s="7"/>
+      <c r="C1421" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1422" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1422" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1422" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1423" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1423" s="7"/>
+      <c r="C1423" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1424" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1424" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1424" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1425" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1425" s="7"/>
+      <c r="C1425" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1426" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1426" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1426" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1427" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1427" s="7"/>
+      <c r="C1427" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1428" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1428" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1428" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1429" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1429" s="7"/>
+      <c r="C1429" s="2"/>
+    </row>
+    <row r="1430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1430" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1430" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1430" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1431" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1431" s="9"/>
+      <c r="C1431" s="8"/>
+    </row>
+    <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1476" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1476" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1476" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1477" s="13"/>
+      <c r="B1477" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1477" s="18"/>
+    </row>
+    <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1478" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1478" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1478" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1479" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1479" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1480" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1480" s="7"/>
+      <c r="C1480" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1481" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1481" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1481" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1482" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1482" s="7"/>
+      <c r="C1482" s="2"/>
+    </row>
+    <row r="1483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1483" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1483" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1483" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1484" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1484" s="7"/>
+      <c r="C1484" s="2"/>
+    </row>
+    <row r="1485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1485" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1485" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1485" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1486" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1486" s="7"/>
+      <c r="C1486" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1487" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1487" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1487" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1488" s="3"/>
+      <c r="B1488" s="22"/>
+      <c r="C1488" s="2"/>
+    </row>
+    <row r="1489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1489" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1489" s="7"/>
+      <c r="C1489" s="2"/>
+    </row>
+    <row r="1490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1490" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1490" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1490" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1491" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1491" s="9"/>
+      <c r="C1491" s="8"/>
+    </row>
+    <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1535" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1535" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1535" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1536" s="13"/>
+      <c r="B1536" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1536" s="21"/>
+    </row>
+    <row r="1537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1537" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1537" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1537" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1538" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1538" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1539" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1539" s="7"/>
+      <c r="C1539" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1540" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1540" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1540" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1541" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1541" s="7"/>
+      <c r="C1541" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1542" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1542" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1542" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1543" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1543" s="7"/>
+      <c r="C1543" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1544" s="3"/>
+      <c r="B1544" s="7"/>
+      <c r="C1544" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1545" s="3"/>
+      <c r="B1545" s="7"/>
+      <c r="C1545" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1546" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1546" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1546" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1547" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1547" s="7"/>
+      <c r="C1547" s="2"/>
+    </row>
+    <row r="1548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1548" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1548" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1548" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1549" s="3"/>
+      <c r="B1549" s="22"/>
+      <c r="C1549" s="2"/>
+    </row>
+    <row r="1550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1550" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1550" s="7"/>
+      <c r="C1550" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1551" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1551" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1551" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1552" s="3"/>
+      <c r="B1552" s="22"/>
+      <c r="C1552" s="2"/>
+    </row>
+    <row r="1553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1553" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1553" s="7"/>
+      <c r="C1553" s="2"/>
+    </row>
+    <row r="1554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1554" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1554" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1554" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1555" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1555" s="9"/>
+      <c r="C1555" s="8"/>
+    </row>
+    <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1594" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1594" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1594" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1595" s="13"/>
+      <c r="B1595" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1595" s="21"/>
+    </row>
+    <row r="1596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1596" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1596" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1596" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1597" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1597" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1598" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1598" s="7"/>
+      <c r="C1598" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1599" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1599" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1599" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1600" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1600" s="7"/>
+      <c r="C1600" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1601" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1601" s="2"/>
+      <c r="C1601" s="2"/>
+    </row>
+    <row r="1602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1602" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1602" s="7"/>
+      <c r="C1602" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1603" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1603" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1603" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1604" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1604" s="7"/>
+      <c r="C1604" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1605" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1605" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1605" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1606" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1606" s="7"/>
+      <c r="C1606" s="2"/>
+    </row>
+    <row r="1607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1607" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1607" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1607" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1608" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1608" s="9"/>
+      <c r="C1608" s="8"/>
+    </row>
+    <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1653" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1653" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1653" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1654" s="13"/>
+      <c r="B1654" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1654" s="18"/>
+    </row>
+    <row r="1655" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1655" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1655" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1655" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1656" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1656" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1657" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1657" s="7"/>
+      <c r="C1657" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1658" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1658" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1658" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1659" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1659" s="7"/>
+      <c r="C1659" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1660" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1660" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1660" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1661" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1661" s="9"/>
+      <c r="C1661" s="8"/>
+    </row>
+    <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1712" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1712" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1712" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1713" s="13"/>
+      <c r="B1713" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1713" s="18"/>
+    </row>
+    <row r="1714" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1714" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1714" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1714" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1715" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1715" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1716" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1716" s="7"/>
+      <c r="C1716" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1717" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1717" s="7"/>
+      <c r="C1717" s="2"/>
+    </row>
+    <row r="1718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1718" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1718" s="7"/>
+      <c r="C1718" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1719" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1719" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1719" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1720" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1720" s="9"/>
+      <c r="C1720" s="8"/>
+    </row>
+    <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1771" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1771" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1771" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1772" s="13"/>
+      <c r="B1772" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1772" s="18"/>
+    </row>
+    <row r="1773" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1773" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1773" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1773" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1774" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1774" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1775" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1775" s="7"/>
+      <c r="C1775" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1776" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1776" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1776" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1777" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1777" s="7"/>
+      <c r="C1777" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1778" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1778" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1778" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1779" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1779" s="7"/>
+      <c r="C1779" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1780" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1780" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1780" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1781" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1781" s="7"/>
+      <c r="C1781" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1782" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1782" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1782" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1783" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1783" s="9"/>
+      <c r="C1783" s="8"/>
+    </row>
+    <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1830" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1830" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1830" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1831" s="13"/>
+      <c r="B1831" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C1831" s="21"/>
+    </row>
+    <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1832" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1832" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1832" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1833" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1833" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1833" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1834" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1834" s="7"/>
+      <c r="C1834" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1835" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1835" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1835" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1836" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1836" s="7"/>
+      <c r="C1836" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1837" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1837" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1837" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1838" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1838" s="7"/>
+      <c r="C1838" s="2"/>
+    </row>
+    <row r="1839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1839" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1839" s="7"/>
+      <c r="C1839" s="2"/>
+    </row>
+    <row r="1840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1840" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1840" s="7"/>
+      <c r="C1840" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1841" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1841" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1841" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1842" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1842" s="7"/>
+      <c r="C1842" s="2"/>
+    </row>
+    <row r="1843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1843" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1843" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1843" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1844" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1844" s="7"/>
+      <c r="C1844" s="2"/>
+    </row>
+    <row r="1845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1845" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1845" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1845" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1846" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1846" s="9"/>
+      <c r="C1846" s="8"/>
+    </row>
+    <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1889" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1889" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1889" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1890" s="13"/>
+      <c r="B1890" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1890" s="18"/>
+    </row>
+    <row r="1891" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1891" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1891" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1891" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1892" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1892" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1892" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1893" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1893" s="7"/>
+      <c r="C1893" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1894" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1894" s="7"/>
+      <c r="C1894" s="2"/>
+    </row>
+    <row r="1895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1895" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1895" s="7"/>
+      <c r="C1895" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1896" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1896" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1896" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1897" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1897" s="9"/>
+      <c r="C1897" s="8"/>
+    </row>
+    <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1948" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1948" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1948" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1949" s="13"/>
+      <c r="B1949" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1949" s="18"/>
+    </row>
+    <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1950" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1950" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1950" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1951" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1951" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1951" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1952" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B1952" s="7"/>
+      <c r="C1952" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1953" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B1953" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1953" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1954" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B1954" s="7"/>
+      <c r="C1954" s="2"/>
+    </row>
+    <row r="1955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1955" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B1955" s="7"/>
+      <c r="C1955" s="2"/>
+    </row>
+    <row r="1956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1956" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B1956" s="7"/>
+      <c r="C1956" s="2"/>
+    </row>
+    <row r="1957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1957" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B1957" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1957" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1958" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B1958" s="7"/>
+      <c r="C1958" s="2"/>
+    </row>
+    <row r="1959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1959" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B1959" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1959" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1960" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B1960" s="7"/>
+      <c r="C1960" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1961" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B1961" s="7"/>
+      <c r="C1961" s="2"/>
+    </row>
+    <row r="1962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1962" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B1962" s="7"/>
+      <c r="C1962" s="2"/>
+    </row>
+    <row r="1963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1963" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B1963" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1963" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1964" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B1964" s="7"/>
+      <c r="C1964" s="2"/>
+    </row>
+    <row r="1965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1965" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B1965" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1965" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1966" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B1966" s="7"/>
+      <c r="C1966" s="2"/>
+    </row>
+    <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1967" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B1967" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1967" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1968" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1968" s="9"/>
+      <c r="C1968" s="8"/>
+    </row>
+    <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2007" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2007" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2007" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2008" s="13"/>
+      <c r="B2008" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2008" s="21"/>
+    </row>
+    <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2009" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2009" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2009" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2010" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2010" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2010" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2011" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2011" s="7"/>
+      <c r="C2011" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2012" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2012" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2012" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2013" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2013" s="7"/>
+      <c r="C2013" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2014" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2014" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2014" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2015" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2015" s="7"/>
+      <c r="C2015" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2016" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2016" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2016" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2017" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2017" s="7"/>
+      <c r="C2017" s="2"/>
+    </row>
+    <row r="2018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2018" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2018" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2018" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2019" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2019" s="9"/>
+      <c r="C2019" s="8"/>
+    </row>
+    <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2066" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2066" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2066" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2067" s="13"/>
+      <c r="B2067" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2067" s="18"/>
+    </row>
+    <row r="2068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2068" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2068" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2068" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2069" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2069" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2070" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2070" s="7"/>
+      <c r="C2070" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2071" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2071" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2071" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2072" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2072" s="7"/>
+      <c r="C2072" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2073" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2073" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2073" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2074" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2074" s="7"/>
+      <c r="C2074" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2075" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2075" s="7"/>
+      <c r="C2075" s="2"/>
+    </row>
+    <row r="2076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2076" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2076" s="7"/>
+      <c r="C2076" s="2"/>
+    </row>
+    <row r="2077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2077" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2077" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2077" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2078" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2078" s="7"/>
+      <c r="C2078" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2079" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2079" s="7"/>
+      <c r="C2079" s="2"/>
+    </row>
+    <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2080" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B2080" s="7"/>
+      <c r="C2080" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2081" s="3"/>
+      <c r="B2081" s="7"/>
+      <c r="C2081" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2082" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B2082" s="7"/>
+      <c r="C2082" s="2"/>
+    </row>
+    <row r="2083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2083" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B2083" s="7"/>
+      <c r="C2083" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2084" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B2084" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2084" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2085" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2085" s="9"/>
+      <c r="C2085" s="8"/>
+    </row>
+    <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2125" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2125" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2125" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2126" s="13"/>
+      <c r="B2126" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2126" s="18"/>
+    </row>
+    <row r="2127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2127" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2127" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2127" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2128" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2128" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2129" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2129" s="7"/>
+      <c r="C2129" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2130" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2130" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2131" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2131" s="7"/>
+      <c r="C2131" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2132" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2132" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2133" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2133" s="7"/>
+      <c r="C2133" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2134" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2134" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2134" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2135" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2135" s="9"/>
+      <c r="C2135" s="8"/>
+    </row>
+    <row r="2184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2184" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2184" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2184" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2185" s="13"/>
+      <c r="B2185" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2185" s="18"/>
+    </row>
+    <row r="2186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2186" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2186" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2186" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2187" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2187" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2188" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2188" s="7"/>
+      <c r="C2188" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2189" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2189" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2189" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2190" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2190" s="7"/>
+      <c r="C2190" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2191" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2191" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2191" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2192" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2192" s="7"/>
+      <c r="C2192" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2193" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2193" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2193" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2194" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2194" s="7"/>
+      <c r="C2194" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2195" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2195" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2195" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2196" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2196" s="9"/>
+      <c r="C2196" s="8"/>
+    </row>
+    <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2243" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B2243" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2243" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2244" s="13"/>
+      <c r="B2244" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2244" s="18"/>
+    </row>
+    <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2245" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2245" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2245" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2246" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2246" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2247" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2247" s="7"/>
+      <c r="C2247" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2248" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2248" s="7"/>
+      <c r="C2248" s="2"/>
+    </row>
+    <row r="2249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2249" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2249" s="7"/>
+      <c r="C2249" s="2"/>
+    </row>
+    <row r="2250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2250" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2250" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2250" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2251" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2251" s="7"/>
+      <c r="C2251" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2252" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2252" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2252" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2253" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2253" s="9"/>
+      <c r="C2253" s="8"/>
+    </row>
+    <row r="2302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2302" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2302" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2302" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2303" s="13"/>
+      <c r="B2303" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2303" s="21"/>
+    </row>
+    <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2304" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2304" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2304" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2305" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2305" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2306" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2306" s="7"/>
+      <c r="C2306" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2307" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2307" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2307" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2308" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2308" s="7"/>
+      <c r="C2308" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2309" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2309" s="7"/>
+      <c r="C2309" s="2"/>
+    </row>
+    <row r="2310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2310" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2310" s="7"/>
+      <c r="C2310" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2311" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2311" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2311" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2312" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2312" s="7"/>
+      <c r="C2312" s="2"/>
+    </row>
+    <row r="2313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2313" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2313" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2313" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2314" s="3"/>
+      <c r="B2314" s="22"/>
+      <c r="C2314" s="2"/>
+    </row>
+    <row r="2315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2315" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2315" s="7"/>
+      <c r="C2315" s="2"/>
+    </row>
+    <row r="2316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2316" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2316" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2316" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2317" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B2317" s="7"/>
+      <c r="C2317" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2318" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B2318" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2318" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2319" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2319" s="9"/>
+      <c r="C2319" s="8"/>
+    </row>
+    <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2361" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2361" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2361" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2362" s="13"/>
+      <c r="B2362" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2362" s="18"/>
+    </row>
+    <row r="2363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2363" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2363" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2363" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2364" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2364" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2364" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2365" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2365" s="7"/>
+      <c r="C2365" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2366" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2366" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2366" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2367" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2367" s="7"/>
+      <c r="C2367" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2368" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2368" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2368" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2369" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2369" s="9"/>
+      <c r="C2369" s="8"/>
+    </row>
+    <row r="2420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2420" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2420" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2420" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2421" s="13"/>
+      <c r="B2421" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2421" s="21"/>
+    </row>
+    <row r="2422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2422" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2422" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2422" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2423" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2423" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2423" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2424" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2424" s="7"/>
+      <c r="C2424" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2425" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2425" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2425" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2426" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2426" s="7"/>
+      <c r="C2426" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2427" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2427" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2427" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2428" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2428" s="7"/>
+      <c r="C2428" s="2"/>
+    </row>
+    <row r="2429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2429" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2429" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2429" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2430" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2430" s="7"/>
+      <c r="C2430" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2431" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2431" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2431" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2432" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2432" s="7"/>
+      <c r="C2432" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2433" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2433" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2433" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2434" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B2434" s="7"/>
+      <c r="C2434" s="2"/>
+    </row>
+    <row r="2435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2435" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B2435" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2435" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2436" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2436" s="9"/>
+      <c r="C2436" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="26">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
     <mergeCell ref="B533:C533"/>
     <mergeCell ref="B651:C651"/>
     <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B356:C356"/>
+    <mergeCell ref="B1831:C1831"/>
+    <mergeCell ref="B2008:C2008"/>
+    <mergeCell ref="B2313:B2314"/>
+    <mergeCell ref="B2303:C2303"/>
+    <mergeCell ref="B2421:C2421"/>
     <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="B1123:C1123"/>
     <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1241:C1241"/>
     <mergeCell ref="B1369:B1370"/>
     <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="B1418:C1418"/>
+    <mergeCell ref="B1487:B1488"/>
     <mergeCell ref="B828:C828"/>
+    <mergeCell ref="B1536:C1536"/>
+    <mergeCell ref="B1595:C1595"/>
+    <mergeCell ref="B1548:B1549"/>
+    <mergeCell ref="B1551:B1552"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A382F0C3-5890-4CFD-8D95-6D1F86205245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFC4898-6508-449A-972B-C58A6906D5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2478</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2714</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="171">
   <si>
     <t>Implied</t>
   </si>
@@ -212,6 +212,9 @@
     <t>NOP (00)</t>
   </si>
   <si>
+    <t>Read PC</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Read </t>
     </r>
@@ -2852,6 +2855,159 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
+  </si>
+  <si>
+    <t>OR1 (2A)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag |= ((Operand &amp; (1 &lt;&lt; Bit)) == 0).</t>
+    </r>
+  </si>
+  <si>
+    <t>Absolute Boolean Bit /m.b</t>
+  </si>
+  <si>
+    <t>ROL (2B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tmp = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80). Operand = (Operand &lt;&lt; 1) | Tmp. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>ROL (2C)</t>
+  </si>
+  <si>
+    <t>PUSH (2D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
     </r>
   </si>
 </sst>
@@ -3420,7 +3576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C2436"/>
+  <dimension ref="A1:C2668"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -3464,7 +3620,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -3498,7 +3654,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -3513,7 +3669,7 @@
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -3545,7 +3701,7 @@
         <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -3565,7 +3721,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -3597,7 +3753,7 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>18</v>
@@ -3615,7 +3771,7 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>19</v>
@@ -3627,7 +3783,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3649,10 +3805,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3667,10 +3823,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3685,7 +3841,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -3700,7 +3856,7 @@
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -3712,7 +3868,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -3732,7 +3888,7 @@
         <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3752,7 +3908,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -3764,7 +3920,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3784,7 +3940,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3795,7 +3951,7 @@
         <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3810,7 +3966,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -3825,10 +3981,10 @@
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>16</v>
@@ -3837,7 +3993,7 @@
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -3857,7 +4013,7 @@
         <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -3877,7 +4033,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -3889,7 +4045,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3909,7 +4065,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3931,7 +4087,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -3943,7 +4099,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3959,14 +4115,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3982,7 +4138,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3990,7 +4146,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -4005,7 +4161,7 @@
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -4017,7 +4173,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -4037,7 +4193,7 @@
         <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -4057,7 +4213,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -4069,7 +4225,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4089,7 +4245,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4097,7 +4253,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -4112,7 +4268,7 @@
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
@@ -4124,7 +4280,7 @@
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -4144,7 +4300,7 @@
         <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -4164,7 +4320,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -4184,7 +4340,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>30</v>
@@ -4216,7 +4372,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4224,7 +4380,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -4239,7 +4395,7 @@
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -4251,7 +4407,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C356" s="21"/>
     </row>
@@ -4271,7 +4427,7 @@
         <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -4305,7 +4461,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -4317,7 +4473,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4325,7 +4481,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -4340,7 +4496,7 @@
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -4352,7 +4508,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -4372,7 +4528,7 @@
         <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -4392,7 +4548,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -4420,7 +4576,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4431,7 +4587,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4446,7 +4602,7 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>20</v>
@@ -4481,7 +4637,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4489,7 +4645,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -4504,7 +4660,7 @@
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -4536,7 +4692,7 @@
         <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -4556,7 +4712,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -4568,7 +4724,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4576,7 +4732,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -4591,7 +4747,7 @@
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
@@ -4603,7 +4759,7 @@
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -4623,7 +4779,7 @@
         <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -4643,7 +4799,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -4655,7 +4811,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4666,7 +4822,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4681,7 +4837,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -4693,7 +4849,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4704,7 +4860,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4713,7 +4869,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4724,7 +4880,7 @@
         <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4739,7 +4895,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -4754,7 +4910,7 @@
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
@@ -4766,7 +4922,7 @@
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -4786,7 +4942,7 @@
         <v>22</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -4806,7 +4962,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -4826,7 +4982,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C598" s="2" t="s">
         <v>30</v>
@@ -4846,7 +5002,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -4858,14 +5014,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4887,7 +5043,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -4902,7 +5058,7 @@
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -4914,7 +5070,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -4934,7 +5090,7 @@
         <v>22</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -4954,7 +5110,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -4966,7 +5122,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4986,7 +5142,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4997,7 +5153,7 @@
         <v>23</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5012,7 +5168,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -5027,7 +5183,7 @@
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
@@ -5039,7 +5195,7 @@
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
       <c r="B710" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C710" s="21"/>
     </row>
@@ -5059,7 +5215,7 @@
         <v>22</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -5079,7 +5235,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -5099,7 +5255,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C716" s="2" t="s">
         <v>30</v>
@@ -5131,7 +5287,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5142,7 +5298,7 @@
         <v>23</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5157,7 +5313,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -5172,7 +5328,7 @@
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -5204,7 +5360,7 @@
         <v>22</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -5224,7 +5380,7 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>26</v>
@@ -5242,10 +5398,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5254,7 +5410,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5276,7 +5432,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -5291,7 +5447,7 @@
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
@@ -5303,7 +5459,7 @@
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
       <c r="B828" s="20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C828" s="21"/>
     </row>
@@ -5323,7 +5479,7 @@
         <v>22</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -5343,7 +5499,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -5363,7 +5519,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C834" s="2" t="s">
         <v>30</v>
@@ -5395,21 +5551,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5438,7 +5594,7 @@
         <v>23</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5453,7 +5609,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -5468,7 +5624,7 @@
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -5500,7 +5656,7 @@
         <v>22</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -5520,7 +5676,7 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>26</v>
@@ -5538,7 +5694,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>18</v>
@@ -5556,7 +5712,7 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>19</v>
@@ -5574,10 +5730,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5586,7 +5742,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,10 +5764,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5626,10 +5782,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5644,7 +5800,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -5662,7 +5818,7 @@
         <v>15</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -5691,7 +5847,7 @@
         <v>22</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -5703,7 +5859,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5711,7 +5867,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -5723,7 +5879,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5739,14 +5895,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5762,7 +5918,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5770,7 +5926,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -5785,7 +5941,7 @@
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -5817,7 +5973,7 @@
         <v>22</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -5837,7 +5993,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -5869,7 +6025,7 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>18</v>
@@ -5887,7 +6043,7 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>19</v>
@@ -5899,7 +6055,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5921,10 +6077,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5939,10 +6095,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5957,7 +6113,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -5972,7 +6128,7 @@
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -5984,7 +6140,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -6004,7 +6160,7 @@
         <v>22</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -6024,7 +6180,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -6036,7 +6192,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6056,7 +6212,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6067,7 +6223,7 @@
         <v>23</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6082,7 +6238,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -6097,10 +6253,10 @@
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1122" s="12" t="s">
         <v>16</v>
@@ -6109,7 +6265,7 @@
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
       <c r="B1123" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C1123" s="21"/>
     </row>
@@ -6129,7 +6285,7 @@
         <v>22</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -6149,7 +6305,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -6161,7 +6317,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6181,7 +6337,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6203,7 +6359,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -6215,7 +6371,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6231,14 +6387,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6254,7 +6410,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6262,7 +6418,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -6277,7 +6433,7 @@
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -6289,7 +6445,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -6309,7 +6465,7 @@
         <v>22</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -6329,7 +6485,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -6357,7 +6513,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6377,7 +6533,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6385,7 +6541,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -6400,7 +6556,7 @@
     </row>
     <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1240" s="11" t="s">
         <v>11</v>
@@ -6412,7 +6568,7 @@
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
       <c r="B1241" s="20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C1241" s="21"/>
     </row>
@@ -6432,7 +6588,7 @@
         <v>22</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1243" t="s">
         <v>5</v>
@@ -6452,7 +6608,7 @@
         <v>1.2</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1245" s="2" t="s">
         <v>14</v>
@@ -6472,7 +6628,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1247" s="2" t="s">
         <v>30</v>
@@ -6500,7 +6656,7 @@
       </c>
       <c r="B1250" s="7"/>
       <c r="C1250" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6520,7 +6676,7 @@
       </c>
       <c r="B1252" s="7"/>
       <c r="C1252" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,7 +6684,7 @@
         <v>5.2</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1253" s="2" t="s">
         <v>5</v>
@@ -6543,7 +6699,7 @@
     </row>
     <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B1299" s="11" t="s">
         <v>11</v>
@@ -6555,7 +6711,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
       <c r="B1300" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C1300" s="21"/>
     </row>
@@ -6575,7 +6731,7 @@
         <v>22</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1302" t="s">
         <v>5</v>
@@ -6595,7 +6751,7 @@
         <v>1.2</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1304" s="2" t="s">
         <v>14</v>
@@ -6615,7 +6771,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1306" s="2" t="s">
         <v>30</v>
@@ -6643,7 +6799,7 @@
       </c>
       <c r="B1309" s="7"/>
       <c r="C1309" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6663,7 +6819,7 @@
       </c>
       <c r="B1311" s="7"/>
       <c r="C1311" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6671,7 +6827,7 @@
         <v>5.2</v>
       </c>
       <c r="B1312" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>5</v>
@@ -6686,7 +6842,7 @@
     </row>
     <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B1358" s="11" t="s">
         <v>3</v>
@@ -6698,7 +6854,7 @@
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
       <c r="B1359" s="20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C1359" s="21"/>
     </row>
@@ -6718,7 +6874,7 @@
         <v>22</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1361" t="s">
         <v>5</v>
@@ -6738,7 +6894,7 @@
         <v>1.2</v>
       </c>
       <c r="B1363" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1363" s="2" t="s">
         <v>6</v>
@@ -6766,7 +6922,7 @@
       </c>
       <c r="B1366" s="7"/>
       <c r="C1366" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6777,7 +6933,7 @@
         <v>7</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6792,7 +6948,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1369" s="2" t="s">
         <v>20</v>
@@ -6809,7 +6965,7 @@
       </c>
       <c r="B1371" s="7"/>
       <c r="C1371" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6829,7 +6985,7 @@
       </c>
       <c r="B1373" s="7"/>
       <c r="C1373" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6837,7 +6993,7 @@
         <v>6.2</v>
       </c>
       <c r="B1374" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1374" s="2" t="s">
         <v>5</v>
@@ -6852,7 +7008,7 @@
     </row>
     <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1417" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1417" s="11" t="s">
         <v>11</v>
@@ -6864,7 +7020,7 @@
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
       <c r="B1418" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1418" s="21"/>
     </row>
@@ -6884,7 +7040,7 @@
         <v>22</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1420" t="s">
         <v>5</v>
@@ -6904,10 +7060,10 @@
         <v>1.2</v>
       </c>
       <c r="B1422" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6924,7 +7080,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1424" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1424" s="2" t="s">
         <v>6</v>
@@ -6936,7 +7092,7 @@
       </c>
       <c r="B1425" s="7"/>
       <c r="C1425" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6947,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="C1426" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6956,7 +7112,7 @@
       </c>
       <c r="B1427" s="7"/>
       <c r="C1427" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6967,7 +7123,7 @@
         <v>23</v>
       </c>
       <c r="C1428" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6982,7 +7138,7 @@
         <v>5.2</v>
       </c>
       <c r="B1430" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1430" s="2" t="s">
         <v>5</v>
@@ -6997,7 +7153,7 @@
     </row>
     <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1476" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1476" s="11" t="s">
         <v>11</v>
@@ -7009,7 +7165,7 @@
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="13"/>
       <c r="B1477" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1477" s="18"/>
     </row>
@@ -7029,7 +7185,7 @@
         <v>22</v>
       </c>
       <c r="B1479" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1479" t="s">
         <v>5</v>
@@ -7049,7 +7205,7 @@
         <v>1.2</v>
       </c>
       <c r="B1481" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1481" s="2" t="s">
         <v>26</v>
@@ -7067,10 +7223,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1483" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C1483" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7085,10 +7241,10 @@
         <v>3.2</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7097,7 +7253,7 @@
       </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7105,10 +7261,10 @@
         <v>4.2</v>
       </c>
       <c r="B1487" s="22" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7128,7 +7284,7 @@
         <v>5.2</v>
       </c>
       <c r="B1490" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1490" s="2" t="s">
         <v>5</v>
@@ -7143,7 +7299,7 @@
     </row>
     <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1535" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1535" s="11" t="s">
         <v>3</v>
@@ -7155,7 +7311,7 @@
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
       <c r="B1536" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1536" s="21"/>
     </row>
@@ -7175,7 +7331,7 @@
         <v>22</v>
       </c>
       <c r="B1538" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1538" t="s">
         <v>5</v>
@@ -7195,7 +7351,7 @@
         <v>1.2</v>
       </c>
       <c r="B1540" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1540" s="2" t="s">
         <v>6</v>
@@ -7207,7 +7363,7 @@
       </c>
       <c r="B1541" s="7"/>
       <c r="C1541" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7227,21 +7383,21 @@
       </c>
       <c r="B1543" s="7"/>
       <c r="C1543" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1544" s="3"/>
       <c r="B1544" s="7"/>
       <c r="C1544" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1545" s="3"/>
       <c r="B1545" s="7"/>
       <c r="C1545" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7252,7 +7408,7 @@
         <v>23</v>
       </c>
       <c r="C1546" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7267,7 +7423,7 @@
         <v>4.2</v>
       </c>
       <c r="B1548" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1548" s="2" t="s">
         <v>6</v>
@@ -7284,7 +7440,7 @@
       </c>
       <c r="B1550" s="7"/>
       <c r="C1550" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7292,10 +7448,10 @@
         <v>5.2</v>
       </c>
       <c r="B1551" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C1551" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7315,7 +7471,7 @@
         <v>6.2</v>
       </c>
       <c r="B1554" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1554" s="2" t="s">
         <v>5</v>
@@ -7330,7 +7486,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1594" s="11" t="s">
         <v>11</v>
@@ -7342,7 +7498,7 @@
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
       <c r="B1595" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C1595" s="21"/>
     </row>
@@ -7362,7 +7518,7 @@
         <v>22</v>
       </c>
       <c r="B1597" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1597" t="s">
         <v>5</v>
@@ -7382,7 +7538,7 @@
         <v>1.2</v>
       </c>
       <c r="B1599" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1599" s="2" t="s">
         <v>6</v>
@@ -7410,7 +7566,7 @@
       </c>
       <c r="B1602" s="7"/>
       <c r="C1602" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7430,7 +7586,7 @@
       </c>
       <c r="B1604" s="7"/>
       <c r="C1604" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7441,7 +7597,7 @@
         <v>23</v>
       </c>
       <c r="C1605" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7456,7 +7612,7 @@
         <v>5.2</v>
       </c>
       <c r="B1607" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1607" s="2" t="s">
         <v>5</v>
@@ -7471,7 +7627,7 @@
     </row>
     <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1653" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1653" s="11" t="s">
         <v>12</v>
@@ -7483,7 +7639,7 @@
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="13"/>
       <c r="B1654" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1654" s="18"/>
     </row>
@@ -7503,7 +7659,7 @@
         <v>22</v>
       </c>
       <c r="B1656" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1656" t="s">
         <v>5</v>
@@ -7523,7 +7679,7 @@
         <v>1.2</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1658" s="2" t="s">
         <v>26</v>
@@ -7535,7 +7691,7 @@
       </c>
       <c r="B1659" s="7"/>
       <c r="C1659" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7543,7 +7699,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1660" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1660" s="2" t="s">
         <v>5</v>
@@ -7558,7 +7714,7 @@
     </row>
     <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1712" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1712" s="11" t="s">
         <v>12</v>
@@ -7590,7 +7746,7 @@
         <v>22</v>
       </c>
       <c r="B1715" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1715" t="s">
         <v>5</v>
@@ -7618,7 +7774,7 @@
       </c>
       <c r="B1718" s="7"/>
       <c r="C1718" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7626,7 +7782,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1719" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1719" s="2" t="s">
         <v>5</v>
@@ -7641,7 +7797,7 @@
     </row>
     <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1771" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1771" s="11" t="s">
         <v>13</v>
@@ -7653,7 +7809,7 @@
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="13"/>
       <c r="B1772" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1772" s="18"/>
     </row>
@@ -7673,7 +7829,7 @@
         <v>22</v>
       </c>
       <c r="B1774" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1774" t="s">
         <v>5</v>
@@ -7693,7 +7849,7 @@
         <v>1.2</v>
       </c>
       <c r="B1776" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1776" s="2" t="s">
         <v>14</v>
@@ -7713,7 +7869,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1778" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1778" s="2" t="s">
         <v>30</v>
@@ -7745,7 +7901,7 @@
       </c>
       <c r="B1781" s="7"/>
       <c r="C1781" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7753,7 +7909,7 @@
         <v>4.2</v>
       </c>
       <c r="B1782" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1782" s="2" t="s">
         <v>5</v>
@@ -7768,7 +7924,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B1830" s="11" t="s">
         <v>3</v>
@@ -7780,7 +7936,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
       <c r="B1831" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C1831" s="21"/>
     </row>
@@ -7800,7 +7956,7 @@
         <v>22</v>
       </c>
       <c r="B1833" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1833" t="s">
         <v>5</v>
@@ -7820,7 +7976,7 @@
         <v>1.2</v>
       </c>
       <c r="B1835" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1835" s="2" t="s">
         <v>14</v>
@@ -7840,7 +7996,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1837" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1837" s="2" t="s">
         <v>30</v>
@@ -7866,7 +8022,7 @@
       </c>
       <c r="B1840" s="7"/>
       <c r="C1840" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7877,7 +8033,7 @@
         <v>31</v>
       </c>
       <c r="C1841" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7895,7 +8051,7 @@
         <v>32</v>
       </c>
       <c r="C1843" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7910,7 +8066,7 @@
         <v>6.2</v>
       </c>
       <c r="B1845" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1845" s="2" t="s">
         <v>5</v>
@@ -7925,7 +8081,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1889" s="11" t="s">
         <v>12</v>
@@ -7957,7 +8113,7 @@
         <v>22</v>
       </c>
       <c r="B1892" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1892" t="s">
         <v>5</v>
@@ -7985,7 +8141,7 @@
       </c>
       <c r="B1895" s="7"/>
       <c r="C1895" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7993,7 +8149,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1896" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1896" s="2" t="s">
         <v>5</v>
@@ -8008,7 +8164,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B1948" s="11" t="s">
         <v>9</v>
@@ -8040,7 +8196,7 @@
         <v>22</v>
       </c>
       <c r="B1951" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1951" t="s">
         <v>5</v>
@@ -8060,7 +8216,7 @@
         <v>1.2</v>
       </c>
       <c r="B1953" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1953" s="2" t="s">
         <v>6</v>
@@ -8092,7 +8248,7 @@
         <v>3.2</v>
       </c>
       <c r="B1957" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1957" s="2" t="s">
         <v>18</v>
@@ -8110,7 +8266,7 @@
         <v>4.2</v>
       </c>
       <c r="B1959" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1959" s="2" t="s">
         <v>19</v>
@@ -8122,7 +8278,7 @@
       </c>
       <c r="B1960" s="7"/>
       <c r="C1960" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8144,10 +8300,10 @@
         <v>6.2</v>
       </c>
       <c r="B1963" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1963" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8162,10 +8318,10 @@
         <v>7.2</v>
       </c>
       <c r="B1965" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C1965" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8180,7 +8336,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1967" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1967" s="2" t="s">
         <v>5</v>
@@ -8195,7 +8351,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2007" s="11" t="s">
         <v>13</v>
@@ -8207,7 +8363,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
       <c r="B2008" s="20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2008" s="21"/>
     </row>
@@ -8227,7 +8383,7 @@
         <v>22</v>
       </c>
       <c r="B2010" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2010" t="s">
         <v>5</v>
@@ -8247,7 +8403,7 @@
         <v>1.2</v>
       </c>
       <c r="B2012" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2012" s="2" t="s">
         <v>6</v>
@@ -8259,7 +8415,7 @@
       </c>
       <c r="B2013" s="7"/>
       <c r="C2013" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8279,7 +8435,7 @@
       </c>
       <c r="B2015" s="7"/>
       <c r="C2015" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8290,7 +8446,7 @@
         <v>23</v>
       </c>
       <c r="C2016" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8305,7 +8461,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2018" s="2" t="s">
         <v>5</v>
@@ -8320,10 +8476,10 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2066" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2066" s="12" t="s">
         <v>16</v>
@@ -8332,7 +8488,7 @@
     <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2067" s="13"/>
       <c r="B2067" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C2067" s="18"/>
     </row>
@@ -8352,7 +8508,7 @@
         <v>22</v>
       </c>
       <c r="B2069" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2069" t="s">
         <v>5</v>
@@ -8372,7 +8528,7 @@
         <v>1.2</v>
       </c>
       <c r="B2071" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2071" s="2" t="s">
         <v>6</v>
@@ -8384,7 +8540,7 @@
       </c>
       <c r="B2072" s="7"/>
       <c r="C2072" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8404,7 +8560,7 @@
       </c>
       <c r="B2074" s="7"/>
       <c r="C2074" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8426,7 +8582,7 @@
         <v>4.2</v>
       </c>
       <c r="B2077" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2077" s="2" t="s">
         <v>6</v>
@@ -8438,7 +8594,7 @@
       </c>
       <c r="B2078" s="7"/>
       <c r="C2078" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8454,14 +8610,14 @@
       </c>
       <c r="B2080" s="7"/>
       <c r="C2080" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2081" s="3"/>
       <c r="B2081" s="7"/>
       <c r="C2081" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8477,7 +8633,7 @@
       </c>
       <c r="B2083" s="7"/>
       <c r="C2083" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8485,7 +8641,7 @@
         <v>7.2</v>
       </c>
       <c r="B2084" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2084" s="2" t="s">
         <v>5</v>
@@ -8500,7 +8656,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2125" s="11" t="s">
         <v>10</v>
@@ -8512,7 +8668,7 @@
     <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2126" s="13"/>
       <c r="B2126" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2126" s="18"/>
     </row>
@@ -8532,7 +8688,7 @@
         <v>22</v>
       </c>
       <c r="B2128" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2128" t="s">
         <v>5</v>
@@ -8552,7 +8708,7 @@
         <v>1.2</v>
       </c>
       <c r="B2130" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2130" s="2" t="s">
         <v>6</v>
@@ -8564,7 +8720,7 @@
       </c>
       <c r="B2131" s="7"/>
       <c r="C2131" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8584,7 +8740,7 @@
       </c>
       <c r="B2133" s="7"/>
       <c r="C2133" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8592,7 +8748,7 @@
         <v>3.2</v>
       </c>
       <c r="B2134" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2134" s="2" t="s">
         <v>5</v>
@@ -8619,7 +8775,7 @@
     <row r="2185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2185" s="13"/>
       <c r="B2185" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C2185" s="18"/>
     </row>
@@ -8639,7 +8795,7 @@
         <v>22</v>
       </c>
       <c r="B2187" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2187" t="s">
         <v>5</v>
@@ -8659,7 +8815,7 @@
         <v>1.2</v>
       </c>
       <c r="B2189" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2189" s="2" t="s">
         <v>14</v>
@@ -8679,7 +8835,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2191" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2191" s="2" t="s">
         <v>30</v>
@@ -8711,7 +8867,7 @@
       </c>
       <c r="B2194" s="7"/>
       <c r="C2194" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8719,7 +8875,7 @@
         <v>4.2</v>
       </c>
       <c r="B2195" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2195" s="2" t="s">
         <v>5</v>
@@ -8734,7 +8890,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B2243" s="11" t="s">
         <v>10</v>
@@ -8746,7 +8902,7 @@
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="13"/>
       <c r="B2244" s="17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2244" s="18"/>
     </row>
@@ -8766,7 +8922,7 @@
         <v>22</v>
       </c>
       <c r="B2246" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2246" t="s">
         <v>5</v>
@@ -8800,7 +8956,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2250" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C2250" s="2" t="s">
         <v>6</v>
@@ -8812,7 +8968,7 @@
       </c>
       <c r="B2251" s="7"/>
       <c r="C2251" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8820,7 +8976,7 @@
         <v>3.2</v>
       </c>
       <c r="B2252" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2252" s="2" t="s">
         <v>5</v>
@@ -8847,7 +9003,7 @@
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
       <c r="B2303" s="20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C2303" s="21"/>
     </row>
@@ -8867,7 +9023,7 @@
         <v>22</v>
       </c>
       <c r="B2305" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2305" t="s">
         <v>5</v>
@@ -8887,7 +9043,7 @@
         <v>1.2</v>
       </c>
       <c r="B2307" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2307" s="2" t="s">
         <v>6</v>
@@ -8915,7 +9071,7 @@
       </c>
       <c r="B2310" s="7"/>
       <c r="C2310" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8926,7 +9082,7 @@
         <v>7</v>
       </c>
       <c r="C2311" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8941,7 +9097,7 @@
         <v>4.2</v>
       </c>
       <c r="B2313" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2313" s="2" t="s">
         <v>20</v>
@@ -8976,7 +9132,7 @@
       </c>
       <c r="B2317" s="7"/>
       <c r="C2317" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8984,7 +9140,7 @@
         <v>6.2</v>
       </c>
       <c r="B2318" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2318" s="2" t="s">
         <v>5</v>
@@ -8999,7 +9155,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B2361" s="11" t="s">
         <v>12</v>
@@ -9031,7 +9187,7 @@
         <v>22</v>
       </c>
       <c r="B2364" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2364" t="s">
         <v>5</v>
@@ -9051,7 +9207,7 @@
         <v>1.2</v>
       </c>
       <c r="B2366" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2366" s="2" t="s">
         <v>6</v>
@@ -9063,7 +9219,7 @@
       </c>
       <c r="B2367" s="7"/>
       <c r="C2367" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9071,7 +9227,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2368" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2368" s="2" t="s">
         <v>5</v>
@@ -9098,7 +9254,7 @@
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
       <c r="B2421" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2421" s="21"/>
     </row>
@@ -9118,7 +9274,7 @@
         <v>22</v>
       </c>
       <c r="B2423" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2423" t="s">
         <v>5</v>
@@ -9138,7 +9294,7 @@
         <v>1.2</v>
       </c>
       <c r="B2425" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2425" s="2" t="s">
         <v>6</v>
@@ -9150,7 +9306,7 @@
       </c>
       <c r="B2426" s="7"/>
       <c r="C2426" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9161,7 +9317,7 @@
         <v>7</v>
       </c>
       <c r="C2427" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9176,7 +9332,7 @@
         <v>3.2</v>
       </c>
       <c r="B2429" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2429" s="2" t="s">
         <v>6</v>
@@ -9188,7 +9344,7 @@
       </c>
       <c r="B2430" s="7"/>
       <c r="C2430" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9199,7 +9355,7 @@
         <v>7</v>
       </c>
       <c r="C2431" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9208,7 +9364,7 @@
       </c>
       <c r="B2432" s="7"/>
       <c r="C2432" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9219,7 +9375,7 @@
         <v>23</v>
       </c>
       <c r="C2433" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9234,7 +9390,7 @@
         <v>6.2</v>
       </c>
       <c r="B2435" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2435" s="2" t="s">
         <v>5</v>
@@ -9247,8 +9403,555 @@
       <c r="B2436" s="9"/>
       <c r="C2436" s="8"/>
     </row>
+    <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2479" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2479" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2479" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2480" s="13"/>
+      <c r="B2480" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2480" s="18"/>
+    </row>
+    <row r="2481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2481" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2481" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2481" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2482" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2482" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2482" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2483" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2483" s="7"/>
+      <c r="C2483" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2484" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2484" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2484" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2485" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2485" s="7"/>
+      <c r="C2485" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2486" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2486" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2486" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2487" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2487" s="7"/>
+      <c r="C2487" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2488" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2488" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2488" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2489" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2489" s="7"/>
+      <c r="C2489" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2490" s="3"/>
+      <c r="B2490" s="7"/>
+      <c r="C2490" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2491" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2491" s="7"/>
+      <c r="C2491" s="2"/>
+    </row>
+    <row r="2492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2492" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2492" s="7"/>
+      <c r="C2492" s="2"/>
+    </row>
+    <row r="2493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2493" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2493" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2493" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2494" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2494" s="9"/>
+      <c r="C2494" s="8"/>
+    </row>
+    <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2538" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2538" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2538" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2539" s="13"/>
+      <c r="B2539" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2539" s="21"/>
+    </row>
+    <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2540" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2540" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2540" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2541" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2541" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2541" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2542" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2542" s="7"/>
+      <c r="C2542" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2543" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2543" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2543" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2544" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2544" s="7"/>
+      <c r="C2544" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2545" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2545" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2545" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2546" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2546" s="7"/>
+      <c r="C2546" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2547" s="3"/>
+      <c r="B2547" s="7"/>
+      <c r="C2547" s="22"/>
+    </row>
+    <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2548" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2548" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2548" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2549" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2549" s="7"/>
+      <c r="C2549" s="2"/>
+    </row>
+    <row r="2550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2550" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2550" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2550" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2551" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2551" s="9"/>
+      <c r="C2551" s="8"/>
+    </row>
+    <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2597" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2597" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2597" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2598" s="13"/>
+      <c r="B2598" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2598" s="21"/>
+    </row>
+    <row r="2599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2599" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2599" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2599" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2600" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2600" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2600" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2601" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2601" s="7"/>
+      <c r="C2601" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2602" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2602" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2602" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2603" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2603" s="7"/>
+      <c r="C2603" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2604" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2604" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2604" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2605" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2605" s="7"/>
+      <c r="C2605" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2606" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2606" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2606" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2607" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2607" s="7"/>
+      <c r="C2607" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2608" s="3"/>
+      <c r="B2608" s="7"/>
+      <c r="C2608" s="22"/>
+    </row>
+    <row r="2609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2609" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2609" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2609" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2610" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2610" s="7"/>
+      <c r="C2610" s="2"/>
+    </row>
+    <row r="2611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2611" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2611" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2611" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2612" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2612" s="9"/>
+      <c r="C2612" s="8"/>
+    </row>
+    <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2656" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2656" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2656" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2657" s="13"/>
+      <c r="B2657" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2657" s="18"/>
+    </row>
+    <row r="2658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2658" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2658" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2658" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2659" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2659" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2659" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2660" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2660" s="7"/>
+      <c r="C2660" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2661" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2661" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2661" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2662" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2662" s="7"/>
+      <c r="C2662" s="2"/>
+    </row>
+    <row r="2663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2663" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2663" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2663" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2664" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2664" s="7"/>
+      <c r="C2664" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2665" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2665" s="7"/>
+      <c r="C2665" s="2"/>
+    </row>
+    <row r="2666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2666" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2666" s="7"/>
+      <c r="C2666" s="2"/>
+    </row>
+    <row r="2667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2667" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2667" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2667" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2668" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2668" s="9"/>
+      <c r="C2668" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="30">
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
@@ -9261,6 +9964,9 @@
     <mergeCell ref="B2313:B2314"/>
     <mergeCell ref="B2303:C2303"/>
     <mergeCell ref="B2421:C2421"/>
+    <mergeCell ref="B2539:C2539"/>
+    <mergeCell ref="C2546:C2547"/>
+    <mergeCell ref="B2598:C2598"/>
     <mergeCell ref="B1064:C1064"/>
     <mergeCell ref="B1123:C1123"/>
     <mergeCell ref="B1182:C1182"/>
@@ -9270,6 +9976,7 @@
     <mergeCell ref="B1300:C1300"/>
     <mergeCell ref="B1418:C1418"/>
     <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="C2607:C2608"/>
     <mergeCell ref="B828:C828"/>
     <mergeCell ref="B1536:C1536"/>
     <mergeCell ref="B1595:C1595"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFC4898-6508-449A-972B-C58A6906D5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF69ECC0-34CD-4DB8-B377-DEA8F9393450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$2714</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$3835</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="207">
   <si>
     <t>Implied</t>
   </si>
@@ -200,6 +200,18 @@
     <t>AND (29)</t>
   </si>
   <si>
+    <t>BMI (30)</t>
+  </si>
+  <si>
+    <t>AND (35)</t>
+  </si>
+  <si>
+    <t>AND (37)</t>
+  </si>
+  <si>
+    <t>AND (39)</t>
+  </si>
+  <si>
     <t>Store as Address.H.</t>
   </si>
   <si>
@@ -321,9 +333,6 @@
     <t>SET1 (02)</t>
   </si>
   <si>
-    <t>Operand = (Operand &amp; ~1) | 1.</t>
-  </si>
-  <si>
     <t>Write Operand.</t>
   </si>
   <si>
@@ -1514,9 +1523,6 @@
     <t>CLR1 (12)</t>
   </si>
   <si>
-    <t>Operand = (Operand &amp; ~1) | 0.</t>
-  </si>
-  <si>
     <t>BBC0 (13)</t>
   </si>
   <si>
@@ -2508,9 +2514,6 @@
     <t>SET1 (22)</t>
   </si>
   <si>
-    <t>Operand = (Operand &amp; ~2) | 2.</t>
-  </si>
-  <si>
     <t>BBS1 (23)</t>
   </si>
   <si>
@@ -3008,6 +3011,664 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>CBNE (2E)</t>
+  </si>
+  <si>
+    <r>
+      <t>Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> != Operand).</t>
+    </r>
+  </si>
+  <si>
+    <t>Direct Page Relative d, r</t>
+  </si>
+  <si>
+    <t>BRA (2F)</t>
+  </si>
+  <si>
+    <t>Relative r</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to true.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80) == $80.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL3 (31)</t>
+  </si>
+  <si>
+    <t>Read $FFD8</t>
+  </si>
+  <si>
+    <t>Read $FFD9</t>
+  </si>
+  <si>
+    <t>CLR1 (32)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$02) | $00.</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$01) | $01.</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$01) | $00.</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$02) | $02.</t>
+  </si>
+  <si>
+    <t>BBC1 (33)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 1)) == (0 &lt;&lt; 1).</t>
+  </si>
+  <si>
+    <t>AND (34)</t>
+  </si>
+  <si>
+    <t>AND (36)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp;= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !A.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND (38)</t>
+  </si>
+  <si>
+    <t>INCW (3A)</t>
+  </si>
+  <si>
+    <t>Overflow = (Operand == $FF).</t>
+  </si>
+  <si>
+    <t>Operand += 1.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand += Overflow. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (LowZero &amp;&amp; !Operand).</t>
+    </r>
+  </si>
+  <si>
+    <t>ROL (3B)</t>
+  </si>
+  <si>
+    <t>ROL (3C)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tmp = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 1) | Tmp. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>INC (3D)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> += 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (3E)</t>
+  </si>
+  <si>
+    <t>CALL (3F)</t>
+  </si>
+  <si>
+    <t>Absolute Call !a</t>
+  </si>
+  <si>
+    <t>SETP (40)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | $20).</t>
     </r>
   </si>
 </sst>
@@ -3576,7 +4237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C2668"/>
+  <dimension ref="A1:C3785"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -3588,7 +4249,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -3620,7 +4281,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -3654,7 +4315,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -3669,7 +4330,7 @@
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -3701,7 +4362,7 @@
         <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -3721,7 +4382,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -3753,7 +4414,7 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>18</v>
@@ -3771,7 +4432,7 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>19</v>
@@ -3783,7 +4444,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3805,10 +4466,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3823,10 +4484,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3841,7 +4502,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -3856,7 +4517,7 @@
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -3868,7 +4529,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -3888,7 +4549,7 @@
         <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -3908,7 +4569,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -3920,7 +4581,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3940,7 +4601,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3951,7 +4612,7 @@
         <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3966,7 +4627,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -3981,10 +4642,10 @@
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>16</v>
@@ -3993,7 +4654,7 @@
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -4013,7 +4674,7 @@
         <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -4033,7 +4694,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -4045,7 +4706,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4065,7 +4726,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4087,7 +4748,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -4099,7 +4760,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4115,14 +4776,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4138,7 +4799,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4146,7 +4807,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -4161,7 +4822,7 @@
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -4173,7 +4834,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -4193,7 +4854,7 @@
         <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -4213,7 +4874,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -4225,7 +4886,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4245,7 +4906,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4253,7 +4914,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -4268,7 +4929,7 @@
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
@@ -4280,7 +4941,7 @@
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -4300,7 +4961,7 @@
         <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -4320,7 +4981,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -4340,10 +5001,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4372,7 +5033,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4380,7 +5041,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -4395,7 +5056,7 @@
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -4407,7 +5068,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C356" s="21"/>
     </row>
@@ -4427,7 +5088,7 @@
         <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -4461,7 +5122,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -4473,7 +5134,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4481,7 +5142,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -4496,7 +5157,7 @@
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -4508,7 +5169,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -4528,7 +5189,7 @@
         <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -4548,7 +5209,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -4576,7 +5237,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4587,7 +5248,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4602,7 +5263,7 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>20</v>
@@ -4625,7 +5286,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -4637,7 +5298,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4645,7 +5306,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -4660,7 +5321,7 @@
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -4692,7 +5353,7 @@
         <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -4712,7 +5373,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -4724,7 +5385,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4732,7 +5393,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -4747,7 +5408,7 @@
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
@@ -4759,7 +5420,7 @@
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -4779,7 +5440,7 @@
         <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -4799,7 +5460,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -4811,7 +5472,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4822,7 +5483,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4837,7 +5498,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -4849,7 +5510,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4860,7 +5521,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4869,7 +5530,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4880,7 +5541,7 @@
         <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4895,7 +5556,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -4910,7 +5571,7 @@
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
@@ -4922,7 +5583,7 @@
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -4942,7 +5603,7 @@
         <v>22</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -4962,7 +5623,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -4982,10 +5643,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5002,7 +5663,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -5014,14 +5675,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5043,7 +5704,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -5058,7 +5719,7 @@
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -5070,7 +5731,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -5090,7 +5751,7 @@
         <v>22</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -5110,7 +5771,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -5122,7 +5783,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5142,7 +5803,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5153,7 +5814,7 @@
         <v>23</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5168,7 +5829,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -5183,7 +5844,7 @@
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
@@ -5195,7 +5856,7 @@
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
       <c r="B710" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C710" s="21"/>
     </row>
@@ -5215,7 +5876,7 @@
         <v>22</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -5235,7 +5896,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -5255,10 +5916,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5287,7 +5948,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5298,7 +5959,7 @@
         <v>23</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5313,7 +5974,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -5328,7 +5989,7 @@
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -5360,7 +6021,7 @@
         <v>22</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -5380,7 +6041,7 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>26</v>
@@ -5398,10 +6059,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5410,7 +6071,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5432,7 +6093,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -5447,7 +6108,7 @@
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
@@ -5459,7 +6120,7 @@
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
       <c r="B828" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C828" s="21"/>
     </row>
@@ -5479,7 +6140,7 @@
         <v>22</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -5499,7 +6160,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -5519,10 +6180,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5551,21 +6212,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5594,7 +6255,7 @@
         <v>23</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5609,7 +6270,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -5624,7 +6285,7 @@
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -5656,7 +6317,7 @@
         <v>22</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -5676,7 +6337,7 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>26</v>
@@ -5694,7 +6355,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>18</v>
@@ -5712,7 +6373,7 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>19</v>
@@ -5730,10 +6391,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5742,7 +6403,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5764,10 +6425,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5782,10 +6443,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5800,7 +6461,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -5818,7 +6479,7 @@
         <v>15</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -5847,7 +6508,7 @@
         <v>22</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -5859,7 +6520,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5867,7 +6528,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -5879,7 +6540,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5895,14 +6556,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5918,7 +6579,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5926,7 +6587,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -5941,7 +6602,7 @@
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -5973,7 +6634,7 @@
         <v>22</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -5993,7 +6654,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -6025,7 +6686,7 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>18</v>
@@ -6043,7 +6704,7 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>19</v>
@@ -6055,7 +6716,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6077,10 +6738,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6095,10 +6756,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6113,7 +6774,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -6128,7 +6789,7 @@
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -6140,7 +6801,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -6160,7 +6821,7 @@
         <v>22</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -6180,7 +6841,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -6192,7 +6853,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6212,7 +6873,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6223,7 +6884,7 @@
         <v>23</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6238,7 +6899,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -6253,10 +6914,10 @@
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C1122" s="12" t="s">
         <v>16</v>
@@ -6265,7 +6926,7 @@
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
       <c r="B1123" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1123" s="21"/>
     </row>
@@ -6285,7 +6946,7 @@
         <v>22</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -6305,7 +6966,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -6317,7 +6978,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6337,7 +6998,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6359,7 +7020,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -6371,7 +7032,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6387,14 +7048,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6410,7 +7071,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6418,7 +7079,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -6433,7 +7094,7 @@
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -6445,7 +7106,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -6465,7 +7126,7 @@
         <v>22</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -6485,7 +7146,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -6513,7 +7174,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6533,7 +7194,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6541,7 +7202,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -6556,7 +7217,7 @@
     </row>
     <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B1240" s="11" t="s">
         <v>11</v>
@@ -6568,7 +7229,7 @@
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
       <c r="B1241" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C1241" s="21"/>
     </row>
@@ -6588,7 +7249,7 @@
         <v>22</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1243" t="s">
         <v>5</v>
@@ -6608,7 +7269,7 @@
         <v>1.2</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1245" s="2" t="s">
         <v>14</v>
@@ -6628,10 +7289,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1247" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6656,7 +7317,7 @@
       </c>
       <c r="B1250" s="7"/>
       <c r="C1250" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6664,7 +7325,7 @@
         <v>4.2</v>
       </c>
       <c r="B1251" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C1251" s="2" t="s">
         <v>6</v>
@@ -6676,7 +7337,7 @@
       </c>
       <c r="B1252" s="7"/>
       <c r="C1252" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6684,7 +7345,7 @@
         <v>5.2</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1253" s="2" t="s">
         <v>5</v>
@@ -6699,7 +7360,7 @@
     </row>
     <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B1299" s="11" t="s">
         <v>11</v>
@@ -6711,7 +7372,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
       <c r="B1300" s="20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C1300" s="21"/>
     </row>
@@ -6731,7 +7392,7 @@
         <v>22</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1302" t="s">
         <v>5</v>
@@ -6751,7 +7412,7 @@
         <v>1.2</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1304" s="2" t="s">
         <v>14</v>
@@ -6771,10 +7432,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1306" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6799,7 +7460,7 @@
       </c>
       <c r="B1309" s="7"/>
       <c r="C1309" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6807,7 +7468,7 @@
         <v>4.2</v>
       </c>
       <c r="B1310" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>6</v>
@@ -6819,7 +7480,7 @@
       </c>
       <c r="B1311" s="7"/>
       <c r="C1311" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6827,7 +7488,7 @@
         <v>5.2</v>
       </c>
       <c r="B1312" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>5</v>
@@ -6842,7 +7503,7 @@
     </row>
     <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1358" s="11" t="s">
         <v>3</v>
@@ -6854,7 +7515,7 @@
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
       <c r="B1359" s="20" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C1359" s="21"/>
     </row>
@@ -6874,7 +7535,7 @@
         <v>22</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1361" t="s">
         <v>5</v>
@@ -6894,7 +7555,7 @@
         <v>1.2</v>
       </c>
       <c r="B1363" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1363" s="2" t="s">
         <v>6</v>
@@ -6922,7 +7583,7 @@
       </c>
       <c r="B1366" s="7"/>
       <c r="C1366" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6933,7 +7594,7 @@
         <v>7</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6948,7 +7609,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C1369" s="2" t="s">
         <v>20</v>
@@ -6965,7 +7626,7 @@
       </c>
       <c r="B1371" s="7"/>
       <c r="C1371" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6985,7 +7646,7 @@
       </c>
       <c r="B1373" s="7"/>
       <c r="C1373" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6993,7 +7654,7 @@
         <v>6.2</v>
       </c>
       <c r="B1374" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1374" s="2" t="s">
         <v>5</v>
@@ -7008,7 +7669,7 @@
     </row>
     <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1417" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B1417" s="11" t="s">
         <v>11</v>
@@ -7020,7 +7681,7 @@
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
       <c r="B1418" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C1418" s="21"/>
     </row>
@@ -7040,7 +7701,7 @@
         <v>22</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1420" t="s">
         <v>5</v>
@@ -7060,10 +7721,10 @@
         <v>1.2</v>
       </c>
       <c r="B1422" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7080,7 +7741,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1424" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1424" s="2" t="s">
         <v>6</v>
@@ -7092,7 +7753,7 @@
       </c>
       <c r="B1425" s="7"/>
       <c r="C1425" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7103,7 +7764,7 @@
         <v>7</v>
       </c>
       <c r="C1426" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7112,7 +7773,7 @@
       </c>
       <c r="B1427" s="7"/>
       <c r="C1427" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7123,7 +7784,7 @@
         <v>23</v>
       </c>
       <c r="C1428" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7138,7 +7799,7 @@
         <v>5.2</v>
       </c>
       <c r="B1430" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1430" s="2" t="s">
         <v>5</v>
@@ -7153,7 +7814,7 @@
     </row>
     <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1476" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B1476" s="11" t="s">
         <v>11</v>
@@ -7165,7 +7826,7 @@
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="13"/>
       <c r="B1477" s="17" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C1477" s="18"/>
     </row>
@@ -7185,7 +7846,7 @@
         <v>22</v>
       </c>
       <c r="B1479" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1479" t="s">
         <v>5</v>
@@ -7205,7 +7866,7 @@
         <v>1.2</v>
       </c>
       <c r="B1481" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1481" s="2" t="s">
         <v>26</v>
@@ -7223,10 +7884,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1483" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C1483" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7241,10 +7902,10 @@
         <v>3.2</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7253,7 +7914,7 @@
       </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7261,10 +7922,10 @@
         <v>4.2</v>
       </c>
       <c r="B1487" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7284,7 +7945,7 @@
         <v>5.2</v>
       </c>
       <c r="B1490" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1490" s="2" t="s">
         <v>5</v>
@@ -7299,7 +7960,7 @@
     </row>
     <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1535" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B1535" s="11" t="s">
         <v>3</v>
@@ -7311,7 +7972,7 @@
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
       <c r="B1536" s="20" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1536" s="21"/>
     </row>
@@ -7331,7 +7992,7 @@
         <v>22</v>
       </c>
       <c r="B1538" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1538" t="s">
         <v>5</v>
@@ -7351,7 +8012,7 @@
         <v>1.2</v>
       </c>
       <c r="B1540" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1540" s="2" t="s">
         <v>6</v>
@@ -7363,7 +8024,7 @@
       </c>
       <c r="B1541" s="7"/>
       <c r="C1541" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7383,21 +8044,21 @@
       </c>
       <c r="B1543" s="7"/>
       <c r="C1543" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1544" s="3"/>
       <c r="B1544" s="7"/>
       <c r="C1544" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1545" s="3"/>
       <c r="B1545" s="7"/>
       <c r="C1545" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7408,7 +8069,7 @@
         <v>23</v>
       </c>
       <c r="C1546" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7423,7 +8084,7 @@
         <v>4.2</v>
       </c>
       <c r="B1548" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C1548" s="2" t="s">
         <v>6</v>
@@ -7440,7 +8101,7 @@
       </c>
       <c r="B1550" s="7"/>
       <c r="C1550" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="1551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7448,10 +8109,10 @@
         <v>5.2</v>
       </c>
       <c r="B1551" s="22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C1551" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7471,7 +8132,7 @@
         <v>6.2</v>
       </c>
       <c r="B1554" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1554" s="2" t="s">
         <v>5</v>
@@ -7486,7 +8147,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B1594" s="11" t="s">
         <v>11</v>
@@ -7498,7 +8159,7 @@
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
       <c r="B1595" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C1595" s="21"/>
     </row>
@@ -7518,7 +8179,7 @@
         <v>22</v>
       </c>
       <c r="B1597" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1597" t="s">
         <v>5</v>
@@ -7538,7 +8199,7 @@
         <v>1.2</v>
       </c>
       <c r="B1599" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1599" s="2" t="s">
         <v>6</v>
@@ -7566,7 +8227,7 @@
       </c>
       <c r="B1602" s="7"/>
       <c r="C1602" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7586,7 +8247,7 @@
       </c>
       <c r="B1604" s="7"/>
       <c r="C1604" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7597,7 +8258,7 @@
         <v>23</v>
       </c>
       <c r="C1605" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7612,7 +8273,7 @@
         <v>5.2</v>
       </c>
       <c r="B1607" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1607" s="2" t="s">
         <v>5</v>
@@ -7627,7 +8288,7 @@
     </row>
     <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1653" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B1653" s="11" t="s">
         <v>12</v>
@@ -7639,7 +8300,7 @@
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="13"/>
       <c r="B1654" s="17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C1654" s="18"/>
     </row>
@@ -7659,7 +8320,7 @@
         <v>22</v>
       </c>
       <c r="B1656" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1656" t="s">
         <v>5</v>
@@ -7679,7 +8340,7 @@
         <v>1.2</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1658" s="2" t="s">
         <v>26</v>
@@ -7691,7 +8352,7 @@
       </c>
       <c r="B1659" s="7"/>
       <c r="C1659" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7699,7 +8360,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1660" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1660" s="2" t="s">
         <v>5</v>
@@ -7714,7 +8375,7 @@
     </row>
     <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1712" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B1712" s="11" t="s">
         <v>12</v>
@@ -7746,7 +8407,7 @@
         <v>22</v>
       </c>
       <c r="B1715" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1715" t="s">
         <v>5</v>
@@ -7774,7 +8435,7 @@
       </c>
       <c r="B1718" s="7"/>
       <c r="C1718" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7782,7 +8443,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1719" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1719" s="2" t="s">
         <v>5</v>
@@ -7797,7 +8458,7 @@
     </row>
     <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1771" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B1771" s="11" t="s">
         <v>13</v>
@@ -7809,7 +8470,7 @@
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="13"/>
       <c r="B1772" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1772" s="18"/>
     </row>
@@ -7829,7 +8490,7 @@
         <v>22</v>
       </c>
       <c r="B1774" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1774" t="s">
         <v>5</v>
@@ -7849,7 +8510,7 @@
         <v>1.2</v>
       </c>
       <c r="B1776" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1776" s="2" t="s">
         <v>14</v>
@@ -7869,10 +8530,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1778" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1778" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7901,7 +8562,7 @@
       </c>
       <c r="B1781" s="7"/>
       <c r="C1781" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7909,7 +8570,7 @@
         <v>4.2</v>
       </c>
       <c r="B1782" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1782" s="2" t="s">
         <v>5</v>
@@ -7924,7 +8585,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B1830" s="11" t="s">
         <v>3</v>
@@ -7936,7 +8597,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
       <c r="B1831" s="20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C1831" s="21"/>
     </row>
@@ -7956,7 +8617,7 @@
         <v>22</v>
       </c>
       <c r="B1833" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1833" t="s">
         <v>5</v>
@@ -7976,7 +8637,7 @@
         <v>1.2</v>
       </c>
       <c r="B1835" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1835" s="2" t="s">
         <v>14</v>
@@ -7996,10 +8657,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1837" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1837" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8022,7 +8683,7 @@
       </c>
       <c r="B1840" s="7"/>
       <c r="C1840" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8030,10 +8691,10 @@
         <v>4.2</v>
       </c>
       <c r="B1841" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C1841" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8048,10 +8709,10 @@
         <v>5.2</v>
       </c>
       <c r="B1843" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C1843" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8066,7 +8727,7 @@
         <v>6.2</v>
       </c>
       <c r="B1845" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1845" s="2" t="s">
         <v>5</v>
@@ -8081,7 +8742,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B1889" s="11" t="s">
         <v>12</v>
@@ -8113,7 +8774,7 @@
         <v>22</v>
       </c>
       <c r="B1892" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1892" t="s">
         <v>5</v>
@@ -8141,7 +8802,7 @@
       </c>
       <c r="B1895" s="7"/>
       <c r="C1895" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8149,7 +8810,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1896" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1896" s="2" t="s">
         <v>5</v>
@@ -8164,7 +8825,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B1948" s="11" t="s">
         <v>9</v>
@@ -8196,7 +8857,7 @@
         <v>22</v>
       </c>
       <c r="B1951" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1951" t="s">
         <v>5</v>
@@ -8216,7 +8877,7 @@
         <v>1.2</v>
       </c>
       <c r="B1953" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1953" s="2" t="s">
         <v>6</v>
@@ -8248,7 +8909,7 @@
         <v>3.2</v>
       </c>
       <c r="B1957" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1957" s="2" t="s">
         <v>18</v>
@@ -8266,7 +8927,7 @@
         <v>4.2</v>
       </c>
       <c r="B1959" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C1959" s="2" t="s">
         <v>19</v>
@@ -8278,7 +8939,7 @@
       </c>
       <c r="B1960" s="7"/>
       <c r="C1960" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8300,10 +8961,10 @@
         <v>6.2</v>
       </c>
       <c r="B1963" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C1963" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8318,10 +8979,10 @@
         <v>7.2</v>
       </c>
       <c r="B1965" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C1965" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8336,7 +8997,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1967" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C1967" s="2" t="s">
         <v>5</v>
@@ -8351,7 +9012,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B2007" s="11" t="s">
         <v>13</v>
@@ -8363,7 +9024,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
       <c r="B2008" s="20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C2008" s="21"/>
     </row>
@@ -8383,7 +9044,7 @@
         <v>22</v>
       </c>
       <c r="B2010" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2010" t="s">
         <v>5</v>
@@ -8403,7 +9064,7 @@
         <v>1.2</v>
       </c>
       <c r="B2012" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2012" s="2" t="s">
         <v>6</v>
@@ -8415,7 +9076,7 @@
       </c>
       <c r="B2013" s="7"/>
       <c r="C2013" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8435,7 +9096,7 @@
       </c>
       <c r="B2015" s="7"/>
       <c r="C2015" s="2" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8446,7 +9107,7 @@
         <v>23</v>
       </c>
       <c r="C2016" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8461,7 +9122,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2018" s="2" t="s">
         <v>5</v>
@@ -8476,10 +9137,10 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B2066" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2066" s="12" t="s">
         <v>16</v>
@@ -8488,7 +9149,7 @@
     <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2067" s="13"/>
       <c r="B2067" s="17" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2067" s="18"/>
     </row>
@@ -8508,7 +9169,7 @@
         <v>22</v>
       </c>
       <c r="B2069" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2069" t="s">
         <v>5</v>
@@ -8528,7 +9189,7 @@
         <v>1.2</v>
       </c>
       <c r="B2071" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2071" s="2" t="s">
         <v>6</v>
@@ -8540,7 +9201,7 @@
       </c>
       <c r="B2072" s="7"/>
       <c r="C2072" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8560,7 +9221,7 @@
       </c>
       <c r="B2074" s="7"/>
       <c r="C2074" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8582,7 +9243,7 @@
         <v>4.2</v>
       </c>
       <c r="B2077" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2077" s="2" t="s">
         <v>6</v>
@@ -8594,7 +9255,7 @@
       </c>
       <c r="B2078" s="7"/>
       <c r="C2078" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8610,14 +9271,14 @@
       </c>
       <c r="B2080" s="7"/>
       <c r="C2080" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2081" s="3"/>
       <c r="B2081" s="7"/>
       <c r="C2081" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8633,7 +9294,7 @@
       </c>
       <c r="B2083" s="7"/>
       <c r="C2083" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8641,7 +9302,7 @@
         <v>7.2</v>
       </c>
       <c r="B2084" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2084" s="2" t="s">
         <v>5</v>
@@ -8656,7 +9317,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B2125" s="11" t="s">
         <v>10</v>
@@ -8668,7 +9329,7 @@
     <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2126" s="13"/>
       <c r="B2126" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C2126" s="18"/>
     </row>
@@ -8688,7 +9349,7 @@
         <v>22</v>
       </c>
       <c r="B2128" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2128" t="s">
         <v>5</v>
@@ -8708,7 +9369,7 @@
         <v>1.2</v>
       </c>
       <c r="B2130" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2130" s="2" t="s">
         <v>6</v>
@@ -8720,7 +9381,7 @@
       </c>
       <c r="B2131" s="7"/>
       <c r="C2131" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8740,7 +9401,7 @@
       </c>
       <c r="B2133" s="7"/>
       <c r="C2133" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8748,7 +9409,7 @@
         <v>3.2</v>
       </c>
       <c r="B2134" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2134" s="2" t="s">
         <v>5</v>
@@ -8775,7 +9436,7 @@
     <row r="2185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2185" s="13"/>
       <c r="B2185" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C2185" s="18"/>
     </row>
@@ -8795,7 +9456,7 @@
         <v>22</v>
       </c>
       <c r="B2187" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2187" t="s">
         <v>5</v>
@@ -8815,7 +9476,7 @@
         <v>1.2</v>
       </c>
       <c r="B2189" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2189" s="2" t="s">
         <v>14</v>
@@ -8835,10 +9496,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2191" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2191" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8867,7 +9528,7 @@
       </c>
       <c r="B2194" s="7"/>
       <c r="C2194" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8875,7 +9536,7 @@
         <v>4.2</v>
       </c>
       <c r="B2195" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2195" s="2" t="s">
         <v>5</v>
@@ -8890,7 +9551,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B2243" s="11" t="s">
         <v>10</v>
@@ -8902,7 +9563,7 @@
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="13"/>
       <c r="B2244" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2244" s="18"/>
     </row>
@@ -8922,7 +9583,7 @@
         <v>22</v>
       </c>
       <c r="B2246" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2246" t="s">
         <v>5</v>
@@ -8956,7 +9617,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2250" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2250" s="2" t="s">
         <v>6</v>
@@ -8968,7 +9629,7 @@
       </c>
       <c r="B2251" s="7"/>
       <c r="C2251" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8976,7 +9637,7 @@
         <v>3.2</v>
       </c>
       <c r="B2252" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2252" s="2" t="s">
         <v>5</v>
@@ -9003,7 +9664,7 @@
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
       <c r="B2303" s="20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2303" s="21"/>
     </row>
@@ -9023,7 +9684,7 @@
         <v>22</v>
       </c>
       <c r="B2305" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2305" t="s">
         <v>5</v>
@@ -9043,7 +9704,7 @@
         <v>1.2</v>
       </c>
       <c r="B2307" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2307" s="2" t="s">
         <v>6</v>
@@ -9071,7 +9732,7 @@
       </c>
       <c r="B2310" s="7"/>
       <c r="C2310" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9082,7 +9743,7 @@
         <v>7</v>
       </c>
       <c r="C2311" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9097,7 +9758,7 @@
         <v>4.2</v>
       </c>
       <c r="B2313" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2313" s="2" t="s">
         <v>20</v>
@@ -9120,7 +9781,7 @@
         <v>5.2</v>
       </c>
       <c r="B2316" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C2316" s="2" t="s">
         <v>6</v>
@@ -9132,7 +9793,7 @@
       </c>
       <c r="B2317" s="7"/>
       <c r="C2317" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9140,7 +9801,7 @@
         <v>6.2</v>
       </c>
       <c r="B2318" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2318" s="2" t="s">
         <v>5</v>
@@ -9155,7 +9816,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B2361" s="11" t="s">
         <v>12</v>
@@ -9187,7 +9848,7 @@
         <v>22</v>
       </c>
       <c r="B2364" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2364" t="s">
         <v>5</v>
@@ -9207,7 +9868,7 @@
         <v>1.2</v>
       </c>
       <c r="B2366" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2366" s="2" t="s">
         <v>6</v>
@@ -9219,7 +9880,7 @@
       </c>
       <c r="B2367" s="7"/>
       <c r="C2367" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9227,7 +9888,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2368" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2368" s="2" t="s">
         <v>5</v>
@@ -9254,7 +9915,7 @@
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
       <c r="B2421" s="20" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C2421" s="21"/>
     </row>
@@ -9274,7 +9935,7 @@
         <v>22</v>
       </c>
       <c r="B2423" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2423" t="s">
         <v>5</v>
@@ -9294,7 +9955,7 @@
         <v>1.2</v>
       </c>
       <c r="B2425" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2425" s="2" t="s">
         <v>6</v>
@@ -9306,7 +9967,7 @@
       </c>
       <c r="B2426" s="7"/>
       <c r="C2426" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9317,7 +9978,7 @@
         <v>7</v>
       </c>
       <c r="C2427" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9332,7 +9993,7 @@
         <v>3.2</v>
       </c>
       <c r="B2429" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2429" s="2" t="s">
         <v>6</v>
@@ -9344,7 +10005,7 @@
       </c>
       <c r="B2430" s="7"/>
       <c r="C2430" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9355,7 +10016,7 @@
         <v>7</v>
       </c>
       <c r="C2431" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9364,7 +10025,7 @@
       </c>
       <c r="B2432" s="7"/>
       <c r="C2432" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9375,7 +10036,7 @@
         <v>23</v>
       </c>
       <c r="C2433" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9390,7 +10051,7 @@
         <v>6.2</v>
       </c>
       <c r="B2435" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2435" s="2" t="s">
         <v>5</v>
@@ -9405,7 +10066,7 @@
     </row>
     <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2479" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B2479" s="11" t="s">
         <v>11</v>
@@ -9417,7 +10078,7 @@
     <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2480" s="13"/>
       <c r="B2480" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2480" s="18"/>
     </row>
@@ -9437,7 +10098,7 @@
         <v>22</v>
       </c>
       <c r="B2482" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2482" t="s">
         <v>5</v>
@@ -9457,7 +10118,7 @@
         <v>1.2</v>
       </c>
       <c r="B2484" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2484" s="2" t="s">
         <v>14</v>
@@ -9477,10 +10138,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2486" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2486" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9497,7 +10158,7 @@
         <v>3.2</v>
       </c>
       <c r="B2488" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C2488" s="2" t="s">
         <v>6</v>
@@ -9509,14 +10170,14 @@
       </c>
       <c r="B2489" s="7"/>
       <c r="C2489" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2490" s="3"/>
       <c r="B2490" s="7"/>
       <c r="C2490" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9538,7 +10199,7 @@
         <v>5.2</v>
       </c>
       <c r="B2493" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2493" s="2" t="s">
         <v>5</v>
@@ -9553,7 +10214,7 @@
     </row>
     <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2538" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B2538" s="11" t="s">
         <v>13</v>
@@ -9565,7 +10226,7 @@
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="13"/>
       <c r="B2539" s="20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C2539" s="21"/>
     </row>
@@ -9585,7 +10246,7 @@
         <v>22</v>
       </c>
       <c r="B2541" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2541" t="s">
         <v>5</v>
@@ -9605,7 +10266,7 @@
         <v>1.2</v>
       </c>
       <c r="B2543" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2543" s="2" t="s">
         <v>6</v>
@@ -9617,7 +10278,7 @@
       </c>
       <c r="B2544" s="7"/>
       <c r="C2544" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9637,7 +10298,7 @@
       </c>
       <c r="B2546" s="7"/>
       <c r="C2546" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9653,7 +10314,7 @@
         <v>23</v>
       </c>
       <c r="C2548" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9668,7 +10329,7 @@
         <v>4.2</v>
       </c>
       <c r="B2550" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2550" s="2" t="s">
         <v>5</v>
@@ -9683,7 +10344,7 @@
     </row>
     <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2597" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B2597" s="11" t="s">
         <v>11</v>
@@ -9695,7 +10356,7 @@
     <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2598" s="13"/>
       <c r="B2598" s="20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C2598" s="21"/>
     </row>
@@ -9715,7 +10376,7 @@
         <v>22</v>
       </c>
       <c r="B2600" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2600" t="s">
         <v>5</v>
@@ -9735,7 +10396,7 @@
         <v>1.2</v>
       </c>
       <c r="B2602" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2602" s="2" t="s">
         <v>14</v>
@@ -9755,10 +10416,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2604" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2604" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9787,7 +10448,7 @@
       </c>
       <c r="B2607" s="7"/>
       <c r="C2607" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9803,7 +10464,7 @@
         <v>23</v>
       </c>
       <c r="C2609" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9818,7 +10479,7 @@
         <v>5.2</v>
       </c>
       <c r="B2611" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2611" s="2" t="s">
         <v>5</v>
@@ -9833,7 +10494,7 @@
     </row>
     <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2656" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B2656" s="11" t="s">
         <v>13</v>
@@ -9865,7 +10526,7 @@
         <v>22</v>
       </c>
       <c r="B2659" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C2659" t="s">
         <v>5</v>
@@ -9885,7 +10546,7 @@
         <v>1.2</v>
       </c>
       <c r="B2661" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2661" s="2" t="s">
         <v>26</v>
@@ -9903,10 +10564,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2663" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C2663" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9915,7 +10576,7 @@
       </c>
       <c r="B2664" s="7"/>
       <c r="C2664" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9937,7 +10598,7 @@
         <v>4.2</v>
       </c>
       <c r="B2667" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2667" s="2" t="s">
         <v>5</v>
@@ -9950,8 +10611,2690 @@
       <c r="B2668" s="9"/>
       <c r="C2668" s="8"/>
     </row>
+    <row r="2715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2715" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2715" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2715" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2716" s="13"/>
+      <c r="B2716" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2716" s="18"/>
+    </row>
+    <row r="2717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2717" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2717" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2717" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2718" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2718" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2718" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2719" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2719" s="7"/>
+      <c r="C2719" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2720" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2720" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2720" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2721" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2721" s="7"/>
+      <c r="C2721" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2722" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2722" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2722" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2723" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2723" s="7"/>
+      <c r="C2723" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2724" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2724" s="7"/>
+      <c r="C2724" s="2"/>
+    </row>
+    <row r="2725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2725" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2725" s="7"/>
+      <c r="C2725" s="2"/>
+    </row>
+    <row r="2726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2726" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2726" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2726" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2727" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2727" s="7"/>
+      <c r="C2727" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2728" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2728" s="7"/>
+      <c r="C2728" s="2"/>
+    </row>
+    <row r="2729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2729" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B2729" s="7"/>
+      <c r="C2729" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2730" s="3"/>
+      <c r="B2730" s="7"/>
+      <c r="C2730" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2731" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B2731" s="7"/>
+      <c r="C2731" s="2"/>
+    </row>
+    <row r="2732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2732" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B2732" s="7"/>
+      <c r="C2732" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2733" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B2733" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2733" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2734" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2734" s="9"/>
+      <c r="C2734" s="8"/>
+    </row>
+    <row r="2774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2774" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2774" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2774" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2775" s="13"/>
+      <c r="B2775" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2775" s="18"/>
+    </row>
+    <row r="2776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2776" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2776" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2776" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2777" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2777" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2777" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2778" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2778" s="7"/>
+      <c r="C2778" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2779" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2779" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2779" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2780" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2780" s="7"/>
+      <c r="C2780" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2781" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2781" s="7"/>
+      <c r="C2781" s="2"/>
+    </row>
+    <row r="2782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2782" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2782" s="7"/>
+      <c r="C2782" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2783" s="3"/>
+      <c r="B2783" s="7"/>
+      <c r="C2783" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2784" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2784" s="7"/>
+      <c r="C2784" s="2"/>
+    </row>
+    <row r="2785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2785" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2785" s="7"/>
+      <c r="C2785" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2786" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2786" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2786" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2787" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2787" s="9"/>
+      <c r="C2787" s="8"/>
+    </row>
+    <row r="2833" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2833" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2833" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2833" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2834" s="13"/>
+      <c r="B2834" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2834" s="18"/>
+    </row>
+    <row r="2835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2835" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2835" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2835" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2836" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2836" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2836" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2837" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2837" s="7"/>
+      <c r="C2837" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2838" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2838" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2838" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2839" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2839" s="7"/>
+      <c r="C2839" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2840" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2840" s="7"/>
+      <c r="C2840" s="2"/>
+    </row>
+    <row r="2841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2841" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2841" s="7"/>
+      <c r="C2841" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2842" s="3"/>
+      <c r="B2842" s="7"/>
+      <c r="C2842" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2843" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2843" s="7"/>
+      <c r="C2843" s="2"/>
+    </row>
+    <row r="2844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2844" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2844" s="7"/>
+      <c r="C2844" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2845" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2845" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2845" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2846" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2846" s="9"/>
+      <c r="C2846" s="8"/>
+    </row>
+    <row r="2892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2892" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2892" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2892" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2893" s="13"/>
+      <c r="B2893" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2893" s="18"/>
+    </row>
+    <row r="2894" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2894" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2894" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2894" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2895" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2895" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2895" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2896" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2896" s="7"/>
+      <c r="C2896" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2897" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2897" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2897" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2898" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2898" s="7"/>
+      <c r="C2898" s="2"/>
+    </row>
+    <row r="2899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2899" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2899" s="7"/>
+      <c r="C2899" s="2"/>
+    </row>
+    <row r="2900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2900" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2900" s="7"/>
+      <c r="C2900" s="2"/>
+    </row>
+    <row r="2901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2901" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2901" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2901" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2902" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2902" s="7"/>
+      <c r="C2902" s="2"/>
+    </row>
+    <row r="2903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2903" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2903" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2903" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2904" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2904" s="7"/>
+      <c r="C2904" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2905" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B2905" s="7"/>
+      <c r="C2905" s="2"/>
+    </row>
+    <row r="2906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2906" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B2906" s="7"/>
+      <c r="C2906" s="2"/>
+    </row>
+    <row r="2907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2907" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B2907" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2907" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2908" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B2908" s="7"/>
+      <c r="C2908" s="2"/>
+    </row>
+    <row r="2909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2909" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B2909" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2909" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2910" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B2910" s="7"/>
+      <c r="C2910" s="2"/>
+    </row>
+    <row r="2911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2911" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B2911" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2911" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2912" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2912" s="9"/>
+      <c r="C2912" s="8"/>
+    </row>
+    <row r="2951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2951" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2951" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2951" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2952" s="13"/>
+      <c r="B2952" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2952" s="21"/>
+    </row>
+    <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2953" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2953" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2953" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2954" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2954" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2954" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2955" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2955" s="7"/>
+      <c r="C2955" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2956" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B2956" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2956" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2957" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B2957" s="7"/>
+      <c r="C2957" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2958" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B2958" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2958" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2959" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B2959" s="7"/>
+      <c r="C2959" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2960" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B2960" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2960" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2961" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B2961" s="7"/>
+      <c r="C2961" s="2"/>
+    </row>
+    <row r="2962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2962" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B2962" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2962" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2963" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2963" s="9"/>
+      <c r="C2963" s="8"/>
+    </row>
+    <row r="3010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3010" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3010" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3010" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3011" s="13"/>
+      <c r="B3011" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3011" s="21"/>
+    </row>
+    <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3012" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3012" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3012" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3013" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3013" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3013" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3014" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3014" s="7"/>
+      <c r="C3014" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3015" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3015" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3015" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3016" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3016" s="7"/>
+      <c r="C3016" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3017" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3017" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3017" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3018" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3018" s="7"/>
+      <c r="C3018" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3019" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3019" s="7"/>
+      <c r="C3019" s="2"/>
+    </row>
+    <row r="3020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3020" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3020" s="7"/>
+      <c r="C3020" s="2"/>
+    </row>
+    <row r="3021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3021" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3021" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3021" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3022" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3022" s="7"/>
+      <c r="C3022" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3023" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3023" s="7"/>
+      <c r="C3023" s="2"/>
+    </row>
+    <row r="3024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3024" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3024" s="7"/>
+      <c r="C3024" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3025" s="3"/>
+      <c r="B3025" s="7"/>
+      <c r="C3025" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3026" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3026" s="7"/>
+      <c r="C3026" s="2"/>
+    </row>
+    <row r="3027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3027" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B3027" s="7"/>
+      <c r="C3027" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3028" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B3028" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3028" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3029" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3029" s="9"/>
+      <c r="C3029" s="8"/>
+    </row>
+    <row r="3069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3069" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3069" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3069" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3070" s="13"/>
+      <c r="B3070" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3070" s="21"/>
+    </row>
+    <row r="3071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3071" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3071" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3071" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3072" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3072" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3072" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3073" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3073" s="7"/>
+      <c r="C3073" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3074" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3074" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3074" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3075" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3075" s="7"/>
+      <c r="C3075" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3076" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3076" s="7"/>
+      <c r="C3076" s="2"/>
+    </row>
+    <row r="3077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3077" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3077" s="7"/>
+      <c r="C3077" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3078" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3078" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3078" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3079" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3079" s="7"/>
+      <c r="C3079" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3080" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3080" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3080" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3081" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3081" s="9"/>
+      <c r="C3081" s="8"/>
+    </row>
+    <row r="3128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3128" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3128" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3128" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3129" s="13"/>
+      <c r="B3129" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3129" s="21"/>
+    </row>
+    <row r="3130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3130" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3130" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3130" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3131" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3131" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3132" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3132" s="7"/>
+      <c r="C3132" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3133" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3133" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3133" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3134" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3134" s="7"/>
+      <c r="C3134" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3135" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3135" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3135" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3136" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3136" s="7"/>
+      <c r="C3136" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3137" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3137" s="7"/>
+      <c r="C3137" s="2"/>
+    </row>
+    <row r="3138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3138" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3138" s="7"/>
+      <c r="C3138" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3139" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3139" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3140" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3140" s="7"/>
+      <c r="C3140" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3141" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3141" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3141" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3142" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3142" s="9"/>
+      <c r="C3142" s="8"/>
+    </row>
+    <row r="3187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3187" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3187" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3187" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3188" s="13"/>
+      <c r="B3188" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3188" s="21"/>
+    </row>
+    <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3189" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3189" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3189" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3190" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3190" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3191" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3191" s="7"/>
+      <c r="C3191" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3192" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3192" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3192" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3193" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3193" s="7"/>
+      <c r="C3193" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3194" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3194" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3194" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3195" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3195" s="7"/>
+      <c r="C3195" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3196" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3196" s="7"/>
+      <c r="C3196" s="2"/>
+    </row>
+    <row r="3197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3197" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3197" s="7"/>
+      <c r="C3197" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3198" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3198" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3198" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3199" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3199" s="7"/>
+      <c r="C3199" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3200" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3200" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3200" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3201" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3201" s="9"/>
+      <c r="C3201" s="8"/>
+    </row>
+    <row r="3246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3246" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3246" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3246" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3247" s="13"/>
+      <c r="B3247" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3247" s="21"/>
+    </row>
+    <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3248" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3248" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3248" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3249" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3249" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3249" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3250" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3250" s="7"/>
+      <c r="C3250" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3251" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3251" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3251" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3252" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3252" s="7"/>
+      <c r="C3252" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3253" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3253" s="7"/>
+      <c r="C3253" s="2"/>
+    </row>
+    <row r="3254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3254" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3254" s="7"/>
+      <c r="C3254" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3255" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3255" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3255" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3256" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3256" s="7"/>
+      <c r="C3256" s="2"/>
+    </row>
+    <row r="3257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3257" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3257" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3257" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3258" s="3"/>
+      <c r="B3258" s="22"/>
+      <c r="C3258" s="2"/>
+    </row>
+    <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3259" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3259" s="7"/>
+      <c r="C3259" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3260" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3260" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3260" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3261" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3261" s="7"/>
+      <c r="C3261" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3262" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3262" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3262" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3263" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3263" s="9"/>
+      <c r="C3263" s="8"/>
+    </row>
+    <row r="3305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3305" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3305" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3305" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3306" s="13"/>
+      <c r="B3306" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3306" s="21"/>
+    </row>
+    <row r="3307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3307" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3307" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3307" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3308" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3308" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3308" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3309" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3309" s="7"/>
+      <c r="C3309" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3310" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3310" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3310" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3311" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3311" s="7"/>
+      <c r="C3311" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3312" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3312" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3312" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3313" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3313" s="7"/>
+      <c r="C3313" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3314" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3314" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3314" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3315" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3315" s="7"/>
+      <c r="C3315" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3316" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3316" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3316" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3317" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3317" s="7"/>
+      <c r="C3317" s="2"/>
+    </row>
+    <row r="3318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3318" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3318" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3318" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3319" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3319" s="9"/>
+      <c r="C3319" s="8"/>
+    </row>
+    <row r="3364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3364" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3364" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3364" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3365" s="13"/>
+      <c r="B3365" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3365" s="21"/>
+    </row>
+    <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3366" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3366" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3366" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3367" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3367" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3367" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3368" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3368" s="7"/>
+      <c r="C3368" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3369" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3369" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3369" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3370" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3370" s="7"/>
+      <c r="C3370" s="2"/>
+    </row>
+    <row r="3371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3371" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3371" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3371" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3372" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3372" s="7"/>
+      <c r="C3372" s="2"/>
+    </row>
+    <row r="3373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3373" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3373" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3373" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3374" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3374" s="7"/>
+      <c r="C3374" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3375" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3375" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3375" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3376" s="3"/>
+      <c r="B3376" s="22"/>
+      <c r="C3376" s="2"/>
+    </row>
+    <row r="3377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3377" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3377" s="7"/>
+      <c r="C3377" s="2"/>
+    </row>
+    <row r="3378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3378" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3378" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3378" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3379" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3379" s="9"/>
+      <c r="C3379" s="8"/>
+    </row>
+    <row r="3423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3423" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3423" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3423" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3424" s="13"/>
+      <c r="B3424" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3424" s="21"/>
+    </row>
+    <row r="3425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3425" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3425" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3425" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3426" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3426" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3426" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3427" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3427" s="7"/>
+      <c r="C3427" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3428" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3428" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3428" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3429" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3429" s="7"/>
+      <c r="C3429" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3430" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3430" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3430" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3431" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3431" s="7"/>
+      <c r="C3431" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3432" s="3"/>
+      <c r="B3432" s="7"/>
+      <c r="C3432" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3433" s="3"/>
+      <c r="B3433" s="7"/>
+      <c r="C3433" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3434" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3434" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3434" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3435" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3435" s="7"/>
+      <c r="C3435" s="2"/>
+    </row>
+    <row r="3436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3436" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3436" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3436" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3437" s="3"/>
+      <c r="B3437" s="22"/>
+      <c r="C3437" s="2"/>
+    </row>
+    <row r="3438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3438" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3438" s="2"/>
+      <c r="C3438" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3439" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3439" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3439" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3440" s="3"/>
+      <c r="B3440" s="22"/>
+      <c r="C3440" s="2"/>
+    </row>
+    <row r="3441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3441" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3441" s="7"/>
+      <c r="C3441" s="2"/>
+    </row>
+    <row r="3442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3442" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3442" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3442" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3443" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3443" s="9"/>
+      <c r="C3443" s="8"/>
+    </row>
+    <row r="3482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3482" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3482" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3482" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3483" s="13"/>
+      <c r="B3483" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3483" s="21"/>
+    </row>
+    <row r="3484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3484" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3484" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3484" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3485" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3485" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3485" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3486" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3486" s="7"/>
+      <c r="C3486" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3487" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3487" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3487" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3488" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3488" s="7"/>
+      <c r="C3488" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3489" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3489" s="7"/>
+      <c r="C3489" s="2"/>
+    </row>
+    <row r="3490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3490" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3490" s="7"/>
+      <c r="C3490" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3491" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3491" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3491" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3492" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3492" s="7"/>
+      <c r="C3492" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3493" s="3"/>
+      <c r="B3493" s="7"/>
+      <c r="C3493" s="22"/>
+    </row>
+    <row r="3494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3494" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3494" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3494" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3495" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3495" s="7"/>
+      <c r="C3495" s="2"/>
+    </row>
+    <row r="3496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3496" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3496" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3496" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3497" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3497" s="9"/>
+      <c r="C3497" s="8"/>
+    </row>
+    <row r="3541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3541" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3541" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3541" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3542" s="13"/>
+      <c r="B3542" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3542" s="18"/>
+    </row>
+    <row r="3543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3543" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3543" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3543" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3544" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3544" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3544" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3545" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3545" s="7"/>
+      <c r="C3545" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3546" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3546" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3546" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3547" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3547" s="7"/>
+      <c r="C3547" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3548" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3548" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3548" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3549" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3549" s="9"/>
+      <c r="C3549" s="8"/>
+    </row>
+    <row r="3600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3600" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3600" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3600" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3601" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3601" s="13"/>
+      <c r="B3601" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3601" s="18"/>
+    </row>
+    <row r="3602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3602" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3602" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3602" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3603" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3603" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3603" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3604" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3604" s="7"/>
+      <c r="C3604" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3605" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3605" s="7"/>
+      <c r="C3605" s="2"/>
+    </row>
+    <row r="3606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3606" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3606" s="7"/>
+      <c r="C3606" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3607" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3607" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3607" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3608" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3608" s="9"/>
+      <c r="C3608" s="8"/>
+    </row>
+    <row r="3659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3659" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3659" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3659" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3660" s="13"/>
+      <c r="B3660" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3660" s="18"/>
+    </row>
+    <row r="3661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3661" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3661" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3661" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3662" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3662" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3662" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3663" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3663" s="7"/>
+      <c r="C3663" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3664" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3664" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3664" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3665" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3665" s="7"/>
+      <c r="C3665" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3666" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3666" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3666" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3667" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3667" s="7"/>
+      <c r="C3667" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3668" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3668" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3668" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3669" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3669" s="9"/>
+      <c r="C3669" s="8"/>
+    </row>
+    <row r="3718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3718" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3718" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3718" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3719" s="13"/>
+      <c r="B3719" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3719" s="18"/>
+    </row>
+    <row r="3720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3720" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3720" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3720" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3721" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3721" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3721" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3722" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3722" s="7"/>
+      <c r="C3722" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3723" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3723" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3723" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3724" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3724" s="7"/>
+      <c r="C3724" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3725" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3725" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3725" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3726" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3726" s="7"/>
+      <c r="C3726" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3727" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3727" s="7"/>
+      <c r="C3727" s="2"/>
+    </row>
+    <row r="3728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3728" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3728" s="7"/>
+      <c r="C3728" s="2"/>
+    </row>
+    <row r="3729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3729" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3729" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3729" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3730" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3730" s="7"/>
+      <c r="C3730" s="2"/>
+    </row>
+    <row r="3731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3731" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3731" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3731" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3732" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3732" s="7"/>
+      <c r="C3732" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3733" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3733" s="7"/>
+      <c r="C3733" s="2"/>
+    </row>
+    <row r="3734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3734" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B3734" s="7"/>
+      <c r="C3734" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3735" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B3735" s="7"/>
+      <c r="C3735" s="2"/>
+    </row>
+    <row r="3736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3736" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B3736" s="7"/>
+      <c r="C3736" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3737" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B3737" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3737" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3738" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3738" s="9"/>
+      <c r="C3738" s="8"/>
+    </row>
+    <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3777" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3777" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3777" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3778" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3778" s="13"/>
+      <c r="B3778" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3778" s="18"/>
+    </row>
+    <row r="3779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3779" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3779" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3779" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3780" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3780" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3780" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3781" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3781" s="7"/>
+      <c r="C3781" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3782" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3782" s="7"/>
+      <c r="C3782" s="2"/>
+    </row>
+    <row r="3783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3783" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3783" s="7"/>
+      <c r="C3783" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3784" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3784" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3784" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3785" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3785" s="9"/>
+      <c r="C3785" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="45">
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B3070:C3070"/>
+    <mergeCell ref="B3129:C3129"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B3257:B3258"/>
+    <mergeCell ref="B3306:C3306"/>
     <mergeCell ref="B120:C120"/>
     <mergeCell ref="B179:C179"/>
     <mergeCell ref="B425:B426"/>
@@ -9982,6 +13325,13 @@
     <mergeCell ref="B1595:C1595"/>
     <mergeCell ref="B1548:B1549"/>
     <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="B3375:B3376"/>
+    <mergeCell ref="B3424:C3424"/>
+    <mergeCell ref="B3436:B3437"/>
+    <mergeCell ref="B3439:B3440"/>
+    <mergeCell ref="B3483:C3483"/>
+    <mergeCell ref="C3492:C3493"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF69ECC0-34CD-4DB8-B377-DEA8F9393450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD7E6E0-94AB-4BBE-8A4E-84013FAD3C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$3835</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$4366</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="223">
   <si>
     <t>Implied</t>
   </si>
@@ -212,6 +212,15 @@
     <t>AND (39)</t>
   </si>
   <si>
+    <t>EOR (45)</t>
+  </si>
+  <si>
+    <t>EOR (47)</t>
+  </si>
+  <si>
+    <t>EOR (49)</t>
+  </si>
+  <si>
     <t>Store as Address.H.</t>
   </si>
   <si>
@@ -3669,6 +3678,321 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> | $20).</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL4 (41)</t>
+  </si>
+  <si>
+    <t>Read $FFD6</t>
+  </si>
+  <si>
+    <t>Read $FFD7</t>
+  </si>
+  <si>
+    <t>SET1 (42)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$04) | $04.</t>
+  </si>
+  <si>
+    <t>BBS2 (43)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 2)) == (1 &lt;&lt; 2).</t>
+  </si>
+  <si>
+    <t>EOR (44)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR (46)</t>
+  </si>
+  <si>
+    <t>EOR (48)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^= Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand0 ^= Operand1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand0 &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand0.</t>
     </r>
   </si>
 </sst>
@@ -4237,7 +4561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C3785"/>
+  <dimension ref="A1:C4324"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -4249,7 +4573,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -4281,7 +4605,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -4315,7 +4639,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -4330,7 +4654,7 @@
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -4362,7 +4686,7 @@
         <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -4382,7 +4706,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -4414,7 +4738,7 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>18</v>
@@ -4432,7 +4756,7 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>19</v>
@@ -4444,7 +4768,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4466,10 +4790,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4484,10 +4808,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4502,7 +4826,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -4517,7 +4841,7 @@
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -4529,7 +4853,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -4549,7 +4873,7 @@
         <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -4569,7 +4893,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -4581,7 +4905,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4601,7 +4925,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4612,7 +4936,7 @@
         <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4627,7 +4951,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -4642,10 +4966,10 @@
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>16</v>
@@ -4654,7 +4978,7 @@
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -4674,7 +4998,7 @@
         <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -4694,7 +5018,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -4706,7 +5030,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4726,7 +5050,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4748,7 +5072,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -4760,7 +5084,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4776,14 +5100,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4799,7 +5123,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4807,7 +5131,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -4822,7 +5146,7 @@
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -4834,7 +5158,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -4854,7 +5178,7 @@
         <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -4874,7 +5198,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -4886,7 +5210,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4906,7 +5230,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4914,7 +5238,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -4929,7 +5253,7 @@
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
@@ -4941,7 +5265,7 @@
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -4961,7 +5285,7 @@
         <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -4981,7 +5305,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -5001,10 +5325,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5033,7 +5357,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5041,7 +5365,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -5056,7 +5380,7 @@
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -5068,7 +5392,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C356" s="21"/>
     </row>
@@ -5088,7 +5412,7 @@
         <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -5122,7 +5446,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -5134,7 +5458,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5142,7 +5466,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -5157,7 +5481,7 @@
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -5169,7 +5493,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -5189,7 +5513,7 @@
         <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -5209,7 +5533,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -5237,7 +5561,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5248,7 +5572,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5263,7 +5587,7 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>20</v>
@@ -5286,7 +5610,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -5298,7 +5622,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5306,7 +5630,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -5321,7 +5645,7 @@
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -5353,7 +5677,7 @@
         <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -5373,7 +5697,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -5385,7 +5709,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5393,7 +5717,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -5408,7 +5732,7 @@
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
@@ -5420,7 +5744,7 @@
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -5440,7 +5764,7 @@
         <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -5460,7 +5784,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -5472,7 +5796,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5483,7 +5807,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5498,7 +5822,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -5510,7 +5834,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5521,7 +5845,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5530,7 +5854,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5541,7 +5865,7 @@
         <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5556,7 +5880,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -5571,7 +5895,7 @@
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
@@ -5583,7 +5907,7 @@
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -5603,7 +5927,7 @@
         <v>22</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -5623,7 +5947,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -5643,10 +5967,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5663,7 +5987,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -5675,14 +5999,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5704,7 +6028,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -5719,7 +6043,7 @@
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -5731,7 +6055,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -5751,7 +6075,7 @@
         <v>22</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -5771,7 +6095,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -5783,7 +6107,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5803,7 +6127,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5814,7 +6138,7 @@
         <v>23</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5829,7 +6153,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -5844,7 +6168,7 @@
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
@@ -5856,7 +6180,7 @@
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
       <c r="B710" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C710" s="21"/>
     </row>
@@ -5876,7 +6200,7 @@
         <v>22</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -5896,7 +6220,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -5916,10 +6240,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5948,7 +6272,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5959,7 +6283,7 @@
         <v>23</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5974,7 +6298,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -5989,7 +6313,7 @@
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -6021,7 +6345,7 @@
         <v>22</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -6041,7 +6365,7 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>26</v>
@@ -6059,10 +6383,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6071,7 +6395,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6093,7 +6417,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -6108,7 +6432,7 @@
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
@@ -6120,7 +6444,7 @@
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
       <c r="B828" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C828" s="21"/>
     </row>
@@ -6140,7 +6464,7 @@
         <v>22</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -6160,7 +6484,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -6180,10 +6504,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6212,21 +6536,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6255,7 +6579,7 @@
         <v>23</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6270,7 +6594,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -6285,7 +6609,7 @@
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -6317,7 +6641,7 @@
         <v>22</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -6337,7 +6661,7 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>26</v>
@@ -6355,7 +6679,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>18</v>
@@ -6373,7 +6697,7 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>19</v>
@@ -6391,10 +6715,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6403,7 +6727,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6425,10 +6749,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6443,10 +6767,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6461,7 +6785,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -6479,7 +6803,7 @@
         <v>15</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -6508,7 +6832,7 @@
         <v>22</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -6520,7 +6844,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6528,7 +6852,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -6540,7 +6864,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6556,14 +6880,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6579,7 +6903,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6587,7 +6911,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -6602,7 +6926,7 @@
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -6634,7 +6958,7 @@
         <v>22</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -6654,7 +6978,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -6686,7 +7010,7 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>18</v>
@@ -6704,7 +7028,7 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>19</v>
@@ -6716,7 +7040,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6738,10 +7062,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6756,10 +7080,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6774,7 +7098,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -6789,7 +7113,7 @@
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -6801,7 +7125,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -6821,7 +7145,7 @@
         <v>22</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -6841,7 +7165,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -6853,7 +7177,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6873,7 +7197,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6884,7 +7208,7 @@
         <v>23</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6899,7 +7223,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -6914,10 +7238,10 @@
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C1122" s="12" t="s">
         <v>16</v>
@@ -6926,7 +7250,7 @@
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
       <c r="B1123" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C1123" s="21"/>
     </row>
@@ -6946,7 +7270,7 @@
         <v>22</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -6966,7 +7290,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -6978,7 +7302,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6998,7 +7322,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7020,7 +7344,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -7032,7 +7356,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7048,14 +7372,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7071,7 +7395,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,7 +7403,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -7094,7 +7418,7 @@
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -7106,7 +7430,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -7126,7 +7450,7 @@
         <v>22</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -7146,7 +7470,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -7174,7 +7498,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7194,7 +7518,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7202,7 +7526,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -7217,7 +7541,7 @@
     </row>
     <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1240" s="11" t="s">
         <v>11</v>
@@ -7229,7 +7553,7 @@
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
       <c r="B1241" s="20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C1241" s="21"/>
     </row>
@@ -7249,7 +7573,7 @@
         <v>22</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1243" t="s">
         <v>5</v>
@@ -7269,7 +7593,7 @@
         <v>1.2</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1245" s="2" t="s">
         <v>14</v>
@@ -7289,10 +7613,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1247" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7317,7 +7641,7 @@
       </c>
       <c r="B1250" s="7"/>
       <c r="C1250" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7325,7 +7649,7 @@
         <v>4.2</v>
       </c>
       <c r="B1251" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1251" s="2" t="s">
         <v>6</v>
@@ -7337,7 +7661,7 @@
       </c>
       <c r="B1252" s="7"/>
       <c r="C1252" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7345,7 +7669,7 @@
         <v>5.2</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1253" s="2" t="s">
         <v>5</v>
@@ -7360,7 +7684,7 @@
     </row>
     <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B1299" s="11" t="s">
         <v>11</v>
@@ -7372,7 +7696,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
       <c r="B1300" s="20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C1300" s="21"/>
     </row>
@@ -7392,7 +7716,7 @@
         <v>22</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1302" t="s">
         <v>5</v>
@@ -7412,7 +7736,7 @@
         <v>1.2</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1304" s="2" t="s">
         <v>14</v>
@@ -7432,10 +7756,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1306" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7460,7 +7784,7 @@
       </c>
       <c r="B1309" s="7"/>
       <c r="C1309" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7468,7 +7792,7 @@
         <v>4.2</v>
       </c>
       <c r="B1310" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>6</v>
@@ -7480,7 +7804,7 @@
       </c>
       <c r="B1311" s="7"/>
       <c r="C1311" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7488,7 +7812,7 @@
         <v>5.2</v>
       </c>
       <c r="B1312" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>5</v>
@@ -7503,7 +7827,7 @@
     </row>
     <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B1358" s="11" t="s">
         <v>3</v>
@@ -7515,7 +7839,7 @@
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
       <c r="B1359" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C1359" s="21"/>
     </row>
@@ -7535,7 +7859,7 @@
         <v>22</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1361" t="s">
         <v>5</v>
@@ -7555,7 +7879,7 @@
         <v>1.2</v>
       </c>
       <c r="B1363" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1363" s="2" t="s">
         <v>6</v>
@@ -7583,7 +7907,7 @@
       </c>
       <c r="B1366" s="7"/>
       <c r="C1366" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7594,7 +7918,7 @@
         <v>7</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7609,7 +7933,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C1369" s="2" t="s">
         <v>20</v>
@@ -7626,7 +7950,7 @@
       </c>
       <c r="B1371" s="7"/>
       <c r="C1371" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7646,7 +7970,7 @@
       </c>
       <c r="B1373" s="7"/>
       <c r="C1373" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7654,7 +7978,7 @@
         <v>6.2</v>
       </c>
       <c r="B1374" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1374" s="2" t="s">
         <v>5</v>
@@ -7669,7 +7993,7 @@
     </row>
     <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1417" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B1417" s="11" t="s">
         <v>11</v>
@@ -7681,7 +8005,7 @@
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
       <c r="B1418" s="20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C1418" s="21"/>
     </row>
@@ -7701,7 +8025,7 @@
         <v>22</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1420" t="s">
         <v>5</v>
@@ -7721,10 +8045,10 @@
         <v>1.2</v>
       </c>
       <c r="B1422" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7741,7 +8065,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1424" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1424" s="2" t="s">
         <v>6</v>
@@ -7753,7 +8077,7 @@
       </c>
       <c r="B1425" s="7"/>
       <c r="C1425" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7764,7 +8088,7 @@
         <v>7</v>
       </c>
       <c r="C1426" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7773,7 +8097,7 @@
       </c>
       <c r="B1427" s="7"/>
       <c r="C1427" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7784,7 +8108,7 @@
         <v>23</v>
       </c>
       <c r="C1428" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7799,7 +8123,7 @@
         <v>5.2</v>
       </c>
       <c r="B1430" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1430" s="2" t="s">
         <v>5</v>
@@ -7814,7 +8138,7 @@
     </row>
     <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1476" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B1476" s="11" t="s">
         <v>11</v>
@@ -7826,7 +8150,7 @@
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="13"/>
       <c r="B1477" s="17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C1477" s="18"/>
     </row>
@@ -7846,7 +8170,7 @@
         <v>22</v>
       </c>
       <c r="B1479" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1479" t="s">
         <v>5</v>
@@ -7866,7 +8190,7 @@
         <v>1.2</v>
       </c>
       <c r="B1481" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1481" s="2" t="s">
         <v>26</v>
@@ -7884,10 +8208,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1483" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C1483" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7902,10 +8226,10 @@
         <v>3.2</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7914,7 +8238,7 @@
       </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7922,10 +8246,10 @@
         <v>4.2</v>
       </c>
       <c r="B1487" s="22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7945,7 +8269,7 @@
         <v>5.2</v>
       </c>
       <c r="B1490" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1490" s="2" t="s">
         <v>5</v>
@@ -7960,7 +8284,7 @@
     </row>
     <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1535" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B1535" s="11" t="s">
         <v>3</v>
@@ -7972,7 +8296,7 @@
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
       <c r="B1536" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1536" s="21"/>
     </row>
@@ -7992,7 +8316,7 @@
         <v>22</v>
       </c>
       <c r="B1538" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1538" t="s">
         <v>5</v>
@@ -8012,7 +8336,7 @@
         <v>1.2</v>
       </c>
       <c r="B1540" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1540" s="2" t="s">
         <v>6</v>
@@ -8024,7 +8348,7 @@
       </c>
       <c r="B1541" s="7"/>
       <c r="C1541" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8044,21 +8368,21 @@
       </c>
       <c r="B1543" s="7"/>
       <c r="C1543" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1544" s="3"/>
       <c r="B1544" s="7"/>
       <c r="C1544" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1545" s="3"/>
       <c r="B1545" s="7"/>
       <c r="C1545" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8069,7 +8393,7 @@
         <v>23</v>
       </c>
       <c r="C1546" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8084,7 +8408,7 @@
         <v>4.2</v>
       </c>
       <c r="B1548" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C1548" s="2" t="s">
         <v>6</v>
@@ -8101,7 +8425,7 @@
       </c>
       <c r="B1550" s="7"/>
       <c r="C1550" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8109,10 +8433,10 @@
         <v>5.2</v>
       </c>
       <c r="B1551" s="22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C1551" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8132,7 +8456,7 @@
         <v>6.2</v>
       </c>
       <c r="B1554" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1554" s="2" t="s">
         <v>5</v>
@@ -8147,7 +8471,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B1594" s="11" t="s">
         <v>11</v>
@@ -8159,7 +8483,7 @@
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
       <c r="B1595" s="20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C1595" s="21"/>
     </row>
@@ -8179,7 +8503,7 @@
         <v>22</v>
       </c>
       <c r="B1597" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1597" t="s">
         <v>5</v>
@@ -8199,7 +8523,7 @@
         <v>1.2</v>
       </c>
       <c r="B1599" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1599" s="2" t="s">
         <v>6</v>
@@ -8227,7 +8551,7 @@
       </c>
       <c r="B1602" s="7"/>
       <c r="C1602" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8247,7 +8571,7 @@
       </c>
       <c r="B1604" s="7"/>
       <c r="C1604" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8258,7 +8582,7 @@
         <v>23</v>
       </c>
       <c r="C1605" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8273,7 +8597,7 @@
         <v>5.2</v>
       </c>
       <c r="B1607" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1607" s="2" t="s">
         <v>5</v>
@@ -8288,7 +8612,7 @@
     </row>
     <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1653" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B1653" s="11" t="s">
         <v>12</v>
@@ -8300,7 +8624,7 @@
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="13"/>
       <c r="B1654" s="17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1654" s="18"/>
     </row>
@@ -8320,7 +8644,7 @@
         <v>22</v>
       </c>
       <c r="B1656" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1656" t="s">
         <v>5</v>
@@ -8340,7 +8664,7 @@
         <v>1.2</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1658" s="2" t="s">
         <v>26</v>
@@ -8352,7 +8676,7 @@
       </c>
       <c r="B1659" s="7"/>
       <c r="C1659" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="1660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8360,7 +8684,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1660" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1660" s="2" t="s">
         <v>5</v>
@@ -8375,7 +8699,7 @@
     </row>
     <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1712" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B1712" s="11" t="s">
         <v>12</v>
@@ -8407,7 +8731,7 @@
         <v>22</v>
       </c>
       <c r="B1715" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1715" t="s">
         <v>5</v>
@@ -8435,7 +8759,7 @@
       </c>
       <c r="B1718" s="7"/>
       <c r="C1718" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8443,7 +8767,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1719" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1719" s="2" t="s">
         <v>5</v>
@@ -8458,7 +8782,7 @@
     </row>
     <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1771" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B1771" s="11" t="s">
         <v>13</v>
@@ -8470,7 +8794,7 @@
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="13"/>
       <c r="B1772" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C1772" s="18"/>
     </row>
@@ -8490,7 +8814,7 @@
         <v>22</v>
       </c>
       <c r="B1774" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1774" t="s">
         <v>5</v>
@@ -8510,7 +8834,7 @@
         <v>1.2</v>
       </c>
       <c r="B1776" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1776" s="2" t="s">
         <v>14</v>
@@ -8530,10 +8854,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1778" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1778" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8562,7 +8886,7 @@
       </c>
       <c r="B1781" s="7"/>
       <c r="C1781" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8570,7 +8894,7 @@
         <v>4.2</v>
       </c>
       <c r="B1782" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1782" s="2" t="s">
         <v>5</v>
@@ -8585,7 +8909,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B1830" s="11" t="s">
         <v>3</v>
@@ -8597,7 +8921,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
       <c r="B1831" s="20" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C1831" s="21"/>
     </row>
@@ -8617,7 +8941,7 @@
         <v>22</v>
       </c>
       <c r="B1833" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1833" t="s">
         <v>5</v>
@@ -8637,7 +8961,7 @@
         <v>1.2</v>
       </c>
       <c r="B1835" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1835" s="2" t="s">
         <v>14</v>
@@ -8657,10 +8981,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1837" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1837" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8683,7 +9007,7 @@
       </c>
       <c r="B1840" s="7"/>
       <c r="C1840" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8691,10 +9015,10 @@
         <v>4.2</v>
       </c>
       <c r="B1841" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1841" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8709,10 +9033,10 @@
         <v>5.2</v>
       </c>
       <c r="B1843" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C1843" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8727,7 +9051,7 @@
         <v>6.2</v>
       </c>
       <c r="B1845" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1845" s="2" t="s">
         <v>5</v>
@@ -8742,7 +9066,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B1889" s="11" t="s">
         <v>12</v>
@@ -8774,7 +9098,7 @@
         <v>22</v>
       </c>
       <c r="B1892" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1892" t="s">
         <v>5</v>
@@ -8802,7 +9126,7 @@
       </c>
       <c r="B1895" s="7"/>
       <c r="C1895" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8810,7 +9134,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1896" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1896" s="2" t="s">
         <v>5</v>
@@ -8825,7 +9149,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B1948" s="11" t="s">
         <v>9</v>
@@ -8857,7 +9181,7 @@
         <v>22</v>
       </c>
       <c r="B1951" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1951" t="s">
         <v>5</v>
@@ -8877,7 +9201,7 @@
         <v>1.2</v>
       </c>
       <c r="B1953" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1953" s="2" t="s">
         <v>6</v>
@@ -8909,7 +9233,7 @@
         <v>3.2</v>
       </c>
       <c r="B1957" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C1957" s="2" t="s">
         <v>18</v>
@@ -8927,7 +9251,7 @@
         <v>4.2</v>
       </c>
       <c r="B1959" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C1959" s="2" t="s">
         <v>19</v>
@@ -8939,7 +9263,7 @@
       </c>
       <c r="B1960" s="7"/>
       <c r="C1960" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8961,10 +9285,10 @@
         <v>6.2</v>
       </c>
       <c r="B1963" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C1963" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8979,10 +9303,10 @@
         <v>7.2</v>
       </c>
       <c r="B1965" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C1965" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8997,7 +9321,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1967" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C1967" s="2" t="s">
         <v>5</v>
@@ -9012,7 +9336,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B2007" s="11" t="s">
         <v>13</v>
@@ -9024,7 +9348,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
       <c r="B2008" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C2008" s="21"/>
     </row>
@@ -9044,7 +9368,7 @@
         <v>22</v>
       </c>
       <c r="B2010" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2010" t="s">
         <v>5</v>
@@ -9064,7 +9388,7 @@
         <v>1.2</v>
       </c>
       <c r="B2012" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2012" s="2" t="s">
         <v>6</v>
@@ -9076,7 +9400,7 @@
       </c>
       <c r="B2013" s="7"/>
       <c r="C2013" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9096,7 +9420,7 @@
       </c>
       <c r="B2015" s="7"/>
       <c r="C2015" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9107,7 +9431,7 @@
         <v>23</v>
       </c>
       <c r="C2016" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9122,7 +9446,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2018" s="2" t="s">
         <v>5</v>
@@ -9137,10 +9461,10 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B2066" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2066" s="12" t="s">
         <v>16</v>
@@ -9149,7 +9473,7 @@
     <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2067" s="13"/>
       <c r="B2067" s="17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C2067" s="18"/>
     </row>
@@ -9169,7 +9493,7 @@
         <v>22</v>
       </c>
       <c r="B2069" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2069" t="s">
         <v>5</v>
@@ -9189,7 +9513,7 @@
         <v>1.2</v>
       </c>
       <c r="B2071" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2071" s="2" t="s">
         <v>6</v>
@@ -9201,7 +9525,7 @@
       </c>
       <c r="B2072" s="7"/>
       <c r="C2072" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9221,7 +9545,7 @@
       </c>
       <c r="B2074" s="7"/>
       <c r="C2074" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9243,7 +9567,7 @@
         <v>4.2</v>
       </c>
       <c r="B2077" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2077" s="2" t="s">
         <v>6</v>
@@ -9255,7 +9579,7 @@
       </c>
       <c r="B2078" s="7"/>
       <c r="C2078" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9271,14 +9595,14 @@
       </c>
       <c r="B2080" s="7"/>
       <c r="C2080" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2081" s="3"/>
       <c r="B2081" s="7"/>
       <c r="C2081" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9294,7 +9618,7 @@
       </c>
       <c r="B2083" s="7"/>
       <c r="C2083" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9302,7 +9626,7 @@
         <v>7.2</v>
       </c>
       <c r="B2084" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2084" s="2" t="s">
         <v>5</v>
@@ -9317,7 +9641,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B2125" s="11" t="s">
         <v>10</v>
@@ -9329,7 +9653,7 @@
     <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2126" s="13"/>
       <c r="B2126" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C2126" s="18"/>
     </row>
@@ -9349,7 +9673,7 @@
         <v>22</v>
       </c>
       <c r="B2128" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2128" t="s">
         <v>5</v>
@@ -9369,7 +9693,7 @@
         <v>1.2</v>
       </c>
       <c r="B2130" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2130" s="2" t="s">
         <v>6</v>
@@ -9381,7 +9705,7 @@
       </c>
       <c r="B2131" s="7"/>
       <c r="C2131" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9401,7 +9725,7 @@
       </c>
       <c r="B2133" s="7"/>
       <c r="C2133" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9409,7 +9733,7 @@
         <v>3.2</v>
       </c>
       <c r="B2134" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2134" s="2" t="s">
         <v>5</v>
@@ -9436,7 +9760,7 @@
     <row r="2185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2185" s="13"/>
       <c r="B2185" s="17" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C2185" s="18"/>
     </row>
@@ -9456,7 +9780,7 @@
         <v>22</v>
       </c>
       <c r="B2187" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2187" t="s">
         <v>5</v>
@@ -9476,7 +9800,7 @@
         <v>1.2</v>
       </c>
       <c r="B2189" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2189" s="2" t="s">
         <v>14</v>
@@ -9496,10 +9820,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2191" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2191" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9528,7 +9852,7 @@
       </c>
       <c r="B2194" s="7"/>
       <c r="C2194" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9536,7 +9860,7 @@
         <v>4.2</v>
       </c>
       <c r="B2195" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2195" s="2" t="s">
         <v>5</v>
@@ -9551,7 +9875,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B2243" s="11" t="s">
         <v>10</v>
@@ -9563,7 +9887,7 @@
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="13"/>
       <c r="B2244" s="17" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C2244" s="18"/>
     </row>
@@ -9583,7 +9907,7 @@
         <v>22</v>
       </c>
       <c r="B2246" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2246" t="s">
         <v>5</v>
@@ -9617,7 +9941,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2250" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2250" s="2" t="s">
         <v>6</v>
@@ -9629,7 +9953,7 @@
       </c>
       <c r="B2251" s="7"/>
       <c r="C2251" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9637,7 +9961,7 @@
         <v>3.2</v>
       </c>
       <c r="B2252" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2252" s="2" t="s">
         <v>5</v>
@@ -9664,7 +9988,7 @@
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
       <c r="B2303" s="20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C2303" s="21"/>
     </row>
@@ -9684,7 +10008,7 @@
         <v>22</v>
       </c>
       <c r="B2305" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2305" t="s">
         <v>5</v>
@@ -9704,7 +10028,7 @@
         <v>1.2</v>
       </c>
       <c r="B2307" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2307" s="2" t="s">
         <v>6</v>
@@ -9732,7 +10056,7 @@
       </c>
       <c r="B2310" s="7"/>
       <c r="C2310" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9743,7 +10067,7 @@
         <v>7</v>
       </c>
       <c r="C2311" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9758,7 +10082,7 @@
         <v>4.2</v>
       </c>
       <c r="B2313" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C2313" s="2" t="s">
         <v>20</v>
@@ -9781,7 +10105,7 @@
         <v>5.2</v>
       </c>
       <c r="B2316" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C2316" s="2" t="s">
         <v>6</v>
@@ -9793,7 +10117,7 @@
       </c>
       <c r="B2317" s="7"/>
       <c r="C2317" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9801,7 +10125,7 @@
         <v>6.2</v>
       </c>
       <c r="B2318" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2318" s="2" t="s">
         <v>5</v>
@@ -9816,7 +10140,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B2361" s="11" t="s">
         <v>12</v>
@@ -9848,7 +10172,7 @@
         <v>22</v>
       </c>
       <c r="B2364" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2364" t="s">
         <v>5</v>
@@ -9868,7 +10192,7 @@
         <v>1.2</v>
       </c>
       <c r="B2366" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2366" s="2" t="s">
         <v>6</v>
@@ -9880,7 +10204,7 @@
       </c>
       <c r="B2367" s="7"/>
       <c r="C2367" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9888,7 +10212,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2368" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2368" s="2" t="s">
         <v>5</v>
@@ -9915,7 +10239,7 @@
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
       <c r="B2421" s="20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C2421" s="21"/>
     </row>
@@ -9935,7 +10259,7 @@
         <v>22</v>
       </c>
       <c r="B2423" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2423" t="s">
         <v>5</v>
@@ -9955,7 +10279,7 @@
         <v>1.2</v>
       </c>
       <c r="B2425" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2425" s="2" t="s">
         <v>6</v>
@@ -9967,7 +10291,7 @@
       </c>
       <c r="B2426" s="7"/>
       <c r="C2426" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9978,7 +10302,7 @@
         <v>7</v>
       </c>
       <c r="C2427" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9993,7 +10317,7 @@
         <v>3.2</v>
       </c>
       <c r="B2429" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2429" s="2" t="s">
         <v>6</v>
@@ -10005,7 +10329,7 @@
       </c>
       <c r="B2430" s="7"/>
       <c r="C2430" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10016,7 +10340,7 @@
         <v>7</v>
       </c>
       <c r="C2431" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10025,7 +10349,7 @@
       </c>
       <c r="B2432" s="7"/>
       <c r="C2432" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10036,7 +10360,7 @@
         <v>23</v>
       </c>
       <c r="C2433" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10051,7 +10375,7 @@
         <v>6.2</v>
       </c>
       <c r="B2435" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2435" s="2" t="s">
         <v>5</v>
@@ -10066,7 +10390,7 @@
     </row>
     <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2479" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B2479" s="11" t="s">
         <v>11</v>
@@ -10078,7 +10402,7 @@
     <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2480" s="13"/>
       <c r="B2480" s="17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C2480" s="18"/>
     </row>
@@ -10098,7 +10422,7 @@
         <v>22</v>
       </c>
       <c r="B2482" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2482" t="s">
         <v>5</v>
@@ -10118,7 +10442,7 @@
         <v>1.2</v>
       </c>
       <c r="B2484" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2484" s="2" t="s">
         <v>14</v>
@@ -10138,10 +10462,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2486" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2486" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10158,7 +10482,7 @@
         <v>3.2</v>
       </c>
       <c r="B2488" s="7" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C2488" s="2" t="s">
         <v>6</v>
@@ -10170,14 +10494,14 @@
       </c>
       <c r="B2489" s="7"/>
       <c r="C2489" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2490" s="3"/>
       <c r="B2490" s="7"/>
       <c r="C2490" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10199,7 +10523,7 @@
         <v>5.2</v>
       </c>
       <c r="B2493" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2493" s="2" t="s">
         <v>5</v>
@@ -10214,7 +10538,7 @@
     </row>
     <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2538" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B2538" s="11" t="s">
         <v>13</v>
@@ -10226,7 +10550,7 @@
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="13"/>
       <c r="B2539" s="20" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C2539" s="21"/>
     </row>
@@ -10246,7 +10570,7 @@
         <v>22</v>
       </c>
       <c r="B2541" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2541" t="s">
         <v>5</v>
@@ -10266,7 +10590,7 @@
         <v>1.2</v>
       </c>
       <c r="B2543" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2543" s="2" t="s">
         <v>6</v>
@@ -10278,7 +10602,7 @@
       </c>
       <c r="B2544" s="7"/>
       <c r="C2544" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10298,7 +10622,7 @@
       </c>
       <c r="B2546" s="7"/>
       <c r="C2546" s="22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10314,7 +10638,7 @@
         <v>23</v>
       </c>
       <c r="C2548" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10329,7 +10653,7 @@
         <v>4.2</v>
       </c>
       <c r="B2550" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2550" s="2" t="s">
         <v>5</v>
@@ -10344,7 +10668,7 @@
     </row>
     <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2597" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B2597" s="11" t="s">
         <v>11</v>
@@ -10356,7 +10680,7 @@
     <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2598" s="13"/>
       <c r="B2598" s="20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C2598" s="21"/>
     </row>
@@ -10376,7 +10700,7 @@
         <v>22</v>
       </c>
       <c r="B2600" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2600" t="s">
         <v>5</v>
@@ -10396,7 +10720,7 @@
         <v>1.2</v>
       </c>
       <c r="B2602" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2602" s="2" t="s">
         <v>14</v>
@@ -10416,10 +10740,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2604" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2604" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10448,7 +10772,7 @@
       </c>
       <c r="B2607" s="7"/>
       <c r="C2607" s="22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10464,7 +10788,7 @@
         <v>23</v>
       </c>
       <c r="C2609" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10479,7 +10803,7 @@
         <v>5.2</v>
       </c>
       <c r="B2611" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2611" s="2" t="s">
         <v>5</v>
@@ -10494,7 +10818,7 @@
     </row>
     <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2656" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B2656" s="11" t="s">
         <v>13</v>
@@ -10526,7 +10850,7 @@
         <v>22</v>
       </c>
       <c r="B2659" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2659" t="s">
         <v>5</v>
@@ -10546,7 +10870,7 @@
         <v>1.2</v>
       </c>
       <c r="B2661" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2661" s="2" t="s">
         <v>26</v>
@@ -10564,10 +10888,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2663" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2663" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10576,7 +10900,7 @@
       </c>
       <c r="B2664" s="7"/>
       <c r="C2664" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10598,7 +10922,7 @@
         <v>4.2</v>
       </c>
       <c r="B2667" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2667" s="2" t="s">
         <v>5</v>
@@ -10613,10 +10937,10 @@
     </row>
     <row r="2715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2715" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B2715" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2715" s="12" t="s">
         <v>16</v>
@@ -10625,7 +10949,7 @@
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="13"/>
       <c r="B2716" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C2716" s="18"/>
     </row>
@@ -10645,7 +10969,7 @@
         <v>22</v>
       </c>
       <c r="B2718" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2718" t="s">
         <v>5</v>
@@ -10665,7 +10989,7 @@
         <v>1.2</v>
       </c>
       <c r="B2720" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2720" s="2" t="s">
         <v>6</v>
@@ -10677,7 +11001,7 @@
       </c>
       <c r="B2721" s="7"/>
       <c r="C2721" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10697,7 +11021,7 @@
       </c>
       <c r="B2723" s="7"/>
       <c r="C2723" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10719,7 +11043,7 @@
         <v>4.2</v>
       </c>
       <c r="B2726" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2726" s="2" t="s">
         <v>6</v>
@@ -10731,7 +11055,7 @@
       </c>
       <c r="B2727" s="7"/>
       <c r="C2727" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10747,14 +11071,14 @@
       </c>
       <c r="B2729" s="7"/>
       <c r="C2729" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="3"/>
       <c r="B2730" s="7"/>
       <c r="C2730" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10770,7 +11094,7 @@
       </c>
       <c r="B2732" s="7"/>
       <c r="C2732" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10778,7 +11102,7 @@
         <v>7.2</v>
       </c>
       <c r="B2733" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2733" s="2" t="s">
         <v>5</v>
@@ -10793,7 +11117,7 @@
     </row>
     <row r="2774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2774" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B2774" s="11" t="s">
         <v>13</v>
@@ -10805,7 +11129,7 @@
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="13"/>
       <c r="B2775" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C2775" s="18"/>
     </row>
@@ -10825,7 +11149,7 @@
         <v>22</v>
       </c>
       <c r="B2777" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2777" t="s">
         <v>5</v>
@@ -10837,7 +11161,7 @@
       </c>
       <c r="B2778" s="7"/>
       <c r="C2778" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10845,7 +11169,7 @@
         <v>1.2</v>
       </c>
       <c r="B2779" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2779" s="2" t="s">
         <v>6</v>
@@ -10857,7 +11181,7 @@
       </c>
       <c r="B2780" s="7"/>
       <c r="C2780" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10873,14 +11197,14 @@
       </c>
       <c r="B2782" s="7"/>
       <c r="C2782" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2783" s="3"/>
       <c r="B2783" s="7"/>
       <c r="C2783" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10896,7 +11220,7 @@
       </c>
       <c r="B2785" s="7"/>
       <c r="C2785" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10904,7 +11228,7 @@
         <v>4.2</v>
       </c>
       <c r="B2786" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2786" s="7" t="s">
         <v>5</v>
@@ -10922,7 +11246,7 @@
         <v>30</v>
       </c>
       <c r="B2833" s="11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C2833" s="12" t="s">
         <v>4</v>
@@ -10931,7 +11255,7 @@
     <row r="2834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2834" s="13"/>
       <c r="B2834" s="17" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C2834" s="18"/>
     </row>
@@ -10951,7 +11275,7 @@
         <v>22</v>
       </c>
       <c r="B2836" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2836" t="s">
         <v>5</v>
@@ -10963,7 +11287,7 @@
       </c>
       <c r="B2837" s="7"/>
       <c r="C2837" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10971,7 +11295,7 @@
         <v>1.2</v>
       </c>
       <c r="B2838" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2838" s="2" t="s">
         <v>6</v>
@@ -10983,7 +11307,7 @@
       </c>
       <c r="B2839" s="7"/>
       <c r="C2839" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10999,14 +11323,14 @@
       </c>
       <c r="B2841" s="7"/>
       <c r="C2841" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2842" s="3"/>
       <c r="B2842" s="7"/>
       <c r="C2842" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11022,7 +11346,7 @@
       </c>
       <c r="B2844" s="7"/>
       <c r="C2844" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11030,7 +11354,7 @@
         <v>4.2</v>
       </c>
       <c r="B2845" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2845" s="7" t="s">
         <v>5</v>
@@ -11045,7 +11369,7 @@
     </row>
     <row r="2892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2892" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B2892" s="11" t="s">
         <v>9</v>
@@ -11077,7 +11401,7 @@
         <v>22</v>
       </c>
       <c r="B2895" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2895" t="s">
         <v>5</v>
@@ -11097,7 +11421,7 @@
         <v>1.2</v>
       </c>
       <c r="B2897" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2897" s="2" t="s">
         <v>6</v>
@@ -11129,7 +11453,7 @@
         <v>3.2</v>
       </c>
       <c r="B2901" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C2901" s="2" t="s">
         <v>18</v>
@@ -11147,7 +11471,7 @@
         <v>4.2</v>
       </c>
       <c r="B2903" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2903" s="2" t="s">
         <v>19</v>
@@ -11159,7 +11483,7 @@
       </c>
       <c r="B2904" s="7"/>
       <c r="C2904" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11181,10 +11505,10 @@
         <v>6.2</v>
       </c>
       <c r="B2907" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C2907" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11199,10 +11523,10 @@
         <v>7.2</v>
       </c>
       <c r="B2909" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C2909" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11217,7 +11541,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B2911" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2911" s="7" t="s">
         <v>5</v>
@@ -11232,7 +11556,7 @@
     </row>
     <row r="2951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2951" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B2951" s="11" t="s">
         <v>13</v>
@@ -11244,7 +11568,7 @@
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="13"/>
       <c r="B2952" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C2952" s="21"/>
     </row>
@@ -11264,7 +11588,7 @@
         <v>22</v>
       </c>
       <c r="B2954" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2954" t="s">
         <v>5</v>
@@ -11284,7 +11608,7 @@
         <v>1.2</v>
       </c>
       <c r="B2956" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2956" s="2" t="s">
         <v>6</v>
@@ -11296,7 +11620,7 @@
       </c>
       <c r="B2957" s="7"/>
       <c r="C2957" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11316,7 +11640,7 @@
       </c>
       <c r="B2959" s="7"/>
       <c r="C2959" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11327,7 +11651,7 @@
         <v>23</v>
       </c>
       <c r="C2960" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11342,7 +11666,7 @@
         <v>4.2</v>
       </c>
       <c r="B2962" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2962" s="2" t="s">
         <v>5</v>
@@ -11357,10 +11681,10 @@
     </row>
     <row r="3010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3010" s="10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B3010" s="11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3010" s="12" t="s">
         <v>16</v>
@@ -11369,7 +11693,7 @@
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="13"/>
       <c r="B3011" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C3011" s="21"/>
     </row>
@@ -11389,7 +11713,7 @@
         <v>22</v>
       </c>
       <c r="B3013" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3013" t="s">
         <v>5</v>
@@ -11409,7 +11733,7 @@
         <v>1.2</v>
       </c>
       <c r="B3015" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3015" s="2" t="s">
         <v>6</v>
@@ -11421,7 +11745,7 @@
       </c>
       <c r="B3016" s="7"/>
       <c r="C3016" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11441,7 +11765,7 @@
       </c>
       <c r="B3018" s="7"/>
       <c r="C3018" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11463,7 +11787,7 @@
         <v>4.2</v>
       </c>
       <c r="B3021" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3021" s="2" t="s">
         <v>6</v>
@@ -11475,7 +11799,7 @@
       </c>
       <c r="B3022" s="7"/>
       <c r="C3022" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11491,14 +11815,14 @@
       </c>
       <c r="B3024" s="7"/>
       <c r="C3024" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3025" s="3"/>
       <c r="B3025" s="7"/>
       <c r="C3025" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11514,7 +11838,7 @@
       </c>
       <c r="B3027" s="7"/>
       <c r="C3027" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11522,7 +11846,7 @@
         <v>7.2</v>
       </c>
       <c r="B3028" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3028" s="2" t="s">
         <v>5</v>
@@ -11537,7 +11861,7 @@
     </row>
     <row r="3069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3069" s="10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B3069" s="11" t="s">
         <v>13</v>
@@ -11549,7 +11873,7 @@
     <row r="3070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3070" s="13"/>
       <c r="B3070" s="20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C3070" s="21"/>
     </row>
@@ -11569,7 +11893,7 @@
         <v>22</v>
       </c>
       <c r="B3072" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3072" t="s">
         <v>5</v>
@@ -11589,7 +11913,7 @@
         <v>1.2</v>
       </c>
       <c r="B3074" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3074" s="2" t="s">
         <v>6</v>
@@ -11617,7 +11941,7 @@
       </c>
       <c r="B3077" s="7"/>
       <c r="C3077" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11637,7 +11961,7 @@
       </c>
       <c r="B3079" s="7"/>
       <c r="C3079" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11645,7 +11969,7 @@
         <v>4.2</v>
       </c>
       <c r="B3080" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3080" s="2" t="s">
         <v>5</v>
@@ -11672,7 +11996,7 @@
     <row r="3129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3129" s="13"/>
       <c r="B3129" s="20" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C3129" s="21"/>
     </row>
@@ -11692,7 +12016,7 @@
         <v>22</v>
       </c>
       <c r="B3131" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3131" t="s">
         <v>5</v>
@@ -11712,7 +12036,7 @@
         <v>1.2</v>
       </c>
       <c r="B3133" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3133" s="2" t="s">
         <v>14</v>
@@ -11732,10 +12056,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3135" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3135" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11760,7 +12084,7 @@
       </c>
       <c r="B3138" s="7"/>
       <c r="C3138" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11768,7 +12092,7 @@
         <v>4.2</v>
       </c>
       <c r="B3139" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C3139" s="2" t="s">
         <v>6</v>
@@ -11780,7 +12104,7 @@
       </c>
       <c r="B3140" s="7"/>
       <c r="C3140" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11788,7 +12112,7 @@
         <v>5.2</v>
       </c>
       <c r="B3141" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3141" s="2" t="s">
         <v>5</v>
@@ -11803,7 +12127,7 @@
     </row>
     <row r="3187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3187" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3187" s="11" t="s">
         <v>11</v>
@@ -11815,7 +12139,7 @@
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="13"/>
       <c r="B3188" s="20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C3188" s="21"/>
     </row>
@@ -11835,7 +12159,7 @@
         <v>22</v>
       </c>
       <c r="B3190" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3190" t="s">
         <v>5</v>
@@ -11855,7 +12179,7 @@
         <v>1.2</v>
       </c>
       <c r="B3192" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3192" s="2" t="s">
         <v>14</v>
@@ -11875,10 +12199,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3194" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3194" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11903,7 +12227,7 @@
       </c>
       <c r="B3197" s="7"/>
       <c r="C3197" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11911,7 +12235,7 @@
         <v>4.2</v>
       </c>
       <c r="B3198" s="7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C3198" s="2" t="s">
         <v>6</v>
@@ -11923,7 +12247,7 @@
       </c>
       <c r="B3199" s="7"/>
       <c r="C3199" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11931,7 +12255,7 @@
         <v>5.2</v>
       </c>
       <c r="B3200" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3200" s="2" t="s">
         <v>5</v>
@@ -11958,7 +12282,7 @@
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="13"/>
       <c r="B3247" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C3247" s="21"/>
     </row>
@@ -11978,7 +12302,7 @@
         <v>22</v>
       </c>
       <c r="B3249" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3249" t="s">
         <v>5</v>
@@ -11998,7 +12322,7 @@
         <v>1.2</v>
       </c>
       <c r="B3251" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3251" s="2" t="s">
         <v>6</v>
@@ -12026,7 +12350,7 @@
       </c>
       <c r="B3254" s="7"/>
       <c r="C3254" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12037,7 +12361,7 @@
         <v>7</v>
       </c>
       <c r="C3255" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12052,7 +12376,7 @@
         <v>4.2</v>
       </c>
       <c r="B3257" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3257" s="2" t="s">
         <v>20</v>
@@ -12069,7 +12393,7 @@
       </c>
       <c r="B3259" s="7"/>
       <c r="C3259" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12089,7 +12413,7 @@
       </c>
       <c r="B3261" s="7"/>
       <c r="C3261" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12097,7 +12421,7 @@
         <v>6.2</v>
       </c>
       <c r="B3262" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3262" s="2" t="s">
         <v>5</v>
@@ -12112,7 +12436,7 @@
     </row>
     <row r="3305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3305" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B3305" s="11" t="s">
         <v>11</v>
@@ -12124,7 +12448,7 @@
     <row r="3306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3306" s="13"/>
       <c r="B3306" s="20" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C3306" s="21"/>
     </row>
@@ -12144,7 +12468,7 @@
         <v>22</v>
       </c>
       <c r="B3308" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3308" t="s">
         <v>5</v>
@@ -12164,10 +12488,10 @@
         <v>1.2</v>
       </c>
       <c r="B3310" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3310" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12184,7 +12508,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3312" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3312" s="2" t="s">
         <v>6</v>
@@ -12196,7 +12520,7 @@
       </c>
       <c r="B3313" s="7"/>
       <c r="C3313" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12207,7 +12531,7 @@
         <v>7</v>
       </c>
       <c r="C3314" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12216,7 +12540,7 @@
       </c>
       <c r="B3315" s="7"/>
       <c r="C3315" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12227,7 +12551,7 @@
         <v>23</v>
       </c>
       <c r="C3316" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12242,7 +12566,7 @@
         <v>5.2</v>
       </c>
       <c r="B3318" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3318" s="2" t="s">
         <v>5</v>
@@ -12269,7 +12593,7 @@
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="13"/>
       <c r="B3365" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C3365" s="21"/>
     </row>
@@ -12289,7 +12613,7 @@
         <v>22</v>
       </c>
       <c r="B3367" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3367" t="s">
         <v>5</v>
@@ -12309,7 +12633,7 @@
         <v>1.2</v>
       </c>
       <c r="B3369" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3369" s="2" t="s">
         <v>26</v>
@@ -12327,10 +12651,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3371" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C3371" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12345,10 +12669,10 @@
         <v>3.2</v>
       </c>
       <c r="B3373" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C3373" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12357,7 +12681,7 @@
       </c>
       <c r="B3374" s="7"/>
       <c r="C3374" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12365,10 +12689,10 @@
         <v>4.2</v>
       </c>
       <c r="B3375" s="22" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C3375" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12388,7 +12712,7 @@
         <v>5.2</v>
       </c>
       <c r="B3378" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3378" s="2" t="s">
         <v>5</v>
@@ -12403,7 +12727,7 @@
     </row>
     <row r="3423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3423" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B3423" s="11" t="s">
         <v>3</v>
@@ -12415,7 +12739,7 @@
     <row r="3424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3424" s="13"/>
       <c r="B3424" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C3424" s="21"/>
     </row>
@@ -12435,7 +12759,7 @@
         <v>22</v>
       </c>
       <c r="B3426" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3426" t="s">
         <v>5</v>
@@ -12455,7 +12779,7 @@
         <v>1.2</v>
       </c>
       <c r="B3428" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3428" s="2" t="s">
         <v>6</v>
@@ -12467,7 +12791,7 @@
       </c>
       <c r="B3429" s="7"/>
       <c r="C3429" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12487,21 +12811,21 @@
       </c>
       <c r="B3431" s="7"/>
       <c r="C3431" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3432" s="3"/>
       <c r="B3432" s="7"/>
       <c r="C3432" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3433" s="3"/>
       <c r="B3433" s="7"/>
       <c r="C3433" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12512,7 +12836,7 @@
         <v>23</v>
       </c>
       <c r="C3434" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12527,7 +12851,7 @@
         <v>4.2</v>
       </c>
       <c r="B3436" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3436" s="2" t="s">
         <v>6</v>
@@ -12544,7 +12868,7 @@
       </c>
       <c r="B3438" s="2"/>
       <c r="C3438" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12552,10 +12876,10 @@
         <v>5.2</v>
       </c>
       <c r="B3439" s="22" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C3439" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12575,7 +12899,7 @@
         <v>6.2</v>
       </c>
       <c r="B3442" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3442" s="2" t="s">
         <v>5</v>
@@ -12590,7 +12914,7 @@
     </row>
     <row r="3482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3482" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B3482" s="11" t="s">
         <v>11</v>
@@ -12602,7 +12926,7 @@
     <row r="3483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3483" s="13"/>
       <c r="B3483" s="20" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C3483" s="21"/>
     </row>
@@ -12622,7 +12946,7 @@
         <v>22</v>
       </c>
       <c r="B3485" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3485" t="s">
         <v>5</v>
@@ -12642,7 +12966,7 @@
         <v>1.2</v>
       </c>
       <c r="B3487" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3487" s="2" t="s">
         <v>6</v>
@@ -12670,7 +12994,7 @@
       </c>
       <c r="B3490" s="7"/>
       <c r="C3490" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12690,7 +13014,7 @@
       </c>
       <c r="B3492" s="7"/>
       <c r="C3492" s="22" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12706,7 +13030,7 @@
         <v>23</v>
       </c>
       <c r="C3494" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12721,7 +13045,7 @@
         <v>5.2</v>
       </c>
       <c r="B3496" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3496" s="2" t="s">
         <v>5</v>
@@ -12736,7 +13060,7 @@
     </row>
     <row r="3541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3541" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B3541" s="11" t="s">
         <v>12</v>
@@ -12748,7 +13072,7 @@
     <row r="3542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3542" s="13"/>
       <c r="B3542" s="17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C3542" s="18"/>
     </row>
@@ -12768,7 +13092,7 @@
         <v>22</v>
       </c>
       <c r="B3544" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3544" t="s">
         <v>5</v>
@@ -12788,7 +13112,7 @@
         <v>1.2</v>
       </c>
       <c r="B3546" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3546" s="2" t="s">
         <v>26</v>
@@ -12800,7 +13124,7 @@
       </c>
       <c r="B3547" s="7"/>
       <c r="C3547" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12808,7 +13132,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3548" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3548" s="2" t="s">
         <v>5</v>
@@ -12823,7 +13147,7 @@
     </row>
     <row r="3600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3600" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B3600" s="11" t="s">
         <v>12</v>
@@ -12855,7 +13179,7 @@
         <v>22</v>
       </c>
       <c r="B3603" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3603" t="s">
         <v>5</v>
@@ -12883,7 +13207,7 @@
       </c>
       <c r="B3606" s="7"/>
       <c r="C3606" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12891,7 +13215,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3607" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3607" s="2" t="s">
         <v>5</v>
@@ -12906,7 +13230,7 @@
     </row>
     <row r="3659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3659" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B3659" s="11" t="s">
         <v>10</v>
@@ -12918,7 +13242,7 @@
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="13"/>
       <c r="B3660" s="17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C3660" s="18"/>
     </row>
@@ -12938,7 +13262,7 @@
         <v>22</v>
       </c>
       <c r="B3662" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3662" t="s">
         <v>5</v>
@@ -12958,7 +13282,7 @@
         <v>1.2</v>
       </c>
       <c r="B3664" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3664" s="2" t="s">
         <v>6</v>
@@ -12970,7 +13294,7 @@
       </c>
       <c r="B3665" s="7"/>
       <c r="C3665" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12990,7 +13314,7 @@
       </c>
       <c r="B3667" s="7"/>
       <c r="C3667" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12998,7 +13322,7 @@
         <v>3.2</v>
       </c>
       <c r="B3668" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3668" s="2" t="s">
         <v>5</v>
@@ -13013,7 +13337,7 @@
     </row>
     <row r="3718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3718" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B3718" s="11" t="s">
         <v>9</v>
@@ -13025,7 +13349,7 @@
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="13"/>
       <c r="B3719" s="17" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C3719" s="18"/>
     </row>
@@ -13045,7 +13369,7 @@
         <v>22</v>
       </c>
       <c r="B3721" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3721" t="s">
         <v>5</v>
@@ -13065,7 +13389,7 @@
         <v>1.2</v>
       </c>
       <c r="B3723" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3723" s="2" t="s">
         <v>14</v>
@@ -13085,10 +13409,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3725" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3725" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13119,7 +13443,7 @@
         <v>4.2</v>
       </c>
       <c r="B3729" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C3729" s="2" t="s">
         <v>18</v>
@@ -13137,7 +13461,7 @@
         <v>5.2</v>
       </c>
       <c r="B3731" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3731" s="2" t="s">
         <v>19</v>
@@ -13149,7 +13473,7 @@
       </c>
       <c r="B3732" s="7"/>
       <c r="C3732" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13165,7 +13489,7 @@
       </c>
       <c r="B3734" s="7"/>
       <c r="C3734" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13181,7 +13505,7 @@
       </c>
       <c r="B3736" s="7"/>
       <c r="C3736" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13189,7 +13513,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B3737" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3737" s="2" t="s">
         <v>5</v>
@@ -13204,7 +13528,7 @@
     </row>
     <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3777" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B3777" s="11" t="s">
         <v>12</v>
@@ -13236,7 +13560,7 @@
         <v>22</v>
       </c>
       <c r="B3780" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3780" t="s">
         <v>5</v>
@@ -13264,7 +13588,7 @@
       </c>
       <c r="B3783" s="7"/>
       <c r="C3783" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13272,7 +13596,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3784" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3784" s="2" t="s">
         <v>5</v>
@@ -13285,8 +13609,1253 @@
       <c r="B3785" s="9"/>
       <c r="C3785" s="8"/>
     </row>
+    <row r="3836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3836" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3836" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3836" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3837" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3837" s="13"/>
+      <c r="B3837" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3837" s="18"/>
+    </row>
+    <row r="3838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3838" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3838" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3838" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3839" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3839" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3839" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3840" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3840" s="7"/>
+      <c r="C3840" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3841" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3841" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3841" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3842" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3842" s="7"/>
+      <c r="C3842" s="2"/>
+    </row>
+    <row r="3843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3843" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3843" s="7"/>
+      <c r="C3843" s="2"/>
+    </row>
+    <row r="3844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3844" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3844" s="7"/>
+      <c r="C3844" s="2"/>
+    </row>
+    <row r="3845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3845" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3845" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3845" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3846" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3846" s="7"/>
+      <c r="C3846" s="2"/>
+    </row>
+    <row r="3847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3847" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3847" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3847" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3848" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3848" s="7"/>
+      <c r="C3848" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3849" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3849" s="7"/>
+      <c r="C3849" s="2"/>
+    </row>
+    <row r="3850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3850" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3850" s="7"/>
+      <c r="C3850" s="2"/>
+    </row>
+    <row r="3851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3851" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3851" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3851" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3852" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B3852" s="7"/>
+      <c r="C3852" s="2"/>
+    </row>
+    <row r="3853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3853" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B3853" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3853" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3854" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B3854" s="7"/>
+      <c r="C3854" s="2"/>
+    </row>
+    <row r="3855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3855" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B3855" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3855" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3856" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3856" s="9"/>
+      <c r="C3856" s="8"/>
+    </row>
+    <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3895" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3895" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3895" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3896" s="13"/>
+      <c r="B3896" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3896" s="21"/>
+    </row>
+    <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3897" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3897" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3897" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3898" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3898" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3898" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3899" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3899" s="7"/>
+      <c r="C3899" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3900" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3900" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3900" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3901" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3901" s="7"/>
+      <c r="C3901" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3902" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3902" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3902" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3903" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3903" s="7"/>
+      <c r="C3903" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3904" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3904" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3904" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3905" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3905" s="7"/>
+      <c r="C3905" s="2"/>
+    </row>
+    <row r="3906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3906" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3906" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3906" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3907" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3907" s="9"/>
+      <c r="C3907" s="8"/>
+    </row>
+    <row r="3954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3954" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3954" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3954" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3955" s="13"/>
+      <c r="B3955" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3955" s="21"/>
+    </row>
+    <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3956" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3956" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3956" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3957" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3957" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3957" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3958" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3958" s="7"/>
+      <c r="C3958" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3959" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B3959" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3959" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3960" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B3960" s="7"/>
+      <c r="C3960" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3961" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B3961" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3961" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3962" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B3962" s="7"/>
+      <c r="C3962" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3963" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B3963" s="7"/>
+      <c r="C3963" s="2"/>
+    </row>
+    <row r="3964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3964" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B3964" s="7"/>
+      <c r="C3964" s="2"/>
+    </row>
+    <row r="3965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3965" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B3965" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3965" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3966" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3966" s="7"/>
+      <c r="C3966" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3967" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B3967" s="7"/>
+      <c r="C3967" s="2"/>
+    </row>
+    <row r="3968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3968" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B3968" s="7"/>
+      <c r="C3968" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3969" s="3"/>
+      <c r="B3969" s="7"/>
+      <c r="C3969" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3970" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B3970" s="7"/>
+      <c r="C3970" s="2"/>
+    </row>
+    <row r="3971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3971" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B3971" s="7"/>
+      <c r="C3971" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3972" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B3972" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3972" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3973" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3973" s="9"/>
+      <c r="C3973" s="8"/>
+    </row>
+    <row r="4013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4013" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4013" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4013" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4014" s="13"/>
+      <c r="B4014" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4014" s="18"/>
+    </row>
+    <row r="4015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4015" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4015" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4015" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4016" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4016" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4016" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4017" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4017" s="7"/>
+      <c r="C4017" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4018" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4018" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4018" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4019" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4019" s="7"/>
+      <c r="C4019" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4020" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4020" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4020" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4021" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4021" s="7"/>
+      <c r="C4021" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4022" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4022" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4022" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4023" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4023" s="9"/>
+      <c r="C4023" s="8"/>
+    </row>
+    <row r="4072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4072" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4072" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4072" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4073" s="13"/>
+      <c r="B4073" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4073" s="18"/>
+    </row>
+    <row r="4074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4074" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4074" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4074" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4075" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4075" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4075" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4076" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4076" s="7"/>
+      <c r="C4076" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4077" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4077" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4077" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4078" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4078" s="7"/>
+      <c r="C4078" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4079" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4079" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4079" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4080" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4080" s="7"/>
+      <c r="C4080" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4081" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4081" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4081" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4082" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4082" s="7"/>
+      <c r="C4082" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4083" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4083" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4083" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4084" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4084" s="9"/>
+      <c r="C4084" s="8"/>
+    </row>
+    <row r="4131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4131" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4131" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4131" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4132" s="13"/>
+      <c r="B4132" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4132" s="18"/>
+    </row>
+    <row r="4133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4133" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4133" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4133" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4134" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4134" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4135" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4135" s="7"/>
+      <c r="C4135" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4136" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4136" s="7"/>
+      <c r="C4136" s="2"/>
+    </row>
+    <row r="4137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4137" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4137" s="7"/>
+      <c r="C4137" s="2"/>
+    </row>
+    <row r="4138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4138" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4138" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4139" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4139" s="7"/>
+      <c r="C4139" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4140" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4140" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4140" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4141" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4141" s="9"/>
+      <c r="C4141" s="8"/>
+    </row>
+    <row r="4190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4190" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4190" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4190" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4191" s="13"/>
+      <c r="B4191" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4191" s="21"/>
+    </row>
+    <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4192" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4192" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4192" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4193" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4193" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4193" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4194" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4194" s="7"/>
+      <c r="C4194" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4195" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4195" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4195" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4196" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4196" s="7"/>
+      <c r="C4196" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4197" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4197" s="7"/>
+      <c r="C4197" s="2"/>
+    </row>
+    <row r="4198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4198" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4198" s="7"/>
+      <c r="C4198" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4199" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4199" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4199" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4200" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4200" s="7"/>
+      <c r="C4200" s="2"/>
+    </row>
+    <row r="4201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4201" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4201" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4201" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4202" s="3"/>
+      <c r="B4202" s="22"/>
+      <c r="C4202" s="2"/>
+    </row>
+    <row r="4203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4203" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4203" s="7"/>
+      <c r="C4203" s="2"/>
+    </row>
+    <row r="4204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4204" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4204" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4204" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4205" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4205" s="7"/>
+      <c r="C4205" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="4206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4206" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4206" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4206" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4207" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4207" s="9"/>
+      <c r="C4207" s="8"/>
+    </row>
+    <row r="4249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4249" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4249" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4249" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4250" s="13"/>
+      <c r="B4250" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4250" s="18"/>
+    </row>
+    <row r="4251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4251" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4251" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4251" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4252" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4252" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4252" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4253" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4253" s="7"/>
+      <c r="C4253" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4254" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4254" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4254" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4255" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4255" s="7"/>
+      <c r="C4255" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4256" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4256" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4256" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4257" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4257" s="9"/>
+      <c r="C4257" s="8"/>
+    </row>
+    <row r="4308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4308" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4308" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4308" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4309" s="13"/>
+      <c r="B4309" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4309" s="21"/>
+    </row>
+    <row r="4310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4310" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4310" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4310" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4311" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4311" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4311" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4312" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4312" s="7"/>
+      <c r="C4312" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4313" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4313" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4313" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4314" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4314" s="7"/>
+      <c r="C4314" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4315" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4315" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4315" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4316" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4316" s="7"/>
+      <c r="C4316" s="2"/>
+    </row>
+    <row r="4317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4317" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4317" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4317" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4318" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4318" s="7"/>
+      <c r="C4318" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4319" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4319" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4319" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4320" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4320" s="7"/>
+      <c r="C4320" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4321" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4321" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4321" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4322" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4322" s="7"/>
+      <c r="C4322" s="2"/>
+    </row>
+    <row r="4323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4323" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4323" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4323" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4324" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4324" s="9"/>
+      <c r="C4324" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="50">
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4201:B4202"/>
+    <mergeCell ref="B4309:C4309"/>
     <mergeCell ref="B2952:C2952"/>
     <mergeCell ref="B3011:C3011"/>
     <mergeCell ref="B3070:C3070"/>
@@ -13332,6 +14901,7 @@
     <mergeCell ref="B3439:B3440"/>
     <mergeCell ref="B3483:C3483"/>
     <mergeCell ref="C3492:C3493"/>
+    <mergeCell ref="B3896:C3896"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD7E6E0-94AB-4BBE-8A4E-84013FAD3C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD98C2C3-AFBB-4A71-8761-3933F587C725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$4366</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$5515</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2121" uniqueCount="259">
   <si>
     <t>Implied</t>
   </si>
@@ -221,6 +221,18 @@
     <t>EOR (49)</t>
   </si>
   <si>
+    <t>BVC (50)</t>
+  </si>
+  <si>
+    <t>EOR (55)</t>
+  </si>
+  <si>
+    <t>EOR (57)</t>
+  </si>
+  <si>
+    <t>EOR (59)</t>
+  </si>
+  <si>
     <t>Store as Address.H.</t>
   </si>
   <si>
@@ -3993,6 +4005,672 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> flag = !Operand0.</t>
+    </r>
+  </si>
+  <si>
+    <t>AND1 (4A)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag &amp;= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
+    </r>
+  </si>
+  <si>
+    <t>LSR (4B)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; 01). Operand &gt;&gt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>LSR (4C)</t>
+  </si>
+  <si>
+    <t>PUSH (4D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Push </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> onto stack.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCLR1 (4E)</t>
+  </si>
+  <si>
+    <r>
+      <t>Operand = (Operand &amp; ~</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <t>PCALL (4F)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.L = Address.L, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.H = $FF.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $40) == $00.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL5 (51)</t>
+  </si>
+  <si>
+    <t>Read $FFD4</t>
+  </si>
+  <si>
+    <t>Read $FFD5</t>
+  </si>
+  <si>
+    <t>CLR1 (52)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$04) | $00.</t>
+  </si>
+  <si>
+    <t>BBC2 (53)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 2)) == (0 &lt;&lt; 2).</t>
+  </si>
+  <si>
+    <t>EOR (54)</t>
+  </si>
+  <si>
+    <t>EOR (56)</t>
+  </si>
+  <si>
+    <t>EOR (58)</t>
+  </si>
+  <si>
+    <t>CMPW (5A)</t>
+  </si>
+  <si>
+    <t>Direct Page d (Read 16)</t>
+  </si>
+  <si>
+    <t>Store as Operand16.L.</t>
+  </si>
+  <si>
+    <t>Store as Operand16.H.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tmp = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Operand16. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &gt;= 0), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &amp; $8000), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = !Tmp.</t>
+    </r>
+  </si>
+  <si>
+    <t>LSR (5B)</t>
+  </si>
+  <si>
+    <t>LSR (5C)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; 01). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt;= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>MOV (5D)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
     </r>
   </si>
 </sst>
@@ -4561,7 +5239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C4324"/>
+  <dimension ref="A1:C5496"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -4573,7 +5251,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>12</v>
@@ -4605,7 +5283,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>5</v>
@@ -4639,7 +5317,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>5</v>
@@ -4654,7 +5332,7 @@
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>9</v>
@@ -4686,7 +5364,7 @@
         <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>5</v>
@@ -4706,7 +5384,7 @@
         <v>1.2</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>6</v>
@@ -4738,7 +5416,7 @@
         <v>3.2</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>18</v>
@@ -4756,7 +5434,7 @@
         <v>4.2</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>19</v>
@@ -4768,7 +5446,7 @@
       </c>
       <c r="B72" s="7"/>
       <c r="C72" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4790,10 +5468,10 @@
         <v>6.2</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4808,10 +5486,10 @@
         <v>7.2</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4826,7 +5504,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>5</v>
@@ -4841,7 +5519,7 @@
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B119" s="11" t="s">
         <v>13</v>
@@ -4853,7 +5531,7 @@
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C120" s="21"/>
     </row>
@@ -4873,7 +5551,7 @@
         <v>22</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C122" t="s">
         <v>5</v>
@@ -4893,7 +5571,7 @@
         <v>1.2</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>6</v>
@@ -4905,7 +5583,7 @@
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4925,7 +5603,7 @@
       </c>
       <c r="B127" s="7"/>
       <c r="C127" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4936,7 +5614,7 @@
         <v>23</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4951,7 +5629,7 @@
         <v>4.2</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>5</v>
@@ -4966,10 +5644,10 @@
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>16</v>
@@ -4978,7 +5656,7 @@
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
       <c r="B179" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C179" s="21"/>
     </row>
@@ -4998,7 +5676,7 @@
         <v>22</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -5018,7 +5696,7 @@
         <v>1.2</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>6</v>
@@ -5030,7 +5708,7 @@
       </c>
       <c r="B184" s="7"/>
       <c r="C184" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5050,7 +5728,7 @@
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5072,7 +5750,7 @@
         <v>4.2</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>6</v>
@@ -5084,7 +5762,7 @@
       </c>
       <c r="B190" s="7"/>
       <c r="C190" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5100,14 +5778,14 @@
       </c>
       <c r="B192" s="7"/>
       <c r="C192" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="7"/>
       <c r="C193" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5123,7 +5801,7 @@
       </c>
       <c r="B195" s="7"/>
       <c r="C195" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5131,7 +5809,7 @@
         <v>7.2</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>5</v>
@@ -5146,7 +5824,7 @@
     </row>
     <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>10</v>
@@ -5158,7 +5836,7 @@
     <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="13"/>
       <c r="B238" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C238" s="18"/>
     </row>
@@ -5178,7 +5856,7 @@
         <v>22</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -5198,7 +5876,7 @@
         <v>1.2</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>6</v>
@@ -5210,7 +5888,7 @@
       </c>
       <c r="B243" s="7"/>
       <c r="C243" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5230,7 +5908,7 @@
       </c>
       <c r="B245" s="7"/>
       <c r="C245" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5238,7 +5916,7 @@
         <v>3.2</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>5</v>
@@ -5253,7 +5931,7 @@
     </row>
     <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>13</v>
@@ -5265,7 +5943,7 @@
     <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="13"/>
       <c r="B297" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C297" s="18"/>
     </row>
@@ -5285,7 +5963,7 @@
         <v>22</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -5305,7 +5983,7 @@
         <v>1.2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>14</v>
@@ -5325,10 +6003,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5357,7 +6035,7 @@
       </c>
       <c r="B306" s="7"/>
       <c r="C306" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5365,7 +6043,7 @@
         <v>4.2</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>5</v>
@@ -5380,7 +6058,7 @@
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>10</v>
@@ -5392,7 +6070,7 @@
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
       <c r="B356" s="20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C356" s="21"/>
     </row>
@@ -5412,7 +6090,7 @@
         <v>22</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C358" t="s">
         <v>5</v>
@@ -5446,7 +6124,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B362" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>6</v>
@@ -5458,7 +6136,7 @@
       </c>
       <c r="B363" s="7"/>
       <c r="C363" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5466,7 +6144,7 @@
         <v>3.2</v>
       </c>
       <c r="B364" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>5</v>
@@ -5481,7 +6159,7 @@
     </row>
     <row r="414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>3</v>
@@ -5493,7 +6171,7 @@
     <row r="415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="13"/>
       <c r="B415" s="17" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C415" s="18"/>
     </row>
@@ -5513,7 +6191,7 @@
         <v>22</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C417" t="s">
         <v>5</v>
@@ -5533,7 +6211,7 @@
         <v>1.2</v>
       </c>
       <c r="B419" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C419" s="2" t="s">
         <v>6</v>
@@ -5561,7 +6239,7 @@
       </c>
       <c r="B422" s="7"/>
       <c r="C422" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5572,7 +6250,7 @@
         <v>7</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5587,7 +6265,7 @@
         <v>4.2</v>
       </c>
       <c r="B425" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C425" s="2" t="s">
         <v>20</v>
@@ -5610,7 +6288,7 @@
         <v>5.2</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C428" s="2" t="s">
         <v>6</v>
@@ -5622,7 +6300,7 @@
       </c>
       <c r="B429" s="7"/>
       <c r="C429" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5630,7 +6308,7 @@
         <v>6.2</v>
       </c>
       <c r="B430" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C430" s="2" t="s">
         <v>5</v>
@@ -5645,7 +6323,7 @@
     </row>
     <row r="473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>12</v>
@@ -5677,7 +6355,7 @@
         <v>22</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C476" t="s">
         <v>5</v>
@@ -5697,7 +6375,7 @@
         <v>1.2</v>
       </c>
       <c r="B478" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C478" s="2" t="s">
         <v>6</v>
@@ -5709,7 +6387,7 @@
       </c>
       <c r="B479" s="7"/>
       <c r="C479" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5717,7 +6395,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B480" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C480" s="2" t="s">
         <v>5</v>
@@ -5732,7 +6410,7 @@
     </row>
     <row r="532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>3</v>
@@ -5744,7 +6422,7 @@
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
       <c r="B533" s="20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C533" s="21"/>
     </row>
@@ -5764,7 +6442,7 @@
         <v>22</v>
       </c>
       <c r="B535" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C535" t="s">
         <v>5</v>
@@ -5784,7 +6462,7 @@
         <v>1.2</v>
       </c>
       <c r="B537" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C537" s="2" t="s">
         <v>6</v>
@@ -5796,7 +6474,7 @@
       </c>
       <c r="B538" s="7"/>
       <c r="C538" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5807,7 +6485,7 @@
         <v>7</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5822,7 +6500,7 @@
         <v>3.2</v>
       </c>
       <c r="B541" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C541" s="2" t="s">
         <v>6</v>
@@ -5834,7 +6512,7 @@
       </c>
       <c r="B542" s="7"/>
       <c r="C542" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5845,7 +6523,7 @@
         <v>7</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5854,7 +6532,7 @@
       </c>
       <c r="B544" s="7"/>
       <c r="C544" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5865,7 +6543,7 @@
         <v>23</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5880,7 +6558,7 @@
         <v>6.2</v>
       </c>
       <c r="B547" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>5</v>
@@ -5895,7 +6573,7 @@
     </row>
     <row r="591" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B591" s="11" t="s">
         <v>11</v>
@@ -5907,7 +6585,7 @@
     <row r="592" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="13"/>
       <c r="B592" s="17" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C592" s="18"/>
     </row>
@@ -5927,7 +6605,7 @@
         <v>22</v>
       </c>
       <c r="B594" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C594" t="s">
         <v>5</v>
@@ -5947,7 +6625,7 @@
         <v>1.2</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C596" s="2" t="s">
         <v>14</v>
@@ -5967,10 +6645,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5987,7 +6665,7 @@
         <v>3.2</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C600" s="2" t="s">
         <v>6</v>
@@ -5999,14 +6677,14 @@
       </c>
       <c r="B601" s="7"/>
       <c r="C601" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="3"/>
       <c r="B602" s="7"/>
       <c r="C602" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6028,7 +6706,7 @@
         <v>5.2</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C605" s="2" t="s">
         <v>5</v>
@@ -6043,7 +6721,7 @@
     </row>
     <row r="650" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B650" s="11" t="s">
         <v>13</v>
@@ -6055,7 +6733,7 @@
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
       <c r="B651" s="20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C651" s="21"/>
     </row>
@@ -6075,7 +6753,7 @@
         <v>22</v>
       </c>
       <c r="B653" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -6095,7 +6773,7 @@
         <v>1.2</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>6</v>
@@ -6107,7 +6785,7 @@
       </c>
       <c r="B656" s="7"/>
       <c r="C656" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6127,7 +6805,7 @@
       </c>
       <c r="B658" s="7"/>
       <c r="C658" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6138,7 +6816,7 @@
         <v>23</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6153,7 +6831,7 @@
         <v>4.2</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C661" s="2" t="s">
         <v>5</v>
@@ -6168,7 +6846,7 @@
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B709" s="11" t="s">
         <v>11</v>
@@ -6180,7 +6858,7 @@
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
       <c r="B710" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C710" s="21"/>
     </row>
@@ -6200,7 +6878,7 @@
         <v>22</v>
       </c>
       <c r="B712" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -6220,7 +6898,7 @@
         <v>1.2</v>
       </c>
       <c r="B714" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>14</v>
@@ -6240,10 +6918,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B716" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="717" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6272,7 +6950,7 @@
       </c>
       <c r="B719" s="7"/>
       <c r="C719" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="720" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6283,7 +6961,7 @@
         <v>23</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6298,7 +6976,7 @@
         <v>5.2</v>
       </c>
       <c r="B722" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C722" s="2" t="s">
         <v>5</v>
@@ -6313,7 +6991,7 @@
     </row>
     <row r="768" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B768" s="11" t="s">
         <v>13</v>
@@ -6345,7 +7023,7 @@
         <v>22</v>
       </c>
       <c r="B771" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C771" t="s">
         <v>5</v>
@@ -6365,7 +7043,7 @@
         <v>1.2</v>
       </c>
       <c r="B773" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C773" s="2" t="s">
         <v>26</v>
@@ -6383,10 +7061,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B775" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="776" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6395,7 +7073,7 @@
       </c>
       <c r="B776" s="7"/>
       <c r="C776" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6417,7 +7095,7 @@
         <v>4.2</v>
       </c>
       <c r="B779" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C779" s="2" t="s">
         <v>5</v>
@@ -6432,7 +7110,7 @@
     </row>
     <row r="827" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B827" s="11" t="s">
         <v>3</v>
@@ -6444,7 +7122,7 @@
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
       <c r="B828" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C828" s="21"/>
     </row>
@@ -6464,7 +7142,7 @@
         <v>22</v>
       </c>
       <c r="B830" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C830" t="s">
         <v>5</v>
@@ -6484,7 +7162,7 @@
         <v>1.2</v>
       </c>
       <c r="B832" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C832" s="2" t="s">
         <v>14</v>
@@ -6504,10 +7182,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B834" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C834" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="835" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6536,21 +7214,21 @@
       </c>
       <c r="B837" s="7"/>
       <c r="C837" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="3"/>
       <c r="B838" s="7"/>
       <c r="C838" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="3"/>
       <c r="B839" s="7"/>
       <c r="C839" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6579,7 +7257,7 @@
         <v>23</v>
       </c>
       <c r="C842" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6594,7 +7272,7 @@
         <v>6.2</v>
       </c>
       <c r="B844" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C844" s="2" t="s">
         <v>5</v>
@@ -6609,7 +7287,7 @@
     </row>
     <row r="886" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B886" s="11" t="s">
         <v>9</v>
@@ -6641,7 +7319,7 @@
         <v>22</v>
       </c>
       <c r="B889" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C889" t="s">
         <v>5</v>
@@ -6661,7 +7339,7 @@
         <v>1.2</v>
       </c>
       <c r="B891" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C891" s="2" t="s">
         <v>26</v>
@@ -6679,7 +7357,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B893" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C893" s="2" t="s">
         <v>18</v>
@@ -6697,7 +7375,7 @@
         <v>3.2</v>
       </c>
       <c r="B895" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C895" s="2" t="s">
         <v>19</v>
@@ -6715,10 +7393,10 @@
         <v>4.2</v>
       </c>
       <c r="B897" s="7" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C897" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6727,7 +7405,7 @@
       </c>
       <c r="B898" s="7"/>
       <c r="C898" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6749,10 +7427,10 @@
         <v>6.2</v>
       </c>
       <c r="B901" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C901" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6767,10 +7445,10 @@
         <v>7.2</v>
       </c>
       <c r="B903" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C903" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6785,7 +7463,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B905" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C905" s="2" t="s">
         <v>5</v>
@@ -6803,7 +7481,7 @@
         <v>15</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C945" s="12" t="s">
         <v>4</v>
@@ -6832,7 +7510,7 @@
         <v>22</v>
       </c>
       <c r="B948" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C948" t="s">
         <v>5</v>
@@ -6844,7 +7522,7 @@
       </c>
       <c r="B949" s="7"/>
       <c r="C949" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6852,7 +7530,7 @@
         <v>1.2</v>
       </c>
       <c r="B950" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C950" s="2" t="s">
         <v>6</v>
@@ -6864,7 +7542,7 @@
       </c>
       <c r="B951" s="7"/>
       <c r="C951" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6880,14 +7558,14 @@
       </c>
       <c r="B953" s="7"/>
       <c r="C953" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="3"/>
       <c r="B954" s="7"/>
       <c r="C954" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6903,7 +7581,7 @@
       </c>
       <c r="B956" s="7"/>
       <c r="C956" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6911,7 +7589,7 @@
         <v>4.2</v>
       </c>
       <c r="B957" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C957" s="2" t="s">
         <v>5</v>
@@ -6926,7 +7604,7 @@
     </row>
     <row r="1004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B1004" s="11" t="s">
         <v>9</v>
@@ -6958,7 +7636,7 @@
         <v>22</v>
       </c>
       <c r="B1007" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1007" t="s">
         <v>5</v>
@@ -6978,7 +7656,7 @@
         <v>1.2</v>
       </c>
       <c r="B1009" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1009" s="2" t="s">
         <v>6</v>
@@ -7010,7 +7688,7 @@
         <v>3.2</v>
       </c>
       <c r="B1013" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C1013" s="2" t="s">
         <v>18</v>
@@ -7028,7 +7706,7 @@
         <v>4.2</v>
       </c>
       <c r="B1015" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C1015" s="2" t="s">
         <v>19</v>
@@ -7040,7 +7718,7 @@
       </c>
       <c r="B1016" s="7"/>
       <c r="C1016" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7062,10 +7740,10 @@
         <v>6.2</v>
       </c>
       <c r="B1019" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C1019" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7080,10 +7758,10 @@
         <v>7.2</v>
       </c>
       <c r="B1021" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C1021" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7098,7 +7776,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1023" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1023" s="2" t="s">
         <v>5</v>
@@ -7113,7 +7791,7 @@
     </row>
     <row r="1063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1063" s="11" t="s">
         <v>13</v>
@@ -7125,7 +7803,7 @@
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
       <c r="B1064" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C1064" s="21"/>
     </row>
@@ -7145,7 +7823,7 @@
         <v>22</v>
       </c>
       <c r="B1066" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1066" t="s">
         <v>5</v>
@@ -7165,7 +7843,7 @@
         <v>1.2</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1068" s="2" t="s">
         <v>6</v>
@@ -7177,7 +7855,7 @@
       </c>
       <c r="B1069" s="7"/>
       <c r="C1069" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7197,7 +7875,7 @@
       </c>
       <c r="B1071" s="7"/>
       <c r="C1071" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="1072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7208,7 +7886,7 @@
         <v>23</v>
       </c>
       <c r="C1072" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7223,7 +7901,7 @@
         <v>4.2</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1074" s="2" t="s">
         <v>5</v>
@@ -7238,10 +7916,10 @@
     </row>
     <row r="1122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1122" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B1122" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C1122" s="12" t="s">
         <v>16</v>
@@ -7250,7 +7928,7 @@
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
       <c r="B1123" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C1123" s="21"/>
     </row>
@@ -7270,7 +7948,7 @@
         <v>22</v>
       </c>
       <c r="B1125" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1125" t="s">
         <v>5</v>
@@ -7290,7 +7968,7 @@
         <v>1.2</v>
       </c>
       <c r="B1127" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1127" s="2" t="s">
         <v>6</v>
@@ -7302,7 +7980,7 @@
       </c>
       <c r="B1128" s="7"/>
       <c r="C1128" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7322,7 +8000,7 @@
       </c>
       <c r="B1130" s="7"/>
       <c r="C1130" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7344,7 +8022,7 @@
         <v>4.2</v>
       </c>
       <c r="B1133" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1133" s="2" t="s">
         <v>6</v>
@@ -7356,7 +8034,7 @@
       </c>
       <c r="B1134" s="7"/>
       <c r="C1134" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7372,14 +8050,14 @@
       </c>
       <c r="B1136" s="7"/>
       <c r="C1136" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1137" s="3"/>
       <c r="B1137" s="7"/>
       <c r="C1137" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7395,7 +8073,7 @@
       </c>
       <c r="B1139" s="7"/>
       <c r="C1139" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7403,7 +8081,7 @@
         <v>7.2</v>
       </c>
       <c r="B1140" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1140" s="2" t="s">
         <v>5</v>
@@ -7418,7 +8096,7 @@
     </row>
     <row r="1181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1181" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B1181" s="11" t="s">
         <v>13</v>
@@ -7430,7 +8108,7 @@
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
       <c r="B1182" s="20" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C1182" s="21"/>
     </row>
@@ -7450,7 +8128,7 @@
         <v>22</v>
       </c>
       <c r="B1184" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1184" t="s">
         <v>5</v>
@@ -7470,7 +8148,7 @@
         <v>1.2</v>
       </c>
       <c r="B1186" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1186" s="2" t="s">
         <v>6</v>
@@ -7498,7 +8176,7 @@
       </c>
       <c r="B1189" s="7"/>
       <c r="C1189" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7518,7 +8196,7 @@
       </c>
       <c r="B1191" s="7"/>
       <c r="C1191" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7526,7 +8204,7 @@
         <v>4.2</v>
       </c>
       <c r="B1192" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1192" s="2" t="s">
         <v>5</v>
@@ -7541,7 +8219,7 @@
     </row>
     <row r="1240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B1240" s="11" t="s">
         <v>11</v>
@@ -7553,7 +8231,7 @@
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
       <c r="B1241" s="20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C1241" s="21"/>
     </row>
@@ -7573,7 +8251,7 @@
         <v>22</v>
       </c>
       <c r="B1243" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1243" t="s">
         <v>5</v>
@@ -7593,7 +8271,7 @@
         <v>1.2</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1245" s="2" t="s">
         <v>14</v>
@@ -7613,10 +8291,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1247" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7641,7 +8319,7 @@
       </c>
       <c r="B1250" s="7"/>
       <c r="C1250" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7649,7 +8327,7 @@
         <v>4.2</v>
       </c>
       <c r="B1251" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1251" s="2" t="s">
         <v>6</v>
@@ -7661,7 +8339,7 @@
       </c>
       <c r="B1252" s="7"/>
       <c r="C1252" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7669,7 +8347,7 @@
         <v>5.2</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1253" s="2" t="s">
         <v>5</v>
@@ -7684,7 +8362,7 @@
     </row>
     <row r="1299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B1299" s="11" t="s">
         <v>11</v>
@@ -7696,7 +8374,7 @@
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
       <c r="B1300" s="20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C1300" s="21"/>
     </row>
@@ -7716,7 +8394,7 @@
         <v>22</v>
       </c>
       <c r="B1302" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1302" t="s">
         <v>5</v>
@@ -7736,7 +8414,7 @@
         <v>1.2</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1304" s="2" t="s">
         <v>14</v>
@@ -7756,10 +8434,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1306" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7784,7 +8462,7 @@
       </c>
       <c r="B1309" s="7"/>
       <c r="C1309" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7792,7 +8470,7 @@
         <v>4.2</v>
       </c>
       <c r="B1310" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1310" s="2" t="s">
         <v>6</v>
@@ -7804,7 +8482,7 @@
       </c>
       <c r="B1311" s="7"/>
       <c r="C1311" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7812,7 +8490,7 @@
         <v>5.2</v>
       </c>
       <c r="B1312" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1312" s="2" t="s">
         <v>5</v>
@@ -7827,7 +8505,7 @@
     </row>
     <row r="1358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1358" s="10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B1358" s="11" t="s">
         <v>3</v>
@@ -7839,7 +8517,7 @@
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
       <c r="B1359" s="20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C1359" s="21"/>
     </row>
@@ -7859,7 +8537,7 @@
         <v>22</v>
       </c>
       <c r="B1361" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1361" t="s">
         <v>5</v>
@@ -7879,7 +8557,7 @@
         <v>1.2</v>
       </c>
       <c r="B1363" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1363" s="2" t="s">
         <v>6</v>
@@ -7907,7 +8585,7 @@
       </c>
       <c r="B1366" s="7"/>
       <c r="C1366" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7918,7 +8596,7 @@
         <v>7</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7933,7 +8611,7 @@
         <v>4.2</v>
       </c>
       <c r="B1369" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1369" s="2" t="s">
         <v>20</v>
@@ -7950,7 +8628,7 @@
       </c>
       <c r="B1371" s="7"/>
       <c r="C1371" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7970,7 +8648,7 @@
       </c>
       <c r="B1373" s="7"/>
       <c r="C1373" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7978,7 +8656,7 @@
         <v>6.2</v>
       </c>
       <c r="B1374" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1374" s="2" t="s">
         <v>5</v>
@@ -7993,7 +8671,7 @@
     </row>
     <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1417" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B1417" s="11" t="s">
         <v>11</v>
@@ -8005,7 +8683,7 @@
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
       <c r="B1418" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C1418" s="21"/>
     </row>
@@ -8025,7 +8703,7 @@
         <v>22</v>
       </c>
       <c r="B1420" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1420" t="s">
         <v>5</v>
@@ -8045,10 +8723,10 @@
         <v>1.2</v>
       </c>
       <c r="B1422" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8065,7 +8743,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1424" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1424" s="2" t="s">
         <v>6</v>
@@ -8077,7 +8755,7 @@
       </c>
       <c r="B1425" s="7"/>
       <c r="C1425" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8088,7 +8766,7 @@
         <v>7</v>
       </c>
       <c r="C1426" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8097,7 +8775,7 @@
       </c>
       <c r="B1427" s="7"/>
       <c r="C1427" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8108,7 +8786,7 @@
         <v>23</v>
       </c>
       <c r="C1428" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8123,7 +8801,7 @@
         <v>5.2</v>
       </c>
       <c r="B1430" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1430" s="2" t="s">
         <v>5</v>
@@ -8138,7 +8816,7 @@
     </row>
     <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1476" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B1476" s="11" t="s">
         <v>11</v>
@@ -8150,7 +8828,7 @@
     <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1477" s="13"/>
       <c r="B1477" s="17" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C1477" s="18"/>
     </row>
@@ -8170,7 +8848,7 @@
         <v>22</v>
       </c>
       <c r="B1479" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1479" t="s">
         <v>5</v>
@@ -8190,7 +8868,7 @@
         <v>1.2</v>
       </c>
       <c r="B1481" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1481" s="2" t="s">
         <v>26</v>
@@ -8208,10 +8886,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1483" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C1483" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8226,10 +8904,10 @@
         <v>3.2</v>
       </c>
       <c r="B1485" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8238,7 +8916,7 @@
       </c>
       <c r="B1486" s="7"/>
       <c r="C1486" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8246,10 +8924,10 @@
         <v>4.2</v>
       </c>
       <c r="B1487" s="22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8269,7 +8947,7 @@
         <v>5.2</v>
       </c>
       <c r="B1490" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1490" s="2" t="s">
         <v>5</v>
@@ -8284,7 +8962,7 @@
     </row>
     <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1535" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B1535" s="11" t="s">
         <v>3</v>
@@ -8296,7 +8974,7 @@
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
       <c r="B1536" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C1536" s="21"/>
     </row>
@@ -8316,7 +8994,7 @@
         <v>22</v>
       </c>
       <c r="B1538" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1538" t="s">
         <v>5</v>
@@ -8336,7 +9014,7 @@
         <v>1.2</v>
       </c>
       <c r="B1540" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1540" s="2" t="s">
         <v>6</v>
@@ -8348,7 +9026,7 @@
       </c>
       <c r="B1541" s="7"/>
       <c r="C1541" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8368,21 +9046,21 @@
       </c>
       <c r="B1543" s="7"/>
       <c r="C1543" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1544" s="3"/>
       <c r="B1544" s="7"/>
       <c r="C1544" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1545" s="3"/>
       <c r="B1545" s="7"/>
       <c r="C1545" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8393,7 +9071,7 @@
         <v>23</v>
       </c>
       <c r="C1546" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8408,7 +9086,7 @@
         <v>4.2</v>
       </c>
       <c r="B1548" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C1548" s="2" t="s">
         <v>6</v>
@@ -8425,7 +9103,7 @@
       </c>
       <c r="B1550" s="7"/>
       <c r="C1550" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="1551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8433,10 +9111,10 @@
         <v>5.2</v>
       </c>
       <c r="B1551" s="22" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C1551" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8456,7 +9134,7 @@
         <v>6.2</v>
       </c>
       <c r="B1554" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1554" s="2" t="s">
         <v>5</v>
@@ -8471,7 +9149,7 @@
     </row>
     <row r="1594" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1594" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B1594" s="11" t="s">
         <v>11</v>
@@ -8483,7 +9161,7 @@
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
       <c r="B1595" s="20" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C1595" s="21"/>
     </row>
@@ -8503,7 +9181,7 @@
         <v>22</v>
       </c>
       <c r="B1597" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1597" t="s">
         <v>5</v>
@@ -8523,7 +9201,7 @@
         <v>1.2</v>
       </c>
       <c r="B1599" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1599" s="2" t="s">
         <v>6</v>
@@ -8551,7 +9229,7 @@
       </c>
       <c r="B1602" s="7"/>
       <c r="C1602" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8571,7 +9249,7 @@
       </c>
       <c r="B1604" s="7"/>
       <c r="C1604" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8582,7 +9260,7 @@
         <v>23</v>
       </c>
       <c r="C1605" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8597,7 +9275,7 @@
         <v>5.2</v>
       </c>
       <c r="B1607" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1607" s="2" t="s">
         <v>5</v>
@@ -8612,7 +9290,7 @@
     </row>
     <row r="1653" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1653" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B1653" s="11" t="s">
         <v>12</v>
@@ -8624,7 +9302,7 @@
     <row r="1654" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1654" s="13"/>
       <c r="B1654" s="17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C1654" s="18"/>
     </row>
@@ -8644,7 +9322,7 @@
         <v>22</v>
       </c>
       <c r="B1656" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1656" t="s">
         <v>5</v>
@@ -8664,7 +9342,7 @@
         <v>1.2</v>
       </c>
       <c r="B1658" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1658" s="2" t="s">
         <v>26</v>
@@ -8676,7 +9354,7 @@
       </c>
       <c r="B1659" s="7"/>
       <c r="C1659" s="2" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="1660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8684,7 +9362,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1660" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1660" s="2" t="s">
         <v>5</v>
@@ -8699,7 +9377,7 @@
     </row>
     <row r="1712" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1712" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B1712" s="11" t="s">
         <v>12</v>
@@ -8731,7 +9409,7 @@
         <v>22</v>
       </c>
       <c r="B1715" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1715" t="s">
         <v>5</v>
@@ -8759,7 +9437,7 @@
       </c>
       <c r="B1718" s="7"/>
       <c r="C1718" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="1719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8767,7 +9445,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1719" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1719" s="2" t="s">
         <v>5</v>
@@ -8782,7 +9460,7 @@
     </row>
     <row r="1771" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1771" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B1771" s="11" t="s">
         <v>13</v>
@@ -8794,7 +9472,7 @@
     <row r="1772" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1772" s="13"/>
       <c r="B1772" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C1772" s="18"/>
     </row>
@@ -8814,7 +9492,7 @@
         <v>22</v>
       </c>
       <c r="B1774" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1774" t="s">
         <v>5</v>
@@ -8834,7 +9512,7 @@
         <v>1.2</v>
       </c>
       <c r="B1776" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1776" s="2" t="s">
         <v>14</v>
@@ -8854,10 +9532,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1778" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1778" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8886,7 +9564,7 @@
       </c>
       <c r="B1781" s="7"/>
       <c r="C1781" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8894,7 +9572,7 @@
         <v>4.2</v>
       </c>
       <c r="B1782" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1782" s="2" t="s">
         <v>5</v>
@@ -8909,7 +9587,7 @@
     </row>
     <row r="1830" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1830" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B1830" s="11" t="s">
         <v>3</v>
@@ -8921,7 +9599,7 @@
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
       <c r="B1831" s="20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C1831" s="21"/>
     </row>
@@ -8941,7 +9619,7 @@
         <v>22</v>
       </c>
       <c r="B1833" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1833" t="s">
         <v>5</v>
@@ -8961,7 +9639,7 @@
         <v>1.2</v>
       </c>
       <c r="B1835" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1835" s="2" t="s">
         <v>14</v>
@@ -8981,10 +9659,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1837" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1837" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9007,7 +9685,7 @@
       </c>
       <c r="B1840" s="7"/>
       <c r="C1840" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9015,10 +9693,10 @@
         <v>4.2</v>
       </c>
       <c r="B1841" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1841" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9033,10 +9711,10 @@
         <v>5.2</v>
       </c>
       <c r="B1843" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C1843" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9051,7 +9729,7 @@
         <v>6.2</v>
       </c>
       <c r="B1845" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1845" s="2" t="s">
         <v>5</v>
@@ -9066,7 +9744,7 @@
     </row>
     <row r="1889" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1889" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B1889" s="11" t="s">
         <v>12</v>
@@ -9098,7 +9776,7 @@
         <v>22</v>
       </c>
       <c r="B1892" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1892" t="s">
         <v>5</v>
@@ -9126,7 +9804,7 @@
       </c>
       <c r="B1895" s="7"/>
       <c r="C1895" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="1896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9134,7 +9812,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B1896" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1896" s="2" t="s">
         <v>5</v>
@@ -9149,7 +9827,7 @@
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1948" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B1948" s="11" t="s">
         <v>9</v>
@@ -9181,7 +9859,7 @@
         <v>22</v>
       </c>
       <c r="B1951" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1951" t="s">
         <v>5</v>
@@ -9201,7 +9879,7 @@
         <v>1.2</v>
       </c>
       <c r="B1953" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1953" s="2" t="s">
         <v>6</v>
@@ -9233,7 +9911,7 @@
         <v>3.2</v>
       </c>
       <c r="B1957" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C1957" s="2" t="s">
         <v>18</v>
@@ -9251,7 +9929,7 @@
         <v>4.2</v>
       </c>
       <c r="B1959" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C1959" s="2" t="s">
         <v>19</v>
@@ -9263,7 +9941,7 @@
       </c>
       <c r="B1960" s="7"/>
       <c r="C1960" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9285,10 +9963,10 @@
         <v>6.2</v>
       </c>
       <c r="B1963" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C1963" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9303,10 +9981,10 @@
         <v>7.2</v>
       </c>
       <c r="B1965" s="7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C1965" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9321,7 +9999,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B1967" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1967" s="2" t="s">
         <v>5</v>
@@ -9336,7 +10014,7 @@
     </row>
     <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2007" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B2007" s="11" t="s">
         <v>13</v>
@@ -9348,7 +10026,7 @@
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
       <c r="B2008" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C2008" s="21"/>
     </row>
@@ -9368,7 +10046,7 @@
         <v>22</v>
       </c>
       <c r="B2010" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2010" t="s">
         <v>5</v>
@@ -9388,7 +10066,7 @@
         <v>1.2</v>
       </c>
       <c r="B2012" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2012" s="2" t="s">
         <v>6</v>
@@ -9400,7 +10078,7 @@
       </c>
       <c r="B2013" s="7"/>
       <c r="C2013" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9420,7 +10098,7 @@
       </c>
       <c r="B2015" s="7"/>
       <c r="C2015" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9431,7 +10109,7 @@
         <v>23</v>
       </c>
       <c r="C2016" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9446,7 +10124,7 @@
         <v>4.2</v>
       </c>
       <c r="B2018" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2018" s="2" t="s">
         <v>5</v>
@@ -9461,10 +10139,10 @@
     </row>
     <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2066" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B2066" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C2066" s="12" t="s">
         <v>16</v>
@@ -9473,7 +10151,7 @@
     <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2067" s="13"/>
       <c r="B2067" s="17" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C2067" s="18"/>
     </row>
@@ -9493,7 +10171,7 @@
         <v>22</v>
       </c>
       <c r="B2069" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2069" t="s">
         <v>5</v>
@@ -9513,7 +10191,7 @@
         <v>1.2</v>
       </c>
       <c r="B2071" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2071" s="2" t="s">
         <v>6</v>
@@ -9525,7 +10203,7 @@
       </c>
       <c r="B2072" s="7"/>
       <c r="C2072" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9545,7 +10223,7 @@
       </c>
       <c r="B2074" s="7"/>
       <c r="C2074" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9567,7 +10245,7 @@
         <v>4.2</v>
       </c>
       <c r="B2077" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2077" s="2" t="s">
         <v>6</v>
@@ -9579,7 +10257,7 @@
       </c>
       <c r="B2078" s="7"/>
       <c r="C2078" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9595,14 +10273,14 @@
       </c>
       <c r="B2080" s="7"/>
       <c r="C2080" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2081" s="3"/>
       <c r="B2081" s="7"/>
       <c r="C2081" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9618,7 +10296,7 @@
       </c>
       <c r="B2083" s="7"/>
       <c r="C2083" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9626,7 +10304,7 @@
         <v>7.2</v>
       </c>
       <c r="B2084" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2084" s="2" t="s">
         <v>5</v>
@@ -9641,7 +10319,7 @@
     </row>
     <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2125" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B2125" s="11" t="s">
         <v>10</v>
@@ -9653,7 +10331,7 @@
     <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2126" s="13"/>
       <c r="B2126" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C2126" s="18"/>
     </row>
@@ -9673,7 +10351,7 @@
         <v>22</v>
       </c>
       <c r="B2128" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2128" t="s">
         <v>5</v>
@@ -9693,7 +10371,7 @@
         <v>1.2</v>
       </c>
       <c r="B2130" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2130" s="2" t="s">
         <v>6</v>
@@ -9705,7 +10383,7 @@
       </c>
       <c r="B2131" s="7"/>
       <c r="C2131" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9725,7 +10403,7 @@
       </c>
       <c r="B2133" s="7"/>
       <c r="C2133" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9733,7 +10411,7 @@
         <v>3.2</v>
       </c>
       <c r="B2134" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2134" s="2" t="s">
         <v>5</v>
@@ -9760,7 +10438,7 @@
     <row r="2185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2185" s="13"/>
       <c r="B2185" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C2185" s="18"/>
     </row>
@@ -9780,7 +10458,7 @@
         <v>22</v>
       </c>
       <c r="B2187" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2187" t="s">
         <v>5</v>
@@ -9800,7 +10478,7 @@
         <v>1.2</v>
       </c>
       <c r="B2189" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2189" s="2" t="s">
         <v>14</v>
@@ -9820,10 +10498,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2191" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2191" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9852,7 +10530,7 @@
       </c>
       <c r="B2194" s="7"/>
       <c r="C2194" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9860,7 +10538,7 @@
         <v>4.2</v>
       </c>
       <c r="B2195" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2195" s="2" t="s">
         <v>5</v>
@@ -9875,7 +10553,7 @@
     </row>
     <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2243" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B2243" s="11" t="s">
         <v>10</v>
@@ -9887,7 +10565,7 @@
     <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2244" s="13"/>
       <c r="B2244" s="17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C2244" s="18"/>
     </row>
@@ -9907,7 +10585,7 @@
         <v>22</v>
       </c>
       <c r="B2246" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2246" t="s">
         <v>5</v>
@@ -9941,7 +10619,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2250" s="7" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C2250" s="2" t="s">
         <v>6</v>
@@ -9953,7 +10631,7 @@
       </c>
       <c r="B2251" s="7"/>
       <c r="C2251" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9961,7 +10639,7 @@
         <v>3.2</v>
       </c>
       <c r="B2252" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2252" s="2" t="s">
         <v>5</v>
@@ -9988,7 +10666,7 @@
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
       <c r="B2303" s="20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C2303" s="21"/>
     </row>
@@ -10008,7 +10686,7 @@
         <v>22</v>
       </c>
       <c r="B2305" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2305" t="s">
         <v>5</v>
@@ -10028,7 +10706,7 @@
         <v>1.2</v>
       </c>
       <c r="B2307" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2307" s="2" t="s">
         <v>6</v>
@@ -10056,7 +10734,7 @@
       </c>
       <c r="B2310" s="7"/>
       <c r="C2310" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10067,7 +10745,7 @@
         <v>7</v>
       </c>
       <c r="C2311" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10082,7 +10760,7 @@
         <v>4.2</v>
       </c>
       <c r="B2313" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C2313" s="2" t="s">
         <v>20</v>
@@ -10105,7 +10783,7 @@
         <v>5.2</v>
       </c>
       <c r="B2316" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2316" s="2" t="s">
         <v>6</v>
@@ -10117,7 +10795,7 @@
       </c>
       <c r="B2317" s="7"/>
       <c r="C2317" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10125,7 +10803,7 @@
         <v>6.2</v>
       </c>
       <c r="B2318" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2318" s="2" t="s">
         <v>5</v>
@@ -10140,7 +10818,7 @@
     </row>
     <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2361" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B2361" s="11" t="s">
         <v>12</v>
@@ -10172,7 +10850,7 @@
         <v>22</v>
       </c>
       <c r="B2364" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2364" t="s">
         <v>5</v>
@@ -10192,7 +10870,7 @@
         <v>1.2</v>
       </c>
       <c r="B2366" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2366" s="2" t="s">
         <v>6</v>
@@ -10204,7 +10882,7 @@
       </c>
       <c r="B2367" s="7"/>
       <c r="C2367" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10212,7 +10890,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2368" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2368" s="2" t="s">
         <v>5</v>
@@ -10239,7 +10917,7 @@
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
       <c r="B2421" s="20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C2421" s="21"/>
     </row>
@@ -10259,7 +10937,7 @@
         <v>22</v>
       </c>
       <c r="B2423" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2423" t="s">
         <v>5</v>
@@ -10279,7 +10957,7 @@
         <v>1.2</v>
       </c>
       <c r="B2425" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2425" s="2" t="s">
         <v>6</v>
@@ -10291,7 +10969,7 @@
       </c>
       <c r="B2426" s="7"/>
       <c r="C2426" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10302,7 +10980,7 @@
         <v>7</v>
       </c>
       <c r="C2427" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10317,7 +10995,7 @@
         <v>3.2</v>
       </c>
       <c r="B2429" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2429" s="2" t="s">
         <v>6</v>
@@ -10329,7 +11007,7 @@
       </c>
       <c r="B2430" s="7"/>
       <c r="C2430" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10340,7 +11018,7 @@
         <v>7</v>
       </c>
       <c r="C2431" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10349,7 +11027,7 @@
       </c>
       <c r="B2432" s="7"/>
       <c r="C2432" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10360,7 +11038,7 @@
         <v>23</v>
       </c>
       <c r="C2433" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10375,7 +11053,7 @@
         <v>6.2</v>
       </c>
       <c r="B2435" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2435" s="2" t="s">
         <v>5</v>
@@ -10390,7 +11068,7 @@
     </row>
     <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2479" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B2479" s="11" t="s">
         <v>11</v>
@@ -10402,7 +11080,7 @@
     <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2480" s="13"/>
       <c r="B2480" s="17" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C2480" s="18"/>
     </row>
@@ -10422,7 +11100,7 @@
         <v>22</v>
       </c>
       <c r="B2482" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2482" t="s">
         <v>5</v>
@@ -10442,7 +11120,7 @@
         <v>1.2</v>
       </c>
       <c r="B2484" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2484" s="2" t="s">
         <v>14</v>
@@ -10462,10 +11140,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2486" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2486" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10482,7 +11160,7 @@
         <v>3.2</v>
       </c>
       <c r="B2488" s="7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C2488" s="2" t="s">
         <v>6</v>
@@ -10494,14 +11172,14 @@
       </c>
       <c r="B2489" s="7"/>
       <c r="C2489" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2490" s="3"/>
       <c r="B2490" s="7"/>
       <c r="C2490" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10523,7 +11201,7 @@
         <v>5.2</v>
       </c>
       <c r="B2493" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2493" s="2" t="s">
         <v>5</v>
@@ -10538,7 +11216,7 @@
     </row>
     <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2538" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B2538" s="11" t="s">
         <v>13</v>
@@ -10550,7 +11228,7 @@
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="13"/>
       <c r="B2539" s="20" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C2539" s="21"/>
     </row>
@@ -10570,7 +11248,7 @@
         <v>22</v>
       </c>
       <c r="B2541" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2541" t="s">
         <v>5</v>
@@ -10590,7 +11268,7 @@
         <v>1.2</v>
       </c>
       <c r="B2543" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2543" s="2" t="s">
         <v>6</v>
@@ -10602,7 +11280,7 @@
       </c>
       <c r="B2544" s="7"/>
       <c r="C2544" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10622,7 +11300,7 @@
       </c>
       <c r="B2546" s="7"/>
       <c r="C2546" s="22" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10638,7 +11316,7 @@
         <v>23</v>
       </c>
       <c r="C2548" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10653,7 +11331,7 @@
         <v>4.2</v>
       </c>
       <c r="B2550" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2550" s="2" t="s">
         <v>5</v>
@@ -10668,7 +11346,7 @@
     </row>
     <row r="2597" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2597" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B2597" s="11" t="s">
         <v>11</v>
@@ -10680,7 +11358,7 @@
     <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2598" s="13"/>
       <c r="B2598" s="20" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C2598" s="21"/>
     </row>
@@ -10700,7 +11378,7 @@
         <v>22</v>
       </c>
       <c r="B2600" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2600" t="s">
         <v>5</v>
@@ -10720,7 +11398,7 @@
         <v>1.2</v>
       </c>
       <c r="B2602" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2602" s="2" t="s">
         <v>14</v>
@@ -10740,10 +11418,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2604" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2604" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10772,7 +11450,7 @@
       </c>
       <c r="B2607" s="7"/>
       <c r="C2607" s="22" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10788,7 +11466,7 @@
         <v>23</v>
       </c>
       <c r="C2609" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10803,7 +11481,7 @@
         <v>5.2</v>
       </c>
       <c r="B2611" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2611" s="2" t="s">
         <v>5</v>
@@ -10818,7 +11496,7 @@
     </row>
     <row r="2656" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2656" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B2656" s="11" t="s">
         <v>13</v>
@@ -10850,7 +11528,7 @@
         <v>22</v>
       </c>
       <c r="B2659" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C2659" t="s">
         <v>5</v>
@@ -10870,7 +11548,7 @@
         <v>1.2</v>
       </c>
       <c r="B2661" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2661" s="2" t="s">
         <v>26</v>
@@ -10888,10 +11566,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B2663" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2663" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10900,7 +11578,7 @@
       </c>
       <c r="B2664" s="7"/>
       <c r="C2664" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10922,7 +11600,7 @@
         <v>4.2</v>
       </c>
       <c r="B2667" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2667" s="2" t="s">
         <v>5</v>
@@ -10937,10 +11615,10 @@
     </row>
     <row r="2715" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2715" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B2715" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C2715" s="12" t="s">
         <v>16</v>
@@ -10949,7 +11627,7 @@
     <row r="2716" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2716" s="13"/>
       <c r="B2716" s="17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C2716" s="18"/>
     </row>
@@ -10969,7 +11647,7 @@
         <v>22</v>
       </c>
       <c r="B2718" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2718" t="s">
         <v>5</v>
@@ -10989,7 +11667,7 @@
         <v>1.2</v>
       </c>
       <c r="B2720" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2720" s="2" t="s">
         <v>6</v>
@@ -11001,7 +11679,7 @@
       </c>
       <c r="B2721" s="7"/>
       <c r="C2721" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11021,7 +11699,7 @@
       </c>
       <c r="B2723" s="7"/>
       <c r="C2723" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11043,7 +11721,7 @@
         <v>4.2</v>
       </c>
       <c r="B2726" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2726" s="2" t="s">
         <v>6</v>
@@ -11055,7 +11733,7 @@
       </c>
       <c r="B2727" s="7"/>
       <c r="C2727" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11071,14 +11749,14 @@
       </c>
       <c r="B2729" s="7"/>
       <c r="C2729" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2730" s="3"/>
       <c r="B2730" s="7"/>
       <c r="C2730" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11094,7 +11772,7 @@
       </c>
       <c r="B2732" s="7"/>
       <c r="C2732" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11102,7 +11780,7 @@
         <v>7.2</v>
       </c>
       <c r="B2733" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2733" s="2" t="s">
         <v>5</v>
@@ -11117,7 +11795,7 @@
     </row>
     <row r="2774" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2774" s="10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B2774" s="11" t="s">
         <v>13</v>
@@ -11129,7 +11807,7 @@
     <row r="2775" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2775" s="13"/>
       <c r="B2775" s="17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C2775" s="18"/>
     </row>
@@ -11149,7 +11827,7 @@
         <v>22</v>
       </c>
       <c r="B2777" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2777" t="s">
         <v>5</v>
@@ -11161,7 +11839,7 @@
       </c>
       <c r="B2778" s="7"/>
       <c r="C2778" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2779" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11169,7 +11847,7 @@
         <v>1.2</v>
       </c>
       <c r="B2779" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2779" s="2" t="s">
         <v>6</v>
@@ -11181,7 +11859,7 @@
       </c>
       <c r="B2780" s="7"/>
       <c r="C2780" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11197,14 +11875,14 @@
       </c>
       <c r="B2782" s="7"/>
       <c r="C2782" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2783" s="3"/>
       <c r="B2783" s="7"/>
       <c r="C2783" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11220,7 +11898,7 @@
       </c>
       <c r="B2785" s="7"/>
       <c r="C2785" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11228,7 +11906,7 @@
         <v>4.2</v>
       </c>
       <c r="B2786" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2786" s="7" t="s">
         <v>5</v>
@@ -11246,7 +11924,7 @@
         <v>30</v>
       </c>
       <c r="B2833" s="11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C2833" s="12" t="s">
         <v>4</v>
@@ -11255,7 +11933,7 @@
     <row r="2834" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2834" s="13"/>
       <c r="B2834" s="17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C2834" s="18"/>
     </row>
@@ -11275,7 +11953,7 @@
         <v>22</v>
       </c>
       <c r="B2836" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2836" t="s">
         <v>5</v>
@@ -11287,7 +11965,7 @@
       </c>
       <c r="B2837" s="7"/>
       <c r="C2837" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2838" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11295,7 +11973,7 @@
         <v>1.2</v>
       </c>
       <c r="B2838" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2838" s="2" t="s">
         <v>6</v>
@@ -11307,7 +11985,7 @@
       </c>
       <c r="B2839" s="7"/>
       <c r="C2839" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11323,14 +12001,14 @@
       </c>
       <c r="B2841" s="7"/>
       <c r="C2841" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2842" s="3"/>
       <c r="B2842" s="7"/>
       <c r="C2842" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11346,7 +12024,7 @@
       </c>
       <c r="B2844" s="7"/>
       <c r="C2844" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11354,7 +12032,7 @@
         <v>4.2</v>
       </c>
       <c r="B2845" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2845" s="7" t="s">
         <v>5</v>
@@ -11369,7 +12047,7 @@
     </row>
     <row r="2892" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2892" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B2892" s="11" t="s">
         <v>9</v>
@@ -11401,7 +12079,7 @@
         <v>22</v>
       </c>
       <c r="B2895" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2895" t="s">
         <v>5</v>
@@ -11421,7 +12099,7 @@
         <v>1.2</v>
       </c>
       <c r="B2897" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2897" s="2" t="s">
         <v>6</v>
@@ -11453,7 +12131,7 @@
         <v>3.2</v>
       </c>
       <c r="B2901" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2901" s="2" t="s">
         <v>18</v>
@@ -11471,7 +12149,7 @@
         <v>4.2</v>
       </c>
       <c r="B2903" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2903" s="2" t="s">
         <v>19</v>
@@ -11483,7 +12161,7 @@
       </c>
       <c r="B2904" s="7"/>
       <c r="C2904" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11505,10 +12183,10 @@
         <v>6.2</v>
       </c>
       <c r="B2907" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C2907" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11523,10 +12201,10 @@
         <v>7.2</v>
       </c>
       <c r="B2909" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C2909" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11541,7 +12219,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B2911" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2911" s="7" t="s">
         <v>5</v>
@@ -11556,7 +12234,7 @@
     </row>
     <row r="2951" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2951" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B2951" s="11" t="s">
         <v>13</v>
@@ -11568,7 +12246,7 @@
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="13"/>
       <c r="B2952" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C2952" s="21"/>
     </row>
@@ -11588,7 +12266,7 @@
         <v>22</v>
       </c>
       <c r="B2954" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2954" t="s">
         <v>5</v>
@@ -11608,7 +12286,7 @@
         <v>1.2</v>
       </c>
       <c r="B2956" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2956" s="2" t="s">
         <v>6</v>
@@ -11620,7 +12298,7 @@
       </c>
       <c r="B2957" s="7"/>
       <c r="C2957" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11640,7 +12318,7 @@
       </c>
       <c r="B2959" s="7"/>
       <c r="C2959" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11651,7 +12329,7 @@
         <v>23</v>
       </c>
       <c r="C2960" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11666,7 +12344,7 @@
         <v>4.2</v>
       </c>
       <c r="B2962" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2962" s="2" t="s">
         <v>5</v>
@@ -11681,10 +12359,10 @@
     </row>
     <row r="3010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3010" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B3010" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3010" s="12" t="s">
         <v>16</v>
@@ -11693,7 +12371,7 @@
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="13"/>
       <c r="B3011" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C3011" s="21"/>
     </row>
@@ -11713,7 +12391,7 @@
         <v>22</v>
       </c>
       <c r="B3013" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3013" t="s">
         <v>5</v>
@@ -11733,7 +12411,7 @@
         <v>1.2</v>
       </c>
       <c r="B3015" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3015" s="2" t="s">
         <v>6</v>
@@ -11745,7 +12423,7 @@
       </c>
       <c r="B3016" s="7"/>
       <c r="C3016" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11765,7 +12443,7 @@
       </c>
       <c r="B3018" s="7"/>
       <c r="C3018" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11787,7 +12465,7 @@
         <v>4.2</v>
       </c>
       <c r="B3021" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3021" s="2" t="s">
         <v>6</v>
@@ -11799,7 +12477,7 @@
       </c>
       <c r="B3022" s="7"/>
       <c r="C3022" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11815,14 +12493,14 @@
       </c>
       <c r="B3024" s="7"/>
       <c r="C3024" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3025" s="3"/>
       <c r="B3025" s="7"/>
       <c r="C3025" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11838,7 +12516,7 @@
       </c>
       <c r="B3027" s="7"/>
       <c r="C3027" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11846,7 +12524,7 @@
         <v>7.2</v>
       </c>
       <c r="B3028" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3028" s="2" t="s">
         <v>5</v>
@@ -11861,7 +12539,7 @@
     </row>
     <row r="3069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3069" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B3069" s="11" t="s">
         <v>13</v>
@@ -11873,7 +12551,7 @@
     <row r="3070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3070" s="13"/>
       <c r="B3070" s="20" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C3070" s="21"/>
     </row>
@@ -11893,7 +12571,7 @@
         <v>22</v>
       </c>
       <c r="B3072" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3072" t="s">
         <v>5</v>
@@ -11913,7 +12591,7 @@
         <v>1.2</v>
       </c>
       <c r="B3074" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3074" s="2" t="s">
         <v>6</v>
@@ -11941,7 +12619,7 @@
       </c>
       <c r="B3077" s="7"/>
       <c r="C3077" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11961,7 +12639,7 @@
       </c>
       <c r="B3079" s="7"/>
       <c r="C3079" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11969,7 +12647,7 @@
         <v>4.2</v>
       </c>
       <c r="B3080" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3080" s="2" t="s">
         <v>5</v>
@@ -11996,7 +12674,7 @@
     <row r="3129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3129" s="13"/>
       <c r="B3129" s="20" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C3129" s="21"/>
     </row>
@@ -12016,7 +12694,7 @@
         <v>22</v>
       </c>
       <c r="B3131" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3131" t="s">
         <v>5</v>
@@ -12036,7 +12714,7 @@
         <v>1.2</v>
       </c>
       <c r="B3133" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3133" s="2" t="s">
         <v>14</v>
@@ -12056,10 +12734,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3135" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3135" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12084,7 +12762,7 @@
       </c>
       <c r="B3138" s="7"/>
       <c r="C3138" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12092,7 +12770,7 @@
         <v>4.2</v>
       </c>
       <c r="B3139" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3139" s="2" t="s">
         <v>6</v>
@@ -12104,7 +12782,7 @@
       </c>
       <c r="B3140" s="7"/>
       <c r="C3140" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12112,7 +12790,7 @@
         <v>5.2</v>
       </c>
       <c r="B3141" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3141" s="2" t="s">
         <v>5</v>
@@ -12127,7 +12805,7 @@
     </row>
     <row r="3187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3187" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B3187" s="11" t="s">
         <v>11</v>
@@ -12139,7 +12817,7 @@
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="13"/>
       <c r="B3188" s="20" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C3188" s="21"/>
     </row>
@@ -12159,7 +12837,7 @@
         <v>22</v>
       </c>
       <c r="B3190" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3190" t="s">
         <v>5</v>
@@ -12179,7 +12857,7 @@
         <v>1.2</v>
       </c>
       <c r="B3192" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3192" s="2" t="s">
         <v>14</v>
@@ -12199,10 +12877,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3194" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3194" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12227,7 +12905,7 @@
       </c>
       <c r="B3197" s="7"/>
       <c r="C3197" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12235,7 +12913,7 @@
         <v>4.2</v>
       </c>
       <c r="B3198" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C3198" s="2" t="s">
         <v>6</v>
@@ -12247,7 +12925,7 @@
       </c>
       <c r="B3199" s="7"/>
       <c r="C3199" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12255,7 +12933,7 @@
         <v>5.2</v>
       </c>
       <c r="B3200" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3200" s="2" t="s">
         <v>5</v>
@@ -12282,7 +12960,7 @@
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="13"/>
       <c r="B3247" s="20" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C3247" s="21"/>
     </row>
@@ -12302,7 +12980,7 @@
         <v>22</v>
       </c>
       <c r="B3249" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3249" t="s">
         <v>5</v>
@@ -12322,7 +13000,7 @@
         <v>1.2</v>
       </c>
       <c r="B3251" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3251" s="2" t="s">
         <v>6</v>
@@ -12350,7 +13028,7 @@
       </c>
       <c r="B3254" s="7"/>
       <c r="C3254" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12361,7 +13039,7 @@
         <v>7</v>
       </c>
       <c r="C3255" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12376,7 +13054,7 @@
         <v>4.2</v>
       </c>
       <c r="B3257" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3257" s="2" t="s">
         <v>20</v>
@@ -12393,7 +13071,7 @@
       </c>
       <c r="B3259" s="7"/>
       <c r="C3259" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12413,7 +13091,7 @@
       </c>
       <c r="B3261" s="7"/>
       <c r="C3261" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12421,7 +13099,7 @@
         <v>6.2</v>
       </c>
       <c r="B3262" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3262" s="2" t="s">
         <v>5</v>
@@ -12436,7 +13114,7 @@
     </row>
     <row r="3305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3305" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B3305" s="11" t="s">
         <v>11</v>
@@ -12448,7 +13126,7 @@
     <row r="3306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3306" s="13"/>
       <c r="B3306" s="20" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C3306" s="21"/>
     </row>
@@ -12468,7 +13146,7 @@
         <v>22</v>
       </c>
       <c r="B3308" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3308" t="s">
         <v>5</v>
@@ -12488,10 +13166,10 @@
         <v>1.2</v>
       </c>
       <c r="B3310" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3310" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12508,7 +13186,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3312" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3312" s="2" t="s">
         <v>6</v>
@@ -12520,7 +13198,7 @@
       </c>
       <c r="B3313" s="7"/>
       <c r="C3313" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12531,7 +13209,7 @@
         <v>7</v>
       </c>
       <c r="C3314" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12540,7 +13218,7 @@
       </c>
       <c r="B3315" s="7"/>
       <c r="C3315" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12551,7 +13229,7 @@
         <v>23</v>
       </c>
       <c r="C3316" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12566,7 +13244,7 @@
         <v>5.2</v>
       </c>
       <c r="B3318" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3318" s="2" t="s">
         <v>5</v>
@@ -12593,7 +13271,7 @@
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="13"/>
       <c r="B3365" s="20" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C3365" s="21"/>
     </row>
@@ -12613,7 +13291,7 @@
         <v>22</v>
       </c>
       <c r="B3367" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3367" t="s">
         <v>5</v>
@@ -12633,7 +13311,7 @@
         <v>1.2</v>
       </c>
       <c r="B3369" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3369" s="2" t="s">
         <v>26</v>
@@ -12651,10 +13329,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3371" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C3371" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12669,10 +13347,10 @@
         <v>3.2</v>
       </c>
       <c r="B3373" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C3373" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12681,7 +13359,7 @@
       </c>
       <c r="B3374" s="7"/>
       <c r="C3374" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12689,10 +13367,10 @@
         <v>4.2</v>
       </c>
       <c r="B3375" s="22" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C3375" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12712,7 +13390,7 @@
         <v>5.2</v>
       </c>
       <c r="B3378" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3378" s="2" t="s">
         <v>5</v>
@@ -12727,7 +13405,7 @@
     </row>
     <row r="3423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3423" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B3423" s="11" t="s">
         <v>3</v>
@@ -12739,7 +13417,7 @@
     <row r="3424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3424" s="13"/>
       <c r="B3424" s="20" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C3424" s="21"/>
     </row>
@@ -12759,7 +13437,7 @@
         <v>22</v>
       </c>
       <c r="B3426" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3426" t="s">
         <v>5</v>
@@ -12779,7 +13457,7 @@
         <v>1.2</v>
       </c>
       <c r="B3428" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3428" s="2" t="s">
         <v>6</v>
@@ -12791,7 +13469,7 @@
       </c>
       <c r="B3429" s="7"/>
       <c r="C3429" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12811,21 +13489,21 @@
       </c>
       <c r="B3431" s="7"/>
       <c r="C3431" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3432" s="3"/>
       <c r="B3432" s="7"/>
       <c r="C3432" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3433" s="3"/>
       <c r="B3433" s="7"/>
       <c r="C3433" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12836,7 +13514,7 @@
         <v>23</v>
       </c>
       <c r="C3434" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12851,7 +13529,7 @@
         <v>4.2</v>
       </c>
       <c r="B3436" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C3436" s="2" t="s">
         <v>6</v>
@@ -12868,7 +13546,7 @@
       </c>
       <c r="B3438" s="2"/>
       <c r="C3438" s="2" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12876,10 +13554,10 @@
         <v>5.2</v>
       </c>
       <c r="B3439" s="22" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C3439" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12899,7 +13577,7 @@
         <v>6.2</v>
       </c>
       <c r="B3442" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3442" s="2" t="s">
         <v>5</v>
@@ -12914,7 +13592,7 @@
     </row>
     <row r="3482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3482" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B3482" s="11" t="s">
         <v>11</v>
@@ -12926,7 +13604,7 @@
     <row r="3483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3483" s="13"/>
       <c r="B3483" s="20" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C3483" s="21"/>
     </row>
@@ -12946,7 +13624,7 @@
         <v>22</v>
       </c>
       <c r="B3485" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3485" t="s">
         <v>5</v>
@@ -12966,7 +13644,7 @@
         <v>1.2</v>
       </c>
       <c r="B3487" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3487" s="2" t="s">
         <v>6</v>
@@ -12994,7 +13672,7 @@
       </c>
       <c r="B3490" s="7"/>
       <c r="C3490" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13014,7 +13692,7 @@
       </c>
       <c r="B3492" s="7"/>
       <c r="C3492" s="22" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13030,7 +13708,7 @@
         <v>23</v>
       </c>
       <c r="C3494" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13045,7 +13723,7 @@
         <v>5.2</v>
       </c>
       <c r="B3496" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3496" s="2" t="s">
         <v>5</v>
@@ -13060,7 +13738,7 @@
     </row>
     <row r="3541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3541" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B3541" s="11" t="s">
         <v>12</v>
@@ -13072,7 +13750,7 @@
     <row r="3542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3542" s="13"/>
       <c r="B3542" s="17" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C3542" s="18"/>
     </row>
@@ -13092,7 +13770,7 @@
         <v>22</v>
       </c>
       <c r="B3544" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3544" t="s">
         <v>5</v>
@@ -13112,7 +13790,7 @@
         <v>1.2</v>
       </c>
       <c r="B3546" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3546" s="2" t="s">
         <v>26</v>
@@ -13124,7 +13802,7 @@
       </c>
       <c r="B3547" s="7"/>
       <c r="C3547" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13132,7 +13810,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3548" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3548" s="2" t="s">
         <v>5</v>
@@ -13147,7 +13825,7 @@
     </row>
     <row r="3600" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3600" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B3600" s="11" t="s">
         <v>12</v>
@@ -13179,7 +13857,7 @@
         <v>22</v>
       </c>
       <c r="B3603" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3603" t="s">
         <v>5</v>
@@ -13207,7 +13885,7 @@
       </c>
       <c r="B3606" s="7"/>
       <c r="C3606" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13215,7 +13893,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3607" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3607" s="2" t="s">
         <v>5</v>
@@ -13230,7 +13908,7 @@
     </row>
     <row r="3659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3659" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B3659" s="11" t="s">
         <v>10</v>
@@ -13242,7 +13920,7 @@
     <row r="3660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3660" s="13"/>
       <c r="B3660" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C3660" s="18"/>
     </row>
@@ -13262,7 +13940,7 @@
         <v>22</v>
       </c>
       <c r="B3662" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3662" t="s">
         <v>5</v>
@@ -13282,7 +13960,7 @@
         <v>1.2</v>
       </c>
       <c r="B3664" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3664" s="2" t="s">
         <v>6</v>
@@ -13294,7 +13972,7 @@
       </c>
       <c r="B3665" s="7"/>
       <c r="C3665" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13314,7 +13992,7 @@
       </c>
       <c r="B3667" s="7"/>
       <c r="C3667" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13322,7 +14000,7 @@
         <v>3.2</v>
       </c>
       <c r="B3668" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3668" s="2" t="s">
         <v>5</v>
@@ -13337,7 +14015,7 @@
     </row>
     <row r="3718" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3718" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B3718" s="11" t="s">
         <v>9</v>
@@ -13349,7 +14027,7 @@
     <row r="3719" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3719" s="13"/>
       <c r="B3719" s="17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C3719" s="18"/>
     </row>
@@ -13369,7 +14047,7 @@
         <v>22</v>
       </c>
       <c r="B3721" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3721" t="s">
         <v>5</v>
@@ -13389,7 +14067,7 @@
         <v>1.2</v>
       </c>
       <c r="B3723" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3723" s="2" t="s">
         <v>14</v>
@@ -13409,10 +14087,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3725" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3725" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13443,7 +14121,7 @@
         <v>4.2</v>
       </c>
       <c r="B3729" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3729" s="2" t="s">
         <v>18</v>
@@ -13461,7 +14139,7 @@
         <v>5.2</v>
       </c>
       <c r="B3731" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3731" s="2" t="s">
         <v>19</v>
@@ -13473,7 +14151,7 @@
       </c>
       <c r="B3732" s="7"/>
       <c r="C3732" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13489,7 +14167,7 @@
       </c>
       <c r="B3734" s="7"/>
       <c r="C3734" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13505,7 +14183,7 @@
       </c>
       <c r="B3736" s="7"/>
       <c r="C3736" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13513,7 +14191,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B3737" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3737" s="2" t="s">
         <v>5</v>
@@ -13528,7 +14206,7 @@
     </row>
     <row r="3777" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3777" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B3777" s="11" t="s">
         <v>12</v>
@@ -13560,7 +14238,7 @@
         <v>22</v>
       </c>
       <c r="B3780" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3780" t="s">
         <v>5</v>
@@ -13588,7 +14266,7 @@
       </c>
       <c r="B3783" s="7"/>
       <c r="C3783" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13596,7 +14274,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B3784" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3784" s="2" t="s">
         <v>5</v>
@@ -13611,7 +14289,7 @@
     </row>
     <row r="3836" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3836" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B3836" s="11" t="s">
         <v>9</v>
@@ -13643,7 +14321,7 @@
         <v>22</v>
       </c>
       <c r="B3839" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3839" t="s">
         <v>5</v>
@@ -13663,7 +14341,7 @@
         <v>1.2</v>
       </c>
       <c r="B3841" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3841" s="2" t="s">
         <v>6</v>
@@ -13695,7 +14373,7 @@
         <v>3.2</v>
       </c>
       <c r="B3845" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C3845" s="2" t="s">
         <v>18</v>
@@ -13713,7 +14391,7 @@
         <v>4.2</v>
       </c>
       <c r="B3847" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3847" s="2" t="s">
         <v>19</v>
@@ -13725,7 +14403,7 @@
       </c>
       <c r="B3848" s="7"/>
       <c r="C3848" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13747,10 +14425,10 @@
         <v>6.2</v>
       </c>
       <c r="B3851" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C3851" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13765,10 +14443,10 @@
         <v>7.2</v>
       </c>
       <c r="B3853" s="7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C3853" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13783,7 +14461,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="B3855" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3855" s="2" t="s">
         <v>5</v>
@@ -13798,7 +14476,7 @@
     </row>
     <row r="3895" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3895" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B3895" s="11" t="s">
         <v>13</v>
@@ -13810,7 +14488,7 @@
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="13"/>
       <c r="B3896" s="20" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C3896" s="21"/>
     </row>
@@ -13830,7 +14508,7 @@
         <v>22</v>
       </c>
       <c r="B3898" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3898" t="s">
         <v>5</v>
@@ -13850,7 +14528,7 @@
         <v>1.2</v>
       </c>
       <c r="B3900" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3900" s="2" t="s">
         <v>6</v>
@@ -13862,7 +14540,7 @@
       </c>
       <c r="B3901" s="7"/>
       <c r="C3901" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13882,7 +14560,7 @@
       </c>
       <c r="B3903" s="7"/>
       <c r="C3903" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13893,7 +14571,7 @@
         <v>23</v>
       </c>
       <c r="C3904" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13908,7 +14586,7 @@
         <v>4.2</v>
       </c>
       <c r="B3906" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3906" s="2" t="s">
         <v>5</v>
@@ -13923,10 +14601,10 @@
     </row>
     <row r="3954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3954" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B3954" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3954" s="12" t="s">
         <v>16</v>
@@ -13935,7 +14613,7 @@
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="13"/>
       <c r="B3955" s="20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C3955" s="21"/>
     </row>
@@ -13955,7 +14633,7 @@
         <v>22</v>
       </c>
       <c r="B3957" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3957" t="s">
         <v>5</v>
@@ -13975,7 +14653,7 @@
         <v>1.2</v>
       </c>
       <c r="B3959" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3959" s="2" t="s">
         <v>6</v>
@@ -13987,7 +14665,7 @@
       </c>
       <c r="B3960" s="7"/>
       <c r="C3960" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14007,7 +14685,7 @@
       </c>
       <c r="B3962" s="7"/>
       <c r="C3962" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14029,7 +14707,7 @@
         <v>4.2</v>
       </c>
       <c r="B3965" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3965" s="2" t="s">
         <v>6</v>
@@ -14041,7 +14719,7 @@
       </c>
       <c r="B3966" s="7"/>
       <c r="C3966" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14057,14 +14735,14 @@
       </c>
       <c r="B3968" s="7"/>
       <c r="C3968" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3969" s="3"/>
       <c r="B3969" s="7"/>
       <c r="C3969" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14080,7 +14758,7 @@
       </c>
       <c r="B3971" s="7"/>
       <c r="C3971" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14088,7 +14766,7 @@
         <v>7.2</v>
       </c>
       <c r="B3972" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3972" s="2" t="s">
         <v>5</v>
@@ -14103,7 +14781,7 @@
     </row>
     <row r="4013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4013" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B4013" s="11" t="s">
         <v>10</v>
@@ -14115,7 +14793,7 @@
     <row r="4014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4014" s="13"/>
       <c r="B4014" s="17" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C4014" s="18"/>
     </row>
@@ -14135,7 +14813,7 @@
         <v>22</v>
       </c>
       <c r="B4016" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4016" t="s">
         <v>5</v>
@@ -14155,7 +14833,7 @@
         <v>1.2</v>
       </c>
       <c r="B4018" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4018" s="2" t="s">
         <v>6</v>
@@ -14167,7 +14845,7 @@
       </c>
       <c r="B4019" s="7"/>
       <c r="C4019" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14187,7 +14865,7 @@
       </c>
       <c r="B4021" s="7"/>
       <c r="C4021" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14195,7 +14873,7 @@
         <v>3.2</v>
       </c>
       <c r="B4022" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4022" s="2" t="s">
         <v>5</v>
@@ -14222,7 +14900,7 @@
     <row r="4073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4073" s="13"/>
       <c r="B4073" s="17" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C4073" s="18"/>
     </row>
@@ -14242,7 +14920,7 @@
         <v>22</v>
       </c>
       <c r="B4075" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4075" t="s">
         <v>5</v>
@@ -14262,7 +14940,7 @@
         <v>1.2</v>
       </c>
       <c r="B4077" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4077" s="2" t="s">
         <v>14</v>
@@ -14282,10 +14960,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4079" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4079" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14314,7 +14992,7 @@
       </c>
       <c r="B4082" s="7"/>
       <c r="C4082" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14322,7 +15000,7 @@
         <v>4.2</v>
       </c>
       <c r="B4083" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4083" s="2" t="s">
         <v>5</v>
@@ -14337,7 +15015,7 @@
     </row>
     <row r="4131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4131" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B4131" s="11" t="s">
         <v>10</v>
@@ -14349,7 +15027,7 @@
     <row r="4132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4132" s="13"/>
       <c r="B4132" s="17" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C4132" s="18"/>
     </row>
@@ -14369,7 +15047,7 @@
         <v>22</v>
       </c>
       <c r="B4134" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4134" t="s">
         <v>5</v>
@@ -14403,7 +15081,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4138" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C4138" s="2" t="s">
         <v>6</v>
@@ -14415,7 +15093,7 @@
       </c>
       <c r="B4139" s="7"/>
       <c r="C4139" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14423,7 +15101,7 @@
         <v>3.2</v>
       </c>
       <c r="B4140" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4140" s="2" t="s">
         <v>5</v>
@@ -14450,7 +15128,7 @@
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="13"/>
       <c r="B4191" s="20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C4191" s="21"/>
     </row>
@@ -14470,7 +15148,7 @@
         <v>22</v>
       </c>
       <c r="B4193" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4193" t="s">
         <v>5</v>
@@ -14490,7 +15168,7 @@
         <v>1.2</v>
       </c>
       <c r="B4195" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4195" s="2" t="s">
         <v>6</v>
@@ -14518,7 +15196,7 @@
       </c>
       <c r="B4198" s="7"/>
       <c r="C4198" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14529,7 +15207,7 @@
         <v>7</v>
       </c>
       <c r="C4199" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14544,7 +15222,7 @@
         <v>4.2</v>
       </c>
       <c r="B4201" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C4201" s="2" t="s">
         <v>20</v>
@@ -14567,7 +15245,7 @@
         <v>5.2</v>
       </c>
       <c r="B4204" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C4204" s="2" t="s">
         <v>6</v>
@@ -14579,7 +15257,7 @@
       </c>
       <c r="B4205" s="7"/>
       <c r="C4205" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14587,7 +15265,7 @@
         <v>6.2</v>
       </c>
       <c r="B4206" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4206" s="2" t="s">
         <v>5</v>
@@ -14602,7 +15280,7 @@
     </row>
     <row r="4249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4249" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B4249" s="11" t="s">
         <v>12</v>
@@ -14634,7 +15312,7 @@
         <v>22</v>
       </c>
       <c r="B4252" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4252" t="s">
         <v>5</v>
@@ -14654,7 +15332,7 @@
         <v>1.2</v>
       </c>
       <c r="B4254" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4254" s="2" t="s">
         <v>6</v>
@@ -14666,7 +15344,7 @@
       </c>
       <c r="B4255" s="7"/>
       <c r="C4255" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14674,7 +15352,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B4256" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4256" s="2" t="s">
         <v>5</v>
@@ -14701,7 +15379,7 @@
     <row r="4309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4309" s="13"/>
       <c r="B4309" s="20" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C4309" s="21"/>
     </row>
@@ -14721,7 +15399,7 @@
         <v>22</v>
       </c>
       <c r="B4311" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4311" t="s">
         <v>5</v>
@@ -14741,7 +15419,7 @@
         <v>1.2</v>
       </c>
       <c r="B4313" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4313" s="2" t="s">
         <v>6</v>
@@ -14753,7 +15431,7 @@
       </c>
       <c r="B4314" s="7"/>
       <c r="C4314" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14764,7 +15442,7 @@
         <v>7</v>
       </c>
       <c r="C4315" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14779,7 +15457,7 @@
         <v>3.2</v>
       </c>
       <c r="B4317" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4317" s="2" t="s">
         <v>6</v>
@@ -14791,7 +15469,7 @@
       </c>
       <c r="B4318" s="7"/>
       <c r="C4318" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14802,7 +15480,7 @@
         <v>7</v>
       </c>
       <c r="C4319" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14811,7 +15489,7 @@
       </c>
       <c r="B4320" s="7"/>
       <c r="C4320" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14822,7 +15500,7 @@
         <v>23</v>
       </c>
       <c r="C4321" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14837,7 +15515,7 @@
         <v>6.2</v>
       </c>
       <c r="B4323" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4323" s="2" t="s">
         <v>5</v>
@@ -14850,12 +15528,2807 @@
       <c r="B4324" s="9"/>
       <c r="C4324" s="8"/>
     </row>
+    <row r="4367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4367" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4367" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4367" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4368" s="13"/>
+      <c r="B4368" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4368" s="21"/>
+    </row>
+    <row r="4369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4369" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4369" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4369" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4370" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4370" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4370" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4371" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4371" s="7"/>
+      <c r="C4371" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4372" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4372" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4372" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4373" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4373" s="7"/>
+      <c r="C4373" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4374" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4374" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4374" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4375" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4375" s="7"/>
+      <c r="C4375" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4376" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4376" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4376" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4377" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4377" s="7"/>
+      <c r="C4377" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4378" s="3"/>
+      <c r="B4378" s="7"/>
+      <c r="C4378" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4379" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4379" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4379" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4380" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4380" s="9"/>
+      <c r="C4380" s="8"/>
+    </row>
+    <row r="4426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4426" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4426" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4426" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4427" s="13"/>
+      <c r="B4427" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4427" s="21"/>
+    </row>
+    <row r="4428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4428" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4428" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4428" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4429" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4429" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4429" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4430" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4430" s="7"/>
+      <c r="C4430" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4431" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4431" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4431" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4432" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4432" s="7"/>
+      <c r="C4432" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4433" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4433" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4433" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4434" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4434" s="7"/>
+      <c r="C4434" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4435" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4435" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4435" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4436" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4436" s="7"/>
+      <c r="C4436" s="2"/>
+    </row>
+    <row r="4437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4437" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4437" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4437" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4438" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4438" s="9"/>
+      <c r="C4438" s="8"/>
+    </row>
+    <row r="4485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4485" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B4485" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4485" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4486" s="13"/>
+      <c r="B4486" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4486" s="21"/>
+    </row>
+    <row r="4487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4487" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4487" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4487" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4488" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4488" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4488" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4489" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4489" s="7"/>
+      <c r="C4489" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4490" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4490" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4490" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4491" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4491" s="7"/>
+      <c r="C4491" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4492" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4492" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4492" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4493" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4493" s="7"/>
+      <c r="C4493" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4494" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4494" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4494" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4495" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4495" s="7"/>
+      <c r="C4495" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4496" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4496" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4496" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4497" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4497" s="7"/>
+      <c r="C4497" s="2"/>
+    </row>
+    <row r="4498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4498" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4498" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4498" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4499" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4499" s="9"/>
+      <c r="C4499" s="8"/>
+    </row>
+    <row r="4544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4544" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4544" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4544" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4545" s="13"/>
+      <c r="B4545" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4545" s="18"/>
+    </row>
+    <row r="4546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4546" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4546" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4546" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4547" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4547" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4547" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4548" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4548" s="7"/>
+      <c r="C4548" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4549" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4549" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4549" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4550" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4550" s="7"/>
+      <c r="C4550" s="2"/>
+    </row>
+    <row r="4551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4551" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4551" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4551" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4552" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4552" s="7"/>
+      <c r="C4552" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4553" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4553" s="7"/>
+      <c r="C4553" s="2"/>
+    </row>
+    <row r="4554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4554" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4554" s="7"/>
+      <c r="C4554" s="2"/>
+    </row>
+    <row r="4555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4555" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4555" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4555" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4556" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4556" s="9"/>
+      <c r="C4556" s="8"/>
+    </row>
+    <row r="4603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4603" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4603" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4603" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4604" s="13"/>
+      <c r="B4604" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4604" s="21"/>
+    </row>
+    <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4605" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4605" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4605" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4606" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4606" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4606" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4607" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4607" s="7"/>
+      <c r="C4607" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4608" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4608" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4608" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4609" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4609" s="7"/>
+      <c r="C4609" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4610" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4610" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4610" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4611" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4611" s="7"/>
+      <c r="C4611" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4612" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4612" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4612" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4613" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4613" s="7"/>
+      <c r="C4613" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4614" s="3"/>
+      <c r="B4614" s="7"/>
+      <c r="C4614" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4615" s="3"/>
+      <c r="B4615" s="7"/>
+      <c r="C4615" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4616" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4616" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4616" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4617" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4617" s="7"/>
+      <c r="C4617" s="2"/>
+    </row>
+    <row r="4618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4618" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4618" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4618" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4619" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4619" s="7"/>
+      <c r="C4619" s="2"/>
+    </row>
+    <row r="4620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4620" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4620" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4620" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4621" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4621" s="9"/>
+      <c r="C4621" s="8"/>
+    </row>
+    <row r="4662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4662" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4662" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4662" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4663" s="13"/>
+      <c r="B4663" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4663" s="18"/>
+    </row>
+    <row r="4664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4664" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4664" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4664" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4665" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4665" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4665" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4666" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4666" s="7"/>
+      <c r="C4666" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4667" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4667" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4667" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4668" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4668" s="7"/>
+      <c r="C4668" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4669" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4669" s="7"/>
+      <c r="C4669" s="2"/>
+    </row>
+    <row r="4670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4670" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4670" s="7"/>
+      <c r="C4670" s="2"/>
+    </row>
+    <row r="4671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4671" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4671" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4671" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4672" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4672" s="7"/>
+      <c r="C4672" s="2"/>
+    </row>
+    <row r="4673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4673" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4673" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4673" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4674" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4674" s="7"/>
+      <c r="C4674" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4675" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4675" s="7"/>
+      <c r="C4675" s="2"/>
+    </row>
+    <row r="4676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4676" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4676" s="7"/>
+      <c r="C4676" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4677" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4677" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4677" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4678" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4678" s="9"/>
+      <c r="C4678" s="8"/>
+    </row>
+    <row r="4721" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4721" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4721" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4721" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4722" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4722" s="13"/>
+      <c r="B4722" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4722" s="18"/>
+    </row>
+    <row r="4723" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4723" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4723" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4723" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4724" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4724" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4724" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4724" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4725" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4725" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4725" s="7"/>
+      <c r="C4725" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4726" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4726" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4726" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4726" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4727" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4727" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4727" s="7"/>
+      <c r="C4727" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4728" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4728" s="7"/>
+      <c r="C4728" s="2"/>
+    </row>
+    <row r="4729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4729" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4729" s="7"/>
+      <c r="C4729" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4730" s="3"/>
+      <c r="B4730" s="7"/>
+      <c r="C4730" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4731" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4731" s="7"/>
+      <c r="C4731" s="2"/>
+    </row>
+    <row r="4732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4732" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4732" s="7"/>
+      <c r="C4732" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4733" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4733" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4733" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4734" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4734" s="9"/>
+      <c r="C4734" s="8"/>
+    </row>
+    <row r="4780" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4780" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4780" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4780" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4781" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4781" s="13"/>
+      <c r="B4781" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4781" s="18"/>
+    </row>
+    <row r="4782" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4782" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4782" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4782" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4783" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4783" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4783" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4783" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4784" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4784" s="7"/>
+      <c r="C4784" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4785" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4785" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4785" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4786" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4786" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4786" s="7"/>
+      <c r="C4786" s="2"/>
+    </row>
+    <row r="4787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4787" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4787" s="7"/>
+      <c r="C4787" s="2"/>
+    </row>
+    <row r="4788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4788" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4788" s="7"/>
+      <c r="C4788" s="2"/>
+    </row>
+    <row r="4789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4789" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4789" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4789" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4790" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4790" s="7"/>
+      <c r="C4790" s="2"/>
+    </row>
+    <row r="4791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4791" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4791" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4791" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4792" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4792" s="7"/>
+      <c r="C4792" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4793" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4793" s="7"/>
+      <c r="C4793" s="2"/>
+    </row>
+    <row r="4794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4794" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4794" s="7"/>
+      <c r="C4794" s="2"/>
+    </row>
+    <row r="4795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4795" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4795" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4795" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4796" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B4796" s="7"/>
+      <c r="C4796" s="2"/>
+    </row>
+    <row r="4797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4797" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B4797" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4797" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4798" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B4798" s="7"/>
+      <c r="C4798" s="2"/>
+    </row>
+    <row r="4799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4799" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B4799" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4799" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4800" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4800" s="9"/>
+      <c r="C4800" s="8"/>
+    </row>
+    <row r="4839" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4839" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4839" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4839" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4840" s="13"/>
+      <c r="B4840" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4840" s="21"/>
+    </row>
+    <row r="4841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4841" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4841" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4841" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4842" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4842" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4842" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4842" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4843" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4843" s="7"/>
+      <c r="C4843" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4844" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4844" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4844" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4845" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4845" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4845" s="7"/>
+      <c r="C4845" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4846" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4846" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4846" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4847" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4847" s="7"/>
+      <c r="C4847" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4848" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4848" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4848" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4849" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4849" s="7"/>
+      <c r="C4849" s="2"/>
+    </row>
+    <row r="4850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4850" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4850" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4850" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4851" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4851" s="9"/>
+      <c r="C4851" s="8"/>
+    </row>
+    <row r="4898" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4898" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4898" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4898" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4899" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4899" s="13"/>
+      <c r="B4899" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4899" s="18"/>
+    </row>
+    <row r="4900" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4900" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4900" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4900" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4901" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4901" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4901" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4901" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4902" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4902" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4902" s="7"/>
+      <c r="C4902" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4903" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4903" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4903" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4903" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4904" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4904" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4904" s="7"/>
+      <c r="C4904" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4905" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4905" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4905" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4906" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4906" s="7"/>
+      <c r="C4906" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4907" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4907" s="7"/>
+      <c r="C4907" s="2"/>
+    </row>
+    <row r="4908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4908" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4908" s="7"/>
+      <c r="C4908" s="2"/>
+    </row>
+    <row r="4909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4909" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4909" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4909" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4910" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B4910" s="7"/>
+      <c r="C4910" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4911" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B4911" s="7"/>
+      <c r="C4911" s="2"/>
+    </row>
+    <row r="4912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4912" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B4912" s="7"/>
+      <c r="C4912" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4913" s="3"/>
+      <c r="B4913" s="7"/>
+      <c r="C4913" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4914" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B4914" s="7"/>
+      <c r="C4914" s="2"/>
+    </row>
+    <row r="4915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4915" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B4915" s="7"/>
+      <c r="C4915" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4916" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B4916" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4916" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4917" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4917" s="9"/>
+      <c r="C4917" s="8"/>
+    </row>
+    <row r="4957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4957" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4957" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4957" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4958" s="13"/>
+      <c r="B4958" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4958" s="21"/>
+    </row>
+    <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4959" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4959" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4959" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4960" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4960" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4960" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4961" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4961" s="7"/>
+      <c r="C4961" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4962" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B4962" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4962" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4963" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B4963" s="7"/>
+      <c r="C4963" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4964" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B4964" s="7"/>
+      <c r="C4964" s="2"/>
+    </row>
+    <row r="4965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4965" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B4965" s="7"/>
+      <c r="C4965" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4966" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B4966" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4966" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4967" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B4967" s="7"/>
+      <c r="C4967" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4968" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B4968" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4968" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4969" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4969" s="9"/>
+      <c r="C4969" s="8"/>
+    </row>
+    <row r="5016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5016" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5016" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5016" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5017" s="13"/>
+      <c r="B5017" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5017" s="21"/>
+    </row>
+    <row r="5018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5018" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5018" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5018" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5019" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5019" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5019" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5020" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5020" s="7"/>
+      <c r="C5020" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5021" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5021" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5021" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5022" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5022" s="7"/>
+      <c r="C5022" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5023" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5023" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5023" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5024" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5024" s="7"/>
+      <c r="C5024" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5025" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5025" s="7"/>
+      <c r="C5025" s="2"/>
+    </row>
+    <row r="5026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5026" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5026" s="7"/>
+      <c r="C5026" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5027" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5027" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5027" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5028" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5028" s="7"/>
+      <c r="C5028" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5029" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5029" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5029" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5030" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5030" s="9"/>
+      <c r="C5030" s="8"/>
+    </row>
+    <row r="5075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5075" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5075" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5075" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5076" s="13"/>
+      <c r="B5076" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5076" s="21"/>
+    </row>
+    <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5077" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5077" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5077" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5078" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5078" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5078" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5079" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5079" s="7"/>
+      <c r="C5079" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5080" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5080" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5080" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5081" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5081" s="7"/>
+      <c r="C5081" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5082" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5082" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5082" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5083" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5083" s="7"/>
+      <c r="C5083" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5084" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5084" s="7"/>
+      <c r="C5084" s="2"/>
+    </row>
+    <row r="5085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5085" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5085" s="7"/>
+      <c r="C5085" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5086" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5086" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5086" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5087" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5087" s="7"/>
+      <c r="C5087" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5088" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5088" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5088" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5089" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5089" s="9"/>
+      <c r="C5089" s="8"/>
+    </row>
+    <row r="5134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5134" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5134" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5134" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5135" s="13"/>
+      <c r="B5135" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5135" s="21"/>
+    </row>
+    <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5136" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5136" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5136" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5137" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5137" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5138" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5138" s="7"/>
+      <c r="C5138" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5139" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5139" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5140" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5140" s="7"/>
+      <c r="C5140" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5141" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5141" s="7"/>
+      <c r="C5141" s="2"/>
+    </row>
+    <row r="5142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5142" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5142" s="7"/>
+      <c r="C5142" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5143" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5143" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5143" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5144" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5144" s="7"/>
+      <c r="C5144" s="2"/>
+    </row>
+    <row r="5145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5145" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5145" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5145" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5146" s="3"/>
+      <c r="B5146" s="22"/>
+      <c r="C5146" s="2"/>
+    </row>
+    <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5147" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5147" s="7"/>
+      <c r="C5147" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5148" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5148" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5148" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5149" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B5149" s="7"/>
+      <c r="C5149" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5150" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B5150" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5150" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5151" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5151" s="9"/>
+      <c r="C5151" s="8"/>
+    </row>
+    <row r="5193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5193" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="B5193" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5193" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5194" s="13"/>
+      <c r="B5194" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5194" s="21"/>
+    </row>
+    <row r="5195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5195" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5195" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5195" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5196" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5196" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5197" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5197" s="7"/>
+      <c r="C5197" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5198" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5198" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5198" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5199" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5199" s="7"/>
+      <c r="C5199" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5200" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5200" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5200" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5201" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5201" s="7"/>
+      <c r="C5201" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5202" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5202" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5202" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5203" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5203" s="7"/>
+      <c r="C5203" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5204" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5204" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5205" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5205" s="2"/>
+      <c r="C5205" s="2"/>
+    </row>
+    <row r="5206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5206" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5206" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5206" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5207" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5207" s="9"/>
+      <c r="C5207" s="8"/>
+    </row>
+    <row r="5252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5252" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5252" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5252" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5253" s="13"/>
+      <c r="B5253" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5253" s="21"/>
+    </row>
+    <row r="5254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5254" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5254" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5254" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5255" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5255" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5255" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5256" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5256" s="7"/>
+      <c r="C5256" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5257" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5257" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5257" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5258" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5258" s="7"/>
+      <c r="C5258" s="2"/>
+    </row>
+    <row r="5259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5259" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5259" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5259" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5260" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5260" s="7"/>
+      <c r="C5260" s="2"/>
+    </row>
+    <row r="5261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5261" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5261" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5261" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5262" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5262" s="7"/>
+      <c r="C5262" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5263" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5263" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5263" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5264" s="3"/>
+      <c r="B5264" s="22"/>
+      <c r="C5264" s="2"/>
+    </row>
+    <row r="5265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5265" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5265" s="7"/>
+      <c r="C5265" s="2"/>
+    </row>
+    <row r="5266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5266" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5266" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5266" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5267" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5267" s="9"/>
+      <c r="C5267" s="8"/>
+    </row>
+    <row r="5311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5311" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="B5311" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5311" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5312" s="13"/>
+      <c r="B5312" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="C5312" s="18"/>
+    </row>
+    <row r="5313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5313" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5313" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5313" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5314" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5314" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5314" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5315" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5315" s="7"/>
+      <c r="C5315" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5316" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5316" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5316" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5317" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5317" s="7"/>
+      <c r="C5317" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5318" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5318" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5318" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5319" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5319" s="7"/>
+      <c r="C5319" s="2"/>
+    </row>
+    <row r="5320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5320" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5320" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5320" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5321" s="3"/>
+      <c r="B5321" s="22"/>
+      <c r="C5321" s="2"/>
+    </row>
+    <row r="5322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5322" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5322" s="7"/>
+      <c r="C5322" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="5323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5323" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5323" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5323" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5324" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5324" s="9"/>
+      <c r="C5324" s="8"/>
+    </row>
+    <row r="5370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5370" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5370" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5370" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5371" s="13"/>
+      <c r="B5371" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5371" s="21"/>
+    </row>
+    <row r="5372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5372" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5372" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5372" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5373" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5373" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5373" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5374" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5374" s="7"/>
+      <c r="C5374" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5375" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5375" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5375" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5376" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5376" s="7"/>
+      <c r="C5376" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5377" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5377" s="7"/>
+      <c r="C5377" s="2"/>
+    </row>
+    <row r="5378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5378" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B5378" s="7"/>
+      <c r="C5378" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5379" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B5379" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5379" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5380" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B5380" s="7"/>
+      <c r="C5380" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5381" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B5381" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5381" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5382" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B5382" s="2"/>
+      <c r="C5382" s="2"/>
+    </row>
+    <row r="5383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5383" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B5383" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5383" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5384" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5384" s="9"/>
+      <c r="C5384" s="8"/>
+    </row>
+    <row r="5429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5429" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5429" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5429" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5430" s="13"/>
+      <c r="B5430" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5430" s="18"/>
+    </row>
+    <row r="5431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5431" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5431" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5431" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5432" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5432" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5432" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5433" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5433" s="7"/>
+      <c r="C5433" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5434" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5434" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5434" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5435" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5435" s="7"/>
+      <c r="C5435" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="5436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5436" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5436" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5436" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5437" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5437" s="9"/>
+      <c r="C5437" s="8"/>
+    </row>
+    <row r="5488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5488" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5488" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5488" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5489" s="13"/>
+      <c r="B5489" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5489" s="18"/>
+    </row>
+    <row r="5490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5490" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5490" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5490" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5491" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5491" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5491" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5492" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5492" s="7"/>
+      <c r="C5492" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5493" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B5493" s="7"/>
+      <c r="C5493" s="2"/>
+    </row>
+    <row r="5494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5494" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B5494" s="7"/>
+      <c r="C5494" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5495" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B5495" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5495" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5496" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5496" s="9"/>
+      <c r="C5496" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="65">
+    <mergeCell ref="B5371:C5371"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5146"/>
+    <mergeCell ref="B5194:C5194"/>
+    <mergeCell ref="B5253:C5253"/>
+    <mergeCell ref="B5263:B5264"/>
+    <mergeCell ref="B5320:B5321"/>
+    <mergeCell ref="B4486:C4486"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4840:C4840"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="B5017:C5017"/>
+    <mergeCell ref="B5076:C5076"/>
     <mergeCell ref="B3955:C3955"/>
     <mergeCell ref="B4191:C4191"/>
     <mergeCell ref="B4201:B4202"/>
     <mergeCell ref="B4309:C4309"/>
+    <mergeCell ref="B4368:C4368"/>
+    <mergeCell ref="B4427:C4427"/>
     <mergeCell ref="B2952:C2952"/>
     <mergeCell ref="B3011:C3011"/>
     <mergeCell ref="B3070:C3070"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6085109C-7CC7-45E5-AF3A-95F1BA18C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DE6DDC-508C-4BEE-BAA0-ADC697C9A0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="9450" yWindow="420" windowWidth="16575" windowHeight="14745" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5748,13 +5748,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6382,10 +6382,10 @@
     </row>
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
-      <c r="B120" s="20" t="s">
+      <c r="B120" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C120" s="21"/>
+      <c r="C120" s="22"/>
     </row>
     <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
@@ -6507,10 +6507,10 @@
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
-      <c r="B179" s="20" t="s">
+      <c r="B179" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C179" s="21"/>
+      <c r="C179" s="22"/>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
@@ -6921,10 +6921,10 @@
     </row>
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
-      <c r="B356" s="20" t="s">
+      <c r="B356" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C356" s="21"/>
+      <c r="C356" s="22"/>
     </row>
     <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
@@ -7116,7 +7116,7 @@
       <c r="A425" s="3">
         <v>4.2</v>
       </c>
-      <c r="B425" s="22" t="s">
+      <c r="B425" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C425" s="2" t="s">
@@ -7125,7 +7125,7 @@
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
-      <c r="B426" s="22"/>
+      <c r="B426" s="20"/>
       <c r="C426" s="2"/>
     </row>
     <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7273,10 +7273,10 @@
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
-      <c r="B533" s="20" t="s">
+      <c r="B533" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C533" s="21"/>
+      <c r="C533" s="22"/>
     </row>
     <row r="534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
@@ -7528,30 +7528,30 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B601" s="7"/>
-      <c r="C601" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="C601" s="2"/>
     </row>
     <row r="602" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A602" s="3"/>
+      <c r="A602" s="3">
+        <v>4.2</v>
+      </c>
       <c r="B602" s="7"/>
-      <c r="C602" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="C602" s="2"/>
     </row>
     <row r="603" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="3">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="B603" s="7"/>
-      <c r="C603" s="2"/>
+      <c r="C603" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A604" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A604" s="3"/>
       <c r="B604" s="7"/>
-      <c r="C604" s="2"/>
+      <c r="C604" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="3">
@@ -7584,10 +7584,10 @@
     </row>
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
-      <c r="B651" s="20" t="s">
+      <c r="B651" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C651" s="21"/>
+      <c r="C651" s="22"/>
     </row>
     <row r="652" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="5" t="s">
@@ -7709,10 +7709,10 @@
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
-      <c r="B710" s="20" t="s">
+      <c r="B710" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C710" s="21"/>
+      <c r="C710" s="22"/>
     </row>
     <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="5" t="s">
@@ -7973,10 +7973,10 @@
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
-      <c r="B828" s="20" t="s">
+      <c r="B828" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C828" s="21"/>
+      <c r="C828" s="22"/>
     </row>
     <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="5" t="s">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
-      <c r="B1064" s="20" t="s">
+      <c r="B1064" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C1064" s="21"/>
+      <c r="C1064" s="22"/>
     </row>
     <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="5" t="s">
@@ -8779,10 +8779,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
-      <c r="B1123" s="20" t="s">
+      <c r="B1123" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C1123" s="21"/>
+      <c r="C1123" s="22"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="5" t="s">
@@ -8959,10 +8959,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
-      <c r="B1182" s="20" t="s">
+      <c r="B1182" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C1182" s="21"/>
+      <c r="C1182" s="22"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="5" t="s">
@@ -9082,10 +9082,10 @@
     </row>
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
-      <c r="B1241" s="20" t="s">
+      <c r="B1241" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C1241" s="21"/>
+      <c r="C1241" s="22"/>
     </row>
     <row r="1242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="5" t="s">
@@ -9225,10 +9225,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
-      <c r="B1300" s="20" t="s">
+      <c r="B1300" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C1300" s="21"/>
+      <c r="C1300" s="22"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="5" t="s">
@@ -9368,10 +9368,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
-      <c r="B1359" s="20" t="s">
+      <c r="B1359" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C1359" s="21"/>
+      <c r="C1359" s="22"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="5" t="s">
@@ -9462,7 +9462,7 @@
       <c r="A1369" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1369" s="22" t="s">
+      <c r="B1369" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C1369" s="2" t="s">
@@ -9471,7 +9471,7 @@
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="3"/>
-      <c r="B1370" s="22"/>
+      <c r="B1370" s="20"/>
       <c r="C1370" s="2"/>
     </row>
     <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9534,10 +9534,10 @@
     </row>
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
-      <c r="B1418" s="20" t="s">
+      <c r="B1418" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C1418" s="21"/>
+      <c r="C1418" s="22"/>
     </row>
     <row r="1419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1419" s="5" t="s">
@@ -9775,7 +9775,7 @@
       <c r="A1487" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1487" s="22" t="s">
+      <c r="B1487" s="20" t="s">
         <v>137</v>
       </c>
       <c r="C1487" s="2" t="s">
@@ -9784,7 +9784,7 @@
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1488" s="3"/>
-      <c r="B1488" s="22"/>
+      <c r="B1488" s="20"/>
       <c r="C1488" s="2"/>
     </row>
     <row r="1489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9825,10 +9825,10 @@
     </row>
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
-      <c r="B1536" s="20" t="s">
+      <c r="B1536" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C1536" s="21"/>
+      <c r="C1536" s="22"/>
     </row>
     <row r="1537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1537" s="5" t="s">
@@ -9937,7 +9937,7 @@
       <c r="A1548" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1548" s="22" t="s">
+      <c r="B1548" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C1548" s="2" t="s">
@@ -9946,7 +9946,7 @@
     </row>
     <row r="1549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1549" s="3"/>
-      <c r="B1549" s="22"/>
+      <c r="B1549" s="20"/>
       <c r="C1549" s="2"/>
     </row>
     <row r="1550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9962,7 +9962,7 @@
       <c r="A1551" s="3">
         <v>5.2</v>
       </c>
-      <c r="B1551" s="22" t="s">
+      <c r="B1551" s="20" t="s">
         <v>150</v>
       </c>
       <c r="C1551" s="2" t="s">
@@ -9971,7 +9971,7 @@
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1552" s="3"/>
-      <c r="B1552" s="22"/>
+      <c r="B1552" s="20"/>
       <c r="C1552" s="2"/>
     </row>
     <row r="1553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,10 +10012,10 @@
     </row>
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
-      <c r="B1595" s="20" t="s">
+      <c r="B1595" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C1595" s="21"/>
+      <c r="C1595" s="22"/>
     </row>
     <row r="1596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1596" s="5" t="s">
@@ -10450,10 +10450,10 @@
     </row>
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
-      <c r="B1831" s="20" t="s">
+      <c r="B1831" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="C1831" s="21"/>
+      <c r="C1831" s="22"/>
     </row>
     <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1832" s="5" t="s">
@@ -10877,10 +10877,10 @@
     </row>
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
-      <c r="B2008" s="20" t="s">
+      <c r="B2008" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C2008" s="21"/>
+      <c r="C2008" s="22"/>
     </row>
     <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2009" s="5" t="s">
@@ -11517,10 +11517,10 @@
     </row>
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
-      <c r="B2303" s="20" t="s">
+      <c r="B2303" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C2303" s="21"/>
+      <c r="C2303" s="22"/>
     </row>
     <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2304" s="5" t="s">
@@ -11611,7 +11611,7 @@
       <c r="A2313" s="3">
         <v>4.2</v>
       </c>
-      <c r="B2313" s="22" t="s">
+      <c r="B2313" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C2313" s="2" t="s">
@@ -11620,7 +11620,7 @@
     </row>
     <row r="2314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2314" s="3"/>
-      <c r="B2314" s="22"/>
+      <c r="B2314" s="20"/>
       <c r="C2314" s="2"/>
     </row>
     <row r="2315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11768,10 +11768,10 @@
     </row>
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
-      <c r="B2421" s="20" t="s">
+      <c r="B2421" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C2421" s="21"/>
+      <c r="C2421" s="22"/>
     </row>
     <row r="2422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2422" s="5" t="s">
@@ -12023,30 +12023,30 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B2489" s="7"/>
-      <c r="C2489" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="C2489" s="2"/>
     </row>
     <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2490" s="3"/>
+      <c r="A2490" s="3">
+        <v>4.2</v>
+      </c>
       <c r="B2490" s="7"/>
-      <c r="C2490" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="C2490" s="2"/>
     </row>
     <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2491" s="3">
-        <v>4.2</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="B2491" s="7"/>
-      <c r="C2491" s="2"/>
+      <c r="C2491" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2492" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A2492" s="3"/>
       <c r="B2492" s="7"/>
-      <c r="C2492" s="2"/>
+      <c r="C2492" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="2493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2493" s="3">
@@ -12079,10 +12079,10 @@
     </row>
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="13"/>
-      <c r="B2539" s="20" t="s">
+      <c r="B2539" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C2539" s="21"/>
+      <c r="C2539" s="22"/>
     </row>
     <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2540" s="5" t="s">
@@ -12151,14 +12151,14 @@
         <v>3.1</v>
       </c>
       <c r="B2546" s="7"/>
-      <c r="C2546" s="22" t="s">
+      <c r="C2546" s="20" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2547" s="3"/>
       <c r="B2547" s="7"/>
-      <c r="C2547" s="22"/>
+      <c r="C2547" s="20"/>
     </row>
     <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2548" s="3">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2598" s="13"/>
-      <c r="B2598" s="20" t="s">
+      <c r="B2598" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C2598" s="21"/>
+      <c r="C2598" s="22"/>
     </row>
     <row r="2599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2599" s="5" t="s">
@@ -12301,14 +12301,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B2607" s="7"/>
-      <c r="C2607" s="22" t="s">
+      <c r="C2607" s="20" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2608" s="3"/>
       <c r="B2608" s="7"/>
-      <c r="C2608" s="22"/>
+      <c r="C2608" s="20"/>
     </row>
     <row r="2609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2609" s="3">
@@ -13097,10 +13097,10 @@
     </row>
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="13"/>
-      <c r="B2952" s="20" t="s">
+      <c r="B2952" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C2952" s="21"/>
+      <c r="C2952" s="22"/>
     </row>
     <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2953" s="5" t="s">
@@ -13222,10 +13222,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="13"/>
-      <c r="B3011" s="20" t="s">
+      <c r="B3011" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C3011" s="21"/>
+      <c r="C3011" s="22"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="5" t="s">
@@ -13402,10 +13402,10 @@
     </row>
     <row r="3070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3070" s="13"/>
-      <c r="B3070" s="20" t="s">
+      <c r="B3070" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C3070" s="21"/>
+      <c r="C3070" s="22"/>
     </row>
     <row r="3071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3071" s="5" t="s">
@@ -13525,10 +13525,10 @@
     </row>
     <row r="3129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3129" s="13"/>
-      <c r="B3129" s="20" t="s">
+      <c r="B3129" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C3129" s="21"/>
+      <c r="C3129" s="22"/>
     </row>
     <row r="3130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3130" s="5" t="s">
@@ -13668,10 +13668,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="13"/>
-      <c r="B3188" s="20" t="s">
+      <c r="B3188" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C3188" s="21"/>
+      <c r="C3188" s="22"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="5" t="s">
@@ -13811,10 +13811,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="13"/>
-      <c r="B3247" s="20" t="s">
+      <c r="B3247" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C3247" s="21"/>
+      <c r="C3247" s="22"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="5" t="s">
@@ -13905,7 +13905,7 @@
       <c r="A3257" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3257" s="22" t="s">
+      <c r="B3257" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C3257" s="2" t="s">
@@ -13914,7 +13914,7 @@
     </row>
     <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3258" s="3"/>
-      <c r="B3258" s="22"/>
+      <c r="B3258" s="20"/>
       <c r="C3258" s="2"/>
     </row>
     <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13977,10 +13977,10 @@
     </row>
     <row r="3306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3306" s="13"/>
-      <c r="B3306" s="20" t="s">
+      <c r="B3306" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C3306" s="21"/>
+      <c r="C3306" s="22"/>
     </row>
     <row r="3307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3307" s="5" t="s">
@@ -14122,10 +14122,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="13"/>
-      <c r="B3365" s="20" t="s">
+      <c r="B3365" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C3365" s="21"/>
+      <c r="C3365" s="22"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="5" t="s">
@@ -14218,7 +14218,7 @@
       <c r="A3375" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3375" s="22" t="s">
+      <c r="B3375" s="20" t="s">
         <v>137</v>
       </c>
       <c r="C3375" s="2" t="s">
@@ -14227,7 +14227,7 @@
     </row>
     <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3376" s="3"/>
-      <c r="B3376" s="22"/>
+      <c r="B3376" s="20"/>
       <c r="C3376" s="2"/>
     </row>
     <row r="3377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14268,10 +14268,10 @@
     </row>
     <row r="3424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3424" s="13"/>
-      <c r="B3424" s="20" t="s">
+      <c r="B3424" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C3424" s="21"/>
+      <c r="C3424" s="22"/>
     </row>
     <row r="3425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3425" s="5" t="s">
@@ -14380,7 +14380,7 @@
       <c r="A3436" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3436" s="22" t="s">
+      <c r="B3436" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C3436" s="2" t="s">
@@ -14389,7 +14389,7 @@
     </row>
     <row r="3437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3437" s="3"/>
-      <c r="B3437" s="22"/>
+      <c r="B3437" s="20"/>
       <c r="C3437" s="2"/>
     </row>
     <row r="3438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14405,7 +14405,7 @@
       <c r="A3439" s="3">
         <v>5.2</v>
       </c>
-      <c r="B3439" s="22" t="s">
+      <c r="B3439" s="20" t="s">
         <v>150</v>
       </c>
       <c r="C3439" s="2" t="s">
@@ -14414,7 +14414,7 @@
     </row>
     <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3440" s="3"/>
-      <c r="B3440" s="22"/>
+      <c r="B3440" s="20"/>
       <c r="C3440" s="2"/>
     </row>
     <row r="3441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14455,10 +14455,10 @@
     </row>
     <row r="3483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3483" s="13"/>
-      <c r="B3483" s="20" t="s">
+      <c r="B3483" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C3483" s="21"/>
+      <c r="C3483" s="22"/>
     </row>
     <row r="3484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3484" s="5" t="s">
@@ -14543,14 +14543,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B3492" s="7"/>
-      <c r="C3492" s="22" t="s">
+      <c r="C3492" s="20" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="3493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3493" s="3"/>
       <c r="B3493" s="7"/>
-      <c r="C3493" s="22"/>
+      <c r="C3493" s="20"/>
     </row>
     <row r="3494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3494" s="3">
@@ -15339,10 +15339,10 @@
     </row>
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="13"/>
-      <c r="B3896" s="20" t="s">
+      <c r="B3896" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C3896" s="21"/>
+      <c r="C3896" s="22"/>
     </row>
     <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3897" s="5" t="s">
@@ -15464,10 +15464,10 @@
     </row>
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="13"/>
-      <c r="B3955" s="20" t="s">
+      <c r="B3955" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C3955" s="21"/>
+      <c r="C3955" s="22"/>
     </row>
     <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3956" s="5" t="s">
@@ -15979,10 +15979,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="13"/>
-      <c r="B4191" s="20" t="s">
+      <c r="B4191" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C4191" s="21"/>
+      <c r="C4191" s="22"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="5" t="s">
@@ -16073,7 +16073,7 @@
       <c r="A4201" s="3">
         <v>4.2</v>
       </c>
-      <c r="B4201" s="22" t="s">
+      <c r="B4201" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C4201" s="2" t="s">
@@ -16082,7 +16082,7 @@
     </row>
     <row r="4202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4202" s="3"/>
-      <c r="B4202" s="22"/>
+      <c r="B4202" s="20"/>
       <c r="C4202" s="2"/>
     </row>
     <row r="4203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16230,10 +16230,10 @@
     </row>
     <row r="4309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4309" s="13"/>
-      <c r="B4309" s="20" t="s">
+      <c r="B4309" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C4309" s="21"/>
+      <c r="C4309" s="22"/>
     </row>
     <row r="4310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4310" s="5" t="s">
@@ -16393,10 +16393,10 @@
     </row>
     <row r="4368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4368" s="13"/>
-      <c r="B4368" s="20" t="s">
+      <c r="B4368" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="C4368" s="21"/>
+      <c r="C4368" s="22"/>
     </row>
     <row r="4369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4369" s="5" t="s">
@@ -16527,10 +16527,10 @@
     </row>
     <row r="4427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4427" s="13"/>
-      <c r="B4427" s="20" t="s">
+      <c r="B4427" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C4427" s="21"/>
+      <c r="C4427" s="22"/>
     </row>
     <row r="4428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4428" s="5" t="s">
@@ -16652,10 +16652,10 @@
     </row>
     <row r="4486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4486" s="13"/>
-      <c r="B4486" s="20" t="s">
+      <c r="B4486" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C4486" s="21"/>
+      <c r="C4486" s="22"/>
     </row>
     <row r="4487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4487" s="5" t="s">
@@ -16916,10 +16916,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="13"/>
-      <c r="B4604" s="20" t="s">
+      <c r="B4604" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C4604" s="21"/>
+      <c r="C4604" s="22"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="5" t="s">
@@ -17561,10 +17561,10 @@
     </row>
     <row r="4840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4840" s="13"/>
-      <c r="B4840" s="20" t="s">
+      <c r="B4840" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C4840" s="21"/>
+      <c r="C4840" s="22"/>
     </row>
     <row r="4841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4841" s="5" t="s">
@@ -17866,10 +17866,10 @@
     </row>
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="13"/>
-      <c r="B4958" s="20" t="s">
+      <c r="B4958" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C4958" s="21"/>
+      <c r="C4958" s="22"/>
     </row>
     <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4959" s="5" t="s">
@@ -17989,10 +17989,10 @@
     </row>
     <row r="5017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5017" s="13"/>
-      <c r="B5017" s="20" t="s">
+      <c r="B5017" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C5017" s="21"/>
+      <c r="C5017" s="22"/>
     </row>
     <row r="5018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5018" s="5" t="s">
@@ -18132,10 +18132,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="13"/>
-      <c r="B5076" s="20" t="s">
+      <c r="B5076" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C5076" s="21"/>
+      <c r="C5076" s="22"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="5" t="s">
@@ -18275,10 +18275,10 @@
     </row>
     <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5135" s="13"/>
-      <c r="B5135" s="20" t="s">
+      <c r="B5135" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C5135" s="21"/>
+      <c r="C5135" s="22"/>
     </row>
     <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5136" s="5" t="s">
@@ -18369,7 +18369,7 @@
       <c r="A5145" s="3">
         <v>4.2</v>
       </c>
-      <c r="B5145" s="22" t="s">
+      <c r="B5145" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C5145" s="2" t="s">
@@ -18378,7 +18378,7 @@
     </row>
     <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5146" s="3"/>
-      <c r="B5146" s="22"/>
+      <c r="B5146" s="20"/>
       <c r="C5146" s="2"/>
     </row>
     <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18441,10 +18441,10 @@
     </row>
     <row r="5194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5194" s="13"/>
-      <c r="B5194" s="20" t="s">
+      <c r="B5194" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C5194" s="21"/>
+      <c r="C5194" s="22"/>
     </row>
     <row r="5195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5195" s="5" t="s">
@@ -18586,10 +18586,10 @@
     </row>
     <row r="5253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5253" s="13"/>
-      <c r="B5253" s="20" t="s">
+      <c r="B5253" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C5253" s="21"/>
+      <c r="C5253" s="22"/>
     </row>
     <row r="5254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5254" s="5" t="s">
@@ -18682,7 +18682,7 @@
       <c r="A5263" s="3">
         <v>4.2</v>
       </c>
-      <c r="B5263" s="22" t="s">
+      <c r="B5263" s="20" t="s">
         <v>137</v>
       </c>
       <c r="C5263" s="2" t="s">
@@ -18691,7 +18691,7 @@
     </row>
     <row r="5264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5264" s="3"/>
-      <c r="B5264" s="22"/>
+      <c r="B5264" s="20"/>
       <c r="C5264" s="2"/>
     </row>
     <row r="5265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18810,7 +18810,7 @@
       <c r="A5320" s="3">
         <v>3.2</v>
       </c>
-      <c r="B5320" s="22" t="s">
+      <c r="B5320" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C5320" s="2" t="s">
@@ -18819,7 +18819,7 @@
     </row>
     <row r="5321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5321" s="3"/>
-      <c r="B5321" s="22"/>
+      <c r="B5321" s="20"/>
       <c r="C5321" s="2"/>
     </row>
     <row r="5322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18862,10 +18862,10 @@
     </row>
     <row r="5371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5371" s="13"/>
-      <c r="B5371" s="20" t="s">
+      <c r="B5371" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C5371" s="21"/>
+      <c r="C5371" s="22"/>
     </row>
     <row r="5372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5372" s="5" t="s">
@@ -19677,10 +19677,10 @@
     </row>
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="13"/>
-      <c r="B5784" s="20" t="s">
+      <c r="B5784" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C5784" s="21"/>
+      <c r="C5784" s="22"/>
     </row>
     <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5785" s="5" t="s">
@@ -19802,10 +19802,10 @@
     </row>
     <row r="5843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5843" s="13"/>
-      <c r="B5843" s="20" t="s">
+      <c r="B5843" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C5843" s="21"/>
+      <c r="C5843" s="22"/>
     </row>
     <row r="5844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5844" s="5" t="s">
@@ -20317,10 +20317,10 @@
     </row>
     <row r="6079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6079" s="13"/>
-      <c r="B6079" s="20" t="s">
+      <c r="B6079" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="C6079" s="21"/>
+      <c r="C6079" s="22"/>
     </row>
     <row r="6080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6080" s="5" t="s">
@@ -20411,7 +20411,7 @@
       <c r="A6089" s="3">
         <v>4.2</v>
       </c>
-      <c r="B6089" s="22" t="s">
+      <c r="B6089" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C6089" s="2" t="s">
@@ -20420,7 +20420,7 @@
     </row>
     <row r="6090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6090" s="3"/>
-      <c r="B6090" s="22"/>
+      <c r="B6090" s="20"/>
       <c r="C6090" s="2"/>
     </row>
     <row r="6091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20568,10 +20568,10 @@
     </row>
     <row r="6197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6197" s="13"/>
-      <c r="B6197" s="20" t="s">
+      <c r="B6197" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="C6197" s="21"/>
+      <c r="C6197" s="22"/>
     </row>
     <row r="6198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6198" s="5" t="s">
@@ -20865,10 +20865,10 @@
     </row>
     <row r="6315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6315" s="13"/>
-      <c r="B6315" s="20" t="s">
+      <c r="B6315" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C6315" s="21"/>
+      <c r="C6315" s="22"/>
     </row>
     <row r="6316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6316" s="5" t="s">
@@ -20937,14 +20937,14 @@
         <v>3.1</v>
       </c>
       <c r="B6322" s="7"/>
-      <c r="C6322" s="22" t="s">
+      <c r="C6322" s="20" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="6323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6323" s="3"/>
       <c r="B6323" s="7"/>
-      <c r="C6323" s="22"/>
+      <c r="C6323" s="20"/>
     </row>
     <row r="6324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6324" s="3">
@@ -20995,10 +20995,10 @@
     </row>
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="13"/>
-      <c r="B6374" s="20" t="s">
+      <c r="B6374" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C6374" s="21"/>
+      <c r="C6374" s="22"/>
     </row>
     <row r="6375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6375" s="5" t="s">
@@ -21900,10 +21900,10 @@
     </row>
     <row r="6728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6728" s="13"/>
-      <c r="B6728" s="20" t="s">
+      <c r="B6728" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C6728" s="21"/>
+      <c r="C6728" s="22"/>
     </row>
     <row r="6729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6729" s="5" t="s">
@@ -22025,10 +22025,10 @@
     </row>
     <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6787" s="13"/>
-      <c r="B6787" s="20" t="s">
+      <c r="B6787" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C6787" s="21"/>
+      <c r="C6787" s="22"/>
     </row>
     <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6788" s="5" t="s">
@@ -22205,10 +22205,10 @@
     </row>
     <row r="6846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6846" s="13"/>
-      <c r="B6846" s="20" t="s">
+      <c r="B6846" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C6846" s="21"/>
+      <c r="C6846" s="22"/>
     </row>
     <row r="6847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6847" s="5" t="s">
@@ -22328,10 +22328,10 @@
     </row>
     <row r="6905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6905" s="13"/>
-      <c r="B6905" s="20" t="s">
+      <c r="B6905" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="C6905" s="21"/>
+      <c r="C6905" s="22"/>
     </row>
     <row r="6906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6906" s="5" t="s">
@@ -22471,10 +22471,10 @@
     </row>
     <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6964" s="13"/>
-      <c r="B6964" s="20" t="s">
+      <c r="B6964" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="C6964" s="21"/>
+      <c r="C6964" s="22"/>
     </row>
     <row r="6965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6965" s="5" t="s">
@@ -22614,10 +22614,10 @@
     </row>
     <row r="7023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7023" s="13"/>
-      <c r="B7023" s="20" t="s">
+      <c r="B7023" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C7023" s="21"/>
+      <c r="C7023" s="22"/>
     </row>
     <row r="7024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7024" s="5" t="s">
@@ -22708,7 +22708,7 @@
       <c r="A7033" s="3">
         <v>4.2</v>
       </c>
-      <c r="B7033" s="22" t="s">
+      <c r="B7033" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C7033" s="2" t="s">
@@ -22717,7 +22717,7 @@
     </row>
     <row r="7034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7034" s="3"/>
-      <c r="B7034" s="22"/>
+      <c r="B7034" s="20"/>
       <c r="C7034" s="2"/>
     </row>
     <row r="7035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,10 +22780,10 @@
     </row>
     <row r="7082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7082" s="13"/>
-      <c r="B7082" s="20" t="s">
+      <c r="B7082" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="C7082" s="21"/>
+      <c r="C7082" s="22"/>
     </row>
     <row r="7083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7083" s="5" t="s">
@@ -22925,10 +22925,10 @@
     </row>
     <row r="7141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7141" s="13"/>
-      <c r="B7141" s="20" t="s">
+      <c r="B7141" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C7141" s="21"/>
+      <c r="C7141" s="22"/>
     </row>
     <row r="7142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7142" s="5" t="s">
@@ -23021,7 +23021,7 @@
       <c r="A7151" s="3">
         <v>4.2</v>
       </c>
-      <c r="B7151" s="22" t="s">
+      <c r="B7151" s="20" t="s">
         <v>137</v>
       </c>
       <c r="C7151" s="2" t="s">
@@ -23030,7 +23030,7 @@
     </row>
     <row r="7152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7152" s="3"/>
-      <c r="B7152" s="22"/>
+      <c r="B7152" s="20"/>
       <c r="C7152" s="2"/>
     </row>
     <row r="7153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23060,56 +23060,11 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="B7151:B7152"/>
-    <mergeCell ref="B7141:C7141"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="B6846:C6846"/>
-    <mergeCell ref="B6905:C6905"/>
-    <mergeCell ref="B6964:C6964"/>
-    <mergeCell ref="B7023:C7023"/>
-    <mergeCell ref="B7033:B7034"/>
-    <mergeCell ref="B7082:C7082"/>
-    <mergeCell ref="B5371:C5371"/>
-    <mergeCell ref="B5784:C5784"/>
-    <mergeCell ref="B5843:C5843"/>
-    <mergeCell ref="B6079:C6079"/>
-    <mergeCell ref="B6089:B6090"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5146"/>
-    <mergeCell ref="B5194:C5194"/>
-    <mergeCell ref="B5253:C5253"/>
-    <mergeCell ref="B5263:B5264"/>
-    <mergeCell ref="B5320:B5321"/>
-    <mergeCell ref="B4486:C4486"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4840:C4840"/>
-    <mergeCell ref="B4958:C4958"/>
-    <mergeCell ref="B5017:C5017"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="B4201:B4202"/>
-    <mergeCell ref="B4309:C4309"/>
-    <mergeCell ref="B4368:C4368"/>
-    <mergeCell ref="B4427:C4427"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="B3070:C3070"/>
-    <mergeCell ref="B3129:C3129"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="B3257:B3258"/>
-    <mergeCell ref="B3306:C3306"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="B425:B426"/>
-    <mergeCell ref="B533:C533"/>
-    <mergeCell ref="B651:C651"/>
-    <mergeCell ref="B710:C710"/>
-    <mergeCell ref="B356:C356"/>
-    <mergeCell ref="B6197:C6197"/>
-    <mergeCell ref="B6315:C6315"/>
-    <mergeCell ref="C6322:C6323"/>
+    <mergeCell ref="B1595:C1595"/>
+    <mergeCell ref="B1548:B1549"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="B3375:B3376"/>
     <mergeCell ref="B6374:C6374"/>
     <mergeCell ref="B6728:C6728"/>
     <mergeCell ref="B1831:C1831"/>
@@ -23120,6 +23075,17 @@
     <mergeCell ref="B2539:C2539"/>
     <mergeCell ref="C2546:C2547"/>
     <mergeCell ref="B2598:C2598"/>
+    <mergeCell ref="C2607:C2608"/>
+    <mergeCell ref="B3424:C3424"/>
+    <mergeCell ref="B3436:B3437"/>
+    <mergeCell ref="B3439:B3440"/>
+    <mergeCell ref="B3483:C3483"/>
+    <mergeCell ref="C3492:C3493"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B356:C356"/>
+    <mergeCell ref="B6197:C6197"/>
+    <mergeCell ref="B6315:C6315"/>
+    <mergeCell ref="C6322:C6323"/>
     <mergeCell ref="B1064:C1064"/>
     <mergeCell ref="B1123:C1123"/>
     <mergeCell ref="B1182:C1182"/>
@@ -23129,20 +23095,54 @@
     <mergeCell ref="B1300:C1300"/>
     <mergeCell ref="B1418:C1418"/>
     <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="C2607:C2608"/>
     <mergeCell ref="B828:C828"/>
     <mergeCell ref="B1536:C1536"/>
-    <mergeCell ref="B1595:C1595"/>
-    <mergeCell ref="B1548:B1549"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="B3375:B3376"/>
-    <mergeCell ref="B3424:C3424"/>
-    <mergeCell ref="B3436:B3437"/>
-    <mergeCell ref="B3439:B3440"/>
-    <mergeCell ref="B3483:C3483"/>
-    <mergeCell ref="C3492:C3493"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B425:B426"/>
+    <mergeCell ref="B533:C533"/>
+    <mergeCell ref="B651:C651"/>
+    <mergeCell ref="B4427:C4427"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B3070:C3070"/>
+    <mergeCell ref="B3129:C3129"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B3257:B3258"/>
+    <mergeCell ref="B3306:C3306"/>
     <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4201:B4202"/>
+    <mergeCell ref="B4309:C4309"/>
+    <mergeCell ref="B4368:C4368"/>
+    <mergeCell ref="B5320:B5321"/>
+    <mergeCell ref="B4486:C4486"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4840:C4840"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="B5017:C5017"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5146"/>
+    <mergeCell ref="B5194:C5194"/>
+    <mergeCell ref="B5253:C5253"/>
+    <mergeCell ref="B5263:B5264"/>
+    <mergeCell ref="B5371:C5371"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B5843:C5843"/>
+    <mergeCell ref="B6079:C6079"/>
+    <mergeCell ref="B6089:B6090"/>
+    <mergeCell ref="B7151:B7152"/>
+    <mergeCell ref="B7141:C7141"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="B6846:C6846"/>
+    <mergeCell ref="B6905:C6905"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7034"/>
+    <mergeCell ref="B7082:C7082"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DE6DDC-508C-4BEE-BAA0-ADC697C9A0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487C70B7-6801-4E42-919B-E5022E7D4F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9450" yWindow="420" windowWidth="16575" windowHeight="14745" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7165</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7259</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="322">
   <si>
     <t>Implied</t>
   </si>
@@ -5524,6 +5524,306 @@
   </si>
   <si>
     <t>CMP (79)</t>
+  </si>
+  <si>
+    <t>ADDW (7A)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (YA == $0000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(Operand16.L).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Tmp &gt; $FF).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = u8(Tmp).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(Operand16.H) + u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ Operand16.H ^ u8(Tmp)) &amp; $10).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ Operand16.H) &amp; (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ u8(Tmp)) &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (u8(Tmp) &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = u8(Tmp).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5748,13 +6048,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6091,7 +6391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C7155"/>
+  <dimension ref="A1:C7223"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -6382,10 +6682,10 @@
     </row>
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
-      <c r="B120" s="21" t="s">
+      <c r="B120" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C120" s="22"/>
+      <c r="C120" s="21"/>
     </row>
     <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
@@ -6507,10 +6807,10 @@
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="13"/>
-      <c r="B179" s="21" t="s">
+      <c r="B179" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C179" s="22"/>
+      <c r="C179" s="21"/>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
@@ -6921,10 +7221,10 @@
     </row>
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="13"/>
-      <c r="B356" s="21" t="s">
+      <c r="B356" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C356" s="22"/>
+      <c r="C356" s="21"/>
     </row>
     <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
@@ -7116,7 +7416,7 @@
       <c r="A425" s="3">
         <v>4.2</v>
       </c>
-      <c r="B425" s="20" t="s">
+      <c r="B425" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C425" s="2" t="s">
@@ -7125,7 +7425,7 @@
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="3"/>
-      <c r="B426" s="20"/>
+      <c r="B426" s="22"/>
       <c r="C426" s="2"/>
     </row>
     <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7273,10 +7573,10 @@
     </row>
     <row r="533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="13"/>
-      <c r="B533" s="21" t="s">
+      <c r="B533" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C533" s="22"/>
+      <c r="C533" s="21"/>
     </row>
     <row r="534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="5" t="s">
@@ -7584,10 +7884,10 @@
     </row>
     <row r="651" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="13"/>
-      <c r="B651" s="21" t="s">
+      <c r="B651" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C651" s="22"/>
+      <c r="C651" s="21"/>
     </row>
     <row r="652" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="5" t="s">
@@ -7709,10 +8009,10 @@
     </row>
     <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="13"/>
-      <c r="B710" s="21" t="s">
+      <c r="B710" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C710" s="22"/>
+      <c r="C710" s="21"/>
     </row>
     <row r="711" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="5" t="s">
@@ -7973,10 +8273,10 @@
     </row>
     <row r="828" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="13"/>
-      <c r="B828" s="21" t="s">
+      <c r="B828" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C828" s="22"/>
+      <c r="C828" s="21"/>
     </row>
     <row r="829" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="5" t="s">
@@ -8654,10 +8954,10 @@
     </row>
     <row r="1064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="13"/>
-      <c r="B1064" s="21" t="s">
+      <c r="B1064" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C1064" s="22"/>
+      <c r="C1064" s="21"/>
     </row>
     <row r="1065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="5" t="s">
@@ -8779,10 +9079,10 @@
     </row>
     <row r="1123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1123" s="13"/>
-      <c r="B1123" s="21" t="s">
+      <c r="B1123" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C1123" s="22"/>
+      <c r="C1123" s="21"/>
     </row>
     <row r="1124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1124" s="5" t="s">
@@ -8959,10 +9259,10 @@
     </row>
     <row r="1182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1182" s="13"/>
-      <c r="B1182" s="21" t="s">
+      <c r="B1182" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C1182" s="22"/>
+      <c r="C1182" s="21"/>
     </row>
     <row r="1183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1183" s="5" t="s">
@@ -9082,10 +9382,10 @@
     </row>
     <row r="1241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="13"/>
-      <c r="B1241" s="21" t="s">
+      <c r="B1241" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C1241" s="22"/>
+      <c r="C1241" s="21"/>
     </row>
     <row r="1242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="5" t="s">
@@ -9225,10 +9525,10 @@
     </row>
     <row r="1300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="13"/>
-      <c r="B1300" s="21" t="s">
+      <c r="B1300" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C1300" s="22"/>
+      <c r="C1300" s="21"/>
     </row>
     <row r="1301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="5" t="s">
@@ -9368,10 +9668,10 @@
     </row>
     <row r="1359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1359" s="13"/>
-      <c r="B1359" s="21" t="s">
+      <c r="B1359" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C1359" s="22"/>
+      <c r="C1359" s="21"/>
     </row>
     <row r="1360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1360" s="5" t="s">
@@ -9462,7 +9762,7 @@
       <c r="A1369" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1369" s="20" t="s">
+      <c r="B1369" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C1369" s="2" t="s">
@@ -9471,7 +9771,7 @@
     </row>
     <row r="1370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1370" s="3"/>
-      <c r="B1370" s="20"/>
+      <c r="B1370" s="22"/>
       <c r="C1370" s="2"/>
     </row>
     <row r="1371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9534,10 +9834,10 @@
     </row>
     <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1418" s="13"/>
-      <c r="B1418" s="21" t="s">
+      <c r="B1418" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C1418" s="22"/>
+      <c r="C1418" s="21"/>
     </row>
     <row r="1419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1419" s="5" t="s">
@@ -9775,7 +10075,7 @@
       <c r="A1487" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1487" s="20" t="s">
+      <c r="B1487" s="22" t="s">
         <v>137</v>
       </c>
       <c r="C1487" s="2" t="s">
@@ -9784,7 +10084,7 @@
     </row>
     <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1488" s="3"/>
-      <c r="B1488" s="20"/>
+      <c r="B1488" s="22"/>
       <c r="C1488" s="2"/>
     </row>
     <row r="1489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9825,10 +10125,10 @@
     </row>
     <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1536" s="13"/>
-      <c r="B1536" s="21" t="s">
+      <c r="B1536" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C1536" s="22"/>
+      <c r="C1536" s="21"/>
     </row>
     <row r="1537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1537" s="5" t="s">
@@ -9937,7 +10237,7 @@
       <c r="A1548" s="3">
         <v>4.2</v>
       </c>
-      <c r="B1548" s="20" t="s">
+      <c r="B1548" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C1548" s="2" t="s">
@@ -9946,7 +10246,7 @@
     </row>
     <row r="1549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1549" s="3"/>
-      <c r="B1549" s="20"/>
+      <c r="B1549" s="22"/>
       <c r="C1549" s="2"/>
     </row>
     <row r="1550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9962,7 +10262,7 @@
       <c r="A1551" s="3">
         <v>5.2</v>
       </c>
-      <c r="B1551" s="20" t="s">
+      <c r="B1551" s="22" t="s">
         <v>150</v>
       </c>
       <c r="C1551" s="2" t="s">
@@ -9971,7 +10271,7 @@
     </row>
     <row r="1552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1552" s="3"/>
-      <c r="B1552" s="20"/>
+      <c r="B1552" s="22"/>
       <c r="C1552" s="2"/>
     </row>
     <row r="1553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10012,10 +10312,10 @@
     </row>
     <row r="1595" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1595" s="13"/>
-      <c r="B1595" s="21" t="s">
+      <c r="B1595" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C1595" s="22"/>
+      <c r="C1595" s="21"/>
     </row>
     <row r="1596" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1596" s="5" t="s">
@@ -10450,10 +10750,10 @@
     </row>
     <row r="1831" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1831" s="13"/>
-      <c r="B1831" s="21" t="s">
+      <c r="B1831" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C1831" s="22"/>
+      <c r="C1831" s="21"/>
     </row>
     <row r="1832" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1832" s="5" t="s">
@@ -10877,10 +11177,10 @@
     </row>
     <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2008" s="13"/>
-      <c r="B2008" s="21" t="s">
+      <c r="B2008" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C2008" s="22"/>
+      <c r="C2008" s="21"/>
     </row>
     <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2009" s="5" t="s">
@@ -11517,10 +11817,10 @@
     </row>
     <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2303" s="13"/>
-      <c r="B2303" s="21" t="s">
+      <c r="B2303" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C2303" s="22"/>
+      <c r="C2303" s="21"/>
     </row>
     <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2304" s="5" t="s">
@@ -11611,7 +11911,7 @@
       <c r="A2313" s="3">
         <v>4.2</v>
       </c>
-      <c r="B2313" s="20" t="s">
+      <c r="B2313" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C2313" s="2" t="s">
@@ -11620,7 +11920,7 @@
     </row>
     <row r="2314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2314" s="3"/>
-      <c r="B2314" s="20"/>
+      <c r="B2314" s="22"/>
       <c r="C2314" s="2"/>
     </row>
     <row r="2315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11768,10 +12068,10 @@
     </row>
     <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2421" s="13"/>
-      <c r="B2421" s="21" t="s">
+      <c r="B2421" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C2421" s="22"/>
+      <c r="C2421" s="21"/>
     </row>
     <row r="2422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2422" s="5" t="s">
@@ -12079,10 +12379,10 @@
     </row>
     <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2539" s="13"/>
-      <c r="B2539" s="21" t="s">
+      <c r="B2539" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C2539" s="22"/>
+      <c r="C2539" s="21"/>
     </row>
     <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2540" s="5" t="s">
@@ -12151,14 +12451,14 @@
         <v>3.1</v>
       </c>
       <c r="B2546" s="7"/>
-      <c r="C2546" s="20" t="s">
+      <c r="C2546" s="22" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2547" s="3"/>
       <c r="B2547" s="7"/>
-      <c r="C2547" s="20"/>
+      <c r="C2547" s="22"/>
     </row>
     <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2548" s="3">
@@ -12209,10 +12509,10 @@
     </row>
     <row r="2598" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2598" s="13"/>
-      <c r="B2598" s="21" t="s">
+      <c r="B2598" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C2598" s="22"/>
+      <c r="C2598" s="21"/>
     </row>
     <row r="2599" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2599" s="5" t="s">
@@ -12301,14 +12601,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B2607" s="7"/>
-      <c r="C2607" s="20" t="s">
+      <c r="C2607" s="22" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="2608" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2608" s="3"/>
       <c r="B2608" s="7"/>
-      <c r="C2608" s="20"/>
+      <c r="C2608" s="22"/>
     </row>
     <row r="2609" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2609" s="3">
@@ -13097,10 +13397,10 @@
     </row>
     <row r="2952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2952" s="13"/>
-      <c r="B2952" s="21" t="s">
+      <c r="B2952" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C2952" s="22"/>
+      <c r="C2952" s="21"/>
     </row>
     <row r="2953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2953" s="5" t="s">
@@ -13222,10 +13522,10 @@
     </row>
     <row r="3011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3011" s="13"/>
-      <c r="B3011" s="21" t="s">
+      <c r="B3011" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C3011" s="22"/>
+      <c r="C3011" s="21"/>
     </row>
     <row r="3012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3012" s="5" t="s">
@@ -13402,10 +13702,10 @@
     </row>
     <row r="3070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3070" s="13"/>
-      <c r="B3070" s="21" t="s">
+      <c r="B3070" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C3070" s="22"/>
+      <c r="C3070" s="21"/>
     </row>
     <row r="3071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3071" s="5" t="s">
@@ -13525,10 +13825,10 @@
     </row>
     <row r="3129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3129" s="13"/>
-      <c r="B3129" s="21" t="s">
+      <c r="B3129" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C3129" s="22"/>
+      <c r="C3129" s="21"/>
     </row>
     <row r="3130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3130" s="5" t="s">
@@ -13668,10 +13968,10 @@
     </row>
     <row r="3188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3188" s="13"/>
-      <c r="B3188" s="21" t="s">
+      <c r="B3188" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C3188" s="22"/>
+      <c r="C3188" s="21"/>
     </row>
     <row r="3189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3189" s="5" t="s">
@@ -13811,10 +14111,10 @@
     </row>
     <row r="3247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3247" s="13"/>
-      <c r="B3247" s="21" t="s">
+      <c r="B3247" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C3247" s="22"/>
+      <c r="C3247" s="21"/>
     </row>
     <row r="3248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3248" s="5" t="s">
@@ -13905,7 +14205,7 @@
       <c r="A3257" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3257" s="20" t="s">
+      <c r="B3257" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C3257" s="2" t="s">
@@ -13914,7 +14214,7 @@
     </row>
     <row r="3258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3258" s="3"/>
-      <c r="B3258" s="20"/>
+      <c r="B3258" s="22"/>
       <c r="C3258" s="2"/>
     </row>
     <row r="3259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13977,10 +14277,10 @@
     </row>
     <row r="3306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3306" s="13"/>
-      <c r="B3306" s="21" t="s">
+      <c r="B3306" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C3306" s="22"/>
+      <c r="C3306" s="21"/>
     </row>
     <row r="3307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3307" s="5" t="s">
@@ -14122,10 +14422,10 @@
     </row>
     <row r="3365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3365" s="13"/>
-      <c r="B3365" s="21" t="s">
+      <c r="B3365" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C3365" s="22"/>
+      <c r="C3365" s="21"/>
     </row>
     <row r="3366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3366" s="5" t="s">
@@ -14218,7 +14518,7 @@
       <c r="A3375" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3375" s="20" t="s">
+      <c r="B3375" s="22" t="s">
         <v>137</v>
       </c>
       <c r="C3375" s="2" t="s">
@@ -14227,7 +14527,7 @@
     </row>
     <row r="3376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3376" s="3"/>
-      <c r="B3376" s="20"/>
+      <c r="B3376" s="22"/>
       <c r="C3376" s="2"/>
     </row>
     <row r="3377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14268,10 +14568,10 @@
     </row>
     <row r="3424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3424" s="13"/>
-      <c r="B3424" s="21" t="s">
+      <c r="B3424" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C3424" s="22"/>
+      <c r="C3424" s="21"/>
     </row>
     <row r="3425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3425" s="5" t="s">
@@ -14380,7 +14680,7 @@
       <c r="A3436" s="3">
         <v>4.2</v>
       </c>
-      <c r="B3436" s="20" t="s">
+      <c r="B3436" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C3436" s="2" t="s">
@@ -14389,7 +14689,7 @@
     </row>
     <row r="3437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3437" s="3"/>
-      <c r="B3437" s="20"/>
+      <c r="B3437" s="22"/>
       <c r="C3437" s="2"/>
     </row>
     <row r="3438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14405,7 +14705,7 @@
       <c r="A3439" s="3">
         <v>5.2</v>
       </c>
-      <c r="B3439" s="20" t="s">
+      <c r="B3439" s="22" t="s">
         <v>150</v>
       </c>
       <c r="C3439" s="2" t="s">
@@ -14414,7 +14714,7 @@
     </row>
     <row r="3440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3440" s="3"/>
-      <c r="B3440" s="20"/>
+      <c r="B3440" s="22"/>
       <c r="C3440" s="2"/>
     </row>
     <row r="3441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -14455,10 +14755,10 @@
     </row>
     <row r="3483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3483" s="13"/>
-      <c r="B3483" s="21" t="s">
+      <c r="B3483" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C3483" s="22"/>
+      <c r="C3483" s="21"/>
     </row>
     <row r="3484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3484" s="5" t="s">
@@ -14543,14 +14843,14 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B3492" s="7"/>
-      <c r="C3492" s="20" t="s">
+      <c r="C3492" s="22" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="3493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3493" s="3"/>
       <c r="B3493" s="7"/>
-      <c r="C3493" s="20"/>
+      <c r="C3493" s="22"/>
     </row>
     <row r="3494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3494" s="3">
@@ -15339,10 +15639,10 @@
     </row>
     <row r="3896" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3896" s="13"/>
-      <c r="B3896" s="21" t="s">
+      <c r="B3896" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C3896" s="22"/>
+      <c r="C3896" s="21"/>
     </row>
     <row r="3897" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3897" s="5" t="s">
@@ -15464,10 +15764,10 @@
     </row>
     <row r="3955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3955" s="13"/>
-      <c r="B3955" s="21" t="s">
+      <c r="B3955" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C3955" s="22"/>
+      <c r="C3955" s="21"/>
     </row>
     <row r="3956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3956" s="5" t="s">
@@ -15979,10 +16279,10 @@
     </row>
     <row r="4191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4191" s="13"/>
-      <c r="B4191" s="21" t="s">
+      <c r="B4191" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C4191" s="22"/>
+      <c r="C4191" s="21"/>
     </row>
     <row r="4192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4192" s="5" t="s">
@@ -16073,7 +16373,7 @@
       <c r="A4201" s="3">
         <v>4.2</v>
       </c>
-      <c r="B4201" s="20" t="s">
+      <c r="B4201" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C4201" s="2" t="s">
@@ -16082,7 +16382,7 @@
     </row>
     <row r="4202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4202" s="3"/>
-      <c r="B4202" s="20"/>
+      <c r="B4202" s="22"/>
       <c r="C4202" s="2"/>
     </row>
     <row r="4203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16230,10 +16530,10 @@
     </row>
     <row r="4309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4309" s="13"/>
-      <c r="B4309" s="21" t="s">
+      <c r="B4309" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C4309" s="22"/>
+      <c r="C4309" s="21"/>
     </row>
     <row r="4310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4310" s="5" t="s">
@@ -16393,10 +16693,10 @@
     </row>
     <row r="4368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4368" s="13"/>
-      <c r="B4368" s="21" t="s">
+      <c r="B4368" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="C4368" s="22"/>
+      <c r="C4368" s="21"/>
     </row>
     <row r="4369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4369" s="5" t="s">
@@ -16527,10 +16827,10 @@
     </row>
     <row r="4427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4427" s="13"/>
-      <c r="B4427" s="21" t="s">
+      <c r="B4427" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C4427" s="22"/>
+      <c r="C4427" s="21"/>
     </row>
     <row r="4428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4428" s="5" t="s">
@@ -16652,10 +16952,10 @@
     </row>
     <row r="4486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4486" s="13"/>
-      <c r="B4486" s="21" t="s">
+      <c r="B4486" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C4486" s="22"/>
+      <c r="C4486" s="21"/>
     </row>
     <row r="4487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4487" s="5" t="s">
@@ -16916,10 +17216,10 @@
     </row>
     <row r="4604" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4604" s="13"/>
-      <c r="B4604" s="21" t="s">
+      <c r="B4604" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C4604" s="22"/>
+      <c r="C4604" s="21"/>
     </row>
     <row r="4605" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4605" s="5" t="s">
@@ -17561,10 +17861,10 @@
     </row>
     <row r="4840" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4840" s="13"/>
-      <c r="B4840" s="21" t="s">
+      <c r="B4840" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C4840" s="22"/>
+      <c r="C4840" s="21"/>
     </row>
     <row r="4841" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4841" s="5" t="s">
@@ -17866,10 +18166,10 @@
     </row>
     <row r="4958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4958" s="13"/>
-      <c r="B4958" s="21" t="s">
+      <c r="B4958" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C4958" s="22"/>
+      <c r="C4958" s="21"/>
     </row>
     <row r="4959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4959" s="5" t="s">
@@ -17989,10 +18289,10 @@
     </row>
     <row r="5017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5017" s="13"/>
-      <c r="B5017" s="21" t="s">
+      <c r="B5017" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C5017" s="22"/>
+      <c r="C5017" s="21"/>
     </row>
     <row r="5018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5018" s="5" t="s">
@@ -18132,10 +18432,10 @@
     </row>
     <row r="5076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5076" s="13"/>
-      <c r="B5076" s="21" t="s">
+      <c r="B5076" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C5076" s="22"/>
+      <c r="C5076" s="21"/>
     </row>
     <row r="5077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5077" s="5" t="s">
@@ -18275,10 +18575,10 @@
     </row>
     <row r="5135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5135" s="13"/>
-      <c r="B5135" s="21" t="s">
+      <c r="B5135" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C5135" s="22"/>
+      <c r="C5135" s="21"/>
     </row>
     <row r="5136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5136" s="5" t="s">
@@ -18369,7 +18669,7 @@
       <c r="A5145" s="3">
         <v>4.2</v>
       </c>
-      <c r="B5145" s="20" t="s">
+      <c r="B5145" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C5145" s="2" t="s">
@@ -18378,7 +18678,7 @@
     </row>
     <row r="5146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5146" s="3"/>
-      <c r="B5146" s="20"/>
+      <c r="B5146" s="22"/>
       <c r="C5146" s="2"/>
     </row>
     <row r="5147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18441,10 +18741,10 @@
     </row>
     <row r="5194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5194" s="13"/>
-      <c r="B5194" s="21" t="s">
+      <c r="B5194" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C5194" s="22"/>
+      <c r="C5194" s="21"/>
     </row>
     <row r="5195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5195" s="5" t="s">
@@ -18586,10 +18886,10 @@
     </row>
     <row r="5253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5253" s="13"/>
-      <c r="B5253" s="21" t="s">
+      <c r="B5253" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C5253" s="22"/>
+      <c r="C5253" s="21"/>
     </row>
     <row r="5254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5254" s="5" t="s">
@@ -18682,7 +18982,7 @@
       <c r="A5263" s="3">
         <v>4.2</v>
       </c>
-      <c r="B5263" s="20" t="s">
+      <c r="B5263" s="22" t="s">
         <v>137</v>
       </c>
       <c r="C5263" s="2" t="s">
@@ -18691,7 +18991,7 @@
     </row>
     <row r="5264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5264" s="3"/>
-      <c r="B5264" s="20"/>
+      <c r="B5264" s="22"/>
       <c r="C5264" s="2"/>
     </row>
     <row r="5265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18810,7 +19110,7 @@
       <c r="A5320" s="3">
         <v>3.2</v>
       </c>
-      <c r="B5320" s="20" t="s">
+      <c r="B5320" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C5320" s="2" t="s">
@@ -18819,7 +19119,7 @@
     </row>
     <row r="5321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5321" s="3"/>
-      <c r="B5321" s="20"/>
+      <c r="B5321" s="22"/>
       <c r="C5321" s="2"/>
     </row>
     <row r="5322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18862,10 +19162,10 @@
     </row>
     <row r="5371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5371" s="13"/>
-      <c r="B5371" s="21" t="s">
+      <c r="B5371" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C5371" s="22"/>
+      <c r="C5371" s="21"/>
     </row>
     <row r="5372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5372" s="5" t="s">
@@ -19677,10 +19977,10 @@
     </row>
     <row r="5784" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5784" s="13"/>
-      <c r="B5784" s="21" t="s">
+      <c r="B5784" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C5784" s="22"/>
+      <c r="C5784" s="21"/>
     </row>
     <row r="5785" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5785" s="5" t="s">
@@ -19802,10 +20102,10 @@
     </row>
     <row r="5843" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5843" s="13"/>
-      <c r="B5843" s="21" t="s">
+      <c r="B5843" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C5843" s="22"/>
+      <c r="C5843" s="21"/>
     </row>
     <row r="5844" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5844" s="5" t="s">
@@ -20317,10 +20617,10 @@
     </row>
     <row r="6079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6079" s="13"/>
-      <c r="B6079" s="21" t="s">
+      <c r="B6079" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="C6079" s="22"/>
+      <c r="C6079" s="21"/>
     </row>
     <row r="6080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6080" s="5" t="s">
@@ -20411,7 +20711,7 @@
       <c r="A6089" s="3">
         <v>4.2</v>
       </c>
-      <c r="B6089" s="20" t="s">
+      <c r="B6089" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C6089" s="2" t="s">
@@ -20420,7 +20720,7 @@
     </row>
     <row r="6090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6090" s="3"/>
-      <c r="B6090" s="20"/>
+      <c r="B6090" s="22"/>
       <c r="C6090" s="2"/>
     </row>
     <row r="6091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20568,10 +20868,10 @@
     </row>
     <row r="6197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6197" s="13"/>
-      <c r="B6197" s="21" t="s">
+      <c r="B6197" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="C6197" s="22"/>
+      <c r="C6197" s="21"/>
     </row>
     <row r="6198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6198" s="5" t="s">
@@ -20865,10 +21165,10 @@
     </row>
     <row r="6315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6315" s="13"/>
-      <c r="B6315" s="21" t="s">
+      <c r="B6315" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C6315" s="22"/>
+      <c r="C6315" s="21"/>
     </row>
     <row r="6316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6316" s="5" t="s">
@@ -20937,14 +21237,14 @@
         <v>3.1</v>
       </c>
       <c r="B6322" s="7"/>
-      <c r="C6322" s="20" t="s">
+      <c r="C6322" s="22" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="6323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6323" s="3"/>
       <c r="B6323" s="7"/>
-      <c r="C6323" s="20"/>
+      <c r="C6323" s="22"/>
     </row>
     <row r="6324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6324" s="3">
@@ -20995,10 +21295,10 @@
     </row>
     <row r="6374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6374" s="13"/>
-      <c r="B6374" s="21" t="s">
+      <c r="B6374" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C6374" s="22"/>
+      <c r="C6374" s="21"/>
     </row>
     <row r="6375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6375" s="5" t="s">
@@ -21900,10 +22200,10 @@
     </row>
     <row r="6728" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6728" s="13"/>
-      <c r="B6728" s="21" t="s">
+      <c r="B6728" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="C6728" s="22"/>
+      <c r="C6728" s="21"/>
     </row>
     <row r="6729" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6729" s="5" t="s">
@@ -22025,10 +22325,10 @@
     </row>
     <row r="6787" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6787" s="13"/>
-      <c r="B6787" s="21" t="s">
+      <c r="B6787" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="C6787" s="22"/>
+      <c r="C6787" s="21"/>
     </row>
     <row r="6788" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6788" s="5" t="s">
@@ -22205,10 +22505,10 @@
     </row>
     <row r="6846" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6846" s="13"/>
-      <c r="B6846" s="21" t="s">
+      <c r="B6846" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="C6846" s="22"/>
+      <c r="C6846" s="21"/>
     </row>
     <row r="6847" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6847" s="5" t="s">
@@ -22328,10 +22628,10 @@
     </row>
     <row r="6905" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6905" s="13"/>
-      <c r="B6905" s="21" t="s">
+      <c r="B6905" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C6905" s="22"/>
+      <c r="C6905" s="21"/>
     </row>
     <row r="6906" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6906" s="5" t="s">
@@ -22471,10 +22771,10 @@
     </row>
     <row r="6964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6964" s="13"/>
-      <c r="B6964" s="21" t="s">
+      <c r="B6964" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C6964" s="22"/>
+      <c r="C6964" s="21"/>
     </row>
     <row r="6965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6965" s="5" t="s">
@@ -22614,10 +22914,10 @@
     </row>
     <row r="7023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7023" s="13"/>
-      <c r="B7023" s="21" t="s">
+      <c r="B7023" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="C7023" s="22"/>
+      <c r="C7023" s="21"/>
     </row>
     <row r="7024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7024" s="5" t="s">
@@ -22708,7 +23008,7 @@
       <c r="A7033" s="3">
         <v>4.2</v>
       </c>
-      <c r="B7033" s="20" t="s">
+      <c r="B7033" s="22" t="s">
         <v>88</v>
       </c>
       <c r="C7033" s="2" t="s">
@@ -22717,7 +23017,7 @@
     </row>
     <row r="7034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7034" s="3"/>
-      <c r="B7034" s="20"/>
+      <c r="B7034" s="22"/>
       <c r="C7034" s="2"/>
     </row>
     <row r="7035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22780,10 +23080,10 @@
     </row>
     <row r="7082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7082" s="13"/>
-      <c r="B7082" s="21" t="s">
+      <c r="B7082" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C7082" s="22"/>
+      <c r="C7082" s="21"/>
     </row>
     <row r="7083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7083" s="5" t="s">
@@ -22925,10 +23225,10 @@
     </row>
     <row r="7141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7141" s="13"/>
-      <c r="B7141" s="21" t="s">
+      <c r="B7141" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="C7141" s="22"/>
+      <c r="C7141" s="21"/>
     </row>
     <row r="7142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7142" s="5" t="s">
@@ -23021,7 +23321,7 @@
       <c r="A7151" s="3">
         <v>4.2</v>
       </c>
-      <c r="B7151" s="20" t="s">
+      <c r="B7151" s="22" t="s">
         <v>137</v>
       </c>
       <c r="C7151" s="2" t="s">
@@ -23030,7 +23330,7 @@
     </row>
     <row r="7152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7152" s="3"/>
-      <c r="B7152" s="20"/>
+      <c r="B7152" s="22"/>
       <c r="C7152" s="2"/>
     </row>
     <row r="7153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23058,13 +23358,279 @@
       <c r="B7155" s="9"/>
       <c r="C7155" s="8"/>
     </row>
+    <row r="7199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7199" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B7199" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7199" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7200" s="13"/>
+      <c r="B7200" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7200" s="21"/>
+    </row>
+    <row r="7201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7201" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7201" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7201" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7202" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7202" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7202" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7203" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7203" s="7"/>
+      <c r="C7203" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7204" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7204" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7204" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7205" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7205" s="7"/>
+      <c r="C7205" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7206" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7206" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7206" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7207" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7207" s="7"/>
+      <c r="C7207" s="2"/>
+    </row>
+    <row r="7208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7208" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7208" s="7"/>
+      <c r="C7208" s="2"/>
+    </row>
+    <row r="7209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7209" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7209" s="7"/>
+      <c r="C7209" s="2"/>
+    </row>
+    <row r="7210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7210" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7210" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7210" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7211" s="3"/>
+      <c r="B7211" s="22"/>
+      <c r="C7211" s="2"/>
+    </row>
+    <row r="7212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7212" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7212" s="7"/>
+      <c r="C7212" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7213" s="3"/>
+      <c r="B7213" s="7"/>
+      <c r="C7213" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7214" s="3"/>
+      <c r="B7214" s="7"/>
+      <c r="C7214" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7215" s="3"/>
+      <c r="B7215" s="7"/>
+      <c r="C7215" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7216" s="3"/>
+      <c r="B7216" s="7"/>
+      <c r="C7216" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7217" s="3"/>
+      <c r="B7217" s="7"/>
+      <c r="C7217" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7218" s="3"/>
+      <c r="B7218" s="7"/>
+      <c r="C7218" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7219" s="3"/>
+      <c r="B7219" s="7"/>
+      <c r="C7219" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7220" s="3"/>
+      <c r="B7220" s="7"/>
+      <c r="C7220" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7221" s="3"/>
+      <c r="B7221" s="7"/>
+      <c r="C7221" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7222" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7222" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7222" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7223" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7223" s="9"/>
+      <c r="C7223" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="83">
-    <mergeCell ref="B1595:C1595"/>
-    <mergeCell ref="B1548:B1549"/>
-    <mergeCell ref="B1551:B1552"/>
-    <mergeCell ref="B3365:C3365"/>
-    <mergeCell ref="B3375:B3376"/>
+  <mergeCells count="85">
+    <mergeCell ref="B7200:C7200"/>
+    <mergeCell ref="B7210:B7211"/>
+    <mergeCell ref="B7151:B7152"/>
+    <mergeCell ref="B7141:C7141"/>
+    <mergeCell ref="B6787:C6787"/>
+    <mergeCell ref="B6846:C6846"/>
+    <mergeCell ref="B6905:C6905"/>
+    <mergeCell ref="B6964:C6964"/>
+    <mergeCell ref="B7023:C7023"/>
+    <mergeCell ref="B7033:B7034"/>
+    <mergeCell ref="B7082:C7082"/>
+    <mergeCell ref="B5371:C5371"/>
+    <mergeCell ref="B5784:C5784"/>
+    <mergeCell ref="B5843:C5843"/>
+    <mergeCell ref="B6079:C6079"/>
+    <mergeCell ref="B6089:B6090"/>
+    <mergeCell ref="B5320:B5321"/>
+    <mergeCell ref="B4486:C4486"/>
+    <mergeCell ref="B4604:C4604"/>
+    <mergeCell ref="B4840:C4840"/>
+    <mergeCell ref="B4958:C4958"/>
+    <mergeCell ref="B5017:C5017"/>
+    <mergeCell ref="B5076:C5076"/>
+    <mergeCell ref="B5135:C5135"/>
+    <mergeCell ref="B5145:B5146"/>
+    <mergeCell ref="B5194:C5194"/>
+    <mergeCell ref="B5253:C5253"/>
+    <mergeCell ref="B5263:B5264"/>
+    <mergeCell ref="B4427:C4427"/>
+    <mergeCell ref="B2952:C2952"/>
+    <mergeCell ref="B3011:C3011"/>
+    <mergeCell ref="B3070:C3070"/>
+    <mergeCell ref="B3129:C3129"/>
+    <mergeCell ref="B3188:C3188"/>
+    <mergeCell ref="B3247:C3247"/>
+    <mergeCell ref="B3257:B3258"/>
+    <mergeCell ref="B3306:C3306"/>
+    <mergeCell ref="B3896:C3896"/>
+    <mergeCell ref="B3955:C3955"/>
+    <mergeCell ref="B4191:C4191"/>
+    <mergeCell ref="B4201:B4202"/>
+    <mergeCell ref="B4309:C4309"/>
+    <mergeCell ref="B4368:C4368"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B179:C179"/>
+    <mergeCell ref="B425:B426"/>
+    <mergeCell ref="B533:C533"/>
+    <mergeCell ref="B651:C651"/>
+    <mergeCell ref="B710:C710"/>
+    <mergeCell ref="B356:C356"/>
+    <mergeCell ref="B6197:C6197"/>
+    <mergeCell ref="B6315:C6315"/>
+    <mergeCell ref="C6322:C6323"/>
+    <mergeCell ref="B1064:C1064"/>
+    <mergeCell ref="B1123:C1123"/>
+    <mergeCell ref="B1182:C1182"/>
+    <mergeCell ref="B1241:C1241"/>
+    <mergeCell ref="B1369:B1370"/>
+    <mergeCell ref="B1359:C1359"/>
+    <mergeCell ref="B1300:C1300"/>
+    <mergeCell ref="B1418:C1418"/>
+    <mergeCell ref="B1487:B1488"/>
+    <mergeCell ref="B828:C828"/>
+    <mergeCell ref="B1536:C1536"/>
     <mergeCell ref="B6374:C6374"/>
     <mergeCell ref="B6728:C6728"/>
     <mergeCell ref="B1831:C1831"/>
@@ -23081,68 +23647,11 @@
     <mergeCell ref="B3439:B3440"/>
     <mergeCell ref="B3483:C3483"/>
     <mergeCell ref="C3492:C3493"/>
-    <mergeCell ref="B710:C710"/>
-    <mergeCell ref="B356:C356"/>
-    <mergeCell ref="B6197:C6197"/>
-    <mergeCell ref="B6315:C6315"/>
-    <mergeCell ref="C6322:C6323"/>
-    <mergeCell ref="B1064:C1064"/>
-    <mergeCell ref="B1123:C1123"/>
-    <mergeCell ref="B1182:C1182"/>
-    <mergeCell ref="B1241:C1241"/>
-    <mergeCell ref="B1369:B1370"/>
-    <mergeCell ref="B1359:C1359"/>
-    <mergeCell ref="B1300:C1300"/>
-    <mergeCell ref="B1418:C1418"/>
-    <mergeCell ref="B1487:B1488"/>
-    <mergeCell ref="B828:C828"/>
-    <mergeCell ref="B1536:C1536"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B179:C179"/>
-    <mergeCell ref="B425:B426"/>
-    <mergeCell ref="B533:C533"/>
-    <mergeCell ref="B651:C651"/>
-    <mergeCell ref="B4427:C4427"/>
-    <mergeCell ref="B2952:C2952"/>
-    <mergeCell ref="B3011:C3011"/>
-    <mergeCell ref="B3070:C3070"/>
-    <mergeCell ref="B3129:C3129"/>
-    <mergeCell ref="B3188:C3188"/>
-    <mergeCell ref="B3247:C3247"/>
-    <mergeCell ref="B3257:B3258"/>
-    <mergeCell ref="B3306:C3306"/>
-    <mergeCell ref="B3896:C3896"/>
-    <mergeCell ref="B3955:C3955"/>
-    <mergeCell ref="B4191:C4191"/>
-    <mergeCell ref="B4201:B4202"/>
-    <mergeCell ref="B4309:C4309"/>
-    <mergeCell ref="B4368:C4368"/>
-    <mergeCell ref="B5320:B5321"/>
-    <mergeCell ref="B4486:C4486"/>
-    <mergeCell ref="B4604:C4604"/>
-    <mergeCell ref="B4840:C4840"/>
-    <mergeCell ref="B4958:C4958"/>
-    <mergeCell ref="B5017:C5017"/>
-    <mergeCell ref="B5076:C5076"/>
-    <mergeCell ref="B5135:C5135"/>
-    <mergeCell ref="B5145:B5146"/>
-    <mergeCell ref="B5194:C5194"/>
-    <mergeCell ref="B5253:C5253"/>
-    <mergeCell ref="B5263:B5264"/>
-    <mergeCell ref="B5371:C5371"/>
-    <mergeCell ref="B5784:C5784"/>
-    <mergeCell ref="B5843:C5843"/>
-    <mergeCell ref="B6079:C6079"/>
-    <mergeCell ref="B6089:B6090"/>
-    <mergeCell ref="B7151:B7152"/>
-    <mergeCell ref="B7141:C7141"/>
-    <mergeCell ref="B6787:C6787"/>
-    <mergeCell ref="B6846:C6846"/>
-    <mergeCell ref="B6905:C6905"/>
-    <mergeCell ref="B6964:C6964"/>
-    <mergeCell ref="B7023:C7023"/>
-    <mergeCell ref="B7033:B7034"/>
-    <mergeCell ref="B7082:C7082"/>
+    <mergeCell ref="B1595:C1595"/>
+    <mergeCell ref="B1548:B1549"/>
+    <mergeCell ref="B1551:B1552"/>
+    <mergeCell ref="B3365:C3365"/>
+    <mergeCell ref="B3375:B3376"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup scale="79" orientation="portrait" r:id="rId1"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487C70B7-6801-4E42-919B-E5022E7D4F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7AE86F-FDF1-4876-80A0-690923420559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$7259</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$9440</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="404">
   <si>
     <t>Implied</t>
   </si>
@@ -5824,6 +5824,2004 @@
       </rPr>
       <t xml:space="preserve"> = u8(Tmp).</t>
     </r>
+  </si>
+  <si>
+    <t>ROR (7B)</t>
+  </si>
+  <si>
+    <t>ROR (7C)</t>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag &lt;&lt; 7). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $01). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt; 1) | Tmp. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>MOV (7D)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMP (7E)</t>
+  </si>
+  <si>
+    <t>RETI (7F)</t>
+  </si>
+  <si>
+    <r>
+      <t>Read u8(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+2) | $0100</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by 2. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pull to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>SETC (80)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> | $01).</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL8 (81)</t>
+  </si>
+  <si>
+    <t>Read $FFCE</t>
+  </si>
+  <si>
+    <t>Read $FFCF</t>
+  </si>
+  <si>
+    <t>SET1 (82)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$10) | $10.</t>
+  </si>
+  <si>
+    <t>BBS4 (83)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 4)) == (1 &lt;&lt; 4).</t>
+  </si>
+  <si>
+    <t>ADC (84)</t>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(Operand) + u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ Operand) &amp; (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ u8(Tmp)) &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ Operand ^ u8(Tmp)) &amp; $10).</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (85)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (u8(Tmp) == $00).</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (86)</t>
+  </si>
+  <si>
+    <t>ADC (87)</t>
+  </si>
+  <si>
+    <t>ADC (88)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(Operand) + u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag).</t>
+    </r>
+  </si>
+  <si>
+    <t>ADC (89)</t>
+  </si>
+  <si>
+    <t>Operand0 = u8(Tmp).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((Operand0 ^ Operand1 ^ u8(Tmp)) &amp; $10).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(Operand0 ^ Operand1) &amp; (Operand0 ^ u8(Tmp)) &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(Operand0) + u32(Operand1) + u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag).</t>
+    </r>
+  </si>
+  <si>
+    <t>EOR1 (8A)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag ^= ((Operand &amp; (1 &lt;&lt; Bit)) != 0).</t>
+    </r>
+  </si>
+  <si>
+    <t>DEC (8B)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Operand -= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>DEC (8C)</t>
+  </si>
+  <si>
+    <t>MOV (8D)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Operand = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (Operand &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !Operand.</t>
+    </r>
+  </si>
+  <si>
+    <t>POP (8E)</t>
+  </si>
+  <si>
+    <t>MOV (8F)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Operand. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>BCC (90)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inc. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Set Jump to (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $01) == $00.</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL9 (91)</t>
+  </si>
+  <si>
+    <t>Read $FFCC</t>
+  </si>
+  <si>
+    <t>Read $FFCD</t>
+  </si>
+  <si>
+    <t>CLR1 (92)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$10) | $00.</t>
+  </si>
+  <si>
+    <t>BBC4 (93)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 4)) == (0 &lt;&lt; 4).</t>
+  </si>
+  <si>
+    <t>ADC (94)</t>
+  </si>
+  <si>
+    <t>ADC (95)</t>
+  </si>
+  <si>
+    <t>ADC (96)</t>
+  </si>
+  <si>
+    <t>ADC (97)</t>
+  </si>
+  <si>
+    <t>ADC (98)</t>
+  </si>
+  <si>
+    <t>ADC (99)</t>
+  </si>
+  <si>
+    <t>SUBW (9A)</t>
+  </si>
+  <si>
+    <t>TmpR = ~Operand16.L.</t>
+  </si>
+  <si>
+    <t>TmpR = ~Operand16.H.</t>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(TmpR) + 1.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> == $0000).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (~(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ TmpR) &amp; (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ u8(Tmp)) &amp; $80).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ^ TmpR ^ u8(Tmp)) &amp; $10).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tmp = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) + u32(TmpR) + u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag).</t>
+    </r>
+  </si>
+  <si>
+    <t>DEC (9B)</t>
+  </si>
+  <si>
+    <t>DEC (9C)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -= 1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>MOV (9D)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>DIV (9E)</t>
+  </si>
+  <si>
+    <t>Cycles: 12</t>
+  </si>
+  <si>
+    <t>DivYa &lt;&lt;= 1.</t>
+  </si>
+  <si>
+    <t>If DivYa &gt;= ShiftedX: DivYa ^= 1.</t>
+  </si>
+  <si>
+    <t>If DivYa &amp; 1: DivYa = (DivYa - ShiftedX) &amp; $1FFFF.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = ((</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; 15) &gt;= (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; 15)), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DivYa = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>YA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), ShiftedX = u32(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) &lt;&lt; 9.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = u8(DivYa &gt;&gt; 9), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = u8(DivYa).</t>
+    </r>
+  </si>
+  <si>
+    <t>If DivYa &amp; $20000: DivYa ^= $20001.</t>
   </si>
 </sst>
 </file>
@@ -5879,7 +7877,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -5985,11 +7983,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6057,6 +8064,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6391,7 +8400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C7223"/>
+  <dimension ref="A1:C9380"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -6830,7 +8839,7 @@
       <c r="B181" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C181" t="s">
+      <c r="C181" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7010,7 +9019,7 @@
       <c r="B240" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C240" t="s">
+      <c r="C240" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7117,7 +9126,7 @@
       <c r="B299" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C299" t="s">
+      <c r="C299" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7244,7 +9253,7 @@
       <c r="B358" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C358" t="s">
+      <c r="C358" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7345,7 +9354,7 @@
       <c r="B417" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C417" t="s">
+      <c r="C417" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7509,7 +9518,7 @@
       <c r="B476" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C476" t="s">
+      <c r="C476" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7596,7 +9605,7 @@
       <c r="B535" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C535" t="s">
+      <c r="C535" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7759,7 +9768,7 @@
       <c r="B594" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C594" t="s">
+      <c r="C594" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -7907,7 +9916,7 @@
       <c r="B653" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C653" t="s">
+      <c r="C653" s="23" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8032,7 +10041,7 @@
       <c r="B712" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C712" t="s">
+      <c r="C712" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8177,7 +10186,7 @@
       <c r="B771" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C771" t="s">
+      <c r="C771" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8296,7 +10305,7 @@
       <c r="B830" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C830" t="s">
+      <c r="C830" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8473,7 +10482,7 @@
       <c r="B889" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C889" t="s">
+      <c r="C889" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8664,7 +10673,7 @@
       <c r="B948" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C948" t="s">
+      <c r="C948" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8790,7 +10799,7 @@
       <c r="B1007" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1007" t="s">
+      <c r="C1007" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -8977,7 +10986,7 @@
       <c r="B1066" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1066" t="s">
+      <c r="C1066" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9102,7 +11111,7 @@
       <c r="B1125" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1125" t="s">
+      <c r="C1125" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9282,7 +11291,7 @@
       <c r="B1184" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1184" t="s">
+      <c r="C1184" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9405,7 +11414,7 @@
       <c r="B1243" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1243" t="s">
+      <c r="C1243" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9548,7 +11557,7 @@
       <c r="B1302" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1302" t="s">
+      <c r="C1302" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9691,7 +11700,7 @@
       <c r="B1361" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1361" t="s">
+      <c r="C1361" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9857,7 +11866,7 @@
       <c r="B1420" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1420" t="s">
+      <c r="C1420" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10002,7 +12011,7 @@
       <c r="B1479" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1479" t="s">
+      <c r="C1479" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10148,7 +12157,7 @@
       <c r="B1538" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1538" t="s">
+      <c r="C1538" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10335,7 +12344,7 @@
       <c r="B1597" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1597" t="s">
+      <c r="C1597" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10476,7 +12485,7 @@
       <c r="B1656" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1656" t="s">
+      <c r="C1656" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10563,7 +12572,7 @@
       <c r="B1715" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1715" t="s">
+      <c r="C1715" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10646,7 +12655,7 @@
       <c r="B1774" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1774" t="s">
+      <c r="C1774" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10773,7 +12782,7 @@
       <c r="B1833" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1833" t="s">
+      <c r="C1833" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -10930,7 +12939,7 @@
       <c r="B1892" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1892" t="s">
+      <c r="C1892" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11013,7 +13022,7 @@
       <c r="B1951" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C1951" t="s">
+      <c r="C1951" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11200,7 +13209,7 @@
       <c r="B2010" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2010" t="s">
+      <c r="C2010" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11325,7 +13334,7 @@
       <c r="B2069" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2069" t="s">
+      <c r="C2069" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11505,7 +13514,7 @@
       <c r="B2128" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2128" t="s">
+      <c r="C2128" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11612,7 +13621,7 @@
       <c r="B2187" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2187" t="s">
+      <c r="C2187" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11739,7 +13748,7 @@
       <c r="B2246" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2246" t="s">
+      <c r="C2246" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -11840,7 +13849,7 @@
       <c r="B2305" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2305" t="s">
+      <c r="C2305" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12004,7 +14013,7 @@
       <c r="B2364" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2364" t="s">
+      <c r="C2364" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12091,7 +14100,7 @@
       <c r="B2423" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2423" t="s">
+      <c r="C2423" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12254,7 +14263,7 @@
       <c r="B2482" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2482" t="s">
+      <c r="C2482" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12402,7 +14411,7 @@
       <c r="B2541" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2541" t="s">
+      <c r="C2541" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12532,7 +14541,7 @@
       <c r="B2600" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2600" t="s">
+      <c r="C2600" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12682,7 +14691,7 @@
       <c r="B2659" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C2659" t="s">
+      <c r="C2659" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12801,7 +14810,7 @@
       <c r="B2718" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2718" t="s">
+      <c r="C2718" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -12981,7 +14990,7 @@
       <c r="B2777" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2777" t="s">
+      <c r="C2777" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13107,7 +15116,7 @@
       <c r="B2836" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2836" t="s">
+      <c r="C2836" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13233,7 +15242,7 @@
       <c r="B2895" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2895" t="s">
+      <c r="C2895" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13420,7 +15429,7 @@
       <c r="B2954" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2954" t="s">
+      <c r="C2954" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13545,7 +15554,7 @@
       <c r="B3013" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3013" t="s">
+      <c r="C3013" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13725,7 +15734,7 @@
       <c r="B3072" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3072" t="s">
+      <c r="C3072" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13848,7 +15857,7 @@
       <c r="B3131" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3131" t="s">
+      <c r="C3131" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -13991,7 +16000,7 @@
       <c r="B3190" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3190" t="s">
+      <c r="C3190" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14134,7 +16143,7 @@
       <c r="B3249" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3249" t="s">
+      <c r="C3249" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14300,7 +16309,7 @@
       <c r="B3308" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3308" t="s">
+      <c r="C3308" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14445,7 +16454,7 @@
       <c r="B3367" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3367" t="s">
+      <c r="C3367" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14591,7 +16600,7 @@
       <c r="B3426" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3426" t="s">
+      <c r="C3426" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14778,7 +16787,7 @@
       <c r="B3485" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3485" t="s">
+      <c r="C3485" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -14924,7 +16933,7 @@
       <c r="B3544" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3544" t="s">
+      <c r="C3544" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15011,7 +17020,7 @@
       <c r="B3603" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3603" t="s">
+      <c r="C3603" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15094,7 +17103,7 @@
       <c r="B3662" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3662" t="s">
+      <c r="C3662" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15201,7 +17210,7 @@
       <c r="B3721" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3721" t="s">
+      <c r="C3721" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15392,7 +17401,7 @@
       <c r="B3780" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3780" t="s">
+      <c r="C3780" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15475,7 +17484,7 @@
       <c r="B3839" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3839" t="s">
+      <c r="C3839" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15662,7 +17671,7 @@
       <c r="B3898" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3898" t="s">
+      <c r="C3898" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15787,7 +17796,7 @@
       <c r="B3957" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C3957" t="s">
+      <c r="C3957" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -15967,7 +17976,7 @@
       <c r="B4016" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4016" t="s">
+      <c r="C4016" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16074,7 +18083,7 @@
       <c r="B4075" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4075" t="s">
+      <c r="C4075" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16201,7 +18210,7 @@
       <c r="B4134" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4134" t="s">
+      <c r="C4134" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16302,7 +18311,7 @@
       <c r="B4193" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4193" t="s">
+      <c r="C4193" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16466,7 +18475,7 @@
       <c r="B4252" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4252" t="s">
+      <c r="C4252" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16553,7 +18562,7 @@
       <c r="B4311" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4311" t="s">
+      <c r="C4311" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16716,7 +18725,7 @@
       <c r="B4370" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4370" t="s">
+      <c r="C4370" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16850,7 +18859,7 @@
       <c r="B4429" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4429" t="s">
+      <c r="C4429" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -16975,7 +18984,7 @@
       <c r="B4488" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4488" t="s">
+      <c r="C4488" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17120,7 +19129,7 @@
       <c r="B4547" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4547" t="s">
+      <c r="C4547" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17239,7 +19248,7 @@
       <c r="B4606" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4606" t="s">
+      <c r="C4606" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17416,7 +19425,7 @@
       <c r="B4665" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4665" t="s">
+      <c r="C4665" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17571,7 +19580,7 @@
       <c r="B4724" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4724" t="s">
+      <c r="C4724" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17697,7 +19706,7 @@
       <c r="B4783" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4783" t="s">
+      <c r="C4783" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -17884,7 +19893,7 @@
       <c r="B4842" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4842" t="s">
+      <c r="C4842" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18009,7 +20018,7 @@
       <c r="B4901" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4901" t="s">
+      <c r="C4901" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18189,7 +20198,7 @@
       <c r="B4960" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C4960" t="s">
+      <c r="C4960" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18312,7 +20321,7 @@
       <c r="B5019" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5019" t="s">
+      <c r="C5019" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18455,7 +20464,7 @@
       <c r="B5078" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5078" t="s">
+      <c r="C5078" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18598,7 +20607,7 @@
       <c r="B5137" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5137" t="s">
+      <c r="C5137" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18764,7 +20773,7 @@
       <c r="B5196" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5196" t="s">
+      <c r="C5196" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -18909,7 +20918,7 @@
       <c r="B5255" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5255" t="s">
+      <c r="C5255" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19055,7 +21064,7 @@
       <c r="B5314" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5314" t="s">
+      <c r="C5314" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19185,7 +21194,7 @@
       <c r="B5373" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5373" t="s">
+      <c r="C5373" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19326,7 +21335,7 @@
       <c r="B5432" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5432" t="s">
+      <c r="C5432" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19413,7 +21422,7 @@
       <c r="B5491" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5491" t="s">
+      <c r="C5491" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19496,7 +21505,7 @@
       <c r="B5550" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5550" t="s">
+      <c r="C5550" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19623,7 +21632,7 @@
       <c r="B5609" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5609" t="s">
+      <c r="C5609" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19730,7 +21739,7 @@
       <c r="B5668" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5668" t="s">
+      <c r="C5668" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -19813,7 +21822,7 @@
       <c r="B5727" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5727" t="s">
+      <c r="C5727" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20000,7 +22009,7 @@
       <c r="B5786" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5786" t="s">
+      <c r="C5786" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20125,7 +22134,7 @@
       <c r="B5845" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5845" t="s">
+      <c r="C5845" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20305,7 +22314,7 @@
       <c r="B5904" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5904" t="s">
+      <c r="C5904" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20412,7 +22421,7 @@
       <c r="B5963" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5963" t="s">
+      <c r="C5963" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20539,7 +22548,7 @@
       <c r="B6022" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6022" t="s">
+      <c r="C6022" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20640,7 +22649,7 @@
       <c r="B6081" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6081" t="s">
+      <c r="C6081" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20804,7 +22813,7 @@
       <c r="B6140" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6140" t="s">
+      <c r="C6140" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -20891,7 +22900,7 @@
       <c r="B6199" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6199" t="s">
+      <c r="C6199" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21054,7 +23063,7 @@
       <c r="B6258" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6258" t="s">
+      <c r="C6258" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21188,7 +23197,7 @@
       <c r="B6317" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6317" t="s">
+      <c r="C6317" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21318,7 +23327,7 @@
       <c r="B6376" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6376" t="s">
+      <c r="C6376" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21468,7 +23477,7 @@
       <c r="B6435" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6435" t="s">
+      <c r="C6435" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21587,7 +23596,7 @@
       <c r="B6494" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6494" t="s">
+      <c r="C6494" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21771,7 +23780,7 @@
       <c r="B6553" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6553" t="s">
+      <c r="C6553" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -21910,7 +23919,7 @@
       <c r="B6612" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6612" t="s">
+      <c r="C6612" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22036,7 +24045,7 @@
       <c r="B6671" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6671" t="s">
+      <c r="C6671" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22223,7 +24232,7 @@
       <c r="B6730" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6730" t="s">
+      <c r="C6730" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22348,7 +24357,7 @@
       <c r="B6789" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6789" t="s">
+      <c r="C6789" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22528,7 +24537,7 @@
       <c r="B6848" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6848" t="s">
+      <c r="C6848" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22651,7 +24660,7 @@
       <c r="B6907" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6907" t="s">
+      <c r="C6907" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22794,7 +24803,7 @@
       <c r="B6966" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C6966" t="s">
+      <c r="C6966" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -22937,7 +24946,7 @@
       <c r="B7025" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7025" t="s">
+      <c r="C7025" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -23103,7 +25112,7 @@
       <c r="B7084" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7084" t="s">
+      <c r="C7084" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -23248,7 +25257,7 @@
       <c r="B7143" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7143" t="s">
+      <c r="C7143" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -23394,7 +25403,7 @@
       <c r="B7202" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C7202" t="s">
+      <c r="C7202" s="24" t="s">
         <v>5</v>
       </c>
     </row>
@@ -23565,10 +25574,5671 @@
       <c r="B7223" s="9"/>
       <c r="C7223" s="8"/>
     </row>
+    <row r="7258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7258" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7258" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7258" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7259" s="13"/>
+      <c r="B7259" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7259" s="21"/>
+    </row>
+    <row r="7260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7260" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7260" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7260" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7261" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7261" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7261" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7262" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7262" s="7"/>
+      <c r="C7262" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7263" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7263" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7263" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7264" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7264" s="7"/>
+      <c r="C7264" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7265" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7265" s="7"/>
+      <c r="C7265" s="2"/>
+    </row>
+    <row r="7266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7266" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7266" s="7"/>
+      <c r="C7266" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7267" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7267" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7267" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7268" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7268" s="7"/>
+      <c r="C7268" s="22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="7269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7269" s="3"/>
+      <c r="B7269" s="7"/>
+      <c r="C7269" s="22"/>
+    </row>
+    <row r="7270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7270" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7270" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7270" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7271" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7271" s="2"/>
+      <c r="C7271" s="2"/>
+    </row>
+    <row r="7272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7272" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7272" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7272" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7273" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7273" s="9"/>
+      <c r="C7273" s="8"/>
+    </row>
+    <row r="7317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7317" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7317" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7317" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7318" s="13"/>
+      <c r="B7318" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7318" s="18"/>
+    </row>
+    <row r="7319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7319" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7319" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7319" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7320" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7320" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7320" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7321" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7321" s="7"/>
+      <c r="C7321" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7322" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7322" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7322" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7323" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7323" s="7"/>
+      <c r="C7323" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7324" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7324" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7324" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7325" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7325" s="9"/>
+      <c r="C7325" s="8"/>
+    </row>
+    <row r="7376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7376" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7376" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7376" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7377" s="13"/>
+      <c r="B7377" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7377" s="18"/>
+    </row>
+    <row r="7378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7378" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7378" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7378" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7379" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7379" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7379" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7380" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7380" s="7"/>
+      <c r="C7380" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7381" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7381" s="7"/>
+      <c r="C7381" s="2"/>
+    </row>
+    <row r="7382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7382" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7382" s="7"/>
+      <c r="C7382" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="7383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7383" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7383" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7383" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7384" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7384" s="9"/>
+      <c r="C7384" s="8"/>
+    </row>
+    <row r="7435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7435" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B7435" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7435" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7436" s="13"/>
+      <c r="B7436" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7436" s="18"/>
+    </row>
+    <row r="7437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7437" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7437" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7437" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7438" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7438" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7438" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7439" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7439" s="7"/>
+      <c r="C7439" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7440" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7440" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7440" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7441" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7441" s="7"/>
+      <c r="C7441" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7442" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7442" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7442" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7443" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7443" s="7"/>
+      <c r="C7443" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7444" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7444" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7444" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7445" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7445" s="9"/>
+      <c r="C7445" s="8"/>
+    </row>
+    <row r="7494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7494" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B7494" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7494" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7495" s="13"/>
+      <c r="B7495" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7495" s="18"/>
+    </row>
+    <row r="7496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7496" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7496" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7496" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7497" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7497" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7497" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7498" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7498" s="7"/>
+      <c r="C7498" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7499" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7499" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7499" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7500" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7500" s="7"/>
+      <c r="C7500" s="2"/>
+    </row>
+    <row r="7501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7501" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7501" s="7"/>
+      <c r="C7501" s="2"/>
+    </row>
+    <row r="7502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7502" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7502" s="7"/>
+      <c r="C7502" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7503" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7503" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7503" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7504" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7504" s="7"/>
+      <c r="C7504" s="2"/>
+    </row>
+    <row r="7505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7505" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7505" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C7505" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7506" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7506" s="7"/>
+      <c r="C7506" s="2"/>
+    </row>
+    <row r="7507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7507" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7507" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7507" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7508" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B7508" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C7508" s="2"/>
+    </row>
+    <row r="7509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7509" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B7509" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7509" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7510" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7510" s="9"/>
+      <c r="C7510" s="8"/>
+    </row>
+    <row r="7553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7553" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B7553" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7553" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7554" s="13"/>
+      <c r="B7554" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7554" s="18"/>
+    </row>
+    <row r="7555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7555" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7555" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7555" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7556" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7556" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7556" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7557" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7557" s="7"/>
+      <c r="C7557" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7558" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7558" s="7"/>
+      <c r="C7558" s="2"/>
+    </row>
+    <row r="7559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7559" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7559" s="7"/>
+      <c r="C7559" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7560" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7560" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7560" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7561" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7561" s="9"/>
+      <c r="C7561" s="8"/>
+    </row>
+    <row r="7612" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7612" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7612" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7612" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7613" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7613" s="13"/>
+      <c r="B7613" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7613" s="18"/>
+    </row>
+    <row r="7614" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7614" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7614" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7614" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7615" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7615" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7615" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7616" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7616" s="7"/>
+      <c r="C7616" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7617" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7617" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7617" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7618" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7618" s="7"/>
+      <c r="C7618" s="2"/>
+    </row>
+    <row r="7619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7619" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7619" s="7"/>
+      <c r="C7619" s="2"/>
+    </row>
+    <row r="7620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7620" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7620" s="7"/>
+      <c r="C7620" s="2"/>
+    </row>
+    <row r="7621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7621" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7621" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7621" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7622" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7622" s="7"/>
+      <c r="C7622" s="2"/>
+    </row>
+    <row r="7623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7623" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7623" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7623" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7624" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7624" s="7"/>
+      <c r="C7624" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7625" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7625" s="7"/>
+      <c r="C7625" s="2"/>
+    </row>
+    <row r="7626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7626" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B7626" s="7"/>
+      <c r="C7626" s="2"/>
+    </row>
+    <row r="7627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7627" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B7627" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7627" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7628" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B7628" s="7"/>
+      <c r="C7628" s="2"/>
+    </row>
+    <row r="7629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7629" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B7629" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7629" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7630" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B7630" s="7"/>
+      <c r="C7630" s="2"/>
+    </row>
+    <row r="7631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7631" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B7631" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7631" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7632" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7632" s="9"/>
+      <c r="C7632" s="8"/>
+    </row>
+    <row r="7671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7671" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7671" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7671" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7672" s="13"/>
+      <c r="B7672" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7672" s="21"/>
+    </row>
+    <row r="7673" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7673" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7673" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7673" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7674" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7674" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7674" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7675" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7675" s="7"/>
+      <c r="C7675" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7676" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7676" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7676" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7677" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7677" s="7"/>
+      <c r="C7677" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7678" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7678" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7678" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7679" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7679" s="7"/>
+      <c r="C7679" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7680" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7680" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7680" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7681" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7681" s="7"/>
+      <c r="C7681" s="2"/>
+    </row>
+    <row r="7682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7682" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7682" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7682" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7683" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7683" s="9"/>
+      <c r="C7683" s="8"/>
+    </row>
+    <row r="7730" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7730" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7730" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7730" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7731" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7731" s="13"/>
+      <c r="B7731" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7731" s="21"/>
+    </row>
+    <row r="7732" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7732" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7732" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7732" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7733" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7733" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7733" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7734" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7734" s="7"/>
+      <c r="C7734" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7735" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7735" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7735" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7736" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7736" s="7"/>
+      <c r="C7736" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7737" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7737" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7737" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7738" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7738" s="7"/>
+      <c r="C7738" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="7739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7739" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7739" s="7"/>
+      <c r="C7739" s="2"/>
+    </row>
+    <row r="7740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7740" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7740" s="7"/>
+      <c r="C7740" s="2"/>
+    </row>
+    <row r="7741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7741" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7741" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7741" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7742" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7742" s="7"/>
+      <c r="C7742" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7743" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7743" s="7"/>
+      <c r="C7743" s="2"/>
+    </row>
+    <row r="7744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7744" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B7744" s="7"/>
+      <c r="C7744" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7745" s="3"/>
+      <c r="B7745" s="7"/>
+      <c r="C7745" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7746" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B7746" s="7"/>
+      <c r="C7746" s="2"/>
+    </row>
+    <row r="7747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7747" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B7747" s="7"/>
+      <c r="C7747" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7748" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B7748" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7748" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7749" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7749" s="9"/>
+      <c r="C7749" s="8"/>
+    </row>
+    <row r="7789" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7789" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B7789" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7789" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7790" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7790" s="13"/>
+      <c r="B7790" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7790" s="18"/>
+    </row>
+    <row r="7791" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7791" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7791" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7791" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7792" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7792" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7792" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7793" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7793" s="7"/>
+      <c r="C7793" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7794" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7794" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7794" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7795" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7795" s="7"/>
+      <c r="C7795" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7796" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7796" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7796" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7797" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7797" s="7"/>
+      <c r="C7797" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7798" s="3"/>
+      <c r="B7798" s="7"/>
+      <c r="C7798" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7799" s="3"/>
+      <c r="B7799" s="7"/>
+      <c r="C7799" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7800" s="3"/>
+      <c r="B7800" s="7"/>
+      <c r="C7800" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7801" s="3"/>
+      <c r="B7801" s="7"/>
+      <c r="C7801" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7802" s="3"/>
+      <c r="B7802" s="7"/>
+      <c r="C7802" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7803" s="3"/>
+      <c r="B7803" s="7"/>
+      <c r="C7803" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7804" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7804" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7804" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7805" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7805" s="9"/>
+      <c r="C7805" s="8"/>
+    </row>
+    <row r="7848" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7848" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B7848" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7848" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7849" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7849" s="13"/>
+      <c r="B7849" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7849" s="18"/>
+    </row>
+    <row r="7850" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7850" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7850" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7850" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7851" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7851" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7851" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7852" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7852" s="7"/>
+      <c r="C7852" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7853" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7853" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7853" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7854" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7854" s="7"/>
+      <c r="C7854" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7855" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7855" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7855" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7856" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7856" s="7"/>
+      <c r="C7856" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7857" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7857" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7857" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7858" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7858" s="7"/>
+      <c r="C7858" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7859" s="3"/>
+      <c r="B7859" s="7"/>
+      <c r="C7859" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7860" s="3"/>
+      <c r="B7860" s="7"/>
+      <c r="C7860" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7861" s="3"/>
+      <c r="B7861" s="7"/>
+      <c r="C7861" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7862" s="3"/>
+      <c r="B7862" s="7"/>
+      <c r="C7862" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7863" s="3"/>
+      <c r="B7863" s="7"/>
+      <c r="C7863" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7864" s="3"/>
+      <c r="B7864" s="7"/>
+      <c r="C7864" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7865" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7865" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7865" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7866" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7866" s="9"/>
+      <c r="C7866" s="8"/>
+    </row>
+    <row r="7907" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7907" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7907" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7907" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7908" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7908" s="13"/>
+      <c r="B7908" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7908" s="18"/>
+    </row>
+    <row r="7909" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7909" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7909" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7909" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7910" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7910" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7910" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7911" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7911" s="7"/>
+      <c r="C7911" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7912" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7912" s="7"/>
+      <c r="C7912" s="2"/>
+    </row>
+    <row r="7913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7913" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7913" s="7"/>
+      <c r="C7913" s="2"/>
+    </row>
+    <row r="7914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7914" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7914" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7914" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7915" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7915" s="7"/>
+      <c r="C7915" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7916" s="3"/>
+      <c r="B7916" s="7"/>
+      <c r="C7916" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7917" s="3"/>
+      <c r="B7917" s="7"/>
+      <c r="C7917" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7918" s="3"/>
+      <c r="B7918" s="7"/>
+      <c r="C7918" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7919" s="3"/>
+      <c r="B7919" s="7"/>
+      <c r="C7919" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7920" s="3"/>
+      <c r="B7920" s="7"/>
+      <c r="C7920" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7921" s="3"/>
+      <c r="B7921" s="7"/>
+      <c r="C7921" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7922" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7922" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7922" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7923" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7923" s="9"/>
+      <c r="C7923" s="8"/>
+    </row>
+    <row r="7966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7966" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B7966" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7966" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7967" s="13"/>
+      <c r="B7967" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7967" s="21"/>
+    </row>
+    <row r="7968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7968" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7968" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7968" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7969" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7969" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7969" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7970" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B7970" s="7"/>
+      <c r="C7970" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7971" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B7971" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7971" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7972" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B7972" s="7"/>
+      <c r="C7972" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7973" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B7973" s="7"/>
+      <c r="C7973" s="2"/>
+    </row>
+    <row r="7974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7974" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B7974" s="7"/>
+      <c r="C7974" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7975" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B7975" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7975" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7976" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B7976" s="7"/>
+      <c r="C7976" s="2"/>
+    </row>
+    <row r="7977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7977" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B7977" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7977" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7978" s="3"/>
+      <c r="B7978" s="22"/>
+      <c r="C7978" s="2"/>
+    </row>
+    <row r="7979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7979" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B7979" s="7"/>
+      <c r="C7979" s="2"/>
+    </row>
+    <row r="7980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7980" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B7980" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7980" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7981" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B7981" s="7"/>
+      <c r="C7981" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7982" s="3"/>
+      <c r="B7982" s="7"/>
+      <c r="C7982" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7983" s="3"/>
+      <c r="B7983" s="7"/>
+      <c r="C7983" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7984" s="3"/>
+      <c r="B7984" s="7"/>
+      <c r="C7984" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7985" s="3"/>
+      <c r="B7985" s="7"/>
+      <c r="C7985" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7986" s="3"/>
+      <c r="B7986" s="7"/>
+      <c r="C7986" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7987" s="3"/>
+      <c r="B7987" s="7"/>
+      <c r="C7987" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7988" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B7988" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7988" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7989" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7989" s="9"/>
+      <c r="C7989" s="8"/>
+    </row>
+    <row r="8025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8025" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="B8025" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8025" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8026" s="13"/>
+      <c r="B8026" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8026" s="18"/>
+    </row>
+    <row r="8027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8027" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8027" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8027" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8028" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8028" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8028" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8029" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8029" s="7"/>
+      <c r="C8029" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8030" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8030" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8030" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8031" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8031" s="7"/>
+      <c r="C8031" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8032" s="3"/>
+      <c r="B8032" s="7"/>
+      <c r="C8032" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8033" s="3"/>
+      <c r="B8033" s="7"/>
+      <c r="C8033" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8034" s="3"/>
+      <c r="B8034" s="7"/>
+      <c r="C8034" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8035" s="3"/>
+      <c r="B8035" s="7"/>
+      <c r="C8035" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8036" s="3"/>
+      <c r="B8036" s="7"/>
+      <c r="C8036" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8037" s="3"/>
+      <c r="B8037" s="7"/>
+      <c r="C8037" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8038" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8038" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8038" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8039" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8039" s="9"/>
+      <c r="C8039" s="8"/>
+    </row>
+    <row r="8084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8084" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8084" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8084" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8085" s="13"/>
+      <c r="B8085" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8085" s="21"/>
+    </row>
+    <row r="8086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8086" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8086" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8086" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8087" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8087" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8087" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8088" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8088" s="7"/>
+      <c r="C8088" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8089" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8089" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8089" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8090" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8090" s="7"/>
+      <c r="C8090" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8091" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8091" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8091" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8092" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8092" s="7"/>
+      <c r="C8092" s="2"/>
+    </row>
+    <row r="8093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8093" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8093" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8093" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8094" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8094" s="7"/>
+      <c r="C8094" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8095" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8095" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8095" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8096" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8096" s="2"/>
+      <c r="C8096" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="8097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8097" s="3"/>
+      <c r="B8097" s="7"/>
+      <c r="C8097" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8098" s="3"/>
+      <c r="B8098" s="7"/>
+      <c r="C8098" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8099" s="3"/>
+      <c r="B8099" s="7"/>
+      <c r="C8099" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8100" s="3"/>
+      <c r="B8100" s="7"/>
+      <c r="C8100" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8101" s="3"/>
+      <c r="B8101" s="7"/>
+      <c r="C8101" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8102" s="3"/>
+      <c r="B8102" s="7"/>
+      <c r="C8102" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8103" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8103" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8103" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8104" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B8104" s="7"/>
+      <c r="C8104" s="2"/>
+    </row>
+    <row r="8105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8105" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B8105" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8105" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8106" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8106" s="9"/>
+      <c r="C8106" s="8"/>
+    </row>
+    <row r="8143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8143" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8143" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8143" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8144" s="13"/>
+      <c r="B8144" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8144" s="21"/>
+    </row>
+    <row r="8145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8145" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8145" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8145" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8146" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8146" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8146" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8147" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8147" s="7"/>
+      <c r="C8147" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8148" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8148" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8148" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8149" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8149" s="7"/>
+      <c r="C8149" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8150" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8150" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8150" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8151" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8151" s="7"/>
+      <c r="C8151" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8152" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8152" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8152" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8153" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8153" s="7"/>
+      <c r="C8153" s="2"/>
+    </row>
+    <row r="8154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8154" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8154" s="2"/>
+      <c r="C8154" s="2"/>
+    </row>
+    <row r="8155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8155" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8155" s="2"/>
+      <c r="C8155" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8156" s="3"/>
+      <c r="B8156" s="7"/>
+      <c r="C8156" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="8157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8157" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8157" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8157" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8158" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8158" s="9"/>
+      <c r="C8158" s="8"/>
+    </row>
+    <row r="8202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8202" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B8202" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8202" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8203" s="13"/>
+      <c r="B8203" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8203" s="21"/>
+    </row>
+    <row r="8204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8204" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8204" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8204" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8205" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8205" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8205" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8206" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8206" s="7"/>
+      <c r="C8206" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8207" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8207" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8207" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8208" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8208" s="7"/>
+      <c r="C8208" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8209" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8209" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8209" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8210" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8210" s="7"/>
+      <c r="C8210" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8211" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8211" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8211" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8212" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8212" s="7"/>
+      <c r="C8212" s="2"/>
+    </row>
+    <row r="8213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8213" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8213" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8213" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8214" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8214" s="9"/>
+      <c r="C8214" s="8"/>
+    </row>
+    <row r="8261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8261" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B8261" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8261" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8262" s="13"/>
+      <c r="B8262" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8262" s="21"/>
+    </row>
+    <row r="8263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8263" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8263" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8263" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8264" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8264" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8264" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8265" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8265" s="7"/>
+      <c r="C8265" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8266" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8266" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8266" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8267" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8267" s="7"/>
+      <c r="C8267" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8268" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8268" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8268" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8269" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8269" s="7"/>
+      <c r="C8269" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8270" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8270" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8270" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8271" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8271" s="7"/>
+      <c r="C8271" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8272" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8272" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8272" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8273" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8273" s="7"/>
+      <c r="C8273" s="2"/>
+    </row>
+    <row r="8274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8274" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8274" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8274" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8275" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8275" s="9"/>
+      <c r="C8275" s="8"/>
+    </row>
+    <row r="8320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8320" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8320" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8320" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8321" s="13"/>
+      <c r="B8321" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8321" s="18"/>
+    </row>
+    <row r="8322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8322" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8322" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8322" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8323" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8323" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8323" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8324" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8324" s="7"/>
+      <c r="C8324" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8325" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8325" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8325" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8326" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8326" s="7"/>
+      <c r="C8326" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="8327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8327" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8327" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8327" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8328" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8328" s="9"/>
+      <c r="C8328" s="8"/>
+    </row>
+    <row r="8379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8379" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8379" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8379" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8380" s="13"/>
+      <c r="B8380" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8380" s="18"/>
+    </row>
+    <row r="8381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8381" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8381" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8381" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8382" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8382" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8382" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8383" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8383" s="7"/>
+      <c r="C8383" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8384" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8384" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8384" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8385" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8385" s="7"/>
+      <c r="C8385" s="2"/>
+    </row>
+    <row r="8386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8386" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8386" s="7"/>
+      <c r="C8386" s="2"/>
+    </row>
+    <row r="8387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8387" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8387" s="7"/>
+      <c r="C8387" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8388" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8388" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8388" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8389" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8389" s="7"/>
+      <c r="C8389" s="2"/>
+    </row>
+    <row r="8390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8390" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8390" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8390" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8391" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8391" s="9"/>
+      <c r="C8391" s="8"/>
+    </row>
+    <row r="8438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8438" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B8438" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8438" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8439" s="13"/>
+      <c r="B8439" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8439" s="21"/>
+    </row>
+    <row r="8440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8440" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8440" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8440" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8441" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8441" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8441" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8442" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8442" s="7"/>
+      <c r="C8442" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8443" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8443" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8443" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8444" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8444" s="7"/>
+      <c r="C8444" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8445" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8445" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8445" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8446" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8446" s="7"/>
+      <c r="C8446" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8447" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8447" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8447" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8448" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8448" s="7"/>
+      <c r="C8448" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8449" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8449" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8449" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8450" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8450" s="7"/>
+      <c r="C8450" s="2"/>
+    </row>
+    <row r="8451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8451" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8451" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8451" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8452" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8452" s="9"/>
+      <c r="C8452" s="8"/>
+    </row>
+    <row r="8497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8497" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B8497" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8497" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8498" s="13"/>
+      <c r="B8498" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8498" s="18"/>
+    </row>
+    <row r="8499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8499" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8499" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8499" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8500" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8500" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8500" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8501" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8501" s="7"/>
+      <c r="C8501" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="8502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8502" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8502" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8502" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8503" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8503" s="7"/>
+      <c r="C8503" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8504" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8504" s="7"/>
+      <c r="C8504" s="2"/>
+    </row>
+    <row r="8505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8505" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8505" s="7"/>
+      <c r="C8505" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8506" s="3"/>
+      <c r="B8506" s="7"/>
+      <c r="C8506" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8507" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8507" s="7"/>
+      <c r="C8507" s="2"/>
+    </row>
+    <row r="8508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8508" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8508" s="7"/>
+      <c r="C8508" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8509" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8509" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8509" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8510" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8510" s="9"/>
+      <c r="C8510" s="8"/>
+    </row>
+    <row r="8556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8556" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B8556" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8556" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8557" s="13"/>
+      <c r="B8557" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8557" s="18"/>
+    </row>
+    <row r="8558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8558" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8558" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8558" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8559" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8559" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8559" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8560" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8560" s="7"/>
+      <c r="C8560" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8561" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8561" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8561" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8562" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8562" s="7"/>
+      <c r="C8562" s="2"/>
+    </row>
+    <row r="8563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8563" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8563" s="7"/>
+      <c r="C8563" s="2"/>
+    </row>
+    <row r="8564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8564" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8564" s="7"/>
+      <c r="C8564" s="2"/>
+    </row>
+    <row r="8565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8565" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8565" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8565" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8566" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8566" s="7"/>
+      <c r="C8566" s="2"/>
+    </row>
+    <row r="8567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8567" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8567" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8567" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8568" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8568" s="7"/>
+      <c r="C8568" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8569" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8569" s="7"/>
+      <c r="C8569" s="2"/>
+    </row>
+    <row r="8570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8570" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B8570" s="7"/>
+      <c r="C8570" s="2"/>
+    </row>
+    <row r="8571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8571" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B8571" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C8571" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8572" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B8572" s="7"/>
+      <c r="C8572" s="2"/>
+    </row>
+    <row r="8573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8573" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B8573" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8573" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8574" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B8574" s="7"/>
+      <c r="C8574" s="2"/>
+    </row>
+    <row r="8575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8575" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B8575" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8575" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8576" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8576" s="9"/>
+      <c r="C8576" s="8"/>
+    </row>
+    <row r="8615" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8615" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8615" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8615" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8616" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8616" s="13"/>
+      <c r="B8616" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8616" s="21"/>
+    </row>
+    <row r="8617" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8617" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8617" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8617" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8618" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8618" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8618" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8619" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8619" s="7"/>
+      <c r="C8619" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8620" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8620" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8620" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8620" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8621" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8621" s="7"/>
+      <c r="C8621" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8622" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8622" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8622" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8623" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8623" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8623" s="7"/>
+      <c r="C8623" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8624" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8624" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8624" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8624" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8625" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8625" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8625" s="7"/>
+      <c r="C8625" s="2"/>
+    </row>
+    <row r="8626" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8626" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8626" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8626" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8627" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8627" s="9"/>
+      <c r="C8627" s="8"/>
+    </row>
+    <row r="8674" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8674" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B8674" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8674" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8675" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8675" s="13"/>
+      <c r="B8675" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8675" s="21"/>
+    </row>
+    <row r="8676" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8676" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8676" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8676" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8677" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8677" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8677" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8678" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8678" s="7"/>
+      <c r="C8678" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8679" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8679" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8679" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8679" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8680" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8680" s="7"/>
+      <c r="C8680" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8681" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8681" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8681" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8682" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8682" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8682" s="7"/>
+      <c r="C8682" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8683" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8683" s="7"/>
+      <c r="C8683" s="2"/>
+    </row>
+    <row r="8684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8684" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8684" s="7"/>
+      <c r="C8684" s="2"/>
+    </row>
+    <row r="8685" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8685" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8685" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8685" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8686" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8686" s="7"/>
+      <c r="C8686" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8687" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8687" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8687" s="7"/>
+      <c r="C8687" s="2"/>
+    </row>
+    <row r="8688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8688" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B8688" s="7"/>
+      <c r="C8688" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8689" s="3"/>
+      <c r="B8689" s="7"/>
+      <c r="C8689" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8690" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B8690" s="7"/>
+      <c r="C8690" s="2"/>
+    </row>
+    <row r="8691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8691" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B8691" s="7"/>
+      <c r="C8691" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8692" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B8692" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8692" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8693" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8693" s="9"/>
+      <c r="C8693" s="8"/>
+    </row>
+    <row r="8733" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8733" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8733" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8733" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8734" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8734" s="13"/>
+      <c r="B8734" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8734" s="18"/>
+    </row>
+    <row r="8735" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8735" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8735" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8735" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8736" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8736" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8736" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8737" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8737" s="7"/>
+      <c r="C8737" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8738" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8738" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8738" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8739" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8739" s="7"/>
+      <c r="C8739" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8740" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8740" s="7"/>
+      <c r="C8740" s="2"/>
+    </row>
+    <row r="8741" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8741" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8741" s="7"/>
+      <c r="C8741" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8742" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8742" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8742" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8743" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8743" s="7"/>
+      <c r="C8743" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8744" s="3"/>
+      <c r="B8744" s="7"/>
+      <c r="C8744" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8745" s="3"/>
+      <c r="B8745" s="7"/>
+      <c r="C8745" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8746" s="3"/>
+      <c r="B8746" s="7"/>
+      <c r="C8746" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8747" s="3"/>
+      <c r="B8747" s="7"/>
+      <c r="C8747" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8748" s="3"/>
+      <c r="B8748" s="7"/>
+      <c r="C8748" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8749" s="3"/>
+      <c r="B8749" s="7"/>
+      <c r="C8749" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8750" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8750" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8750" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8751" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8751" s="9"/>
+      <c r="C8751" s="8"/>
+    </row>
+    <row r="8792" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8792" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8792" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8792" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8793" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8793" s="13"/>
+      <c r="B8793" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8793" s="21"/>
+    </row>
+    <row r="8794" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8794" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8794" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8794" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8795" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8795" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8795" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8796" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8796" s="7"/>
+      <c r="C8796" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8797" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8797" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8797" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8798" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8798" s="7"/>
+      <c r="C8798" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8799" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8799" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8799" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8800" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8800" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8800" s="7"/>
+      <c r="C8800" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8801" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8801" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8801" s="7"/>
+      <c r="C8801" s="2"/>
+    </row>
+    <row r="8802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8802" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8802" s="7"/>
+      <c r="C8802" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8803" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8803" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8803" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8804" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8804" s="7"/>
+      <c r="C8804" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8805" s="3"/>
+      <c r="B8805" s="7"/>
+      <c r="C8805" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8806" s="3"/>
+      <c r="B8806" s="7"/>
+      <c r="C8806" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8807" s="3"/>
+      <c r="B8807" s="7"/>
+      <c r="C8807" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8808" s="3"/>
+      <c r="B8808" s="7"/>
+      <c r="C8808" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8809" s="3"/>
+      <c r="B8809" s="7"/>
+      <c r="C8809" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8810" s="3"/>
+      <c r="B8810" s="7"/>
+      <c r="C8810" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8811" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8811" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8811" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8812" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8812" s="9"/>
+      <c r="C8812" s="8"/>
+    </row>
+    <row r="8851" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8851" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8851" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8851" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8852" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8852" s="13"/>
+      <c r="B8852" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8852" s="21"/>
+    </row>
+    <row r="8853" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8853" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8853" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8853" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8854" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8854" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8854" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8855" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8855" s="7"/>
+      <c r="C8855" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8856" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8856" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8856" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8857" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8857" s="7"/>
+      <c r="C8857" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8858" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8858" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8858" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8859" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8859" s="7"/>
+      <c r="C8859" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8860" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8860" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8860" s="7"/>
+      <c r="C8860" s="2"/>
+    </row>
+    <row r="8861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8861" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8861" s="7"/>
+      <c r="C8861" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8862" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8862" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8862" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8863" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8863" s="7"/>
+      <c r="C8863" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8864" s="3"/>
+      <c r="B8864" s="7"/>
+      <c r="C8864" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8865" s="3"/>
+      <c r="B8865" s="7"/>
+      <c r="C8865" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8866" s="3"/>
+      <c r="B8866" s="7"/>
+      <c r="C8866" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8867" s="3"/>
+      <c r="B8867" s="7"/>
+      <c r="C8867" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8868" s="3"/>
+      <c r="B8868" s="7"/>
+      <c r="C8868" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8869" s="3"/>
+      <c r="B8869" s="7"/>
+      <c r="C8869" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8870" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8870" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8870" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8871" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8871" s="9"/>
+      <c r="C8871" s="8"/>
+    </row>
+    <row r="8910" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8910" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8910" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8910" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8911" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8911" s="13"/>
+      <c r="B8911" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8911" s="21"/>
+    </row>
+    <row r="8912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8912" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8912" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8912" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8913" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8913" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8913" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8914" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8914" s="7"/>
+      <c r="C8914" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8915" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8915" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8915" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8916" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8916" s="7"/>
+      <c r="C8916" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8917" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8917" s="7"/>
+      <c r="C8917" s="2"/>
+    </row>
+    <row r="8918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8918" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8918" s="7"/>
+      <c r="C8918" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8919" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8919" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8919" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8920" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8920" s="7"/>
+      <c r="C8920" s="2"/>
+    </row>
+    <row r="8921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8921" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8921" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8921" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8922" s="3"/>
+      <c r="B8922" s="22"/>
+      <c r="C8922" s="2"/>
+    </row>
+    <row r="8923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8923" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8923" s="7"/>
+      <c r="C8923" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8924" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8924" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8924" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8925" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B8925" s="7"/>
+      <c r="C8925" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8926" s="3"/>
+      <c r="B8926" s="7"/>
+      <c r="C8926" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8927" s="3"/>
+      <c r="B8927" s="7"/>
+      <c r="C8927" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8928" s="3"/>
+      <c r="B8928" s="7"/>
+      <c r="C8928" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8929" s="3"/>
+      <c r="B8929" s="7"/>
+      <c r="C8929" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8930" s="3"/>
+      <c r="B8930" s="7"/>
+      <c r="C8930" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8931" s="3"/>
+      <c r="B8931" s="7"/>
+      <c r="C8931" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="8932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8932" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B8932" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8932" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8933" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8933" s="9"/>
+      <c r="C8933" s="8"/>
+    </row>
+    <row r="8969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8969" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8969" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8969" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8970" s="13"/>
+      <c r="B8970" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8970" s="21"/>
+    </row>
+    <row r="8971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8971" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8971" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8971" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8972" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8972" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8972" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8973" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B8973" s="7"/>
+      <c r="C8973" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8974" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B8974" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8974" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8975" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B8975" s="7"/>
+      <c r="C8975" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8976" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B8976" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8976" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8977" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B8977" s="7"/>
+      <c r="C8977" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8978" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B8978" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8978" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8979" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B8979" s="7"/>
+      <c r="C8979" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="8980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8980" s="3"/>
+      <c r="B8980" s="2"/>
+      <c r="C8980" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="8981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8981" s="3"/>
+      <c r="B8981" s="2"/>
+      <c r="C8981" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="8982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8982" s="3"/>
+      <c r="B8982" s="7"/>
+      <c r="C8982" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8983" s="3"/>
+      <c r="B8983" s="7"/>
+      <c r="C8983" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="8984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8984" s="3"/>
+      <c r="B8984" s="7"/>
+      <c r="C8984" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8985" s="3"/>
+      <c r="B8985" s="7"/>
+      <c r="C8985" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="8986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8986" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B8986" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8986" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8987" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B8987" s="7"/>
+      <c r="C8987" s="2"/>
+    </row>
+    <row r="8988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8988" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B8988" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8988" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8989" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8989" s="9"/>
+      <c r="C8989" s="8"/>
+    </row>
+    <row r="9028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9028" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9028" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9028" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9029" s="13"/>
+      <c r="B9029" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9029" s="21"/>
+    </row>
+    <row r="9030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9030" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9030" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9030" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9031" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9031" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9031" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9032" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9032" s="7"/>
+      <c r="C9032" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9033" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9033" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9033" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9034" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9034" s="7"/>
+      <c r="C9034" s="2"/>
+    </row>
+    <row r="9035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9035" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9035" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9035" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9036" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B9036" s="7"/>
+      <c r="C9036" s="2"/>
+    </row>
+    <row r="9037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9037" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9037" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9037" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9038" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9038" s="7"/>
+      <c r="C9038" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9039" s="3"/>
+      <c r="B9039" s="2"/>
+      <c r="C9039" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9040" s="3"/>
+      <c r="B9040" s="2"/>
+      <c r="C9040" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9041" s="3"/>
+      <c r="B9041" s="7"/>
+      <c r="C9041" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9042" s="3"/>
+      <c r="B9042" s="7"/>
+      <c r="C9042" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9043" s="3"/>
+      <c r="B9043" s="7"/>
+      <c r="C9043" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9044" s="3"/>
+      <c r="B9044" s="7"/>
+      <c r="C9044" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9045" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9045" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9045" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9046" s="3"/>
+      <c r="B9046" s="22"/>
+      <c r="C9046" s="2"/>
+    </row>
+    <row r="9047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9047" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9047" s="7"/>
+      <c r="C9047" s="2"/>
+    </row>
+    <row r="9048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9048" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9048" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9048" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9049" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9049" s="9"/>
+      <c r="C9049" s="8"/>
+    </row>
+    <row r="9087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9087" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9087" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9087" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9088" s="13"/>
+      <c r="B9088" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9088" s="18"/>
+    </row>
+    <row r="9089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9089" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9089" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9089" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9090" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9090" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9090" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9091" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9091" s="7"/>
+      <c r="C9091" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9092" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9092" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9092" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9093" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9093" s="7"/>
+      <c r="C9093" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9094" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9094" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9094" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9095" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B9095" s="7"/>
+      <c r="C9095" s="2"/>
+    </row>
+    <row r="9096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9096" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9096" s="7"/>
+      <c r="C9096" s="2"/>
+    </row>
+    <row r="9097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9097" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9097" s="7"/>
+      <c r="C9097" s="2"/>
+    </row>
+    <row r="9098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9098" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9098" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9098" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="9099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9099" s="3"/>
+      <c r="B9099" s="22"/>
+      <c r="C9099" s="2"/>
+    </row>
+    <row r="9100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9100" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9100" s="7"/>
+      <c r="C9100" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9101" s="3"/>
+      <c r="B9101" s="2"/>
+      <c r="C9101" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9102" s="3"/>
+      <c r="B9102" s="2"/>
+      <c r="C9102" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9103" s="3"/>
+      <c r="B9103" s="7"/>
+      <c r="C9103" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="9104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9104" s="3"/>
+      <c r="B9104" s="7"/>
+      <c r="C9104" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="9105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9105" s="3"/>
+      <c r="B9105" s="7"/>
+      <c r="C9105" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9106" s="3"/>
+      <c r="B9106" s="7"/>
+      <c r="C9106" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9107" s="3"/>
+      <c r="B9107" s="7"/>
+      <c r="C9107" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="9108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9108" s="3"/>
+      <c r="B9108" s="7"/>
+      <c r="C9108" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9109" s="3"/>
+      <c r="B9109" s="7"/>
+      <c r="C9109" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9110" s="3"/>
+      <c r="B9110" s="7"/>
+      <c r="C9110" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9111" s="3"/>
+      <c r="B9111" s="7"/>
+      <c r="C9111" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9112" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9112" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9112" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9113" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9113" s="9"/>
+      <c r="C9113" s="8"/>
+    </row>
+    <row r="9146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9146" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9146" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9146" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9147" s="13"/>
+      <c r="B9147" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9147" s="21"/>
+    </row>
+    <row r="9148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9148" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9148" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9148" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9149" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9149" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9149" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9150" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9150" s="7"/>
+      <c r="C9150" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9151" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9151" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9151" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9152" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9152" s="7"/>
+      <c r="C9152" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9153" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9153" s="7"/>
+      <c r="C9153" s="2"/>
+    </row>
+    <row r="9154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9154" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B9154" s="7"/>
+      <c r="C9154" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9155" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9155" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9155" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9156" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9156" s="7"/>
+      <c r="C9156" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="9157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9157" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9157" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9157" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9158" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9158" s="2"/>
+      <c r="C9158" s="2"/>
+    </row>
+    <row r="9159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9159" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9159" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9159" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9160" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9160" s="9"/>
+      <c r="C9160" s="8"/>
+    </row>
+    <row r="9205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9205" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B9205" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9205" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9206" s="13"/>
+      <c r="B9206" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9206" s="18"/>
+    </row>
+    <row r="9207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9207" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9207" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9207" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9208" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9208" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9208" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9209" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9209" s="7"/>
+      <c r="C9209" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9210" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9210" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9210" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9211" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9211" s="7"/>
+      <c r="C9211" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9212" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9212" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9212" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9213" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9213" s="9"/>
+      <c r="C9213" s="8"/>
+    </row>
+    <row r="9264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9264" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B9264" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9264" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9265" s="13"/>
+      <c r="B9265" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9265" s="18"/>
+    </row>
+    <row r="9266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9266" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9266" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9266" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9267" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9267" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9267" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9268" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9268" s="7"/>
+      <c r="C9268" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9269" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9269" s="7"/>
+      <c r="C9269" s="2"/>
+    </row>
+    <row r="9270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9270" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9270" s="7"/>
+      <c r="C9270" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9271" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9271" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9271" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9272" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9272" s="9"/>
+      <c r="C9272" s="8"/>
+    </row>
+    <row r="9323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9323" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9323" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="C9323" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9324" s="13"/>
+      <c r="B9324" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9324" s="18"/>
+    </row>
+    <row r="9325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9325" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9325" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9325" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9326" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9326" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9326" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9327" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9327" s="7"/>
+      <c r="C9327" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9328" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9328" s="7"/>
+      <c r="C9328" s="2"/>
+    </row>
+    <row r="9329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9329" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9329" s="7"/>
+      <c r="C9329" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9330" s="3"/>
+      <c r="B9330" s="7"/>
+      <c r="C9330" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9331" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9331" s="7"/>
+      <c r="C9331" s="2"/>
+    </row>
+    <row r="9332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9332" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B9332" s="7"/>
+      <c r="C9332" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9333" s="3"/>
+      <c r="B9333" s="7"/>
+      <c r="C9333" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9334" s="3"/>
+      <c r="B9334" s="7"/>
+      <c r="C9334" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9335" s="3"/>
+      <c r="B9335" s="7"/>
+      <c r="C9335" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9336" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9336" s="7"/>
+      <c r="C9336" s="2"/>
+    </row>
+    <row r="9337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9337" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9337" s="7"/>
+      <c r="C9337" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9338" s="3"/>
+      <c r="B9338" s="7"/>
+      <c r="C9338" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9339" s="3"/>
+      <c r="B9339" s="7"/>
+      <c r="C9339" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9340" s="3"/>
+      <c r="B9340" s="7"/>
+      <c r="C9340" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9341" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9341" s="7"/>
+      <c r="C9341" s="2"/>
+    </row>
+    <row r="9342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9342" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9342" s="7"/>
+      <c r="C9342" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9343" s="3"/>
+      <c r="B9343" s="7"/>
+      <c r="C9343" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9344" s="3"/>
+      <c r="B9344" s="7"/>
+      <c r="C9344" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9345" s="3"/>
+      <c r="B9345" s="7"/>
+      <c r="C9345" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9346" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9346" s="7"/>
+      <c r="C9346" s="2"/>
+    </row>
+    <row r="9347" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9347" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B9347" s="7"/>
+      <c r="C9347" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9348" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9348" s="3"/>
+      <c r="B9348" s="7"/>
+      <c r="C9348" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9349" s="3"/>
+      <c r="B9349" s="7"/>
+      <c r="C9349" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9350" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9350" s="3"/>
+      <c r="B9350" s="7"/>
+      <c r="C9350" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9351" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B9351" s="7"/>
+      <c r="C9351" s="2"/>
+    </row>
+    <row r="9352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9352" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B9352" s="7"/>
+      <c r="C9352" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9353" s="3"/>
+      <c r="B9353" s="7"/>
+      <c r="C9353" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9354" s="3"/>
+      <c r="B9354" s="7"/>
+      <c r="C9354" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9355" s="3"/>
+      <c r="B9355" s="7"/>
+      <c r="C9355" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9356" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B9356" s="7"/>
+      <c r="C9356" s="2"/>
+    </row>
+    <row r="9357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9357" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B9357" s="7"/>
+      <c r="C9357" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9358" s="3"/>
+      <c r="B9358" s="7"/>
+      <c r="C9358" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9359" s="3"/>
+      <c r="B9359" s="7"/>
+      <c r="C9359" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9360" s="3"/>
+      <c r="B9360" s="7"/>
+      <c r="C9360" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9361" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B9361" s="7"/>
+      <c r="C9361" s="2"/>
+    </row>
+    <row r="9362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9362" s="3">
+        <v>9.1</v>
+      </c>
+      <c r="B9362" s="7"/>
+      <c r="C9362" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9363" s="3"/>
+      <c r="B9363" s="7"/>
+      <c r="C9363" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9364" s="3"/>
+      <c r="B9364" s="7"/>
+      <c r="C9364" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9365" s="3"/>
+      <c r="B9365" s="7"/>
+      <c r="C9365" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9366" s="3">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="B9366" s="7"/>
+      <c r="C9366" s="2"/>
+    </row>
+    <row r="9367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9367" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="B9367" s="7"/>
+      <c r="C9367" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9368" s="3"/>
+      <c r="B9368" s="7"/>
+      <c r="C9368" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9369" s="3"/>
+      <c r="B9369" s="7"/>
+      <c r="C9369" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9370" s="3"/>
+      <c r="B9370" s="7"/>
+      <c r="C9370" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9371" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="B9371" s="7"/>
+      <c r="C9371" s="2"/>
+    </row>
+    <row r="9372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9372" s="3">
+        <v>11.1</v>
+      </c>
+      <c r="B9372" s="7"/>
+      <c r="C9372" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="9373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9373" s="3"/>
+      <c r="B9373" s="7"/>
+      <c r="C9373" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9374" s="3"/>
+      <c r="B9374" s="7"/>
+      <c r="C9374" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9375" s="3"/>
+      <c r="B9375" s="7"/>
+      <c r="C9375" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9376" s="3">
+        <v>11.2</v>
+      </c>
+      <c r="B9376" s="7"/>
+      <c r="C9376" s="2"/>
+    </row>
+    <row r="9377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9377" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="B9377" s="7"/>
+      <c r="C9377" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9378" s="3"/>
+      <c r="B9378" s="7"/>
+      <c r="C9378" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9379" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="B9379" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9379" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9380" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9380" s="9"/>
+      <c r="C9380" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="107">
+    <mergeCell ref="B9098:B9099"/>
+    <mergeCell ref="B9147:C9147"/>
+    <mergeCell ref="B8921:B8922"/>
+    <mergeCell ref="B8970:C8970"/>
+    <mergeCell ref="B9029:C9029"/>
+    <mergeCell ref="B9045:B9046"/>
+    <mergeCell ref="B8675:C8675"/>
+    <mergeCell ref="B8793:C8793"/>
+    <mergeCell ref="B8852:C8852"/>
+    <mergeCell ref="B8911:C8911"/>
+    <mergeCell ref="B8203:C8203"/>
+    <mergeCell ref="B8262:C8262"/>
+    <mergeCell ref="B8439:C8439"/>
+    <mergeCell ref="B8616:C8616"/>
+    <mergeCell ref="B8085:C8085"/>
+    <mergeCell ref="B8144:C8144"/>
+    <mergeCell ref="B7672:C7672"/>
+    <mergeCell ref="B7731:C7731"/>
+    <mergeCell ref="B7967:C7967"/>
+    <mergeCell ref="B7977:B7978"/>
     <mergeCell ref="B7200:C7200"/>
     <mergeCell ref="B7210:B7211"/>
+    <mergeCell ref="B7259:C7259"/>
+    <mergeCell ref="C7268:C7269"/>
     <mergeCell ref="B7151:B7152"/>
     <mergeCell ref="B7141:C7141"/>
     <mergeCell ref="B6787:C6787"/>

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7AE86F-FDF1-4876-80A0-690923420559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1385263-710F-42A8-91EC-37991203BF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3686" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3704" uniqueCount="407">
   <si>
     <t>Implied</t>
   </si>
@@ -7822,6 +7822,223 @@
   </si>
   <si>
     <t>If DivYa &amp; $20000: DivYa ^= $20001.</t>
+  </si>
+  <si>
+    <t>XCN (9F)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt; 7) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 1).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &gt;&gt; 7) | (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;&lt; 1). </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; $80), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> flag = !</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8400,7 +8617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C9380"/>
+  <dimension ref="A1:C9396"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -31212,6 +31429,137 @@
       </c>
       <c r="B9380" s="9"/>
       <c r="C9380" s="8"/>
+    </row>
+    <row r="9382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9382" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B9382" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9382" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9383" s="13"/>
+      <c r="B9383" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9383" s="18"/>
+    </row>
+    <row r="9384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9384" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9384" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9384" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9385" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9385" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9385" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9386" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B9386" s="7"/>
+      <c r="C9386" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9387" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B9387" s="7"/>
+      <c r="C9387" s="2"/>
+    </row>
+    <row r="9388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9388" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B9388" s="7"/>
+      <c r="C9388" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9389" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9389" s="7"/>
+      <c r="C9389" s="2"/>
+    </row>
+    <row r="9390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9390" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B9390" s="7"/>
+      <c r="C9390" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9391" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9391" s="7"/>
+      <c r="C9391" s="2"/>
+    </row>
+    <row r="9392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9392" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B9392" s="7"/>
+      <c r="C9392" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9393" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9393" s="7"/>
+      <c r="C9393" s="2"/>
+    </row>
+    <row r="9394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9394" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9394" s="7"/>
+      <c r="C9394" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9395" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9395" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9395" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9396" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9396" s="9"/>
+      <c r="C9396" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="107">

--- a/Research/Instructions/SPC-700 Instructions SNES.xlsx
+++ b/Research/Instructions/SPC-700 Instructions SNES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Projects\BirdSNES\Research\Instructions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9CBFA-9462-46D4-97FC-BF20AF5B0C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2C45C-7AC4-4466-B214-DD17A5E88B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7ED93F2B-FF78-48E4-8428-9E2E36877943}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$11210</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$C$11553</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4433" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4564" uniqueCount="483">
   <si>
     <t>Implied</t>
   </si>
@@ -8995,6 +8995,86 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>DI (C0)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PSW</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; ~$04).</t>
+    </r>
+  </si>
+  <si>
+    <t>TCALL12 (C1)</t>
+  </si>
+  <si>
+    <t>Read $FFC6</t>
+  </si>
+  <si>
+    <t>Read $FFC7</t>
+  </si>
+  <si>
+    <t>SET1 (A2)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$20) | $20.</t>
+  </si>
+  <si>
+    <t>SET1 (C2)</t>
+  </si>
+  <si>
+    <t>Operand = (Operand &amp; ~$40) | $40.</t>
+  </si>
+  <si>
+    <t>BBS6 (C3)</t>
+  </si>
+  <si>
+    <t>Set Jump to (Operand &amp; (1 &lt;&lt; 6)) == (1 &lt;&lt; 6).</t>
+  </si>
+  <si>
+    <t>MOV (C4)</t>
+  </si>
+  <si>
+    <t>Direct Page d (Write)</t>
   </si>
 </sst>
 </file>
@@ -9576,7 +9656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236A51FB-68FA-4644-A8C6-D47AA32EBCC5}">
-  <dimension ref="A1:C11164"/>
+  <dimension ref="A1:C11518"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" style="19" customWidth="1"/>
@@ -32806,21 +32886,21 @@
     </row>
     <row r="9559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9559" s="10" t="s">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="B9559" s="11" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C9559" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9560" s="13"/>
-      <c r="B9560" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9560" s="18"/>
+      <c r="B9560" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9560" s="23"/>
     </row>
     <row r="9561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9561" s="5" t="s">
@@ -32890,15 +32970,19 @@
       </c>
       <c r="B9567" s="7"/>
       <c r="C9567" s="2" t="s">
-        <v>401</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9568" s="3">
         <v>3.2</v>
       </c>
-      <c r="B9568" s="7"/>
-      <c r="C9568" s="2"/>
+      <c r="B9568" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9568" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9569" s="3">
@@ -32915,90 +32999,31 @@
         <v>47</v>
       </c>
       <c r="C9570" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9571" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B9571" s="7"/>
-      <c r="C9571" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9572" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B9572" s="7"/>
-      <c r="C9572" s="2"/>
-    </row>
-    <row r="9573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9573" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="B9573" s="7"/>
-      <c r="C9573" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="9574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9574" s="3"/>
-      <c r="B9574" s="7"/>
-      <c r="C9574" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9575" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B9575" s="7"/>
-      <c r="C9575" s="2"/>
-    </row>
-    <row r="9576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9576" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="B9576" s="7"/>
-      <c r="C9576" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9577" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="B9577" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9577" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9578" s="16" t="s">
+      <c r="A9571" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9578" s="9"/>
-      <c r="C9578" s="8"/>
+      <c r="B9571" s="9"/>
+      <c r="C9571" s="8"/>
     </row>
     <row r="9618" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9618" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B9618" s="11" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C9618" s="12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9619" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9619" s="13"/>
       <c r="B9619" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9619" s="18"/>
     </row>
@@ -33070,91 +33095,115 @@
       </c>
       <c r="B9626" s="7"/>
       <c r="C9626" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9627" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9627" s="3"/>
+      <c r="A9627" s="3">
+        <v>3.2</v>
+      </c>
       <c r="B9627" s="7"/>
-      <c r="C9627" s="2" t="s">
-        <v>404</v>
-      </c>
+      <c r="C9627" s="2"/>
     </row>
     <row r="9628" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9628" s="3"/>
+      <c r="A9628" s="3">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="B9628" s="7"/>
-      <c r="C9628" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="C9628" s="2"/>
     </row>
     <row r="9629" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9629" s="3"/>
-      <c r="B9629" s="7"/>
+      <c r="A9629" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9629" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C9629" s="2" t="s">
-        <v>334</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9630" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9630" s="3"/>
+      <c r="A9630" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="B9630" s="7"/>
       <c r="C9630" s="2" t="s">
-        <v>405</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9631" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9631" s="3"/>
+      <c r="A9631" s="3">
+        <v>5.2</v>
+      </c>
       <c r="B9631" s="7"/>
-      <c r="C9631" s="2" t="s">
-        <v>406</v>
-      </c>
+      <c r="C9631" s="2"/>
     </row>
     <row r="9632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9632" s="3"/>
+      <c r="A9632" s="3">
+        <v>6.1</v>
+      </c>
       <c r="B9632" s="7"/>
       <c r="C9632" s="2" t="s">
-        <v>308</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9633" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9633" s="3"/>
       <c r="B9633" s="7"/>
       <c r="C9633" s="2" t="s">
-        <v>304</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9634" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9634" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B9634" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9634" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>6.2</v>
+      </c>
+      <c r="B9634" s="7"/>
+      <c r="C9634" s="2"/>
     </row>
     <row r="9635" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9635" s="16" t="s">
+      <c r="A9635" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B9635" s="7"/>
+      <c r="C9635" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9636" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9636" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B9636" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9636" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9637" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9637" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9635" s="9"/>
-      <c r="C9635" s="8"/>
+      <c r="B9637" s="9"/>
+      <c r="C9637" s="8"/>
     </row>
     <row r="9677" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9677" s="10" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B9677" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C9677" s="12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9678" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9678" s="13"/>
       <c r="B9678" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C9678" s="18"/>
     </row>
@@ -33193,22 +33242,28 @@
       <c r="A9682" s="3">
         <v>1.2</v>
       </c>
-      <c r="B9682" s="7"/>
-      <c r="C9682" s="2"/>
+      <c r="B9682" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9682" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9683" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9683" s="3">
         <v>2.1</v>
       </c>
       <c r="B9683" s="7"/>
-      <c r="C9683" s="2"/>
+      <c r="C9683" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="9684" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9684" s="3">
         <v>2.2000000000000002</v>
       </c>
       <c r="B9684" s="7" t="s">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="C9684" s="2" t="s">
         <v>6</v>
@@ -33292,21 +33347,21 @@
     </row>
     <row r="9736" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9736" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B9736" s="11" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C9736" s="12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9737" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9737" s="13"/>
-      <c r="B9737" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9737" s="23"/>
+      <c r="B9737" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9737" s="18"/>
     </row>
     <row r="9738" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9738" s="5" t="s">
@@ -33343,28 +33398,26 @@
       <c r="A9741" s="3">
         <v>1.2</v>
       </c>
-      <c r="B9741" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9741" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B9741" s="7"/>
+      <c r="C9741" s="2"/>
     </row>
     <row r="9742" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9742" s="3">
         <v>2.1</v>
       </c>
       <c r="B9742" s="7"/>
-      <c r="C9742" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="C9742" s="2"/>
     </row>
     <row r="9743" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9743" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B9743" s="7"/>
-      <c r="C9743" s="2"/>
+      <c r="B9743" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9743" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9744" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9744" s="3">
@@ -33372,143 +33425,82 @@
       </c>
       <c r="B9744" s="7"/>
       <c r="C9744" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9745" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B9745" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A9745" s="3"/>
+      <c r="B9745" s="7"/>
       <c r="C9745" s="2" t="s">
-        <v>65</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9746" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9746" s="3">
-        <v>4.0999999999999996</v>
-      </c>
+      <c r="A9746" s="3"/>
       <c r="B9746" s="7"/>
-      <c r="C9746" s="2"/>
+      <c r="C9746" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="9747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9747" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B9747" s="24" t="s">
-        <v>412</v>
-      </c>
+      <c r="A9747" s="3"/>
+      <c r="B9747" s="7"/>
       <c r="C9747" s="2" t="s">
-        <v>20</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9748" s="3"/>
-      <c r="B9748" s="24"/>
-      <c r="C9748" s="2"/>
+      <c r="B9748" s="7"/>
+      <c r="C9748" s="2" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="9749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9749" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A9749" s="3"/>
       <c r="B9749" s="7"/>
-      <c r="C9749" s="2"/>
+      <c r="C9749" s="2" t="s">
+        <v>406</v>
+      </c>
     </row>
     <row r="9750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9750" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B9750" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="A9750" s="3"/>
+      <c r="B9750" s="7"/>
       <c r="C9750" s="2" t="s">
-        <v>6</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9751" s="3">
-        <v>6.1</v>
-      </c>
+      <c r="A9751" s="3"/>
       <c r="B9751" s="7"/>
       <c r="C9751" s="2" t="s">
-        <v>403</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9752" s="3"/>
-      <c r="B9752" s="7"/>
+      <c r="A9752" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9752" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C9752" s="2" t="s">
-        <v>404</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9753" s="3"/>
-      <c r="B9753" s="7"/>
-      <c r="C9753" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9754" s="3"/>
-      <c r="B9754" s="7"/>
-      <c r="C9754" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9755" s="3"/>
-      <c r="B9755" s="7"/>
-      <c r="C9755" s="2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="9756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9756" s="3"/>
-      <c r="B9756" s="7"/>
-      <c r="C9756" s="2" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="9757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9757" s="3"/>
-      <c r="B9757" s="7"/>
-      <c r="C9757" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="9758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9758" s="3"/>
-      <c r="B9758" s="7"/>
-      <c r="C9758" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="9759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9759" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B9759" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9759" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9760" s="16" t="s">
+      <c r="A9753" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9760" s="9"/>
-      <c r="C9760" s="8"/>
+      <c r="B9753" s="9"/>
+      <c r="C9753" s="8"/>
     </row>
     <row r="9795" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9795" s="10" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B9795" s="11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C9795" s="12" t="s">
         <v>4</v>
@@ -33516,10 +33508,10 @@
     </row>
     <row r="9796" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9796" s="13"/>
-      <c r="B9796" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9796" s="18"/>
+      <c r="B9796" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9796" s="23"/>
     </row>
     <row r="9797" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9797" s="5" t="s">
@@ -33569,93 +33561,170 @@
       </c>
       <c r="B9801" s="7"/>
       <c r="C9801" s="2" t="s">
-        <v>418</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9802" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9802" s="3"/>
+      <c r="A9802" s="3">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="B9802" s="7"/>
-      <c r="C9802" s="2" t="s">
-        <v>404</v>
-      </c>
+      <c r="C9802" s="2"/>
     </row>
     <row r="9803" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9803" s="3"/>
+      <c r="A9803" s="3">
+        <v>3.1</v>
+      </c>
       <c r="B9803" s="7"/>
       <c r="C9803" s="2" t="s">
-        <v>303</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9804" s="3"/>
-      <c r="B9804" s="7"/>
+      <c r="A9804" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B9804" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="C9804" s="2" t="s">
-        <v>334</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9805" s="3"/>
+      <c r="A9805" s="3">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="B9805" s="7"/>
-      <c r="C9805" s="2" t="s">
-        <v>405</v>
-      </c>
+      <c r="C9805" s="2"/>
     </row>
     <row r="9806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9806" s="3"/>
-      <c r="B9806" s="2"/>
+      <c r="A9806" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9806" s="24" t="s">
+        <v>412</v>
+      </c>
       <c r="C9806" s="2" t="s">
-        <v>406</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9807" s="3"/>
-      <c r="B9807" s="2"/>
-      <c r="C9807" s="2" t="s">
-        <v>308</v>
-      </c>
+      <c r="B9807" s="24"/>
+      <c r="C9807" s="2"/>
     </row>
     <row r="9808" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9808" s="3"/>
+      <c r="A9808" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="B9808" s="7"/>
-      <c r="C9808" s="2" t="s">
-        <v>304</v>
-      </c>
+      <c r="C9808" s="2"/>
     </row>
     <row r="9809" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9809" s="3">
-        <v>2.2000000000000002</v>
+        <v>5.2</v>
       </c>
       <c r="B9809" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C9809" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9810" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9810" s="16" t="s">
+      <c r="A9810" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B9810" s="7"/>
+      <c r="C9810" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="9811" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9811" s="3"/>
+      <c r="B9811" s="7"/>
+      <c r="C9811" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9812" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9812" s="3"/>
+      <c r="B9812" s="7"/>
+      <c r="C9812" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9813" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9813" s="3"/>
+      <c r="B9813" s="7"/>
+      <c r="C9813" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9814" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9814" s="3"/>
+      <c r="B9814" s="7"/>
+      <c r="C9814" s="2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9815" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9815" s="3"/>
+      <c r="B9815" s="7"/>
+      <c r="C9815" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9816" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9816" s="3"/>
+      <c r="B9816" s="7"/>
+      <c r="C9816" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9817" s="3"/>
+      <c r="B9817" s="7"/>
+      <c r="C9817" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9818" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B9818" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9818" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9819" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9810" s="9"/>
-      <c r="C9810" s="8"/>
+      <c r="B9819" s="9"/>
+      <c r="C9819" s="8"/>
     </row>
     <row r="9854" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9854" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B9854" s="11" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C9854" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9855" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9855" s="13"/>
-      <c r="B9855" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9855" s="23"/>
+      <c r="B9855" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9855" s="18"/>
     </row>
     <row r="9856" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9856" s="5" t="s">
@@ -33705,158 +33774,82 @@
       </c>
       <c r="B9860" s="7"/>
       <c r="C9860" s="2" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9861" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9861" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B9861" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A9861" s="3"/>
+      <c r="B9861" s="7"/>
       <c r="C9861" s="2" t="s">
-        <v>68</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9862" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9862" s="3">
-        <v>3.1</v>
-      </c>
+      <c r="A9862" s="3"/>
       <c r="B9862" s="7"/>
-      <c r="C9862" s="2"/>
+      <c r="C9862" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="9863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9863" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B9863" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="A9863" s="3"/>
+      <c r="B9863" s="7"/>
       <c r="C9863" s="2" t="s">
-        <v>6</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9864" s="3">
-        <v>4.0999999999999996</v>
-      </c>
+      <c r="A9864" s="3"/>
       <c r="B9864" s="7"/>
       <c r="C9864" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9865" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B9865" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A9865" s="3"/>
+      <c r="B9865" s="2"/>
       <c r="C9865" s="2" t="s">
-        <v>69</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9866" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9866" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B9866" s="7"/>
+      <c r="A9866" s="3"/>
+      <c r="B9866" s="2"/>
       <c r="C9866" s="2" t="s">
-        <v>420</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9867" s="3"/>
       <c r="B9867" s="7"/>
       <c r="C9867" s="2" t="s">
-        <v>421</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9868" s="3"/>
-      <c r="B9868" s="7"/>
+      <c r="A9868" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B9868" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C9868" s="2" t="s">
-        <v>303</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9869" s="3"/>
-      <c r="B9869" s="7"/>
-      <c r="C9869" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9870" s="3"/>
-      <c r="B9870" s="7"/>
-      <c r="C9870" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="9871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9871" s="3"/>
-      <c r="B9871" s="7"/>
-      <c r="C9871" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="9872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9872" s="3"/>
-      <c r="B9872" s="7"/>
-      <c r="C9872" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="9873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9873" s="3"/>
-      <c r="B9873" s="7"/>
-      <c r="C9873" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="9874" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9874" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B9874" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9874" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9875" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="B9875" s="2"/>
-      <c r="C9875" s="2"/>
-    </row>
-    <row r="9876" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9876" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B9876" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9876" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9877" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9877" s="16" t="s">
+      <c r="A9869" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9877" s="9"/>
-      <c r="C9877" s="8"/>
+      <c r="B9869" s="9"/>
+      <c r="C9869" s="8"/>
     </row>
     <row r="9913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9913" s="10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B9913" s="11" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C9913" s="12" t="s">
         <v>16</v>
@@ -33864,10 +33857,10 @@
     </row>
     <row r="9914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9914" s="13"/>
-      <c r="B9914" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9914" s="18"/>
+      <c r="B9914" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9914" s="23"/>
     </row>
     <row r="9915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9915" s="5" t="s">
@@ -33908,7 +33901,7 @@
         <v>47</v>
       </c>
       <c r="C9918" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33917,7 +33910,7 @@
       </c>
       <c r="B9919" s="7"/>
       <c r="C9919" s="2" t="s">
-        <v>25</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33925,10 +33918,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B9920" s="7" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C9920" s="2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33936,16 +33929,14 @@
         <v>3.1</v>
       </c>
       <c r="B9921" s="7"/>
-      <c r="C9921" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="C9921" s="2"/>
     </row>
     <row r="9922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9922" s="3">
         <v>3.2</v>
       </c>
       <c r="B9922" s="7" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C9922" s="2" t="s">
         <v>6</v>
@@ -33957,51 +33948,131 @@
       </c>
       <c r="B9923" s="7"/>
       <c r="C9923" s="2" t="s">
-        <v>73</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9924" s="3"/>
-      <c r="B9924" s="7"/>
+      <c r="A9924" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B9924" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="C9924" s="2" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9925" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B9925" s="7" t="s">
-        <v>47</v>
-      </c>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B9925" s="7"/>
       <c r="C9925" s="2" t="s">
-        <v>5</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9926" s="16" t="s">
+      <c r="A9926" s="3"/>
+      <c r="B9926" s="7"/>
+      <c r="C9926" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="9927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9927" s="3"/>
+      <c r="B9927" s="7"/>
+      <c r="C9927" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9928" s="3"/>
+      <c r="B9928" s="7"/>
+      <c r="C9928" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9929" s="3"/>
+      <c r="B9929" s="7"/>
+      <c r="C9929" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="9930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9930" s="3"/>
+      <c r="B9930" s="7"/>
+      <c r="C9930" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9931" s="3"/>
+      <c r="B9931" s="7"/>
+      <c r="C9931" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9932" s="3"/>
+      <c r="B9932" s="7"/>
+      <c r="C9932" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9933" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B9933" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9933" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9934" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B9934" s="2"/>
+      <c r="C9934" s="2"/>
+    </row>
+    <row r="9935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9935" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B9935" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9935" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9936" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9926" s="9"/>
-      <c r="C9926" s="8"/>
+      <c r="B9936" s="9"/>
+      <c r="C9936" s="8"/>
     </row>
     <row r="9972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9972" s="10" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B9972" s="11" t="s">
         <v>13</v>
       </c>
       <c r="C9972" s="12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9973" s="13"/>
-      <c r="B9973" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9973" s="23"/>
+      <c r="B9973" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9973" s="18"/>
     </row>
     <row r="9974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9974" s="5" t="s">
@@ -34042,7 +34113,7 @@
         <v>47</v>
       </c>
       <c r="C9977" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34051,7 +34122,7 @@
       </c>
       <c r="B9978" s="7"/>
       <c r="C9978" s="2" t="s">
-        <v>409</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34059,10 +34130,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B9979" s="7" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C9979" s="2" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34071,7 +34142,7 @@
       </c>
       <c r="B9980" s="7"/>
       <c r="C9980" s="2" t="s">
-        <v>427</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34079,10 +34150,10 @@
         <v>3.2</v>
       </c>
       <c r="B9981" s="7" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="C9981" s="2" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34090,41 +34161,50 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B9982" s="7"/>
-      <c r="C9982" s="2"/>
+      <c r="C9982" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="9983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9983" s="3">
+      <c r="A9983" s="3"/>
+      <c r="B9983" s="7"/>
+      <c r="C9983" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9984" s="3">
         <v>4.2</v>
       </c>
-      <c r="B9983" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9983" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9984" s="16" t="s">
+      <c r="B9984" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9984" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9985" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B9984" s="9"/>
-      <c r="C9984" s="8"/>
+      <c r="B9985" s="9"/>
+      <c r="C9985" s="8"/>
     </row>
     <row r="10031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10031" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B10031" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10031" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10032" s="13"/>
       <c r="B10032" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10032" s="23"/>
     </row>
@@ -34167,7 +34247,7 @@
         <v>47</v>
       </c>
       <c r="C10036" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34176,7 +34256,7 @@
       </c>
       <c r="B10037" s="7"/>
       <c r="C10037" s="2" t="s">
-        <v>25</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34184,10 +34264,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="B10038" s="7" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C10038" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34196,7 +34276,7 @@
       </c>
       <c r="B10039" s="7"/>
       <c r="C10039" s="2" t="s">
-        <v>25</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34204,10 +34284,10 @@
         <v>3.2</v>
       </c>
       <c r="B10040" s="7" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C10040" s="2" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34215,63 +34295,43 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B10041" s="7"/>
-      <c r="C10041" s="2" t="s">
-        <v>427</v>
-      </c>
+      <c r="C10041" s="2"/>
     </row>
     <row r="10042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10042" s="3">
         <v>4.2</v>
       </c>
       <c r="B10042" s="7" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C10042" s="2" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10043" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B10043" s="7"/>
-      <c r="C10043" s="2"/>
-    </row>
-    <row r="10044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10044" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10044" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10044" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10045" s="16" t="s">
+      <c r="A10043" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10045" s="9"/>
-      <c r="C10045" s="8"/>
+      <c r="B10043" s="9"/>
+      <c r="C10043" s="8"/>
     </row>
     <row r="10090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10090" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B10090" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10090" s="12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10091" s="13"/>
-      <c r="B10091" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10091" s="18"/>
+      <c r="B10091" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10091" s="23"/>
     </row>
     <row r="10092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10092" s="5" t="s">
@@ -34312,7 +34372,7 @@
         <v>47</v>
       </c>
       <c r="C10095" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34321,7 +34381,7 @@
       </c>
       <c r="B10096" s="7"/>
       <c r="C10096" s="2" t="s">
-        <v>430</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34332,31 +34392,89 @@
         <v>47</v>
       </c>
       <c r="C10097" s="2" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10098" s="16" t="s">
+      <c r="A10098" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B10098" s="7"/>
+      <c r="C10098" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10099" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B10099" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10099" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10100" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10100" s="7"/>
+      <c r="C10100" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10101" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10101" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10101" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10102" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10102" s="7"/>
+      <c r="C10102" s="2"/>
+    </row>
+    <row r="10103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10103" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B10103" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10103" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10104" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10098" s="9"/>
-      <c r="C10098" s="8"/>
+      <c r="B10104" s="9"/>
+      <c r="C10104" s="8"/>
     </row>
     <row r="10149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10149" s="10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B10149" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10149" s="12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10150" s="13"/>
       <c r="B10150" s="17" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C10150" s="18"/>
     </row>
@@ -34399,7 +34517,7 @@
         <v>47</v>
       </c>
       <c r="C10154" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34407,63 +34525,31 @@
         <v>2.1</v>
       </c>
       <c r="B10155" s="7"/>
-      <c r="C10155" s="2"/>
+      <c r="C10155" s="2" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="10156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10156" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10156" s="7"/>
-      <c r="C10156" s="2"/>
+      <c r="B10156" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10156" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10157" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="B10157" s="7"/>
-      <c r="C10157" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10158" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B10158" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C10158" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10159" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B10159" s="7"/>
-      <c r="C10159" s="2"/>
-    </row>
-    <row r="10160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10160" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10160" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10160" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10161" s="16" t="s">
+      <c r="A10157" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10161" s="9"/>
-      <c r="C10161" s="8"/>
+      <c r="B10157" s="9"/>
+      <c r="C10157" s="8"/>
     </row>
     <row r="10208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10208" s="25" t="s">
-        <v>433</v>
+      <c r="A10208" s="10" t="s">
+        <v>431</v>
       </c>
       <c r="B10208" s="11" t="s">
         <v>13</v>
@@ -34474,10 +34560,10 @@
     </row>
     <row r="10209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10209" s="13"/>
-      <c r="B10209" s="22" t="s">
-        <v>434</v>
-      </c>
-      <c r="C10209" s="23"/>
+      <c r="B10209" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10209" s="18"/>
     </row>
     <row r="10210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10210" s="5" t="s">
@@ -34526,9 +34612,7 @@
         <v>2.1</v>
       </c>
       <c r="B10214" s="7"/>
-      <c r="C10214" s="2" t="s">
-        <v>436</v>
-      </c>
+      <c r="C10214" s="2"/>
     </row>
     <row r="10215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10215" s="3">
@@ -34542,17 +34626,19 @@
         <v>3.1</v>
       </c>
       <c r="B10216" s="7"/>
-      <c r="C10216" s="2"/>
+      <c r="C10216" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="10217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10217" s="3">
         <v>3.2</v>
       </c>
       <c r="B10217" s="7" t="s">
-        <v>23</v>
+        <v>284</v>
       </c>
       <c r="C10217" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34560,9 +34646,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B10218" s="7"/>
-      <c r="C10218" s="2" t="s">
-        <v>435</v>
-      </c>
+      <c r="C10218" s="2"/>
     </row>
     <row r="10219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10219" s="3">
@@ -34583,22 +34667,22 @@
       <c r="C10220" s="8"/>
     </row>
     <row r="10267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10267" s="10" t="s">
-        <v>438</v>
+      <c r="A10267" s="25" t="s">
+        <v>433</v>
       </c>
       <c r="B10267" s="11" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="C10267" s="12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10268" s="13"/>
-      <c r="B10268" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10268" s="18"/>
+      <c r="B10268" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10268" s="23"/>
     </row>
     <row r="10269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10269" s="5" t="s">
@@ -34628,7 +34712,7 @@
       </c>
       <c r="B10271" s="7"/>
       <c r="C10271" s="2" t="s">
-        <v>439</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34639,7 +34723,7 @@
         <v>47</v>
       </c>
       <c r="C10272" s="2" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34648,7 +34732,7 @@
       </c>
       <c r="B10273" s="7"/>
       <c r="C10273" s="2" t="s">
-        <v>93</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34663,66 +34747,61 @@
         <v>3.1</v>
       </c>
       <c r="B10275" s="7"/>
-      <c r="C10275" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="C10275" s="2"/>
     </row>
     <row r="10276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10276" s="3"/>
-      <c r="B10276" s="7"/>
+      <c r="A10276" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B10276" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="C10276" s="2" t="s">
-        <v>58</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10277" s="3">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="B10277" s="7"/>
-      <c r="C10277" s="2"/>
+      <c r="C10277" s="2" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="10278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10278" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B10278" s="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="B10278" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C10278" s="2" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10279" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10279" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10279" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10280" s="16" t="s">
+      <c r="A10279" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10280" s="9"/>
-      <c r="C10280" s="8"/>
+      <c r="B10279" s="9"/>
+      <c r="C10279" s="8"/>
     </row>
     <row r="10326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10326" s="10" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B10326" s="11" t="s">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="C10326" s="12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10327" s="13"/>
       <c r="B10327" s="17" t="s">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="C10327" s="18"/>
     </row>
@@ -34754,7 +34833,7 @@
       </c>
       <c r="B10330" s="7"/>
       <c r="C10330" s="2" t="s">
-        <v>25</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34773,7 +34852,9 @@
         <v>2.1</v>
       </c>
       <c r="B10332" s="7"/>
-      <c r="C10332" s="2"/>
+      <c r="C10332" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="10333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10333" s="3">
@@ -34787,131 +34868,68 @@
         <v>3.1</v>
       </c>
       <c r="B10334" s="7"/>
-      <c r="C10334" s="2"/>
+      <c r="C10334" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="10335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10335" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B10335" s="7" t="s">
-        <v>82</v>
-      </c>
+      <c r="A10335" s="3"/>
+      <c r="B10335" s="7"/>
       <c r="C10335" s="2" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10336" s="3">
-        <v>4.0999999999999996</v>
+        <v>3.2</v>
       </c>
       <c r="B10336" s="7"/>
       <c r="C10336" s="2"/>
     </row>
     <row r="10337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10337" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10337" s="7" t="s">
-        <v>83</v>
-      </c>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10337" s="7"/>
       <c r="C10337" s="2" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10338" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B10338" s="7"/>
+        <v>4.2</v>
+      </c>
+      <c r="B10338" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C10338" s="2" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10339" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10339" s="7"/>
-      <c r="C10339" s="2"/>
-    </row>
-    <row r="10340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10340" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="B10340" s="7"/>
-      <c r="C10340" s="2"/>
-    </row>
-    <row r="10341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10341" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B10341" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="C10341" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10342" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="B10342" s="7"/>
-      <c r="C10342" s="2"/>
-    </row>
-    <row r="10343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10343" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="B10343" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10343" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10344" s="3">
-        <v>8.1</v>
-      </c>
-      <c r="B10344" s="7"/>
-      <c r="C10344" s="2"/>
-    </row>
-    <row r="10345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10345" s="3">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="B10345" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10345" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10346" s="16" t="s">
+      <c r="A10339" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10346" s="9"/>
-      <c r="C10346" s="8"/>
+      <c r="B10339" s="9"/>
+      <c r="C10339" s="8"/>
     </row>
     <row r="10385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10385" s="10" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B10385" s="11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10385" s="12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10386" s="13"/>
-      <c r="B10386" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10386" s="23"/>
+      <c r="B10386" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10386" s="18"/>
     </row>
     <row r="10387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10387" s="5" t="s">
@@ -34960,39 +34978,31 @@
         <v>2.1</v>
       </c>
       <c r="B10391" s="7"/>
-      <c r="C10391" s="2" t="s">
-        <v>409</v>
-      </c>
+      <c r="C10391" s="2"/>
     </row>
     <row r="10392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10392" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10392" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10392" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B10392" s="7"/>
+      <c r="C10392" s="2"/>
     </row>
     <row r="10393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10393" s="3">
         <v>3.1</v>
       </c>
       <c r="B10393" s="7"/>
-      <c r="C10393" s="2" t="s">
-        <v>444</v>
-      </c>
+      <c r="C10393" s="2"/>
     </row>
     <row r="10394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10394" s="3">
         <v>3.2</v>
       </c>
       <c r="B10394" s="7" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="C10394" s="2" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35007,36 +35017,106 @@
         <v>4.2</v>
       </c>
       <c r="B10396" s="7" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C10396" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10397" s="16" t="s">
+      <c r="A10397" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10397" s="7"/>
+      <c r="C10397" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10398" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B10398" s="7"/>
+      <c r="C10398" s="2"/>
+    </row>
+    <row r="10399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10399" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B10399" s="7"/>
+      <c r="C10399" s="2"/>
+    </row>
+    <row r="10400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10400" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B10400" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10400" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10401" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B10401" s="7"/>
+      <c r="C10401" s="2"/>
+    </row>
+    <row r="10402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10402" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B10402" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10402" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10403" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B10403" s="7"/>
+      <c r="C10403" s="2"/>
+    </row>
+    <row r="10404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10404" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B10404" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10404" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10405" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10397" s="9"/>
-      <c r="C10397" s="8"/>
+      <c r="B10405" s="9"/>
+      <c r="C10405" s="8"/>
     </row>
     <row r="10444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10444" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B10444" s="11" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C10444" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10445" s="13"/>
-      <c r="B10445" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10445" s="18"/>
+      <c r="B10445" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10445" s="23"/>
     </row>
     <row r="10446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10446" s="5" t="s">
@@ -35106,15 +35186,19 @@
       </c>
       <c r="B10452" s="7"/>
       <c r="C10452" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10453" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10453" s="7"/>
-      <c r="C10453" s="2"/>
+      <c r="B10453" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10453" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10454" s="3">
@@ -35131,92 +35215,33 @@
         <v>47</v>
       </c>
       <c r="C10455" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10456" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B10456" s="7"/>
-      <c r="C10456" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10457" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10457" s="7"/>
-      <c r="C10457" s="2"/>
-    </row>
-    <row r="10458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10458" s="3">
-        <v>6.1</v>
-      </c>
-      <c r="B10458" s="7"/>
-      <c r="C10458" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="10459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10459" s="3"/>
-      <c r="B10459" s="7"/>
-      <c r="C10459" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10460" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B10460" s="7"/>
-      <c r="C10460" s="2"/>
-    </row>
-    <row r="10461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10461" s="3">
-        <v>7.1</v>
-      </c>
-      <c r="B10461" s="7"/>
-      <c r="C10461" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10462" s="3">
-        <v>7.2</v>
-      </c>
-      <c r="B10462" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10462" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10463" s="16" t="s">
+      <c r="A10456" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10463" s="9"/>
-      <c r="C10463" s="8"/>
+      <c r="B10456" s="9"/>
+      <c r="C10456" s="8"/>
     </row>
     <row r="10503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10503" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B10503" s="11" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C10503" s="12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10504" s="13"/>
-      <c r="B10504" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C10504" s="23"/>
+      <c r="B10504" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10504" s="18"/>
     </row>
     <row r="10505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10505" s="5" t="s">
@@ -35266,15 +35291,19 @@
       </c>
       <c r="B10509" s="7"/>
       <c r="C10509" s="2" t="s">
-        <v>25</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10510" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10510" s="7"/>
-      <c r="C10510" s="2"/>
+      <c r="B10510" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10510" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10511" s="3">
@@ -35282,81 +35311,85 @@
       </c>
       <c r="B10511" s="7"/>
       <c r="C10511" s="2" t="s">
-        <v>411</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10512" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10512" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10512" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B10512" s="7"/>
+      <c r="C10512" s="2"/>
     </row>
     <row r="10513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10513" s="3">
         <v>4.0999999999999996</v>
       </c>
       <c r="B10513" s="7"/>
-      <c r="C10513" s="2" t="s">
-        <v>403</v>
-      </c>
+      <c r="C10513" s="2"/>
     </row>
     <row r="10514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10514" s="3"/>
-      <c r="B10514" s="7"/>
+      <c r="A10514" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10514" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C10514" s="2" t="s">
-        <v>404</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10515" s="3"/>
+      <c r="A10515" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="B10515" s="7"/>
       <c r="C10515" s="2" t="s">
-        <v>303</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10516" s="3"/>
+      <c r="A10516" s="3">
+        <v>5.2</v>
+      </c>
       <c r="B10516" s="7"/>
-      <c r="C10516" s="2" t="s">
-        <v>334</v>
-      </c>
+      <c r="C10516" s="2"/>
     </row>
     <row r="10517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10517" s="3"/>
+      <c r="A10517" s="3">
+        <v>6.1</v>
+      </c>
       <c r="B10517" s="7"/>
       <c r="C10517" s="2" t="s">
-        <v>405</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10518" s="3"/>
       <c r="B10518" s="7"/>
       <c r="C10518" s="2" t="s">
-        <v>406</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10519" s="3"/>
+      <c r="A10519" s="3">
+        <v>6.2</v>
+      </c>
       <c r="B10519" s="7"/>
-      <c r="C10519" s="2" t="s">
-        <v>308</v>
-      </c>
+      <c r="C10519" s="2"/>
     </row>
     <row r="10520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10520" s="3"/>
+      <c r="A10520" s="3">
+        <v>7.1</v>
+      </c>
       <c r="B10520" s="7"/>
       <c r="C10520" s="2" t="s">
-        <v>304</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10521" s="3">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="B10521" s="7" t="s">
         <v>47</v>
@@ -35374,19 +35407,19 @@
     </row>
     <row r="10562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10562" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B10562" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10562" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10563" s="13"/>
       <c r="B10563" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C10563" s="23"/>
     </row>
@@ -35429,7 +35462,7 @@
         <v>47</v>
       </c>
       <c r="C10567" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35445,12 +35478,8 @@
       <c r="A10569" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10569" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10569" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="B10569" s="7"/>
+      <c r="C10569" s="2"/>
     </row>
     <row r="10570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10570" s="3">
@@ -35458,15 +35487,19 @@
       </c>
       <c r="B10570" s="7"/>
       <c r="C10570" s="2" t="s">
-        <v>25</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10571" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10571" s="7"/>
-      <c r="C10571" s="2"/>
+      <c r="B10571" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10571" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="10572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10572" s="3">
@@ -35474,99 +35507,79 @@
       </c>
       <c r="B10572" s="7"/>
       <c r="C10572" s="2" t="s">
-        <v>104</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10573" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10573" s="7" t="s">
-        <v>42</v>
-      </c>
+      <c r="A10573" s="3"/>
+      <c r="B10573" s="7"/>
       <c r="C10573" s="2" t="s">
-        <v>6</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10574" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A10574" s="3"/>
       <c r="B10574" s="7"/>
       <c r="C10574" s="2" t="s">
-        <v>403</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10575" s="3"/>
       <c r="B10575" s="7"/>
       <c r="C10575" s="2" t="s">
-        <v>404</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10576" s="3"/>
       <c r="B10576" s="7"/>
       <c r="C10576" s="2" t="s">
-        <v>303</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10577" s="3"/>
       <c r="B10577" s="7"/>
       <c r="C10577" s="2" t="s">
-        <v>334</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10578" s="3"/>
       <c r="B10578" s="7"/>
       <c r="C10578" s="2" t="s">
-        <v>405</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10579" s="3"/>
       <c r="B10579" s="7"/>
       <c r="C10579" s="2" t="s">
-        <v>406</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10580" s="3"/>
-      <c r="B10580" s="7"/>
+      <c r="A10580" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10580" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C10580" s="2" t="s">
-        <v>308</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10581" s="3"/>
-      <c r="B10581" s="7"/>
-      <c r="C10581" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="10582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10582" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10582" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10582" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10583" s="16" t="s">
+      <c r="A10581" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10583" s="9"/>
-      <c r="C10583" s="8"/>
+      <c r="B10581" s="9"/>
+      <c r="C10581" s="8"/>
     </row>
     <row r="10621" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10621" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B10621" s="11" t="s">
         <v>11</v>
@@ -35578,7 +35591,7 @@
     <row r="10622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10622" s="13"/>
       <c r="B10622" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C10622" s="23"/>
     </row>
@@ -35666,7 +35679,7 @@
       </c>
       <c r="B10631" s="7"/>
       <c r="C10631" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10632" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35758,19 +35771,19 @@
     </row>
     <row r="10680" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10680" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B10680" s="11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10680" s="12" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10681" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10681" s="13"/>
       <c r="B10681" s="22" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C10681" s="23"/>
     </row>
@@ -35813,7 +35826,7 @@
         <v>47</v>
       </c>
       <c r="C10685" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10686" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -35829,8 +35842,12 @@
       <c r="A10687" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10687" s="7"/>
-      <c r="C10687" s="2"/>
+      <c r="B10687" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10687" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10688" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10688" s="3">
@@ -35838,154 +35855,127 @@
       </c>
       <c r="B10688" s="7"/>
       <c r="C10688" s="2" t="s">
-        <v>413</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10689" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10689" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10689" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10689" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="B10689" s="7"/>
+      <c r="C10689" s="2"/>
     </row>
     <row r="10690" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10690" s="3">
         <v>4.0999999999999996</v>
       </c>
       <c r="B10690" s="7"/>
-      <c r="C10690" s="2"/>
+      <c r="C10690" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="10691" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10691" s="3">
         <v>4.2</v>
       </c>
-      <c r="B10691" s="24" t="s">
-        <v>412</v>
+      <c r="B10691" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="C10691" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10692" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10692" s="3"/>
-      <c r="B10692" s="24"/>
-      <c r="C10692" s="2"/>
+      <c r="A10692" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10692" s="7"/>
+      <c r="C10692" s="2" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="10693" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10693" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A10693" s="3"/>
       <c r="B10693" s="7"/>
       <c r="C10693" s="2" t="s">
-        <v>109</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10694" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10694" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10694" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A10694" s="3"/>
+      <c r="B10694" s="7"/>
       <c r="C10694" s="2" t="s">
-        <v>6</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10695" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10695" s="3">
-        <v>6.1</v>
-      </c>
+      <c r="A10695" s="3"/>
       <c r="B10695" s="7"/>
       <c r="C10695" s="2" t="s">
-        <v>403</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10696" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10696" s="3"/>
       <c r="B10696" s="7"/>
       <c r="C10696" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10697" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10697" s="3"/>
       <c r="B10697" s="7"/>
       <c r="C10697" s="2" t="s">
-        <v>303</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10698" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10698" s="3"/>
       <c r="B10698" s="7"/>
       <c r="C10698" s="2" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10699" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10699" s="3"/>
       <c r="B10699" s="7"/>
       <c r="C10699" s="2" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10700" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10700" s="3"/>
-      <c r="B10700" s="7"/>
+      <c r="A10700" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B10700" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C10700" s="2" t="s">
-        <v>406</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10701" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10701" s="3"/>
-      <c r="B10701" s="7"/>
-      <c r="C10701" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="10702" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10702" s="3"/>
-      <c r="B10702" s="7"/>
-      <c r="C10702" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="10703" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10703" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="B10703" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10703" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10704" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10704" s="16" t="s">
+      <c r="A10701" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10704" s="9"/>
-      <c r="C10704" s="8"/>
+      <c r="B10701" s="9"/>
+      <c r="C10701" s="8"/>
     </row>
     <row r="10739" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10739" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B10739" s="11" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C10739" s="12" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10740" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10740" s="13"/>
       <c r="B10740" s="22" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C10740" s="23"/>
     </row>
@@ -36028,7 +36018,7 @@
         <v>47</v>
       </c>
       <c r="C10744" s="2" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10745" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36044,12 +36034,8 @@
       <c r="A10746" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10746" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10746" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B10746" s="7"/>
+      <c r="C10746" s="2"/>
     </row>
     <row r="10747" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10747" s="3">
@@ -36057,7 +36043,7 @@
       </c>
       <c r="B10747" s="7"/>
       <c r="C10747" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10748" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36068,7 +36054,7 @@
         <v>7</v>
       </c>
       <c r="C10748" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10749" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36076,110 +36062,135 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="B10749" s="7"/>
-      <c r="C10749" s="2" t="s">
-        <v>420</v>
-      </c>
+      <c r="C10749" s="2"/>
     </row>
     <row r="10750" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10750" s="3"/>
-      <c r="B10750" s="2"/>
+      <c r="A10750" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10750" s="24" t="s">
+        <v>412</v>
+      </c>
       <c r="C10750" s="2" t="s">
-        <v>421</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10751" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10751" s="3"/>
-      <c r="B10751" s="2"/>
-      <c r="C10751" s="2" t="s">
-        <v>303</v>
-      </c>
+      <c r="B10751" s="24"/>
+      <c r="C10751" s="2"/>
     </row>
     <row r="10752" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10752" s="3"/>
+      <c r="A10752" s="3">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="B10752" s="7"/>
       <c r="C10752" s="2" t="s">
-        <v>334</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10753" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10753" s="3"/>
-      <c r="B10753" s="7"/>
+      <c r="A10753" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B10753" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="C10753" s="2" t="s">
-        <v>422</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10754" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10754" s="3"/>
+      <c r="A10754" s="3">
+        <v>6.1</v>
+      </c>
       <c r="B10754" s="7"/>
       <c r="C10754" s="2" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10755" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10755" s="3"/>
       <c r="B10755" s="7"/>
       <c r="C10755" s="2" t="s">
-        <v>308</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10756" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10756" s="3"/>
       <c r="B10756" s="7"/>
       <c r="C10756" s="2" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10757" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10757" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10757" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="A10757" s="3"/>
+      <c r="B10757" s="7"/>
       <c r="C10757" s="2" t="s">
-        <v>70</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10758" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10758" s="3">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="A10758" s="3"/>
       <c r="B10758" s="7"/>
-      <c r="C10758" s="2"/>
+      <c r="C10758" s="2" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="10759" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10759" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10759" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="A10759" s="3"/>
+      <c r="B10759" s="7"/>
       <c r="C10759" s="2" t="s">
-        <v>5</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10760" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10760" s="16" t="s">
+      <c r="A10760" s="3"/>
+      <c r="B10760" s="7"/>
+      <c r="C10760" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10761" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10761" s="3"/>
+      <c r="B10761" s="7"/>
+      <c r="C10761" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10762" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10762" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B10762" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10762" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10763" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10763" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10760" s="9"/>
-      <c r="C10760" s="8"/>
+      <c r="B10763" s="9"/>
+      <c r="C10763" s="8"/>
     </row>
     <row r="10798" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10798" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B10798" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10798" s="12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10799" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10799" s="13"/>
       <c r="B10799" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C10799" s="23"/>
     </row>
@@ -36222,7 +36233,7 @@
         <v>47</v>
       </c>
       <c r="C10803" s="2" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10804" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36230,17 +36241,19 @@
         <v>2.1</v>
       </c>
       <c r="B10804" s="7"/>
-      <c r="C10804" s="2"/>
+      <c r="C10804" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10805" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10805" s="3">
         <v>2.2000000000000002</v>
       </c>
       <c r="B10805" s="7" t="s">
-        <v>414</v>
+        <v>47</v>
       </c>
       <c r="C10805" s="2" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10806" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36248,14 +36261,16 @@
         <v>3.1</v>
       </c>
       <c r="B10806" s="7"/>
-      <c r="C10806" s="2"/>
+      <c r="C10806" s="2" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="10807" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10807" s="3">
         <v>3.2</v>
       </c>
       <c r="B10807" s="7" t="s">
-        <v>410</v>
+        <v>7</v>
       </c>
       <c r="C10807" s="2" t="s">
         <v>69</v>
@@ -36323,60 +36338,55 @@
       <c r="A10816" s="3">
         <v>4.2</v>
       </c>
-      <c r="B10816" s="24" t="s">
-        <v>415</v>
+      <c r="B10816" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C10816" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="10817" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10817" s="3"/>
-      <c r="B10817" s="24"/>
+      <c r="A10817" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10817" s="7"/>
       <c r="C10817" s="2"/>
     </row>
     <row r="10818" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10818" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B10818" s="7"/>
-      <c r="C10818" s="2"/>
+        <v>5.2</v>
+      </c>
+      <c r="B10818" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10818" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="10819" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10819" s="3">
-        <v>5.2</v>
-      </c>
-      <c r="B10819" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10819" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10820" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10820" s="16" t="s">
+      <c r="A10819" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10820" s="9"/>
-      <c r="C10820" s="8"/>
+      <c r="B10819" s="9"/>
+      <c r="C10819" s="8"/>
     </row>
     <row r="10857" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10857" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10857" s="11" t="s">
         <v>11</v>
       </c>
       <c r="C10857" s="12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10858" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10858" s="13"/>
-      <c r="B10858" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="C10858" s="18"/>
+      <c r="B10858" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10858" s="23"/>
     </row>
     <row r="10859" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10859" s="5" t="s">
@@ -36417,7 +36427,7 @@
         <v>47</v>
       </c>
       <c r="C10862" s="2" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10863" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36425,19 +36435,17 @@
         <v>2.1</v>
       </c>
       <c r="B10863" s="7"/>
-      <c r="C10863" s="2" t="s">
-        <v>409</v>
-      </c>
+      <c r="C10863" s="2"/>
     </row>
     <row r="10864" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10864" s="3">
         <v>2.2000000000000002</v>
       </c>
       <c r="B10864" s="7" t="s">
-        <v>7</v>
+        <v>414</v>
       </c>
       <c r="C10864" s="2" t="s">
-        <v>455</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10865" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36451,62 +36459,115 @@
       <c r="A10866" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10866" s="7"/>
-      <c r="C10866" s="2"/>
+      <c r="B10866" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C10866" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="10867" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10867" s="3">
         <v>4.0999999999999996</v>
       </c>
       <c r="B10867" s="7"/>
-      <c r="C10867" s="2"/>
+      <c r="C10867" s="2" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="10868" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10868" s="3">
-        <v>4.2</v>
-      </c>
-      <c r="B10868" s="24" t="s">
-        <v>412</v>
-      </c>
+      <c r="A10868" s="3"/>
+      <c r="B10868" s="2"/>
       <c r="C10868" s="2" t="s">
-        <v>454</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10869" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10869" s="3"/>
-      <c r="B10869" s="24"/>
-      <c r="C10869" s="2"/>
+      <c r="B10869" s="2"/>
+      <c r="C10869" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="10870" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10870" s="3">
+      <c r="A10870" s="3"/>
+      <c r="B10870" s="7"/>
+      <c r="C10870" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10871" s="3"/>
+      <c r="B10871" s="7"/>
+      <c r="C10871" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="10872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10872" s="3"/>
+      <c r="B10872" s="7"/>
+      <c r="C10872" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10873" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10873" s="3"/>
+      <c r="B10873" s="7"/>
+      <c r="C10873" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10874" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10874" s="3"/>
+      <c r="B10874" s="7"/>
+      <c r="C10874" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="10875" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10875" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10875" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="C10875" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10876" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10876" s="3"/>
+      <c r="B10876" s="24"/>
+      <c r="C10876" s="2"/>
+    </row>
+    <row r="10877" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10877" s="3">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B10870" s="2"/>
-      <c r="C10870" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="10871" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10871" s="3">
+      <c r="B10877" s="7"/>
+      <c r="C10877" s="2"/>
+    </row>
+    <row r="10878" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10878" s="3">
         <v>5.2</v>
       </c>
-      <c r="B10871" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10871" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10872" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10872" s="16" t="s">
+      <c r="B10878" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10878" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10879" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10879" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10872" s="9"/>
-      <c r="C10872" s="8"/>
+      <c r="B10879" s="9"/>
+      <c r="C10879" s="8"/>
     </row>
     <row r="10916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10916" s="10" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B10916" s="11" t="s">
         <v>11</v>
@@ -36517,10 +36578,10 @@
     </row>
     <row r="10917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10917" s="13"/>
-      <c r="B10917" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10917" s="23"/>
+      <c r="B10917" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10917" s="18"/>
     </row>
     <row r="10918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10918" s="5" t="s">
@@ -36570,98 +36631,101 @@
       </c>
       <c r="B10922" s="7"/>
       <c r="C10922" s="2" t="s">
-        <v>25</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10923" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10923" s="7"/>
-      <c r="C10923" s="2"/>
+      <c r="B10923" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10923" s="2" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="10924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10924" s="3">
         <v>3.1</v>
       </c>
       <c r="B10924" s="7"/>
-      <c r="C10924" s="2" t="s">
-        <v>411</v>
-      </c>
+      <c r="C10924" s="2"/>
     </row>
     <row r="10925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10925" s="3">
         <v>3.2</v>
       </c>
-      <c r="B10925" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10925" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B10925" s="7"/>
+      <c r="C10925" s="2"/>
     </row>
     <row r="10926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10926" s="3">
         <v>4.0999999999999996</v>
       </c>
       <c r="B10926" s="7"/>
-      <c r="C10926" s="2" t="s">
-        <v>427</v>
-      </c>
+      <c r="C10926" s="2"/>
     </row>
     <row r="10927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10927" s="3">
         <v>4.2</v>
       </c>
-      <c r="B10927" s="2" t="s">
-        <v>23</v>
+      <c r="B10927" s="24" t="s">
+        <v>412</v>
       </c>
       <c r="C10927" s="2" t="s">
-        <v>55</v>
+        <v>454</v>
       </c>
     </row>
     <row r="10928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10928" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B10928" s="2"/>
+      <c r="A10928" s="3"/>
+      <c r="B10928" s="24"/>
       <c r="C10928" s="2"/>
     </row>
     <row r="10929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10929" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10929" s="2"/>
+      <c r="C10929" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10930" s="3">
         <v>5.2</v>
       </c>
-      <c r="B10929" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10929" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10930" s="16" t="s">
+      <c r="B10930" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10930" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10931" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10930" s="9"/>
-      <c r="C10930" s="8"/>
+      <c r="B10931" s="9"/>
+      <c r="C10931" s="8"/>
     </row>
     <row r="10975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10975" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B10975" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10975" s="12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10976" s="13"/>
-      <c r="B10976" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10976" s="18"/>
+      <c r="B10976" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10976" s="23"/>
     </row>
     <row r="10977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10977" s="5" t="s">
@@ -36702,7 +36766,7 @@
         <v>47</v>
       </c>
       <c r="C10980" s="2" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36711,30 +36775,84 @@
       </c>
       <c r="B10981" s="7"/>
       <c r="C10981" s="2" t="s">
-        <v>459</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10982" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B10982" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10982" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B10982" s="7"/>
+      <c r="C10982" s="2"/>
     </row>
     <row r="10983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10983" s="16" t="s">
+      <c r="A10983" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B10983" s="7"/>
+      <c r="C10983" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10984" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B10984" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10984" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10985" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B10985" s="7"/>
+      <c r="C10985" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="10986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10986" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B10986" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10986" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10987" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B10987" s="2"/>
+      <c r="C10987" s="2"/>
+    </row>
+    <row r="10988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10988" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B10988" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10988" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10989" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B10983" s="9"/>
-      <c r="C10983" s="8"/>
+      <c r="B10989" s="9"/>
+      <c r="C10989" s="8"/>
     </row>
     <row r="11034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11034" s="10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B11034" s="11" t="s">
         <v>12</v>
@@ -36746,7 +36864,7 @@
     <row r="11035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11035" s="13"/>
       <c r="B11035" s="17" t="s">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="C11035" s="18"/>
     </row>
@@ -36785,8 +36903,12 @@
       <c r="A11039" s="3">
         <v>1.2</v>
       </c>
-      <c r="B11039" s="7"/>
-      <c r="C11039" s="2"/>
+      <c r="B11039" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11039" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="11040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11040" s="3">
@@ -36794,7 +36916,7 @@
       </c>
       <c r="B11040" s="7"/>
       <c r="C11040" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -36817,10 +36939,10 @@
     </row>
     <row r="11093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11093" s="10" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B11093" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11093" s="12" t="s">
         <v>8</v>
@@ -36877,70 +36999,33 @@
       </c>
       <c r="B11099" s="7"/>
       <c r="C11099" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11100" s="3"/>
-      <c r="B11100" s="7"/>
+      <c r="A11100" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11100" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="C11100" s="2" t="s">
-        <v>463</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11101" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B11101" s="7"/>
-      <c r="C11101" s="2"/>
-    </row>
-    <row r="11102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11102" s="3">
-        <v>3.1</v>
-      </c>
-      <c r="B11102" s="7"/>
-      <c r="C11102" s="2" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="11103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11103" s="3"/>
-      <c r="B11103" s="7"/>
-      <c r="C11103" s="2" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="11104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11104" s="3"/>
-      <c r="B11104" s="7"/>
-      <c r="C11104" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="11105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11105" s="3">
-        <v>3.2</v>
-      </c>
-      <c r="B11105" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11105" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11106" s="16" t="s">
+      <c r="A11101" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B11106" s="9"/>
-      <c r="C11106" s="8"/>
+      <c r="B11101" s="9"/>
+      <c r="C11101" s="8"/>
     </row>
     <row r="11152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11152" s="10" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B11152" s="11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C11152" s="12" t="s">
         <v>8</v>
@@ -36948,10 +37033,10 @@
     </row>
     <row r="11153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11153" s="13"/>
-      <c r="B11153" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11153" s="23"/>
+      <c r="B11153" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11153" s="18"/>
     </row>
     <row r="11154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11154" s="5" t="s">
@@ -36988,12 +37073,8 @@
       <c r="A11157" s="3">
         <v>1.2</v>
       </c>
-      <c r="B11157" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11157" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B11157" s="7"/>
+      <c r="C11157" s="2"/>
     </row>
     <row r="11158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11158" s="3">
@@ -37001,83 +37082,921 @@
       </c>
       <c r="B11158" s="7"/>
       <c r="C11158" s="2" t="s">
-        <v>436</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11159" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B11159" s="7" t="s">
-        <v>7</v>
-      </c>
+      <c r="A11159" s="3"/>
+      <c r="B11159" s="7"/>
       <c r="C11159" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11160" s="3">
-        <v>3.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="B11160" s="7"/>
-      <c r="C11160" s="2" t="s">
-        <v>469</v>
-      </c>
+      <c r="C11160" s="2"/>
     </row>
     <row r="11161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11161" s="3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="B11161" s="7"/>
-      <c r="C11161" s="2"/>
+      <c r="C11161" s="2" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="11162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11162" s="3">
-        <v>4.0999999999999996</v>
-      </c>
+      <c r="A11162" s="3"/>
       <c r="B11162" s="7"/>
       <c r="C11162" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="11163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11163" s="3"/>
+      <c r="B11163" s="7"/>
+      <c r="C11163" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="11164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11164" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11164" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11164" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11165" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11165" s="9"/>
+      <c r="C11165" s="8"/>
+    </row>
+    <row r="11211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11211" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11211" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11211" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11212" s="13"/>
+      <c r="B11212" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C11212" s="23"/>
+    </row>
+    <row r="11213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11213" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11213" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11213" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11214" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11214" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11214" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11215" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11215" s="7"/>
+      <c r="C11215" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11216" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11216" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11216" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11217" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11217" s="7"/>
+      <c r="C11217" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11218" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11218" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11218" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="11219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11219" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11219" s="7"/>
+      <c r="C11219" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="11220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11220" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11220" s="7"/>
+      <c r="C11220" s="2"/>
+    </row>
+    <row r="11221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11221" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11221" s="7"/>
+      <c r="C11221" s="2" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="11163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11163" s="3">
+    <row r="11222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11222" s="3">
         <v>4.2</v>
       </c>
-      <c r="B11163" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11163" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11164" s="16" t="s">
+      <c r="B11222" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11222" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11223" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B11164" s="9"/>
-      <c r="C11164" s="8"/>
+      <c r="B11223" s="9"/>
+      <c r="C11223" s="8"/>
+    </row>
+    <row r="11270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11270" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B11270" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11270" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11271" s="13"/>
+      <c r="B11271" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11271" s="18"/>
+    </row>
+    <row r="11272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11272" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11272" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11272" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11273" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11273" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11273" s="20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11274" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11274" s="7"/>
+      <c r="C11274" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11275" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11275" s="7"/>
+      <c r="C11275" s="2"/>
+    </row>
+    <row r="11276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11276" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11276" s="7"/>
+      <c r="C11276" s="2"/>
+    </row>
+    <row r="11277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11277" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11277" s="7"/>
+      <c r="C11277" s="2"/>
+    </row>
+    <row r="11278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11278" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11278" s="7"/>
+      <c r="C11278" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11279" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11279" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11279" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11280" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11280" s="9"/>
+      <c r="C11280" s="8"/>
+    </row>
+    <row r="11329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11329" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B11329" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11329" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11330" s="13"/>
+      <c r="B11330" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11330" s="18"/>
+    </row>
+    <row r="11331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11331" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11331" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11331" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11332" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11332" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11332" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11333" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11333" s="7"/>
+      <c r="C11333" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11334" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11334" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11334" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11335" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11335" s="7"/>
+      <c r="C11335" s="2"/>
+    </row>
+    <row r="11336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11336" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11336" s="7"/>
+      <c r="C11336" s="2"/>
+    </row>
+    <row r="11337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11337" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11337" s="7"/>
+      <c r="C11337" s="2"/>
+    </row>
+    <row r="11338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11338" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11338" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11338" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11339" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11339" s="7"/>
+      <c r="C11339" s="2"/>
+    </row>
+    <row r="11340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11340" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B11340" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11340" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11341" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11341" s="7"/>
+      <c r="C11341" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11342" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B11342" s="7"/>
+      <c r="C11342" s="2"/>
+    </row>
+    <row r="11343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11343" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B11343" s="7"/>
+      <c r="C11343" s="2"/>
+    </row>
+    <row r="11344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11344" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B11344" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11344" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11345" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B11345" s="7"/>
+      <c r="C11345" s="2"/>
+    </row>
+    <row r="11346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11346" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B11346" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="C11346" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11347" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11347" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="B11347" s="7"/>
+      <c r="C11347" s="2"/>
+    </row>
+    <row r="11348" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11348" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B11348" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11348" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11349" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11349" s="9"/>
+      <c r="C11349" s="8"/>
+    </row>
+    <row r="11388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11388" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11388" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11388" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11389" s="13"/>
+      <c r="B11389" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11389" s="23"/>
+    </row>
+    <row r="11390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11390" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11390" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11390" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11391" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11391" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11391" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11392" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11392" s="7"/>
+      <c r="C11392" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11393" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11393" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11393" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11394" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11394" s="7"/>
+      <c r="C11394" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11395" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11395" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11395" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11396" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11396" s="7"/>
+      <c r="C11396" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="11397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11397" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11397" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11397" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11398" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11398" s="7"/>
+      <c r="C11398" s="2"/>
+    </row>
+    <row r="11399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11399" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B11399" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11399" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11400" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11400" s="9"/>
+      <c r="C11400" s="8"/>
+    </row>
+    <row r="11447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11447" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="B11447" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11447" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11448" s="13"/>
+      <c r="B11448" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11448" s="18"/>
+    </row>
+    <row r="11449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11449" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11449" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11449" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11450" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11450" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11450" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11451" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11451" s="7"/>
+      <c r="C11451" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11452" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11452" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11452" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11453" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11453" s="7"/>
+      <c r="C11453" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11454" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11454" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11454" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11455" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11455" s="7"/>
+      <c r="C11455" s="2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="11456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11456" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11456" s="7"/>
+      <c r="C11456" s="2"/>
+    </row>
+    <row r="11457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11457" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11457" s="7"/>
+      <c r="C11457" s="2"/>
+    </row>
+    <row r="11458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11458" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B11458" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11458" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11459" s="3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11459" s="7"/>
+      <c r="C11459" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11460" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="B11460" s="7"/>
+      <c r="C11460" s="2"/>
+    </row>
+    <row r="11461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11461" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="B11461" s="7"/>
+      <c r="C11461" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11462" s="3"/>
+      <c r="B11462" s="7"/>
+      <c r="C11462" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11463" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="B11463" s="7"/>
+      <c r="C11463" s="2"/>
+    </row>
+    <row r="11464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11464" s="3">
+        <v>7.1</v>
+      </c>
+      <c r="B11464" s="7"/>
+      <c r="C11464" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11465" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="B11465" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11465" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11466" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11466" s="9"/>
+      <c r="C11466" s="8"/>
+    </row>
+    <row r="11506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11506" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="B11506" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11506" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11507" s="13"/>
+      <c r="B11507" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="C11507" s="18"/>
+    </row>
+    <row r="11508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11508" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11508" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11508" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11509" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11509" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11509" s="21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11510" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B11510" s="7"/>
+      <c r="C11510" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11511" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="B11511" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11511" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11512" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="B11512" s="7"/>
+      <c r="C11512" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="11513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11513" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B11513" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11513" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11514" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="B11514" s="7"/>
+      <c r="C11514" s="2"/>
+    </row>
+    <row r="11515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11515" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="B11515" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11515" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11516" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B11516" s="7"/>
+      <c r="C11516" s="2"/>
+    </row>
+    <row r="11517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11517" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="B11517" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11517" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11518" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11518" s="9"/>
+      <c r="C11518" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="125">
-    <mergeCell ref="B11153:C11153"/>
-    <mergeCell ref="B10740:C10740"/>
+  <mergeCells count="127">
+    <mergeCell ref="B11212:C11212"/>
+    <mergeCell ref="B9560:C9560"/>
+    <mergeCell ref="B11389:C11389"/>
     <mergeCell ref="B10799:C10799"/>
-    <mergeCell ref="B10816:B10817"/>
-    <mergeCell ref="B10868:B10869"/>
-    <mergeCell ref="B10917:C10917"/>
-    <mergeCell ref="B10209:C10209"/>
-    <mergeCell ref="B10386:C10386"/>
-    <mergeCell ref="B10504:C10504"/>
+    <mergeCell ref="B10858:C10858"/>
+    <mergeCell ref="B10875:B10876"/>
+    <mergeCell ref="B10927:B10928"/>
+    <mergeCell ref="B10976:C10976"/>
+    <mergeCell ref="B10268:C10268"/>
+    <mergeCell ref="B10445:C10445"/>
     <mergeCell ref="B10563:C10563"/>
     <mergeCell ref="B10622:C10622"/>
     <mergeCell ref="B10681:C10681"/>
-    <mergeCell ref="B10691:B10692"/>
-    <mergeCell ref="B9747:B9748"/>
-    <mergeCell ref="B9737:C9737"/>
-    <mergeCell ref="B9855:C9855"/>
-    <mergeCell ref="B9973:C9973"/>
+    <mergeCell ref="B10740:C10740"/>
+    <mergeCell ref="B10750:B10751"/>
+    <mergeCell ref="B9806:B9807"/>
+    <mergeCell ref="B9796:C9796"/>
+    <mergeCell ref="B9914:C9914"/>
     <mergeCell ref="B10032:C10032"/>
+    <mergeCell ref="B10091:C10091"/>
     <mergeCell ref="B9098:B9099"/>
     <mergeCell ref="B9147:C9147"/>
     <mergeCell ref="B8921:B8922"/>
